--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8076,22 +8076,22 @@
         <v>77270.22</v>
       </c>
       <c r="C91" t="n">
-        <v>77308.94</v>
+        <v>77407.08</v>
       </c>
       <c r="D91" t="n">
-        <v>76570.99000000001</v>
+        <v>76503.83</v>
       </c>
       <c r="E91" t="n">
-        <v>76643.16</v>
+        <v>76983.95</v>
       </c>
       <c r="F91" t="n">
-        <v>-627.3099999999999</v>
+        <v>-286.52</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0037</v>
       </c>
       <c r="H91" t="n">
-        <v>737.95</v>
+        <v>903.25</v>
       </c>
       <c r="I91" t="n">
         <v>76610.34</v>
@@ -8116,17 +8116,17 @@
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S91" s="7" t="inlineStr">
@@ -8157,25 +8157,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>75833.05</v>
+        <v>75600.58</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>75756.81</v>
+        <v>76094.95</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>76274.17999999999</v>
+        <v>76532.33</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>76791.56</v>
+        <v>76969.7</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>77012.13</v>
+        <v>77435.58</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>77232.7</v>
+        <v>77901.45</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>78046.88</v>
+        <v>78310.33</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66289.46000000001</v>
+        <v>65600.42999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>66928.61</v>
+        <v>66354.62</v>
       </c>
       <c r="D2" t="n">
-        <v>65315.07</v>
+        <v>63870.93</v>
       </c>
       <c r="E2" t="n">
-        <v>65600.64</v>
+        <v>64418.45</v>
       </c>
       <c r="F2" t="n">
-        <v>-688.86</v>
+        <v>-1182.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0104</v>
+        <v>-0.018</v>
       </c>
       <c r="H2" t="n">
-        <v>1613.54</v>
+        <v>2483.7</v>
       </c>
       <c r="I2" t="n">
-        <v>63383.54</v>
+        <v>63701.53</v>
       </c>
       <c r="J2" t="n">
-        <v>64360.96</v>
+        <v>63726.5</v>
       </c>
       <c r="K2" t="n">
-        <v>65323.35</v>
+        <v>64793.87</v>
       </c>
       <c r="L2" t="n">
-        <v>66285.74000000001</v>
+        <v>65861.24000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>67255.64999999999</v>
+        <v>66407.41</v>
       </c>
       <c r="N2" t="n">
-        <v>68225.55</v>
+        <v>66953.58</v>
       </c>
       <c r="O2" t="n">
-        <v>69180.42999999999</v>
+        <v>68542.14999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -725,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65600.42999999999</v>
+        <v>64419.64</v>
       </c>
       <c r="C3" t="n">
-        <v>66354.62</v>
+        <v>64736.92</v>
       </c>
       <c r="D3" t="n">
-        <v>63870.93</v>
+        <v>62201.14</v>
       </c>
       <c r="E3" t="n">
-        <v>64418.45</v>
+        <v>62896.47</v>
       </c>
       <c r="F3" t="n">
-        <v>-1182.2</v>
+        <v>-1521.97</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0236</v>
       </c>
       <c r="H3" t="n">
-        <v>2483.7</v>
+        <v>2535.78</v>
       </c>
       <c r="I3" t="n">
-        <v>63701.53</v>
+        <v>61387.23</v>
       </c>
       <c r="J3" t="n">
-        <v>63726.5</v>
+        <v>61587.58</v>
       </c>
       <c r="K3" t="n">
-        <v>64793.87</v>
+        <v>63176.6</v>
       </c>
       <c r="L3" t="n">
-        <v>65861.24000000001</v>
+        <v>64765.61</v>
       </c>
       <c r="M3" t="n">
-        <v>66407.41</v>
+        <v>65660.28999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>66953.58</v>
+        <v>66554.97</v>
       </c>
       <c r="O3" t="n">
-        <v>68542.14999999999</v>
+        <v>68838.32000000001</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -809,50 +809,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64419.64</v>
+        <v>62897.52</v>
       </c>
       <c r="C4" t="n">
-        <v>64736.92</v>
+        <v>63568.22</v>
       </c>
       <c r="D4" t="n">
-        <v>62201.14</v>
+        <v>62275.58</v>
       </c>
       <c r="E4" t="n">
-        <v>62896.47</v>
+        <v>63540.84</v>
       </c>
       <c r="F4" t="n">
-        <v>-1521.97</v>
+        <v>644.36</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0236</v>
+        <v>0.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>2535.78</v>
+        <v>1292.64</v>
       </c>
       <c r="I4" t="n">
-        <v>61387.23</v>
+        <v>59665.37</v>
       </c>
       <c r="J4" t="n">
-        <v>61587.58</v>
+        <v>60074.42</v>
       </c>
       <c r="K4" t="n">
-        <v>63176.6</v>
+        <v>61628.58</v>
       </c>
       <c r="L4" t="n">
-        <v>64765.61</v>
+        <v>63182.75</v>
       </c>
       <c r="M4" t="n">
-        <v>65660.28999999999</v>
+        <v>64164.36</v>
       </c>
       <c r="N4" t="n">
-        <v>66554.97</v>
+        <v>65145.97</v>
       </c>
       <c r="O4" t="n">
-        <v>68838.32000000001</v>
+        <v>67272.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,14 +860,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -886,57 +884,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62897.52</v>
+        <v>63535.81</v>
       </c>
       <c r="C5" t="n">
-        <v>63568.22</v>
+        <v>64307.14</v>
       </c>
       <c r="D5" t="n">
-        <v>62275.58</v>
+        <v>63149.66</v>
       </c>
       <c r="E5" t="n">
-        <v>63540.84</v>
+        <v>64239.68</v>
       </c>
       <c r="F5" t="n">
-        <v>644.36</v>
+        <v>698.84</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="H5" t="n">
-        <v>1292.64</v>
+        <v>1157.48</v>
       </c>
       <c r="I5" t="n">
-        <v>59665.37</v>
+        <v>60982.94</v>
       </c>
       <c r="J5" t="n">
-        <v>60074.42</v>
+        <v>62557.66</v>
       </c>
       <c r="K5" t="n">
-        <v>61628.58</v>
+        <v>62894.52</v>
       </c>
       <c r="L5" t="n">
-        <v>63182.75</v>
+        <v>63231.37</v>
       </c>
       <c r="M5" t="n">
-        <v>64164.36</v>
+        <v>64187.16</v>
       </c>
       <c r="N5" t="n">
-        <v>65145.97</v>
+        <v>65142.94</v>
       </c>
       <c r="O5" t="n">
-        <v>67272.7</v>
+        <v>64860.86</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -949,11 +947,13 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -966,164 +966,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63535.81</v>
+        <v>64242.32</v>
       </c>
       <c r="C6" t="n">
-        <v>64307.14</v>
+        <v>64506.58</v>
       </c>
       <c r="D6" t="n">
-        <v>63149.66</v>
+        <v>63221</v>
       </c>
       <c r="E6" t="n">
-        <v>64239.68</v>
+        <v>63237.54</v>
       </c>
       <c r="F6" t="n">
-        <v>698.84</v>
+        <v>-1002.14</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.0156</v>
       </c>
       <c r="H6" t="n">
-        <v>1157.48</v>
+        <v>1285.58</v>
       </c>
       <c r="I6" t="n">
-        <v>60982.94</v>
+        <v>61992.18</v>
       </c>
       <c r="J6" t="n">
-        <v>62557.66</v>
+        <v>63337.84</v>
       </c>
       <c r="K6" t="n">
-        <v>62894.52</v>
+        <v>63660.94</v>
       </c>
       <c r="L6" t="n">
-        <v>63231.37</v>
+        <v>63984.04</v>
       </c>
       <c r="M6" t="n">
-        <v>64187.16</v>
+        <v>64818.41</v>
       </c>
       <c r="N6" t="n">
-        <v>65142.94</v>
+        <v>65652.78999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>64860.86</v>
+        <v>65464.61</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64242.32</v>
+        <v>63240.79</v>
       </c>
       <c r="C7" t="n">
-        <v>64506.58</v>
+        <v>65544</v>
       </c>
       <c r="D7" t="n">
-        <v>63221</v>
+        <v>63233.53</v>
       </c>
       <c r="E7" t="n">
-        <v>63237.54</v>
+        <v>63952.11</v>
       </c>
       <c r="F7" t="n">
-        <v>-1002.14</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0113</v>
       </c>
       <c r="H7" t="n">
-        <v>1285.58</v>
+        <v>2310.47</v>
       </c>
       <c r="I7" t="n">
-        <v>61992.18</v>
+        <v>61935.42</v>
       </c>
       <c r="J7" t="n">
-        <v>63337.84</v>
+        <v>61638.84</v>
       </c>
       <c r="K7" t="n">
-        <v>63660.94</v>
+        <v>62594.75</v>
       </c>
       <c r="L7" t="n">
-        <v>63984.04</v>
+        <v>63550.66</v>
       </c>
       <c r="M7" t="n">
-        <v>64818.41</v>
+        <v>63880.33</v>
       </c>
       <c r="N7" t="n">
-        <v>65652.78999999999</v>
+        <v>64209.99</v>
       </c>
       <c r="O7" t="n">
-        <v>65464.61</v>
+        <v>65792.16</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1134,57 +1136,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63240.79</v>
+        <v>63952.79</v>
       </c>
       <c r="C8" t="n">
-        <v>65544</v>
+        <v>64196.56</v>
       </c>
       <c r="D8" t="n">
-        <v>63233.53</v>
+        <v>61893.21</v>
       </c>
       <c r="E8" t="n">
-        <v>63952.11</v>
+        <v>62668.02</v>
       </c>
       <c r="F8" t="n">
-        <v>714.5700000000001</v>
+        <v>-1284.09</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0201</v>
       </c>
       <c r="H8" t="n">
-        <v>2310.47</v>
+        <v>2303.36</v>
       </c>
       <c r="I8" t="n">
-        <v>61935.42</v>
+        <v>60923.06</v>
       </c>
       <c r="J8" t="n">
-        <v>61638.84</v>
+        <v>61423.31</v>
       </c>
       <c r="K8" t="n">
-        <v>62594.75</v>
+        <v>62796.87</v>
       </c>
       <c r="L8" t="n">
-        <v>63550.66</v>
+        <v>64170.44</v>
       </c>
       <c r="M8" t="n">
-        <v>63880.33</v>
+        <v>65107.34</v>
       </c>
       <c r="N8" t="n">
-        <v>64209.99</v>
+        <v>66044.24000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>65792.16</v>
+        <v>67854.47</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,23 +1194,21 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1218,65 +1218,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63952.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C9" t="n">
-        <v>64196.56</v>
+        <v>63097.76</v>
       </c>
       <c r="D9" t="n">
-        <v>61893.21</v>
+        <v>59029.86</v>
       </c>
       <c r="E9" t="n">
-        <v>62668.02</v>
+        <v>60995.13</v>
       </c>
       <c r="F9" t="n">
-        <v>-1284.09</v>
+        <v>-1672.89</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0267</v>
       </c>
       <c r="H9" t="n">
-        <v>2303.36</v>
+        <v>4067.9</v>
       </c>
       <c r="I9" t="n">
-        <v>60923.06</v>
+        <v>59589.85</v>
       </c>
       <c r="J9" t="n">
-        <v>61423.31</v>
+        <v>60176.23</v>
       </c>
       <c r="K9" t="n">
-        <v>62796.87</v>
+        <v>61516.34</v>
       </c>
       <c r="L9" t="n">
-        <v>64170.44</v>
+        <v>62856.45</v>
       </c>
       <c r="M9" t="n">
-        <v>65107.34</v>
+        <v>63819.7</v>
       </c>
       <c r="N9" t="n">
-        <v>66044.24000000001</v>
+        <v>64782.94</v>
       </c>
       <c r="O9" t="n">
-        <v>67854.47</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+        <v>66499.92</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1307,60 +1307,56 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C10" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D10" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E10" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F10" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H10" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I10" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J10" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K10" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L10" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M10" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N10" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O10" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1391,50 +1387,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C11" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D11" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E11" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F11" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H11" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I11" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J11" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K11" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L11" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M11" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N11" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O11" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,14 +1438,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1466,55 +1460,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C12" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D12" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E12" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F12" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H12" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I12" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J12" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K12" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L12" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M12" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N12" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O12" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1553,50 +1551,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C13" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D13" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E13" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F13" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H13" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I13" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J13" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K13" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L13" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M13" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N13" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O13" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,12 +1602,14 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1626,59 +1626,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C14" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D14" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E14" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F14" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H14" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I14" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J14" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K14" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L14" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M14" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N14" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O14" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,19 +1682,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1710,75 +1706,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C15" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D15" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E15" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F15" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H15" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I15" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J15" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K15" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L15" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M15" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N15" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O15" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1790,84 +1792,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C16" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D16" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E16" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F16" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H16" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I16" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J16" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K16" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L16" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M16" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N16" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O16" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1876,55 +1874,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C17" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D17" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E17" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F17" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H17" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I17" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J17" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K17" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L17" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M17" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N17" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O17" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,14 +1944,12 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1960,57 +1960,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C18" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D18" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E18" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F18" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H18" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I18" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J18" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K18" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L18" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M18" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N18" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O18" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2051,50 +2051,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C19" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D19" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E19" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F19" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I19" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J19" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K19" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L19" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M19" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N19" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O19" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2135,50 +2135,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C20" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D20" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E20" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F20" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H20" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I20" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J20" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K20" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L20" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M20" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N20" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O20" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,8 +2186,10 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
@@ -2219,56 +2221,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C21" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D21" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E21" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F21" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H21" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I21" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J21" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K21" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L21" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M21" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N21" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O21" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
@@ -2298,80 +2302,74 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C22" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D22" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E22" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F22" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H22" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I22" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J22" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K22" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L22" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M22" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N22" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O22" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2386,70 +2384,74 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C23" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D23" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E23" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F23" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H23" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I23" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J23" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K23" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L23" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M23" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N23" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O23" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2466,81 +2468,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C24" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D24" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E24" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F24" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H24" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I24" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J24" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K24" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L24" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M24" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N24" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O24" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2552,55 +2548,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C25" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D25" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E25" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F25" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H25" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I25" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J25" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K25" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L25" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M25" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N25" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O25" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2634,57 +2634,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C26" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D26" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E26" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F26" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H26" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I26" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J26" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K26" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L26" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M26" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N26" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O26" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,15 +2695,13 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2718,57 +2716,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C27" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D27" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E27" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F27" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H27" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J27" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K27" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L27" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M27" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N27" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O27" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,8 +2782,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2798,72 +2798,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C28" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D28" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E28" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F28" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H28" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I28" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J28" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K28" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L28" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M28" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N28" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O28" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2871,8 +2873,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2882,147 +2886,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C29" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D29" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E29" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F29" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H29" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I29" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J29" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K29" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L29" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M29" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N29" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O29" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C30" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D30" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E30" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F30" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H30" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I30" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J30" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K30" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L30" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M30" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N30" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O30" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,18 +3033,14 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3056,68 +3050,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C31" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D31" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E31" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F31" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H31" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I31" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J31" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K31" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L31" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M31" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N31" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O31" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3136,65 +3138,63 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C32" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D32" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E32" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F32" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H32" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I32" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J32" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K32" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L32" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M32" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N32" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O32" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q32" s="6" t="n">
+        <v/>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3222,57 +3222,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C33" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D33" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E33" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F33" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H33" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I33" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J33" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K33" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L33" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M33" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N33" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O33" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,18 +3280,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3304,59 +3304,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C34" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D34" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E34" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F34" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H34" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I34" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J34" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K34" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L34" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M34" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N34" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,18 +3360,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3388,61 +3384,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C35" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D35" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E35" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F35" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I35" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J35" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K35" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L35" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M35" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N35" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O35" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3451,17 +3453,23 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3477,63 +3485,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C36" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D36" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E36" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F36" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H36" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I36" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J36" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K36" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L36" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M36" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N36" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O36" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
@@ -3542,77 +3546,69 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E37" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F37" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H37" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I37" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J37" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K37" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L37" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N37" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O37" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3620,18 +3616,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3644,61 +3640,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C38" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D38" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E38" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F38" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H38" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I38" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J38" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K38" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L38" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N38" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3707,7 +3709,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3726,69 +3728,67 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C39" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D39" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E39" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H39" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I39" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J39" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K39" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L39" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M39" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N39" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -3819,50 +3819,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C40" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D40" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E40" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F40" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H40" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I40" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J40" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K40" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L40" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M40" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N40" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O40" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,14 +3870,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3896,57 +3894,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C41" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D41" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E41" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F41" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H41" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I41" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J41" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K41" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L41" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M41" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N41" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O41" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3957,179 +3955,179 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C42" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D42" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E42" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F42" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H42" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I42" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J42" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K42" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L42" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M42" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C43" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D43" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E43" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F43" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H43" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I43" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J43" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K43" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L43" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M43" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N43" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O43" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4155,50 +4153,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C44" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D44" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E44" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F44" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I44" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J44" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K44" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L44" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M44" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N44" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O44" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4206,16 +4204,20 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4230,57 +4232,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C45" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D45" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E45" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F45" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H45" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I45" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J45" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K45" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L45" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M45" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N45" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O45" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4288,19 +4290,17 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4323,70 +4323,72 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C46" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D46" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E46" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F46" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H46" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I46" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J46" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K46" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L46" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M46" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N46" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O46" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4400,74 +4402,70 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C47" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D47" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E47" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F47" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H47" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I47" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J47" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K47" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L47" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M47" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N47" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O47" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4484,59 +4482,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C48" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D48" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E48" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F48" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H48" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I48" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J48" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K48" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L48" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M48" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N48" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O48" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4547,16 +4541,20 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4566,68 +4564,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C49" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D49" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E49" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F49" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H49" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I49" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J49" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K49" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L49" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M49" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N49" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O49" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4635,10 +4641,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4650,79 +4654,75 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C50" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D50" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E50" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F50" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H50" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I50" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J50" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K50" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L50" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M50" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N50" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O50" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4738,57 +4738,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C51" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D51" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E51" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F51" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I51" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J51" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K51" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L51" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M51" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N51" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O51" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4829,50 +4829,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C52" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D52" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E52" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F52" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H52" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I52" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J52" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K52" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L52" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M52" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N52" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O52" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,19 +4880,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4906,57 +4906,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C53" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D53" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E53" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F53" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I53" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J53" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K53" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L53" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M53" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N53" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O53" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4964,22 +4964,24 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4990,57 +4992,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C54" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D54" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E54" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F54" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H54" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I54" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J54" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K54" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L54" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M54" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N54" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5053,18 +5055,14 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5076,57 +5074,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C55" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D55" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E55" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F55" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H55" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I55" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J55" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K55" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L55" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M55" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N55" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O55" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5134,19 +5132,25 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5158,63 +5162,67 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C56" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D56" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E56" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F56" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H56" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I56" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J56" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K56" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L56" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M56" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N56" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O56" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5223,7 +5231,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5231,10 +5239,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5244,84 +5250,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C57" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D57" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E57" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F57" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H57" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I57" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J57" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K57" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L57" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M57" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N57" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O57" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5339,50 +5335,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C58" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D58" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E58" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F58" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H58" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I58" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J58" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K58" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L58" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M58" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N58" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O58" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5390,18 +5386,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5414,55 +5410,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C59" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D59" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E59" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F59" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H59" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I59" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J59" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K59" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L59" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M59" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N59" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O59" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5470,18 +5470,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5494,59 +5494,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C60" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D60" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E60" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H60" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I60" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J60" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K60" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L60" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M60" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N60" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O60" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5556,12 +5552,12 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5583,50 +5579,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C61" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D61" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E61" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F61" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H61" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I61" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J61" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K61" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L61" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M61" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N61" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O61" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5634,14 +5630,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5658,72 +5652,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C62" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D62" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E62" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F62" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H62" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I62" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J62" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K62" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L62" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M62" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N62" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O62" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5738,145 +5742,141 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C63" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D63" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E63" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F63" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H63" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I63" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J63" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K63" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L63" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M63" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N63" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O63" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C64" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D64" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E64" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F64" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H64" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I64" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J64" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K64" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L64" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M64" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N64" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O64" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5889,23 +5889,17 @@
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5917,50 +5911,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C65" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D65" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E65" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F65" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H65" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I65" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J65" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K65" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L65" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M65" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N65" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O65" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5968,22 +5962,30 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
@@ -5995,50 +5997,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C66" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D66" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E66" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H66" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I66" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J66" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K66" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L66" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N66" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O66" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6046,10 +6048,8 @@
       <c r="Q66" s="6" t="n">
         <v/>
       </c>
-      <c r="R66" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R66" s="6" t="n">
+        <v/>
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
@@ -6058,18 +6058,14 @@
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V66" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V66" s="8" t="n">
+        <v/>
       </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
@@ -6081,50 +6077,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C67" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E67" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F67" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H67" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I67" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J67" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K67" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L67" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N67" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O67" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6142,14 +6138,18 @@
       </c>
       <c r="T67" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U67" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V67" s="8" t="n">
-        <v/>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W67" s="9" t="inlineStr">
         <is>
@@ -6161,50 +6161,50 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C68" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F68" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H68" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I68" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J68" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K68" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M68" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N68" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O68" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6215,80 +6215,78 @@
       <c r="R68" s="6" t="n">
         <v/>
       </c>
-      <c r="S68" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U68" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V68" s="8" t="n">
+        <v/>
       </c>
       <c r="W68" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C69" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D69" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E69" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F69" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I69" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J69" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K69" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L69" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M69" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N69" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O69" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6296,12 +6294,14 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S69" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T69" s="8" t="n">
@@ -6327,50 +6327,50 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C70" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D70" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E70" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F70" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H70" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I70" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J70" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K70" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L70" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M70" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N70" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O70" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6378,18 +6378,18 @@
       <c r="Q70" s="6" t="n">
         <v/>
       </c>
-      <c r="R70" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R70" s="6" t="n">
+        <v/>
       </c>
       <c r="S70" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6402,59 +6402,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C71" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D71" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E71" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F71" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H71" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I71" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J71" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L71" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M71" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N71" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O71" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6465,14 +6461,14 @@
       <c r="R71" s="6" t="n">
         <v/>
       </c>
-      <c r="S71" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T71" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U71" s="8" t="n">
@@ -6486,55 +6482,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C72" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D72" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E72" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F72" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H72" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I72" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J72" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K72" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L72" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O72" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6550,10 +6550,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T72" s="8" t="n">
+        <v/>
       </c>
       <c r="U72" s="8" t="n">
         <v/>
@@ -6568,57 +6566,57 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C73" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D73" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H73" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I73" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J73" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K73" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L73" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N73" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O73" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6629,13 +6627,15 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U73" s="8" t="n">
         <v/>
@@ -6648,156 +6648,154 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C74" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D74" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H74" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I74" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J74" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L74" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M74" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N74" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O74" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S74" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
+      <c r="Q74" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
+      </c>
       <c r="U74" s="8" t="n">
         <v/>
       </c>
       <c r="V74" s="8" t="n">
         <v/>
       </c>
-      <c r="W74" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr"/>
+      <c r="W74" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C75" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D75" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F75" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H75" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I75" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J75" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M75" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N75" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O75" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v/>
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T75" s="8" t="n">
@@ -6816,80 +6814,88 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C76" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H76" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I76" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M76" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N76" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O76" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R76" s="6" t="n">
-        <v/>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
       </c>
-      <c r="V76" s="8" t="n">
-        <v/>
+      <c r="V76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W76" s="11" t="inlineStr">
         <is>
@@ -6898,88 +6904,82 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C77" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D77" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E77" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F77" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H77" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I77" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J77" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L77" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M77" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N77" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O77" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R77" s="6" t="inlineStr">
+      <c r="Q77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U77" s="8" t="n">
         <v/>
       </c>
-      <c r="V77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V77" s="8" t="n">
+        <v/>
       </c>
       <c r="W77" s="11" t="inlineStr">
         <is>
@@ -6988,77 +6988,79 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C78" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D78" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E78" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F78" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H78" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I78" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J78" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N78" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O78" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S78" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="inlineStr">
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
+      </c>
       <c r="U78" s="8" t="n">
         <v/>
       </c>
@@ -7070,76 +7072,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C79" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D79" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E79" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F79" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H79" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I79" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J79" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K79" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N79" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O79" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
       </c>
-      <c r="Q79" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R79" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R79" s="6" t="n">
+        <v/>
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T79" s="8" t="n">
@@ -7161,50 +7155,50 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C80" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D80" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E80" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H80" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I80" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J80" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L80" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M80" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N80" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O80" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7215,23 +7209,29 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W80" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V80" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W80" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X80" t="inlineStr"/>
@@ -7239,50 +7239,50 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C81" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E81" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F81" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H81" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I81" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J81" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L81" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M81" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N81" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O81" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7293,80 +7293,78 @@
       <c r="R81" s="6" t="n">
         <v/>
       </c>
-      <c r="S81" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V81" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V81" s="8" t="n">
+        <v/>
       </c>
       <c r="W81" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C82" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E82" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F82" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H82" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I82" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M82" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N82" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O82" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7398,57 +7396,57 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C83" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E83" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F83" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H83" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I83" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J83" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L83" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M83" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N83" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7456,16 +7454,20 @@
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S83" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="n">
-        <v/>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7487,71 +7489,71 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C84" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D84" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E84" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H84" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I84" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K84" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L84" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M84" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N84" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O84" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
       </c>
-      <c r="Q84" s="6" t="n">
-        <v/>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7559,76 +7561,70 @@
       <c r="V84" s="8" t="n">
         <v/>
       </c>
-      <c r="W84" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W84" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C85" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D85" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E85" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F85" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H85" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I85" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J85" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K85" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L85" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M85" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O85" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
       </c>
-      <c r="Q85" s="6" t="inlineStr">
+      <c r="Q85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R85" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S85" s="7" t="inlineStr">
@@ -7655,50 +7651,50 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C86" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D86" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E86" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F86" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H86" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I86" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M86" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N86" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O86" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7706,18 +7702,18 @@
       <c r="Q86" s="6" t="n">
         <v/>
       </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R86" s="6" t="n">
+        <v/>
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7730,74 +7726,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C87" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D87" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E87" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F87" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H87" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I87" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J87" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K87" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L87" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M87" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N87" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O87" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
       </c>
-      <c r="Q87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R87" s="6" t="n">
-        <v/>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
       </c>
       <c r="U87" s="8" t="n">
         <v/>
@@ -7810,83 +7812,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C88" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D88" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E88" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F88" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I88" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J88" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N88" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O88" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
       </c>
-      <c r="Q88" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="Q88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U88" s="8" t="n">
-        <v/>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V88" s="8" t="n">
         <v/>
@@ -7896,55 +7894,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D89" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E89" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F89" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H89" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I89" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K89" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L89" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N89" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O89" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7955,20 +7957,16 @@
       <c r="R89" s="6" t="n">
         <v/>
       </c>
-      <c r="S89" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
       </c>
       <c r="V89" s="8" t="n">
         <v/>
@@ -7987,63 +7985,69 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D90" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E90" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F90" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H90" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I90" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J90" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K90" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L90" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M90" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N90" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O90" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R90" s="6" t="n">
-        <v/>
+        <v>77914.31</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">
@@ -8060,95 +8064,95 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>77270.22</v>
+        <v>76806.19</v>
       </c>
       <c r="C91" t="n">
-        <v>77407.08</v>
+        <v>79435.67999999999</v>
       </c>
       <c r="D91" t="n">
-        <v>76503.83</v>
+        <v>76452.55</v>
       </c>
       <c r="E91" t="n">
-        <v>76983.95</v>
+        <v>78740.3</v>
       </c>
       <c r="F91" t="n">
-        <v>-286.52</v>
+        <v>1902.14</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0248</v>
       </c>
       <c r="H91" t="n">
-        <v>903.25</v>
+        <v>2983.13</v>
       </c>
       <c r="I91" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J91" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K91" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L91" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M91" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N91" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O91" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P91" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q91" s="6" t="inlineStr">
+      <c r="U91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R91" s="6" t="inlineStr">
+      <c r="V91" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr"/>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -8157,25 +8161,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>75600.58</v>
+        <v>73469.41</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>76094.95</v>
+        <v>76155.25999999999</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>76532.33</v>
+        <v>77248.73</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>76969.7</v>
+        <v>78342.21000000001</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>77435.58</v>
+        <v>80231.86</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>77901.45</v>
+        <v>82121.52</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>78310.33</v>
+        <v>82418.81</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65600.42999999999</v>
+        <v>64419.64</v>
       </c>
       <c r="C2" t="n">
-        <v>66354.62</v>
+        <v>64736.92</v>
       </c>
       <c r="D2" t="n">
-        <v>63870.93</v>
+        <v>62201.14</v>
       </c>
       <c r="E2" t="n">
-        <v>64418.45</v>
+        <v>62896.47</v>
       </c>
       <c r="F2" t="n">
-        <v>-1182.2</v>
+        <v>-1521.97</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0236</v>
       </c>
       <c r="H2" t="n">
-        <v>2483.7</v>
+        <v>2535.78</v>
       </c>
       <c r="I2" t="n">
-        <v>63701.53</v>
+        <v>61387.23</v>
       </c>
       <c r="J2" t="n">
-        <v>63726.5</v>
+        <v>61587.58</v>
       </c>
       <c r="K2" t="n">
-        <v>64793.87</v>
+        <v>63176.6</v>
       </c>
       <c r="L2" t="n">
-        <v>65861.24000000001</v>
+        <v>64765.61</v>
       </c>
       <c r="M2" t="n">
-        <v>66407.41</v>
+        <v>65660.28999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>66953.58</v>
+        <v>66554.97</v>
       </c>
       <c r="O2" t="n">
-        <v>68542.14999999999</v>
+        <v>68838.32000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -725,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64419.64</v>
+        <v>62897.52</v>
       </c>
       <c r="C3" t="n">
-        <v>64736.92</v>
+        <v>63568.22</v>
       </c>
       <c r="D3" t="n">
-        <v>62201.14</v>
+        <v>62275.58</v>
       </c>
       <c r="E3" t="n">
-        <v>62896.47</v>
+        <v>63540.84</v>
       </c>
       <c r="F3" t="n">
-        <v>-1521.97</v>
+        <v>644.36</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0236</v>
+        <v>0.0102</v>
       </c>
       <c r="H3" t="n">
-        <v>2535.78</v>
+        <v>1292.64</v>
       </c>
       <c r="I3" t="n">
-        <v>61387.23</v>
+        <v>59665.37</v>
       </c>
       <c r="J3" t="n">
-        <v>61587.58</v>
+        <v>60074.42</v>
       </c>
       <c r="K3" t="n">
-        <v>63176.6</v>
+        <v>61628.58</v>
       </c>
       <c r="L3" t="n">
-        <v>64765.61</v>
+        <v>63182.75</v>
       </c>
       <c r="M3" t="n">
-        <v>65660.28999999999</v>
+        <v>64164.36</v>
       </c>
       <c r="N3" t="n">
-        <v>66554.97</v>
+        <v>65145.97</v>
       </c>
       <c r="O3" t="n">
-        <v>68838.32000000001</v>
+        <v>67272.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,14 +776,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -802,57 +800,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62897.52</v>
+        <v>63535.81</v>
       </c>
       <c r="C4" t="n">
-        <v>63568.22</v>
+        <v>64307.14</v>
       </c>
       <c r="D4" t="n">
-        <v>62275.58</v>
+        <v>63149.66</v>
       </c>
       <c r="E4" t="n">
-        <v>63540.84</v>
+        <v>64239.68</v>
       </c>
       <c r="F4" t="n">
-        <v>644.36</v>
+        <v>698.84</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="H4" t="n">
-        <v>1292.64</v>
+        <v>1157.48</v>
       </c>
       <c r="I4" t="n">
-        <v>59665.37</v>
+        <v>60982.94</v>
       </c>
       <c r="J4" t="n">
-        <v>60074.42</v>
+        <v>62557.66</v>
       </c>
       <c r="K4" t="n">
-        <v>61628.58</v>
+        <v>62894.52</v>
       </c>
       <c r="L4" t="n">
-        <v>63182.75</v>
+        <v>63231.37</v>
       </c>
       <c r="M4" t="n">
-        <v>64164.36</v>
+        <v>64187.16</v>
       </c>
       <c r="N4" t="n">
-        <v>65145.97</v>
+        <v>65142.94</v>
       </c>
       <c r="O4" t="n">
-        <v>67272.7</v>
+        <v>64860.86</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -865,11 +863,13 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -882,164 +882,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63535.81</v>
+        <v>64242.32</v>
       </c>
       <c r="C5" t="n">
-        <v>64307.14</v>
+        <v>64506.58</v>
       </c>
       <c r="D5" t="n">
-        <v>63149.66</v>
+        <v>63221</v>
       </c>
       <c r="E5" t="n">
-        <v>64239.68</v>
+        <v>63237.54</v>
       </c>
       <c r="F5" t="n">
-        <v>698.84</v>
+        <v>-1002.14</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.0156</v>
       </c>
       <c r="H5" t="n">
-        <v>1157.48</v>
+        <v>1285.58</v>
       </c>
       <c r="I5" t="n">
-        <v>60982.94</v>
+        <v>61992.18</v>
       </c>
       <c r="J5" t="n">
-        <v>62557.66</v>
+        <v>63337.84</v>
       </c>
       <c r="K5" t="n">
-        <v>62894.52</v>
+        <v>63660.94</v>
       </c>
       <c r="L5" t="n">
-        <v>63231.37</v>
+        <v>63984.04</v>
       </c>
       <c r="M5" t="n">
-        <v>64187.16</v>
+        <v>64818.41</v>
       </c>
       <c r="N5" t="n">
-        <v>65142.94</v>
+        <v>65652.78999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>64860.86</v>
+        <v>65464.61</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64242.32</v>
+        <v>63240.79</v>
       </c>
       <c r="C6" t="n">
-        <v>64506.58</v>
+        <v>65544</v>
       </c>
       <c r="D6" t="n">
-        <v>63221</v>
+        <v>63233.53</v>
       </c>
       <c r="E6" t="n">
-        <v>63237.54</v>
+        <v>63952.11</v>
       </c>
       <c r="F6" t="n">
-        <v>-1002.14</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0113</v>
       </c>
       <c r="H6" t="n">
-        <v>1285.58</v>
+        <v>2310.47</v>
       </c>
       <c r="I6" t="n">
-        <v>61992.18</v>
+        <v>61935.42</v>
       </c>
       <c r="J6" t="n">
-        <v>63337.84</v>
+        <v>61638.84</v>
       </c>
       <c r="K6" t="n">
-        <v>63660.94</v>
+        <v>62594.75</v>
       </c>
       <c r="L6" t="n">
-        <v>63984.04</v>
+        <v>63550.66</v>
       </c>
       <c r="M6" t="n">
-        <v>64818.41</v>
+        <v>63880.33</v>
       </c>
       <c r="N6" t="n">
-        <v>65652.78999999999</v>
+        <v>64209.99</v>
       </c>
       <c r="O6" t="n">
-        <v>65464.61</v>
+        <v>65792.16</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1050,57 +1052,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63240.79</v>
+        <v>63952.79</v>
       </c>
       <c r="C7" t="n">
-        <v>65544</v>
+        <v>64196.56</v>
       </c>
       <c r="D7" t="n">
-        <v>63233.53</v>
+        <v>61893.21</v>
       </c>
       <c r="E7" t="n">
-        <v>63952.11</v>
+        <v>62668.02</v>
       </c>
       <c r="F7" t="n">
-        <v>714.5700000000001</v>
+        <v>-1284.09</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0201</v>
       </c>
       <c r="H7" t="n">
-        <v>2310.47</v>
+        <v>2303.36</v>
       </c>
       <c r="I7" t="n">
-        <v>61935.42</v>
+        <v>60923.06</v>
       </c>
       <c r="J7" t="n">
-        <v>61638.84</v>
+        <v>61423.31</v>
       </c>
       <c r="K7" t="n">
-        <v>62594.75</v>
+        <v>62796.87</v>
       </c>
       <c r="L7" t="n">
-        <v>63550.66</v>
+        <v>64170.44</v>
       </c>
       <c r="M7" t="n">
-        <v>63880.33</v>
+        <v>65107.34</v>
       </c>
       <c r="N7" t="n">
-        <v>64209.99</v>
+        <v>66044.24000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>65792.16</v>
+        <v>67854.47</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,23 +1110,21 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1134,65 +1134,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63952.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C8" t="n">
-        <v>64196.56</v>
+        <v>63097.76</v>
       </c>
       <c r="D8" t="n">
-        <v>61893.21</v>
+        <v>59029.86</v>
       </c>
       <c r="E8" t="n">
-        <v>62668.02</v>
+        <v>60995.13</v>
       </c>
       <c r="F8" t="n">
-        <v>-1284.09</v>
+        <v>-1672.89</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0267</v>
       </c>
       <c r="H8" t="n">
-        <v>2303.36</v>
+        <v>4067.9</v>
       </c>
       <c r="I8" t="n">
-        <v>60923.06</v>
+        <v>59589.85</v>
       </c>
       <c r="J8" t="n">
-        <v>61423.31</v>
+        <v>60176.23</v>
       </c>
       <c r="K8" t="n">
-        <v>62796.87</v>
+        <v>61516.34</v>
       </c>
       <c r="L8" t="n">
-        <v>64170.44</v>
+        <v>62856.45</v>
       </c>
       <c r="M8" t="n">
-        <v>65107.34</v>
+        <v>63819.7</v>
       </c>
       <c r="N8" t="n">
-        <v>66044.24000000001</v>
+        <v>64782.94</v>
       </c>
       <c r="O8" t="n">
-        <v>67854.47</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+        <v>66499.92</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
@@ -1223,60 +1223,56 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C9" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D9" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E9" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F9" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H9" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I9" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J9" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K9" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L9" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M9" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N9" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O9" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1307,50 +1303,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C10" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D10" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E10" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F10" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H10" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I10" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J10" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K10" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L10" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M10" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N10" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O10" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,14 +1354,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1382,55 +1376,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C11" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D11" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E11" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F11" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H11" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I11" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J11" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K11" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L11" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M11" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N11" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O11" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1469,50 +1467,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C12" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D12" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E12" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F12" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H12" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I12" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J12" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K12" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L12" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M12" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N12" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O12" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,12 +1518,14 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1542,59 +1542,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C13" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D13" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E13" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F13" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H13" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I13" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J13" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K13" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L13" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M13" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N13" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O13" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,19 +1598,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1626,75 +1622,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C14" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D14" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E14" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F14" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H14" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I14" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J14" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K14" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L14" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M14" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N14" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O14" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1706,84 +1708,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C15" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D15" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E15" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F15" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H15" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I15" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J15" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K15" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L15" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M15" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N15" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O15" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1792,55 +1790,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C16" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D16" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E16" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F16" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H16" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I16" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J16" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K16" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L16" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M16" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N16" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O16" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,14 +1860,12 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1876,57 +1876,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C17" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D17" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E17" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H17" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I17" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J17" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K17" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L17" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M17" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N17" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O17" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1967,50 +1967,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C18" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D18" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E18" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F18" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I18" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J18" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K18" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L18" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M18" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N18" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O18" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2051,50 +2051,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C19" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D19" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E19" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F19" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H19" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I19" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J19" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K19" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L19" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M19" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N19" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O19" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,8 +2102,10 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
@@ -2135,56 +2137,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C20" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D20" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E20" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F20" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I20" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J20" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K20" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L20" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M20" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N20" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O20" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2214,80 +2218,74 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C21" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D21" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E21" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F21" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H21" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I21" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J21" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K21" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L21" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M21" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N21" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O21" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2302,70 +2300,74 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C22" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D22" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E22" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F22" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H22" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I22" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J22" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K22" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L22" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M22" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N22" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O22" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2382,81 +2384,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C23" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D23" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E23" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F23" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H23" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I23" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J23" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K23" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L23" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M23" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N23" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O23" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2468,55 +2464,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C24" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D24" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E24" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F24" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H24" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I24" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J24" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K24" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L24" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M24" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N24" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O24" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2550,57 +2550,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C25" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D25" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E25" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F25" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H25" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I25" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J25" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K25" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L25" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M25" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N25" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O25" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,15 +2611,13 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2634,57 +2632,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C26" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D26" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E26" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F26" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H26" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J26" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K26" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L26" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M26" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N26" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O26" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2700,8 +2698,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2714,72 +2714,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C27" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D27" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E27" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F27" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H27" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I27" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J27" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K27" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L27" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M27" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N27" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O27" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2787,8 +2789,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2798,147 +2802,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C28" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D28" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E28" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F28" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H28" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I28" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J28" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K28" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L28" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M28" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N28" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O28" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C29" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D29" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E29" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F29" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H29" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I29" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J29" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K29" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L29" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M29" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N29" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O29" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,18 +2949,14 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2972,68 +2966,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C30" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D30" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E30" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F30" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H30" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I30" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J30" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K30" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L30" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M30" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N30" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O30" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3052,65 +3054,63 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C31" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D31" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E31" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F31" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H31" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I31" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J31" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K31" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L31" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M31" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N31" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O31" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3138,57 +3138,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C32" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D32" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E32" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F32" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H32" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I32" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J32" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K32" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L32" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M32" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N32" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O32" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,18 +3196,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3220,59 +3220,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C33" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D33" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E33" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F33" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H33" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I33" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J33" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K33" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L33" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M33" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N33" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,18 +3276,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3304,61 +3300,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C34" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D34" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E34" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I34" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J34" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K34" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L34" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M34" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N34" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O34" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
@@ -3367,17 +3369,23 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3393,63 +3401,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C35" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D35" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E35" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F35" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H35" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I35" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J35" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K35" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L35" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M35" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N35" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O35" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
@@ -3458,77 +3462,69 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E36" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F36" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H36" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I36" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J36" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K36" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L36" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N36" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O36" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3536,18 +3532,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3560,61 +3556,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C37" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D37" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E37" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F37" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H37" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I37" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J37" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K37" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L37" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N37" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3623,7 +3625,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3642,69 +3644,67 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C38" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D38" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E38" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H38" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I38" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J38" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K38" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L38" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M38" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N38" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -3735,50 +3735,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C39" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D39" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E39" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F39" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H39" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I39" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J39" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K39" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L39" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M39" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N39" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O39" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,14 +3786,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3812,57 +3810,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C40" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D40" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E40" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F40" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H40" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I40" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J40" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K40" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L40" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M40" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N40" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O40" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,179 +3871,179 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C41" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D41" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E41" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F41" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H41" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I41" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J41" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K41" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L41" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M41" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C42" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D42" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E42" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F42" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H42" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I42" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J42" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K42" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L42" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M42" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N42" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O42" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4071,50 +4069,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C43" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D43" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E43" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F43" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I43" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J43" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K43" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L43" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M43" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N43" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O43" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4122,16 +4120,20 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4146,57 +4148,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C44" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D44" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E44" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F44" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H44" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I44" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J44" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K44" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L44" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M44" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N44" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O44" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4204,19 +4206,17 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4239,70 +4239,72 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C45" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D45" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E45" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F45" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H45" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I45" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J45" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K45" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L45" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M45" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N45" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O45" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4316,74 +4318,70 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C46" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D46" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E46" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F46" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H46" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I46" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J46" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K46" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L46" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M46" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N46" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O46" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4400,59 +4398,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C47" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D47" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E47" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F47" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H47" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I47" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J47" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K47" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L47" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M47" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N47" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O47" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4463,16 +4457,20 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4482,68 +4480,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C48" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D48" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E48" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F48" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H48" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I48" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J48" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K48" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L48" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M48" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N48" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O48" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4551,10 +4557,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4566,79 +4570,75 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C49" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D49" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E49" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F49" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H49" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I49" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J49" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K49" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L49" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M49" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N49" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O49" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4654,57 +4654,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C50" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D50" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E50" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F50" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I50" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J50" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K50" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L50" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M50" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N50" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O50" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4745,50 +4745,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C51" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D51" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E51" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F51" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H51" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I51" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J51" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K51" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L51" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M51" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N51" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O51" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4796,19 +4796,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4822,57 +4822,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C52" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D52" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E52" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F52" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I52" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J52" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K52" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L52" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M52" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N52" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O52" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,22 +4880,24 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4906,57 +4908,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C53" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D53" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E53" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F53" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H53" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I53" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J53" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K53" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L53" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M53" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N53" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4969,18 +4971,14 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4992,57 +4990,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C54" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D54" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E54" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F54" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H54" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I54" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J54" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K54" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L54" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M54" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N54" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O54" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5050,19 +5048,25 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5074,63 +5078,67 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C55" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D55" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E55" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F55" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H55" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I55" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J55" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K55" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L55" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M55" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N55" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O55" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5139,7 +5147,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5147,10 +5155,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5160,84 +5166,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C56" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D56" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E56" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F56" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H56" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I56" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J56" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K56" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L56" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M56" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N56" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O56" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5255,50 +5251,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C57" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D57" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E57" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F57" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H57" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I57" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J57" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K57" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L57" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M57" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N57" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O57" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5306,18 +5302,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5330,55 +5326,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C58" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D58" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E58" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F58" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H58" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I58" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J58" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K58" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L58" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M58" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N58" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O58" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5386,18 +5386,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5410,59 +5410,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C59" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D59" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E59" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H59" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I59" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J59" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K59" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L59" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M59" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N59" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O59" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5472,12 +5468,12 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5499,50 +5495,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C60" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D60" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E60" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F60" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H60" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I60" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J60" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K60" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L60" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M60" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N60" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O60" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5550,14 +5546,12 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5574,72 +5568,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C61" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D61" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E61" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F61" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H61" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I61" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J61" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K61" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L61" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M61" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N61" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O61" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5654,145 +5658,141 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C62" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D62" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E62" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H62" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I62" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J62" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K62" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L62" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M62" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N62" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O62" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C63" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D63" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E63" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F63" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H63" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I63" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J63" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K63" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L63" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M63" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N63" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O63" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5805,23 +5805,17 @@
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5833,50 +5827,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C64" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D64" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E64" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F64" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H64" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I64" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J64" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K64" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L64" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M64" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N64" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O64" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5884,22 +5878,30 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5911,50 +5913,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C65" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D65" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E65" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H65" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I65" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J65" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K65" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L65" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M65" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N65" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O65" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5962,10 +5964,8 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R65" s="6" t="n">
+        <v/>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
@@ -5974,18 +5974,14 @@
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
@@ -5997,50 +5993,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C66" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D66" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E66" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F66" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H66" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I66" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J66" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K66" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L66" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N66" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O66" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6058,14 +6054,18 @@
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U66" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V66" s="8" t="n">
-        <v/>
+      <c r="V66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
@@ -6077,50 +6077,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C67" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F67" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H67" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I67" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J67" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K67" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M67" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N67" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O67" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6131,80 +6131,78 @@
       <c r="R67" s="6" t="n">
         <v/>
       </c>
-      <c r="S67" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U67" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U67" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V67" s="8" t="n">
+        <v/>
       </c>
       <c r="W67" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C68" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D68" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E68" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F68" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I68" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J68" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K68" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L68" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M68" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N68" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O68" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6212,12 +6210,14 @@
       <c r="Q68" s="6" t="n">
         <v/>
       </c>
-      <c r="R68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T68" s="8" t="n">
@@ -6243,50 +6243,50 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C69" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D69" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E69" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F69" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H69" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I69" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J69" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K69" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L69" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M69" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N69" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O69" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6294,18 +6294,18 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R69" s="6" t="n">
+        <v/>
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6318,59 +6318,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C70" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D70" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E70" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F70" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H70" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I70" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J70" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L70" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M70" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N70" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O70" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6381,14 +6377,14 @@
       <c r="R70" s="6" t="n">
         <v/>
       </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T70" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U70" s="8" t="n">
@@ -6402,55 +6398,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C71" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D71" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E71" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F71" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H71" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I71" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J71" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K71" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L71" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6466,10 +6466,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T71" s="8" t="n">
+        <v/>
       </c>
       <c r="U71" s="8" t="n">
         <v/>
@@ -6484,57 +6482,57 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C72" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D72" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H72" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I72" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J72" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K72" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L72" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N72" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O72" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6545,13 +6543,15 @@
       <c r="R72" s="6" t="n">
         <v/>
       </c>
-      <c r="S72" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="n">
-        <v/>
+      <c r="S72" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U72" s="8" t="n">
         <v/>
@@ -6564,156 +6564,154 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D73" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H73" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I73" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J73" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L73" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M73" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N73" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O73" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
       </c>
-      <c r="Q73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
+      <c r="Q73" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
+      </c>
       <c r="U73" s="8" t="n">
         <v/>
       </c>
       <c r="V73" s="8" t="n">
         <v/>
       </c>
-      <c r="W73" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr"/>
+      <c r="W73" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C74" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D74" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F74" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H74" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I74" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J74" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M74" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N74" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O74" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T74" s="8" t="n">
@@ -6732,80 +6730,88 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C75" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H75" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I75" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M75" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N75" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O75" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R75" s="6" t="n">
-        <v/>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U75" s="8" t="n">
         <v/>
       </c>
-      <c r="V75" s="8" t="n">
-        <v/>
+      <c r="V75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W75" s="11" t="inlineStr">
         <is>
@@ -6814,88 +6820,82 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C76" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D76" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E76" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F76" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H76" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I76" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J76" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L76" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M76" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N76" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O76" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R76" s="6" t="inlineStr">
+      <c r="Q76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S76" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S76" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U76" s="8" t="n">
         <v/>
       </c>
-      <c r="V76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V76" s="8" t="n">
+        <v/>
       </c>
       <c r="W76" s="11" t="inlineStr">
         <is>
@@ -6904,77 +6904,79 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C77" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D77" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E77" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F77" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H77" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I77" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J77" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N77" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O77" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S77" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
+      </c>
       <c r="U77" s="8" t="n">
         <v/>
       </c>
@@ -6986,76 +6988,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C78" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D78" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E78" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F78" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H78" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I78" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J78" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K78" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O78" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R78" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R78" s="6" t="n">
+        <v/>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T78" s="8" t="n">
@@ -7077,50 +7071,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C79" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E79" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H79" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I79" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J79" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L79" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M79" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N79" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O79" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7131,23 +7125,29 @@
       <c r="R79" s="6" t="n">
         <v/>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W79" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V79" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W79" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X79" t="inlineStr"/>
@@ -7155,50 +7155,50 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E80" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F80" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H80" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I80" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J80" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L80" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M80" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N80" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O80" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7209,80 +7209,78 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V80" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V80" s="8" t="n">
+        <v/>
       </c>
       <c r="W80" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C81" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E81" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F81" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H81" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I81" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M81" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N81" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O81" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7314,57 +7312,57 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C82" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E82" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F82" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H82" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I82" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J82" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L82" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M82" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N82" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O82" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7372,16 +7370,20 @@
       <c r="Q82" s="6" t="n">
         <v/>
       </c>
-      <c r="R82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="n">
-        <v/>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U82" s="8" t="n">
         <v/>
@@ -7403,71 +7405,71 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C83" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D83" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H83" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I83" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K83" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L83" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M83" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N83" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O83" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
       </c>
-      <c r="Q83" s="6" t="n">
-        <v/>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S83" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7475,76 +7477,70 @@
       <c r="V83" s="8" t="n">
         <v/>
       </c>
-      <c r="W83" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W83" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C84" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D84" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E84" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F84" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H84" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I84" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J84" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K84" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L84" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O84" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
+      <c r="Q84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S84" s="7" t="inlineStr">
@@ -7571,50 +7567,50 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C85" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D85" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F85" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H85" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I85" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M85" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N85" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O85" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7622,18 +7618,18 @@
       <c r="Q85" s="6" t="n">
         <v/>
       </c>
-      <c r="R85" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R85" s="6" t="n">
+        <v/>
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U85" s="8" t="n">
         <v/>
@@ -7646,74 +7642,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr"/>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C86" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D86" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E86" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F86" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H86" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I86" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J86" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K86" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L86" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M86" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N86" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O86" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
       </c>
-      <c r="Q86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R86" s="6" t="n">
-        <v/>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v/>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7726,83 +7728,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C87" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D87" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E87" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F87" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I87" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J87" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N87" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O87" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
       </c>
-      <c r="Q87" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R87" s="6" t="inlineStr">
+      <c r="Q87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S87" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U87" s="8" t="n">
-        <v/>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V87" s="8" t="n">
         <v/>
@@ -7812,55 +7810,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr"/>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D88" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E88" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F88" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H88" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I88" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L88" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N88" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O88" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7871,20 +7873,16 @@
       <c r="R88" s="6" t="n">
         <v/>
       </c>
-      <c r="S88" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
       </c>
       <c r="V88" s="8" t="n">
         <v/>
@@ -7903,63 +7901,69 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C89" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D89" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E89" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F89" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H89" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I89" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J89" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K89" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L89" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M89" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N89" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O89" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P89" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q89" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R89" s="6" t="n">
-        <v/>
+        <v>77914.31</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T89" s="8" t="n">
@@ -7976,210 +7980,116 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>77270.17999999999</v>
+        <v>78181.33</v>
       </c>
       <c r="C90" t="n">
-        <v>77415.66</v>
+        <v>78232.38</v>
       </c>
       <c r="D90" t="n">
-        <v>76498.38</v>
+        <v>77752.48</v>
       </c>
       <c r="E90" t="n">
-        <v>76838.16</v>
+        <v>77967.62</v>
       </c>
       <c r="F90" t="n">
-        <v>-432.31</v>
+        <v>1129.46</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0147</v>
       </c>
       <c r="H90" t="n">
-        <v>917.27</v>
+        <v>479.89</v>
       </c>
       <c r="I90" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J90" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K90" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L90" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M90" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N90" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O90" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P90" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q90" s="6" t="inlineStr">
+      <c r="U90" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S90" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U90" s="8" t="n">
-        <v/>
-      </c>
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W90" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>76806.19</v>
-      </c>
-      <c r="C91" t="n">
-        <v>79435.67999999999</v>
-      </c>
-      <c r="D91" t="n">
-        <v>76452.55</v>
-      </c>
-      <c r="E91" t="n">
-        <v>78740.3</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1902.14</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2983.13</v>
-      </c>
-      <c r="I91" t="n">
-        <v>75581.11</v>
-      </c>
-      <c r="J91" t="n">
-        <v>75861.45</v>
-      </c>
-      <c r="K91" t="n">
-        <v>76379.52</v>
-      </c>
-      <c r="L91" t="n">
-        <v>76897.59</v>
-      </c>
-      <c r="M91" t="n">
-        <v>77296.78999999999</v>
-      </c>
-      <c r="N91" t="n">
-        <v>77696</v>
-      </c>
-      <c r="O91" t="n">
-        <v>78332.92999999999</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V91" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I92" s="13" t="n">
-        <v>73469.41</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>76155.25999999999</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>77248.73</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>78342.21000000001</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>80231.86</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>82121.52</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>82418.81</v>
+      <c r="I91" s="13" t="n">
+        <v>77272.59</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>77475.32000000001</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>77727.67</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>77980.02</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>78207.56</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>78435.10000000001</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>78712.27</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7998,13 +7998,13 @@
         <v>77752.48</v>
       </c>
       <c r="E90" t="n">
-        <v>77967.62</v>
+        <v>77908.47</v>
       </c>
       <c r="F90" t="n">
-        <v>1129.46</v>
+        <v>1070.31</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0139</v>
       </c>
       <c r="H90" t="n">
         <v>479.89</v>
@@ -8074,19 +8074,19 @@
         <v>77272.59</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>77475.32000000001</v>
+        <v>77386.60000000001</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>77727.67</v>
+        <v>77668.52</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>77980.02</v>
+        <v>77950.45</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>78207.56</v>
+        <v>78148.41</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>78435.10000000001</v>
+        <v>78346.38</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>78712.27</v>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7995,19 +7995,19 @@
         <v>78232.38</v>
       </c>
       <c r="D90" t="n">
-        <v>77752.48</v>
+        <v>77703.44</v>
       </c>
       <c r="E90" t="n">
-        <v>77908.47</v>
+        <v>77736.21000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>1070.31</v>
+        <v>898.05</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0117</v>
       </c>
       <c r="H90" t="n">
-        <v>479.89</v>
+        <v>528.9400000000001</v>
       </c>
       <c r="I90" t="n">
         <v>75581.11</v>
@@ -8071,25 +8071,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>77272.59</v>
+        <v>77174.5</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>77386.60000000001</v>
+        <v>77091.42999999999</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>77668.52</v>
+        <v>77471.74000000001</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>77950.45</v>
+        <v>77852.06</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>78148.41</v>
+        <v>78000.67999999999</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>78346.38</v>
+        <v>78149.3</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>78712.27</v>
+        <v>78761.31</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7995,19 +7995,19 @@
         <v>78232.38</v>
       </c>
       <c r="D90" t="n">
-        <v>77703.44</v>
+        <v>77638.84</v>
       </c>
       <c r="E90" t="n">
-        <v>77736.21000000001</v>
+        <v>77620.53999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>898.05</v>
+        <v>782.38</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0102</v>
       </c>
       <c r="H90" t="n">
-        <v>528.9400000000001</v>
+        <v>593.53</v>
       </c>
       <c r="I90" t="n">
         <v>75581.11</v>
@@ -8057,12 +8057,16 @@
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr"/>
+      <c r="W90" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -8071,25 +8075,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>77174.5</v>
+        <v>77045.31</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>77091.42999999999</v>
+        <v>76869.47</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>77471.74000000001</v>
+        <v>77323.77</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>77852.06</v>
+        <v>77778.07000000001</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>78000.67999999999</v>
+        <v>77917.3</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>78149.3</v>
+        <v>78056.53999999999</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>78761.31</v>
+        <v>78825.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7985,29 +7985,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>78181.33</v>
+        <v>76830.28</v>
       </c>
       <c r="C90" t="n">
-        <v>78232.38</v>
+        <v>79568.95</v>
       </c>
       <c r="D90" t="n">
-        <v>77638.84</v>
+        <v>76367.38</v>
       </c>
       <c r="E90" t="n">
-        <v>77620.53999999999</v>
+        <v>78163.38</v>
       </c>
       <c r="F90" t="n">
-        <v>782.38</v>
+        <v>1325.23</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0172</v>
       </c>
       <c r="H90" t="n">
-        <v>593.53</v>
+        <v>3201.58</v>
       </c>
       <c r="I90" t="n">
         <v>75581.11</v>
@@ -8036,8 +8036,10 @@
       <c r="Q90" s="6" t="n">
         <v/>
       </c>
-      <c r="R90" s="6" t="n">
-        <v/>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
@@ -8051,49 +8053,137 @@
       </c>
       <c r="U90" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W90" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W90" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>78181.33</v>
+      </c>
+      <c r="C91" t="n">
+        <v>78232.38</v>
+      </c>
+      <c r="D91" t="n">
+        <v>74984.84</v>
+      </c>
+      <c r="E91" t="n">
+        <v>75377.52</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-2785.86</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.0356</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3247.53</v>
+      </c>
+      <c r="I91" t="n">
+        <v>73165.8</v>
+      </c>
+      <c r="J91" t="n">
+        <v>75059.41</v>
+      </c>
+      <c r="K91" t="n">
+        <v>76562.59</v>
+      </c>
+      <c r="L91" t="n">
+        <v>78065.77</v>
+      </c>
+      <c r="M91" t="n">
+        <v>79764.17</v>
+      </c>
+      <c r="N91" t="n">
+        <v>81462.57000000001</v>
+      </c>
+      <c r="O91" t="n">
+        <v>82770.53</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
           <t>強警訊</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
-        <v>77045.31</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>76869.47</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>77323.77</v>
-      </c>
-      <c r="L91" s="13" t="n">
-        <v>77778.07000000001</v>
-      </c>
-      <c r="M91" s="13" t="n">
-        <v>77917.3</v>
-      </c>
-      <c r="N91" s="13" t="n">
-        <v>78056.53999999999</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>78825.91</v>
+      <c r="I92" s="13" t="n">
+        <v>71737.31</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>71514.45</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>73753.75999999999</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>75993.07000000001</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>77001.28999999999</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>78009.50999999999</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>81479.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64419.64</v>
+        <v>62897.52</v>
       </c>
       <c r="C2" t="n">
-        <v>64736.92</v>
+        <v>63568.22</v>
       </c>
       <c r="D2" t="n">
-        <v>62201.14</v>
+        <v>62275.58</v>
       </c>
       <c r="E2" t="n">
-        <v>62896.47</v>
+        <v>63540.84</v>
       </c>
       <c r="F2" t="n">
-        <v>-1521.97</v>
+        <v>644.36</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0236</v>
+        <v>0.0102</v>
       </c>
       <c r="H2" t="n">
-        <v>2535.78</v>
+        <v>1292.64</v>
       </c>
       <c r="I2" t="n">
-        <v>61387.23</v>
+        <v>59665.37</v>
       </c>
       <c r="J2" t="n">
-        <v>61587.58</v>
+        <v>60074.42</v>
       </c>
       <c r="K2" t="n">
-        <v>63176.6</v>
+        <v>61628.58</v>
       </c>
       <c r="L2" t="n">
-        <v>64765.61</v>
+        <v>63182.75</v>
       </c>
       <c r="M2" t="n">
-        <v>65660.28999999999</v>
+        <v>64164.36</v>
       </c>
       <c r="N2" t="n">
-        <v>66554.97</v>
+        <v>65145.97</v>
       </c>
       <c r="O2" t="n">
-        <v>68838.32000000001</v>
+        <v>67272.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,14 +692,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -718,57 +716,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62897.52</v>
+        <v>63535.81</v>
       </c>
       <c r="C3" t="n">
-        <v>63568.22</v>
+        <v>64307.14</v>
       </c>
       <c r="D3" t="n">
-        <v>62275.58</v>
+        <v>63149.66</v>
       </c>
       <c r="E3" t="n">
-        <v>63540.84</v>
+        <v>64239.68</v>
       </c>
       <c r="F3" t="n">
-        <v>644.36</v>
+        <v>698.84</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="H3" t="n">
-        <v>1292.64</v>
+        <v>1157.48</v>
       </c>
       <c r="I3" t="n">
-        <v>59665.37</v>
+        <v>60982.94</v>
       </c>
       <c r="J3" t="n">
-        <v>60074.42</v>
+        <v>62557.66</v>
       </c>
       <c r="K3" t="n">
-        <v>61628.58</v>
+        <v>62894.52</v>
       </c>
       <c r="L3" t="n">
-        <v>63182.75</v>
+        <v>63231.37</v>
       </c>
       <c r="M3" t="n">
-        <v>64164.36</v>
+        <v>64187.16</v>
       </c>
       <c r="N3" t="n">
-        <v>65145.97</v>
+        <v>65142.94</v>
       </c>
       <c r="O3" t="n">
-        <v>67272.7</v>
+        <v>64860.86</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,13 +777,15 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,78 +798,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63535.81</v>
+        <v>64242.32</v>
       </c>
       <c r="C4" t="n">
-        <v>64307.14</v>
+        <v>64506.58</v>
       </c>
       <c r="D4" t="n">
-        <v>63149.66</v>
+        <v>63221</v>
       </c>
       <c r="E4" t="n">
-        <v>64239.68</v>
+        <v>63237.54</v>
       </c>
       <c r="F4" t="n">
-        <v>698.84</v>
+        <v>-1002.14</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.0156</v>
       </c>
       <c r="H4" t="n">
-        <v>1157.48</v>
+        <v>1285.58</v>
       </c>
       <c r="I4" t="n">
-        <v>60982.94</v>
+        <v>61992.18</v>
       </c>
       <c r="J4" t="n">
-        <v>62557.66</v>
+        <v>63337.84</v>
       </c>
       <c r="K4" t="n">
-        <v>62894.52</v>
+        <v>63660.94</v>
       </c>
       <c r="L4" t="n">
-        <v>63231.37</v>
+        <v>63984.04</v>
       </c>
       <c r="M4" t="n">
-        <v>64187.16</v>
+        <v>64818.41</v>
       </c>
       <c r="N4" t="n">
-        <v>65142.94</v>
+        <v>65652.78999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>64860.86</v>
+        <v>65464.61</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -877,85 +875,89 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64242.32</v>
+        <v>63240.79</v>
       </c>
       <c r="C5" t="n">
-        <v>64506.58</v>
+        <v>65544</v>
       </c>
       <c r="D5" t="n">
-        <v>63221</v>
+        <v>63233.53</v>
       </c>
       <c r="E5" t="n">
-        <v>63237.54</v>
+        <v>63952.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-1002.14</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0113</v>
       </c>
       <c r="H5" t="n">
-        <v>1285.58</v>
+        <v>2310.47</v>
       </c>
       <c r="I5" t="n">
-        <v>61992.18</v>
+        <v>61935.42</v>
       </c>
       <c r="J5" t="n">
-        <v>63337.84</v>
+        <v>61638.84</v>
       </c>
       <c r="K5" t="n">
-        <v>63660.94</v>
+        <v>62594.75</v>
       </c>
       <c r="L5" t="n">
-        <v>63984.04</v>
+        <v>63550.66</v>
       </c>
       <c r="M5" t="n">
-        <v>64818.41</v>
+        <v>63880.33</v>
       </c>
       <c r="N5" t="n">
-        <v>65652.78999999999</v>
+        <v>64209.99</v>
       </c>
       <c r="O5" t="n">
-        <v>65464.61</v>
+        <v>65792.16</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -966,57 +968,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63240.79</v>
+        <v>63952.79</v>
       </c>
       <c r="C6" t="n">
-        <v>65544</v>
+        <v>64196.56</v>
       </c>
       <c r="D6" t="n">
-        <v>63233.53</v>
+        <v>61893.21</v>
       </c>
       <c r="E6" t="n">
-        <v>63952.11</v>
+        <v>62668.02</v>
       </c>
       <c r="F6" t="n">
-        <v>714.5700000000001</v>
+        <v>-1284.09</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0201</v>
       </c>
       <c r="H6" t="n">
-        <v>2310.47</v>
+        <v>2303.36</v>
       </c>
       <c r="I6" t="n">
-        <v>61935.42</v>
+        <v>60923.06</v>
       </c>
       <c r="J6" t="n">
-        <v>61638.84</v>
+        <v>61423.31</v>
       </c>
       <c r="K6" t="n">
-        <v>62594.75</v>
+        <v>62796.87</v>
       </c>
       <c r="L6" t="n">
-        <v>63550.66</v>
+        <v>64170.44</v>
       </c>
       <c r="M6" t="n">
-        <v>63880.33</v>
+        <v>65107.34</v>
       </c>
       <c r="N6" t="n">
-        <v>64209.99</v>
+        <v>66044.24000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>65792.16</v>
+        <v>67854.47</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,23 +1026,21 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1050,72 +1050,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63952.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C7" t="n">
-        <v>64196.56</v>
+        <v>63097.76</v>
       </c>
       <c r="D7" t="n">
-        <v>61893.21</v>
+        <v>59029.86</v>
       </c>
       <c r="E7" t="n">
-        <v>62668.02</v>
+        <v>60995.13</v>
       </c>
       <c r="F7" t="n">
-        <v>-1284.09</v>
+        <v>-1672.89</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0267</v>
       </c>
       <c r="H7" t="n">
-        <v>2303.36</v>
+        <v>4067.9</v>
       </c>
       <c r="I7" t="n">
-        <v>60923.06</v>
+        <v>59589.85</v>
       </c>
       <c r="J7" t="n">
-        <v>61423.31</v>
+        <v>60176.23</v>
       </c>
       <c r="K7" t="n">
-        <v>62796.87</v>
+        <v>61516.34</v>
       </c>
       <c r="L7" t="n">
-        <v>64170.44</v>
+        <v>62856.45</v>
       </c>
       <c r="M7" t="n">
-        <v>65107.34</v>
+        <v>63819.7</v>
       </c>
       <c r="N7" t="n">
-        <v>66044.24000000001</v>
+        <v>64782.94</v>
       </c>
       <c r="O7" t="n">
-        <v>67854.47</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+        <v>66499.92</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1139,67 +1139,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C8" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D8" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E8" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F8" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H8" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I8" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J8" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K8" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L8" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M8" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N8" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O8" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1223,50 +1219,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C9" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D9" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E9" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F9" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H9" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I9" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J9" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K9" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L9" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M9" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N9" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O9" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,14 +1270,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1298,55 +1292,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C10" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D10" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E10" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F10" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H10" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I10" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J10" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K10" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L10" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M10" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N10" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O10" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,7 +1355,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1385,50 +1383,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C11" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D11" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E11" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F11" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H11" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I11" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J11" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K11" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L11" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M11" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N11" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O11" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,12 +1434,14 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1458,59 +1458,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C12" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D12" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E12" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F12" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H12" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I12" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J12" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K12" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L12" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M12" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N12" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O12" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,19 +1514,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1542,74 +1538,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C13" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D13" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E13" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F13" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H13" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I13" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J13" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K13" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L13" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M13" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N13" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O13" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1622,84 +1624,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C14" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D14" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E14" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F14" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H14" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I14" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J14" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K14" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L14" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M14" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N14" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O14" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1708,55 +1706,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C15" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D15" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E15" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F15" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H15" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I15" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J15" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K15" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L15" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M15" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N15" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O15" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,21 +1769,19 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1792,57 +1792,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C16" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D16" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E16" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H16" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I16" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J16" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K16" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L16" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M16" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N16" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O16" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,7 +1853,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1883,50 +1883,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C17" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D17" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E17" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F17" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I17" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J17" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K17" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L17" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M17" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N17" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O17" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,7 +1937,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1967,50 +1967,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C18" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D18" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E18" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F18" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H18" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I18" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J18" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K18" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L18" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M18" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N18" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O18" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2018,10 +2018,12 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2051,63 +2053,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C19" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D19" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E19" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F19" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H19" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I19" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J19" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K19" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L19" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M19" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N19" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O19" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2130,80 +2134,74 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C20" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D20" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E20" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F20" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H20" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I20" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J20" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K20" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L20" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M20" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N20" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O20" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2218,70 +2216,74 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C21" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D21" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E21" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F21" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H21" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I21" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J21" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K21" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L21" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M21" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N21" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O21" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2298,81 +2300,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C22" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D22" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E22" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F22" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H22" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I22" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J22" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K22" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L22" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M22" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N22" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O22" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2384,55 +2380,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C23" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D23" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E23" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F23" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H23" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I23" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J23" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K23" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L23" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M23" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N23" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O23" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2443,7 +2443,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2466,57 +2466,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C24" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D24" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E24" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F24" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H24" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I24" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J24" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K24" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L24" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M24" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N24" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O24" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2529,13 +2529,11 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2550,57 +2548,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C25" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D25" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E25" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F25" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H25" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J25" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K25" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L25" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M25" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N25" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O25" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,13 +2609,15 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2630,72 +2630,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C26" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D26" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E26" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F26" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H26" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I26" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J26" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K26" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L26" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M26" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N26" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O26" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>64879.44</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2703,8 +2705,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2714,147 +2718,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C27" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D27" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E27" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F27" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H27" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I27" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J27" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K27" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L27" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M27" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N27" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O27" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C28" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D28" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E28" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F28" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H28" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I28" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J28" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K28" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L28" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M28" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N28" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O28" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2865,20 +2863,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2888,68 +2882,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C29" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D29" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E29" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F29" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H29" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I29" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J29" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K29" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L29" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M29" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N29" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O29" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2968,74 +2970,72 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C30" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D30" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E30" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F30" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H30" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I30" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J30" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K30" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L30" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M30" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N30" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O30" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3054,57 +3054,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C31" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D31" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E31" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F31" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H31" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I31" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J31" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K31" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L31" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M31" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N31" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O31" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,18 +3112,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3136,59 +3136,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C32" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D32" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E32" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F32" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H32" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I32" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J32" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K32" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L32" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M32" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N32" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,18 +3192,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3220,80 +3216,92 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C33" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D33" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E33" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I33" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J33" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K33" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L33" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M33" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N33" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O33" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3309,142 +3317,130 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C34" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D34" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E34" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F34" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H34" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I34" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J34" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K34" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L34" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M34" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N34" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O34" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E35" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F35" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H35" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I35" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J35" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K35" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L35" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N35" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O35" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3452,18 +3448,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3476,70 +3472,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C36" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D36" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E36" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F36" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H36" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I36" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J36" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K36" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L36" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N36" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3558,72 +3560,70 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C37" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D37" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E37" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H37" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I37" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J37" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K37" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L37" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M37" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N37" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3651,50 +3651,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C38" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D38" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E38" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F38" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H38" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I38" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J38" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K38" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L38" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M38" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N38" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O38" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,14 +3702,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3728,57 +3726,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C39" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D39" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E39" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F39" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H39" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I39" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J39" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K39" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L39" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M39" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N39" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O39" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3791,177 +3789,177 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C40" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D40" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E40" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F40" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H40" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I40" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J40" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K40" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L40" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M40" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C41" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D41" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E41" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F41" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H41" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I41" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J41" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K41" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L41" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M41" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N41" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O41" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3987,50 +3985,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C42" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D42" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E42" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F42" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I42" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J42" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K42" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L42" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M42" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N42" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O42" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4038,16 +4036,20 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4062,57 +4064,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C43" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D43" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E43" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F43" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H43" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I43" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J43" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K43" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L43" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M43" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N43" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O43" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4120,19 +4122,17 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4155,69 +4155,71 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C44" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D44" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E44" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F44" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H44" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I44" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J44" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K44" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L44" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M44" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N44" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O44" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4232,74 +4234,70 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C45" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D45" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E45" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F45" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H45" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I45" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J45" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K45" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L45" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M45" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N45" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O45" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4316,59 +4314,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C46" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D46" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E46" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F46" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H46" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I46" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J46" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K46" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L46" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M46" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N46" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O46" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4381,14 +4375,18 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4398,68 +4396,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C47" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D47" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E47" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F47" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H47" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I47" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J47" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K47" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L47" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M47" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N47" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O47" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4467,10 +4473,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4482,79 +4486,75 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C48" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D48" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E48" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F48" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H48" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I48" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J48" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K48" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L48" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M48" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N48" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O48" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4570,57 +4570,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C49" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D49" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E49" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F49" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I49" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J49" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K49" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L49" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M49" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N49" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O49" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,7 +4631,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4661,50 +4661,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C50" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D50" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E50" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F50" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H50" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I50" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J50" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K50" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L50" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M50" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N50" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O50" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4712,18 +4712,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4738,57 +4738,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C51" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D51" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E51" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F51" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I51" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J51" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K51" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L51" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M51" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N51" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O51" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4796,22 +4796,24 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4822,57 +4824,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C52" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D52" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E52" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F52" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H52" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I52" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J52" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K52" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L52" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M52" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N52" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4883,20 +4885,16 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4908,57 +4906,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C53" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D53" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E53" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F53" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H53" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I53" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J53" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K53" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L53" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M53" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N53" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O53" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4966,19 +4964,25 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4990,72 +4994,76 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C54" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D54" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E54" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F54" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H54" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I54" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J54" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K54" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L54" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M54" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N54" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O54" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -5063,10 +5071,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5076,84 +5082,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C55" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D55" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E55" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F55" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H55" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I55" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J55" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K55" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L55" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M55" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N55" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O55" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5171,50 +5167,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C56" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D56" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E56" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F56" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H56" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I56" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J56" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K56" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L56" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M56" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N56" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O56" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5222,18 +5218,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5246,55 +5242,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C57" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D57" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E57" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F57" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H57" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I57" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J57" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K57" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L57" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M57" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N57" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O57" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5302,18 +5302,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5326,59 +5326,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C58" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D58" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E58" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H58" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I58" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J58" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K58" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L58" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M58" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N58" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O58" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5388,12 +5384,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5415,50 +5411,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C59" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D59" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E59" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F59" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H59" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I59" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J59" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K59" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L59" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M59" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N59" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O59" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5466,14 +5462,12 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5490,72 +5484,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C60" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D60" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E60" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F60" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H60" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I60" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J60" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K60" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L60" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M60" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N60" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O60" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5570,145 +5574,141 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C61" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D61" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E61" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F61" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H61" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I61" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J61" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K61" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L61" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M61" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N61" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O61" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C62" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D62" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E62" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F62" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H62" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I62" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J62" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K62" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L62" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M62" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N62" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O62" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5719,25 +5719,19 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5749,50 +5743,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C63" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D63" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E63" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F63" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H63" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I63" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J63" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K63" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L63" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M63" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N63" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O63" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5800,22 +5794,30 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5827,50 +5829,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C64" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D64" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E64" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H64" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I64" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J64" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K64" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L64" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M64" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N64" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O64" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5878,30 +5880,24 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5913,50 +5909,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C65" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E65" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F65" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H65" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I65" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J65" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K65" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L65" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M65" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N65" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O65" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5967,21 +5963,25 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="10" t="inlineStr">
+      <c r="S65" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
@@ -5993,50 +5993,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C66" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F66" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H66" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I66" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J66" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K66" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M66" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N66" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O66" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6049,78 +6049,76 @@
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U66" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V66" s="8" t="n">
+        <v/>
       </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C67" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D67" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E67" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F67" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I67" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J67" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K67" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L67" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M67" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N67" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O67" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6128,12 +6126,14 @@
       <c r="Q67" s="6" t="n">
         <v/>
       </c>
-      <c r="R67" s="6" t="n">
-        <v/>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T67" s="8" t="n">
@@ -6159,50 +6159,50 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C68" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D68" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E68" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F68" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H68" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I68" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J68" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K68" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L68" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M68" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N68" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O68" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6210,18 +6210,18 @@
       <c r="Q68" s="6" t="n">
         <v/>
       </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S68" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="n">
-        <v/>
+      <c r="R68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U68" s="8" t="n">
         <v/>
@@ -6234,59 +6234,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C69" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D69" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E69" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F69" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H69" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I69" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J69" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L69" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M69" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N69" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O69" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6299,12 +6295,12 @@
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T69" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U69" s="8" t="n">
@@ -6318,55 +6314,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C70" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D70" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E70" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F70" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H70" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I70" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J70" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K70" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L70" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M70" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O70" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6377,15 +6377,13 @@
       <c r="R70" s="6" t="n">
         <v/>
       </c>
-      <c r="S70" s="7" t="inlineStr">
+      <c r="S70" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T70" s="8" t="n">
+        <v/>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6400,57 +6398,57 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C71" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D71" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H71" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I71" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J71" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K71" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L71" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N71" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6463,11 +6461,13 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U71" s="8" t="n">
         <v/>
@@ -6480,78 +6480,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D72" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H72" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I72" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J72" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L72" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M72" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N72" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O72" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R72" s="6" t="n">
-        <v/>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S72" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="n">
+        <v/>
       </c>
       <c r="U72" s="8" t="n">
         <v/>
@@ -6559,77 +6557,77 @@
       <c r="V72" s="8" t="n">
         <v/>
       </c>
-      <c r="W72" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr"/>
+      <c r="W72" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C73" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D73" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F73" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H73" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I73" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J73" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M73" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N73" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O73" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
       </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R73" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T73" s="8" t="n">
@@ -6648,80 +6646,88 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C74" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H74" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I74" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M74" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N74" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O74" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="n">
-        <v/>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
       </c>
-      <c r="V74" s="8" t="n">
-        <v/>
+      <c r="V74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W74" s="11" t="inlineStr">
         <is>
@@ -6730,88 +6736,82 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C75" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D75" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E75" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F75" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H75" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I75" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J75" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L75" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M75" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N75" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O75" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U75" s="8" t="n">
         <v/>
       </c>
-      <c r="V75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V75" s="8" t="n">
+        <v/>
       </c>
       <c r="W75" s="11" t="inlineStr">
         <is>
@@ -6820,76 +6820,78 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C76" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D76" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E76" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F76" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H76" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I76" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J76" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N76" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O76" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R76" s="6" t="n">
-        <v/>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v/>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
@@ -6902,76 +6904,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C77" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D77" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E77" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F77" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H77" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I77" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J77" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K77" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M77" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O77" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R77" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T77" s="8" t="n">
@@ -6993,50 +6987,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C78" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E78" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H78" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I78" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J78" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L78" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M78" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7049,21 +7043,27 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W78" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V78" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W78" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X78" t="inlineStr"/>
@@ -7071,50 +7071,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E79" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F79" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H79" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I79" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J79" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L79" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M79" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N79" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O79" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7127,78 +7127,76 @@
       </c>
       <c r="S79" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V79" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V79" s="8" t="n">
+        <v/>
       </c>
       <c r="W79" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr"/>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C80" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E80" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F80" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H80" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I80" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N80" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O80" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7209,7 +7207,7 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="7" t="inlineStr">
+      <c r="S80" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -7230,57 +7228,57 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E81" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F81" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H81" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I81" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J81" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L81" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M81" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N81" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O81" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7288,16 +7286,20 @@
       <c r="Q81" s="6" t="n">
         <v/>
       </c>
-      <c r="R81" s="6" t="n">
-        <v/>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U81" s="8" t="n">
         <v/>
@@ -7319,56 +7321,58 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C82" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D82" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E82" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H82" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I82" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K82" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L82" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M82" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N82" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O82" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
       </c>
-      <c r="Q82" s="6" t="n">
-        <v/>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
@@ -7377,13 +7381,11 @@
       </c>
       <c r="S82" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v/>
       </c>
       <c r="U82" s="8" t="n">
         <v/>
@@ -7391,79 +7393,73 @@
       <c r="V82" s="8" t="n">
         <v/>
       </c>
-      <c r="W82" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W82" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C83" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D83" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E83" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F83" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H83" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I83" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J83" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K83" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L83" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
       </c>
-      <c r="Q83" s="6" t="inlineStr">
+      <c r="Q83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S83" s="7" t="inlineStr">
+      <c r="S83" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -7487,50 +7483,50 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C84" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D84" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E84" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F84" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H84" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I84" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M84" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N84" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O84" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7538,18 +7534,18 @@
       <c r="Q84" s="6" t="n">
         <v/>
       </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S84" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="n">
-        <v/>
+      <c r="R84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7562,75 +7558,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C85" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D85" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E85" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F85" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H85" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I85" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J85" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K85" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L85" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M85" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O85" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
       </c>
-      <c r="Q85" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R85" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="inlineStr">
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S85" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
+      </c>
       <c r="U85" s="8" t="n">
         <v/>
       </c>
@@ -7642,83 +7644,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C86" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D86" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E86" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F86" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I86" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J86" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O86" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
       </c>
-      <c r="Q86" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
+      <c r="Q86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S86" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U86" s="8" t="n">
-        <v/>
+      <c r="U86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V86" s="8" t="n">
         <v/>
@@ -7728,55 +7726,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D87" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E87" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F87" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H87" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I87" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L87" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N87" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O87" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7789,18 +7791,14 @@
       </c>
       <c r="S87" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
       </c>
       <c r="V87" s="8" t="n">
         <v/>
@@ -7819,63 +7817,69 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C88" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D88" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E88" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F88" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H88" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I88" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J88" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K88" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L88" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M88" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N88" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O88" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>77914.31</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T88" s="8" t="n">
@@ -7892,149 +7896,153 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C89" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D89" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E89" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F89" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H89" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I89" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J89" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K89" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L89" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M89" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N89" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O89" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P89" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q89" s="6" t="inlineStr">
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R89" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S89" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W89" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="W89" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>76830.28</v>
+        <v>75586.50999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>79568.95</v>
+        <v>75865.09</v>
       </c>
       <c r="D90" t="n">
-        <v>76367.38</v>
+        <v>75404.10000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>78163.38</v>
+        <v>75465</v>
       </c>
       <c r="F90" t="n">
-        <v>1325.23</v>
+        <v>-2698.38</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0345</v>
       </c>
       <c r="H90" t="n">
-        <v>3201.58</v>
+        <v>460.98</v>
       </c>
       <c r="I90" t="n">
-        <v>75581.11</v>
+        <v>73165.8</v>
       </c>
       <c r="J90" t="n">
-        <v>75861.45</v>
+        <v>75059.41</v>
       </c>
       <c r="K90" t="n">
-        <v>76379.52</v>
+        <v>76562.59</v>
       </c>
       <c r="L90" t="n">
-        <v>76897.59</v>
+        <v>78065.77</v>
       </c>
       <c r="M90" t="n">
-        <v>77296.78999999999</v>
+        <v>79764.17</v>
       </c>
       <c r="N90" t="n">
-        <v>77696</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O90" t="n">
-        <v>78332.92999999999</v>
+        <v>82770.53</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
@@ -8043,23 +8051,17 @@
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V90" s="8" t="n">
+        <v/>
       </c>
       <c r="W90" s="9" t="inlineStr">
         <is>
@@ -8068,122 +8070,36 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>78181.33</v>
-      </c>
-      <c r="C91" t="n">
-        <v>78232.38</v>
-      </c>
-      <c r="D91" t="n">
-        <v>74984.84</v>
-      </c>
-      <c r="E91" t="n">
-        <v>75377.52</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-2785.86</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.0356</v>
-      </c>
-      <c r="H91" t="n">
-        <v>3247.53</v>
-      </c>
-      <c r="I91" t="n">
-        <v>73165.8</v>
-      </c>
-      <c r="J91" t="n">
-        <v>75059.41</v>
-      </c>
-      <c r="K91" t="n">
-        <v>76562.59</v>
-      </c>
-      <c r="L91" t="n">
-        <v>78065.77</v>
-      </c>
-      <c r="M91" t="n">
-        <v>79764.17</v>
-      </c>
-      <c r="N91" t="n">
-        <v>81462.57000000001</v>
-      </c>
-      <c r="O91" t="n">
-        <v>82770.53</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I92" s="13" t="n">
-        <v>71737.31</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>71514.45</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>73753.75999999999</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>75993.07000000001</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>77001.28999999999</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>78009.50999999999</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>81479.91</v>
+      <c r="I91" s="13" t="n">
+        <v>74943.12</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>74919.22</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>75234.50999999999</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>75549.8</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>75695.49000000001</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>75841.19</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>76326.07000000001</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7998,22 +7998,22 @@
         <v>75586.50999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>75865.09</v>
+        <v>76003.17999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>75404.10000000001</v>
+        <v>75417.87</v>
       </c>
       <c r="E90" t="n">
-        <v>75465</v>
+        <v>75949.36</v>
       </c>
       <c r="F90" t="n">
-        <v>-2698.38</v>
+        <v>-2214.02</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0345</v>
+        <v>-0.0283</v>
       </c>
       <c r="H90" t="n">
-        <v>460.98</v>
+        <v>585.3099999999999</v>
       </c>
       <c r="I90" t="n">
         <v>73165.8</v>
@@ -8039,14 +8039,12 @@
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="inlineStr">
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S90" s="10" t="inlineStr">
@@ -8081,25 +8079,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>74943.12</v>
+        <v>74832.55</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>74919.22</v>
+        <v>75483.46000000001</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>75234.50999999999</v>
+        <v>75656.7</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>75549.8</v>
+        <v>75829.94</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>75695.49000000001</v>
+        <v>76242.02</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>75841.19</v>
+        <v>76654.09</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>76326.07000000001</v>
+        <v>76588.49000000001</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7991,29 +7991,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>75586.50999999999</v>
+        <v>78162.48</v>
       </c>
       <c r="C90" t="n">
-        <v>76003.17999999999</v>
+        <v>78242.55</v>
       </c>
       <c r="D90" t="n">
-        <v>75417.87</v>
+        <v>74944.59</v>
       </c>
       <c r="E90" t="n">
-        <v>75949.36</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>-2214.02</v>
+        <v>-2550.88</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0326</v>
       </c>
       <c r="H90" t="n">
-        <v>585.3099999999999</v>
+        <v>3297.95</v>
       </c>
       <c r="I90" t="n">
         <v>73165.8</v>
@@ -8039,12 +8039,14 @@
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S90" s="10" t="inlineStr">
@@ -8073,31 +8075,113 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>75586.50999999999</v>
+      </c>
+      <c r="C91" t="n">
+        <v>76009.16</v>
+      </c>
+      <c r="D91" t="n">
+        <v>75349.47</v>
+      </c>
+      <c r="E91" t="n">
+        <v>75941.33</v>
+      </c>
+      <c r="F91" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H91" t="n">
+        <v>659.7</v>
+      </c>
+      <c r="I91" t="n">
+        <v>71646.64</v>
+      </c>
+      <c r="J91" t="n">
+        <v>71824.02</v>
+      </c>
+      <c r="K91" t="n">
+        <v>73963.53</v>
+      </c>
+      <c r="L91" t="n">
+        <v>76103.03999999999</v>
+      </c>
+      <c r="M91" t="n">
+        <v>77261.48</v>
+      </c>
+      <c r="N91" t="n">
+        <v>78419.92999999999</v>
+      </c>
+      <c r="O91" t="n">
+        <v>81540.5</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
-        <v>74832.55</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>75483.46000000001</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>75656.7</v>
-      </c>
-      <c r="L91" s="13" t="n">
-        <v>75829.94</v>
-      </c>
-      <c r="M91" s="13" t="n">
-        <v>76242.02</v>
-      </c>
-      <c r="N91" s="13" t="n">
-        <v>76654.09</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>76588.49000000001</v>
+      <c r="I92" s="13" t="n">
+        <v>74689.77</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>75412.64</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>75611.48</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>75810.32000000001</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>76271.17999999999</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>76732.03</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>76668.86</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8084,22 +8084,22 @@
         <v>75586.50999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>76009.16</v>
+        <v>76185.77</v>
       </c>
       <c r="D91" t="n">
         <v>75349.47</v>
       </c>
       <c r="E91" t="n">
-        <v>75941.33</v>
+        <v>76176.73</v>
       </c>
       <c r="F91" t="n">
-        <v>328.82</v>
+        <v>564.22</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0075</v>
       </c>
       <c r="H91" t="n">
-        <v>659.7</v>
+        <v>836.3</v>
       </c>
       <c r="I91" t="n">
         <v>71646.64</v>
@@ -8131,9 +8131,9 @@
       <c r="R91" s="6" t="n">
         <v/>
       </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T91" s="8" t="n">
@@ -8163,25 +8163,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>74689.77</v>
+        <v>74513.17</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>75412.64</v>
+        <v>75544.98</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>75611.48</v>
+        <v>75758.58</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>75810.32000000001</v>
+        <v>75972.17</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>76271.17999999999</v>
+        <v>76594.88</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>76732.03</v>
+        <v>77217.58</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>76668.86</v>
+        <v>77022.06</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8084,22 +8084,22 @@
         <v>75586.50999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>76185.77</v>
+        <v>76228.23</v>
       </c>
       <c r="D91" t="n">
         <v>75349.47</v>
       </c>
       <c r="E91" t="n">
-        <v>76176.73</v>
+        <v>76028.89</v>
       </c>
       <c r="F91" t="n">
-        <v>564.22</v>
+        <v>416.38</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0075</v>
+        <v>0.0055</v>
       </c>
       <c r="H91" t="n">
-        <v>836.3</v>
+        <v>878.76</v>
       </c>
       <c r="I91" t="n">
         <v>71646.64</v>
@@ -8131,9 +8131,9 @@
       <c r="R91" s="6" t="n">
         <v/>
       </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T91" s="8" t="n">
@@ -8163,25 +8163,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>74513.17</v>
+        <v>74470.71000000001</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>75544.98</v>
+        <v>75270.14999999999</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>75758.58</v>
+        <v>75589.50999999999</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>75972.17</v>
+        <v>75908.87</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>76594.88</v>
+        <v>76468.27</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>77217.58</v>
+        <v>77027.67</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>77022.06</v>
+        <v>77106.98</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8084,22 +8084,22 @@
         <v>75586.50999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>76228.23</v>
+        <v>76249.8</v>
       </c>
       <c r="D91" t="n">
-        <v>75349.47</v>
+        <v>75288.47</v>
       </c>
       <c r="E91" t="n">
-        <v>76028.89</v>
+        <v>75816.42</v>
       </c>
       <c r="F91" t="n">
-        <v>416.38</v>
+        <v>203.91</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0027</v>
       </c>
       <c r="H91" t="n">
-        <v>878.76</v>
+        <v>961.33</v>
       </c>
       <c r="I91" t="n">
         <v>71646.64</v>
@@ -8163,25 +8163,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>74470.71000000001</v>
+        <v>74327.14</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>75270.14999999999</v>
+        <v>74878.74000000001</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>75589.50999999999</v>
+        <v>75335.75999999999</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>75908.87</v>
+        <v>75792.78</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>76468.27</v>
+        <v>76297.09</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>77027.67</v>
+        <v>76801.39</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>77106.98</v>
+        <v>77211.12</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62897.52</v>
+        <v>63535.81</v>
       </c>
       <c r="C2" t="n">
-        <v>63568.22</v>
+        <v>64307.14</v>
       </c>
       <c r="D2" t="n">
-        <v>62275.58</v>
+        <v>63149.66</v>
       </c>
       <c r="E2" t="n">
-        <v>63540.84</v>
+        <v>64239.68</v>
       </c>
       <c r="F2" t="n">
-        <v>644.36</v>
+        <v>698.84</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="H2" t="n">
-        <v>1292.64</v>
+        <v>1157.48</v>
       </c>
       <c r="I2" t="n">
-        <v>59665.37</v>
+        <v>60982.94</v>
       </c>
       <c r="J2" t="n">
-        <v>60074.42</v>
+        <v>62557.66</v>
       </c>
       <c r="K2" t="n">
-        <v>61628.58</v>
+        <v>62894.52</v>
       </c>
       <c r="L2" t="n">
-        <v>63182.75</v>
+        <v>63231.37</v>
       </c>
       <c r="M2" t="n">
-        <v>64164.36</v>
+        <v>64187.16</v>
       </c>
       <c r="N2" t="n">
-        <v>65145.97</v>
+        <v>65142.94</v>
       </c>
       <c r="O2" t="n">
-        <v>67272.7</v>
+        <v>64860.86</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -697,11 +697,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -714,164 +716,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63535.81</v>
+        <v>64242.32</v>
       </c>
       <c r="C3" t="n">
-        <v>64307.14</v>
+        <v>64506.58</v>
       </c>
       <c r="D3" t="n">
-        <v>63149.66</v>
+        <v>63221</v>
       </c>
       <c r="E3" t="n">
-        <v>64239.68</v>
+        <v>63237.54</v>
       </c>
       <c r="F3" t="n">
-        <v>698.84</v>
+        <v>-1002.14</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.0156</v>
       </c>
       <c r="H3" t="n">
-        <v>1157.48</v>
+        <v>1285.58</v>
       </c>
       <c r="I3" t="n">
-        <v>60982.94</v>
+        <v>61992.18</v>
       </c>
       <c r="J3" t="n">
-        <v>62557.66</v>
+        <v>63337.84</v>
       </c>
       <c r="K3" t="n">
-        <v>62894.52</v>
+        <v>63660.94</v>
       </c>
       <c r="L3" t="n">
-        <v>63231.37</v>
+        <v>63984.04</v>
       </c>
       <c r="M3" t="n">
-        <v>64187.16</v>
+        <v>64818.41</v>
       </c>
       <c r="N3" t="n">
-        <v>65142.94</v>
+        <v>65652.78999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>64860.86</v>
+        <v>65464.61</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64242.32</v>
+        <v>63240.79</v>
       </c>
       <c r="C4" t="n">
-        <v>64506.58</v>
+        <v>65544</v>
       </c>
       <c r="D4" t="n">
-        <v>63221</v>
+        <v>63233.53</v>
       </c>
       <c r="E4" t="n">
-        <v>63237.54</v>
+        <v>63952.11</v>
       </c>
       <c r="F4" t="n">
-        <v>-1002.14</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0113</v>
       </c>
       <c r="H4" t="n">
-        <v>1285.58</v>
+        <v>2310.47</v>
       </c>
       <c r="I4" t="n">
-        <v>61992.18</v>
+        <v>61935.42</v>
       </c>
       <c r="J4" t="n">
-        <v>63337.84</v>
+        <v>61638.84</v>
       </c>
       <c r="K4" t="n">
-        <v>63660.94</v>
+        <v>62594.75</v>
       </c>
       <c r="L4" t="n">
-        <v>63984.04</v>
+        <v>63550.66</v>
       </c>
       <c r="M4" t="n">
-        <v>64818.41</v>
+        <v>63880.33</v>
       </c>
       <c r="N4" t="n">
-        <v>65652.78999999999</v>
+        <v>64209.99</v>
       </c>
       <c r="O4" t="n">
-        <v>65464.61</v>
+        <v>65792.16</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -882,57 +886,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63240.79</v>
+        <v>63952.79</v>
       </c>
       <c r="C5" t="n">
-        <v>65544</v>
+        <v>64196.56</v>
       </c>
       <c r="D5" t="n">
-        <v>63233.53</v>
+        <v>61893.21</v>
       </c>
       <c r="E5" t="n">
-        <v>63952.11</v>
+        <v>62668.02</v>
       </c>
       <c r="F5" t="n">
-        <v>714.5700000000001</v>
+        <v>-1284.09</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0201</v>
       </c>
       <c r="H5" t="n">
-        <v>2310.47</v>
+        <v>2303.36</v>
       </c>
       <c r="I5" t="n">
-        <v>61935.42</v>
+        <v>60923.06</v>
       </c>
       <c r="J5" t="n">
-        <v>61638.84</v>
+        <v>61423.31</v>
       </c>
       <c r="K5" t="n">
-        <v>62594.75</v>
+        <v>62796.87</v>
       </c>
       <c r="L5" t="n">
-        <v>63550.66</v>
+        <v>64170.44</v>
       </c>
       <c r="M5" t="n">
-        <v>63880.33</v>
+        <v>65107.34</v>
       </c>
       <c r="N5" t="n">
-        <v>64209.99</v>
+        <v>66044.24000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>65792.16</v>
+        <v>67854.47</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,23 +944,21 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -966,65 +968,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63952.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C6" t="n">
-        <v>64196.56</v>
+        <v>63097.76</v>
       </c>
       <c r="D6" t="n">
-        <v>61893.21</v>
+        <v>59029.86</v>
       </c>
       <c r="E6" t="n">
-        <v>62668.02</v>
+        <v>60995.13</v>
       </c>
       <c r="F6" t="n">
-        <v>-1284.09</v>
+        <v>-1672.89</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0267</v>
       </c>
       <c r="H6" t="n">
-        <v>2303.36</v>
+        <v>4067.9</v>
       </c>
       <c r="I6" t="n">
-        <v>60923.06</v>
+        <v>59589.85</v>
       </c>
       <c r="J6" t="n">
-        <v>61423.31</v>
+        <v>60176.23</v>
       </c>
       <c r="K6" t="n">
-        <v>62796.87</v>
+        <v>61516.34</v>
       </c>
       <c r="L6" t="n">
-        <v>64170.44</v>
+        <v>62856.45</v>
       </c>
       <c r="M6" t="n">
-        <v>65107.34</v>
+        <v>63819.7</v>
       </c>
       <c r="N6" t="n">
-        <v>66044.24000000001</v>
+        <v>64782.94</v>
       </c>
       <c r="O6" t="n">
-        <v>67854.47</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>66499.92</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
@@ -1055,60 +1057,56 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C7" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D7" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E7" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F7" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H7" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I7" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J7" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K7" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L7" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M7" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N7" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O7" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
@@ -1139,50 +1137,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C8" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D8" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E8" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F8" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H8" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I8" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J8" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K8" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L8" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M8" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N8" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O8" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,14 +1188,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1214,55 +1210,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C9" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D9" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E9" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F9" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H9" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I9" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J9" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K9" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L9" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M9" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N9" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O9" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1301,50 +1301,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C10" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D10" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E10" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F10" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H10" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I10" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J10" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K10" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L10" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M10" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N10" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O10" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,12 +1352,14 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1374,59 +1376,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C11" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D11" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E11" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F11" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H11" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I11" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J11" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K11" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L11" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M11" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N11" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O11" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1434,19 +1432,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1458,75 +1456,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C12" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D12" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E12" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F12" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H12" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I12" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J12" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K12" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L12" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M12" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N12" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O12" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1538,84 +1542,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C13" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D13" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E13" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F13" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H13" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I13" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J13" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K13" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L13" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M13" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N13" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O13" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1624,55 +1624,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C14" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D14" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E14" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F14" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H14" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I14" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J14" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K14" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L14" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M14" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N14" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O14" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,14 +1694,12 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1708,57 +1710,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C15" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D15" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E15" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H15" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I15" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J15" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K15" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L15" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M15" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N15" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O15" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1799,50 +1801,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C16" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D16" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E16" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F16" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I16" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J16" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K16" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L16" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M16" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N16" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O16" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1883,50 +1885,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C17" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D17" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E17" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F17" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H17" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I17" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J17" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K17" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L17" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M17" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N17" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O17" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1934,8 +1936,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1967,56 +1971,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C18" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D18" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E18" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F18" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H18" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I18" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J18" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K18" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L18" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M18" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N18" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O18" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
@@ -2046,80 +2052,74 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C19" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D19" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E19" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F19" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H19" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I19" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J19" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K19" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L19" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M19" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N19" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O19" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2134,70 +2134,74 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C20" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D20" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E20" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F20" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H20" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I20" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J20" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K20" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L20" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M20" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N20" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O20" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2214,81 +2218,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C21" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D21" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E21" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F21" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H21" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I21" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J21" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K21" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L21" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M21" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N21" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O21" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2300,55 +2298,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C22" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D22" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E22" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F22" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H22" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I22" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J22" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K22" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L22" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M22" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N22" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O22" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2382,57 +2384,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C23" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D23" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E23" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F23" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H23" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I23" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J23" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K23" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L23" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M23" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N23" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O23" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2443,15 +2445,13 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2466,57 +2466,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C24" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D24" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E24" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F24" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H24" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J24" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K24" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L24" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M24" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N24" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O24" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2532,8 +2532,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2546,72 +2548,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C25" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D25" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E25" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F25" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H25" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I25" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J25" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K25" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L25" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M25" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N25" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O25" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2619,8 +2623,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2630,147 +2636,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C26" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D26" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E26" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F26" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H26" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I26" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J26" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K26" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L26" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M26" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N26" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O26" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C27" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D27" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E27" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F27" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H27" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I27" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J27" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K27" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L27" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M27" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N27" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O27" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2783,18 +2783,14 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2804,68 +2800,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C28" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D28" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E28" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F28" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H28" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I28" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J28" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K28" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L28" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M28" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N28" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O28" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2884,65 +2888,63 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C29" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D29" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E29" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F29" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H29" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I29" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J29" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K29" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L29" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M29" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N29" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O29" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2951,7 +2953,7 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2970,57 +2972,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C30" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D30" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E30" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F30" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H30" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I30" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J30" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K30" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L30" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M30" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N30" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O30" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3028,18 +3030,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3052,59 +3054,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C31" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D31" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E31" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F31" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H31" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I31" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J31" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K31" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L31" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M31" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N31" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,18 +3110,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3136,61 +3134,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C32" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D32" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E32" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I32" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J32" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K32" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L32" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M32" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N32" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O32" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
@@ -3199,17 +3203,23 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3225,63 +3235,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C33" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D33" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E33" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F33" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H33" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I33" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J33" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K33" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L33" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M33" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N33" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O33" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
@@ -3290,77 +3296,69 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E34" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F34" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H34" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I34" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J34" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K34" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L34" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N34" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O34" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3368,18 +3366,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3392,61 +3390,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C35" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D35" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E35" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F35" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H35" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I35" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J35" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K35" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L35" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N35" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3455,7 +3459,7 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3474,69 +3478,67 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C36" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D36" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E36" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F36" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H36" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I36" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J36" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K36" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L36" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M36" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N36" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
@@ -3567,50 +3569,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C37" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D37" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E37" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F37" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H37" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I37" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J37" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K37" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L37" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M37" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N37" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O37" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3618,14 +3620,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3644,57 +3644,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C38" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D38" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E38" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F38" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H38" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I38" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J38" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K38" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L38" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M38" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N38" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O38" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,179 +3705,179 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C39" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D39" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E39" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F39" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H39" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I39" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J39" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K39" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L39" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M39" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C40" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D40" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E40" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H40" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I40" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J40" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K40" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L40" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M40" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N40" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O40" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3903,50 +3903,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C41" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D41" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E41" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F41" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I41" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J41" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K41" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L41" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M41" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N41" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O41" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,16 +3954,20 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3978,57 +3982,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C42" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D42" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E42" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F42" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H42" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I42" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J42" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K42" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L42" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M42" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N42" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O42" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4036,19 +4040,17 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4071,70 +4073,72 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C43" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D43" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E43" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F43" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H43" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I43" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J43" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K43" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L43" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M43" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N43" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O43" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4148,74 +4152,70 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C44" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D44" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E44" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F44" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H44" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I44" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J44" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K44" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L44" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M44" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N44" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O44" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4232,59 +4232,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C45" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D45" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E45" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F45" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H45" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I45" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J45" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K45" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L45" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M45" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N45" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O45" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4295,16 +4291,20 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4314,68 +4314,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C46" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D46" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E46" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F46" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H46" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I46" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J46" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K46" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L46" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M46" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N46" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O46" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4383,10 +4391,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4398,79 +4404,75 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C47" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D47" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E47" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F47" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H47" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I47" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J47" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K47" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L47" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M47" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N47" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O47" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4486,57 +4488,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C48" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D48" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E48" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F48" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I48" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J48" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K48" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L48" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M48" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N48" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O48" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4577,50 +4579,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C49" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D49" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E49" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F49" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H49" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I49" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J49" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K49" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L49" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M49" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N49" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O49" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4628,19 +4630,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4654,57 +4656,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C50" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D50" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E50" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F50" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I50" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J50" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K50" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L50" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M50" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N50" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O50" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4712,22 +4714,24 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4738,57 +4742,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C51" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D51" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E51" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F51" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H51" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I51" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J51" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K51" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L51" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M51" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N51" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4801,18 +4805,14 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4824,57 +4824,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C52" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D52" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E52" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F52" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H52" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I52" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J52" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K52" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L52" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M52" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N52" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O52" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4882,19 +4882,25 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4906,63 +4912,67 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C53" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D53" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E53" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F53" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H53" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I53" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J53" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K53" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L53" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M53" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N53" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O53" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4971,7 +4981,7 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
@@ -4979,10 +4989,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4992,84 +5000,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C54" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D54" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E54" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F54" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H54" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I54" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J54" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K54" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L54" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M54" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N54" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O54" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5087,50 +5085,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C55" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D55" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E55" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F55" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H55" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I55" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J55" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K55" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L55" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M55" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N55" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O55" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5138,18 +5136,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5162,55 +5160,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C56" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D56" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E56" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F56" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H56" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I56" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J56" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K56" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L56" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M56" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N56" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O56" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5218,18 +5220,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5242,59 +5244,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C57" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D57" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E57" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H57" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I57" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J57" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K57" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L57" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M57" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N57" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O57" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5304,12 +5302,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5331,50 +5329,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C58" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D58" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E58" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F58" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H58" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I58" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J58" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K58" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L58" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M58" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N58" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O58" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5382,14 +5380,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5406,72 +5402,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C59" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D59" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E59" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F59" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H59" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I59" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J59" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K59" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L59" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M59" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N59" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O59" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5486,145 +5492,141 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C60" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D60" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E60" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F60" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H60" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I60" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J60" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K60" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L60" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M60" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N60" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O60" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C61" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D61" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E61" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F61" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H61" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I61" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J61" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K61" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L61" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M61" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N61" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O61" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5637,23 +5639,17 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5665,50 +5661,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C62" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D62" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E62" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F62" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H62" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I62" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J62" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K62" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L62" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M62" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N62" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O62" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5716,22 +5712,30 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5743,50 +5747,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C63" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D63" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E63" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H63" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I63" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J63" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K63" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L63" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N63" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O63" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5794,10 +5798,8 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R63" s="6" t="n">
+        <v/>
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
@@ -5806,18 +5808,14 @@
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5829,50 +5827,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C64" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E64" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F64" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H64" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I64" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J64" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K64" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L64" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M64" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N64" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O64" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5890,14 +5888,18 @@
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5909,50 +5911,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C65" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F65" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H65" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I65" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J65" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K65" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M65" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N65" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O65" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5963,80 +5965,78 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C66" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D66" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E66" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F66" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I66" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J66" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K66" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L66" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M66" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N66" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O66" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6044,12 +6044,14 @@
       <c r="Q66" s="6" t="n">
         <v/>
       </c>
-      <c r="R66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S66" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T66" s="8" t="n">
@@ -6075,50 +6077,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C67" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D67" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E67" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F67" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H67" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I67" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J67" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K67" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L67" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M67" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N67" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O67" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6126,18 +6128,18 @@
       <c r="Q67" s="6" t="n">
         <v/>
       </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R67" s="6" t="n">
+        <v/>
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U67" s="8" t="n">
         <v/>
@@ -6150,59 +6152,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C68" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D68" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E68" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F68" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H68" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I68" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J68" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L68" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M68" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N68" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O68" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6213,14 +6211,14 @@
       <c r="R68" s="6" t="n">
         <v/>
       </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T68" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U68" s="8" t="n">
@@ -6234,55 +6232,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C69" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D69" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E69" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F69" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H69" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I69" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J69" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K69" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L69" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O69" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6298,10 +6300,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T69" s="8" t="n">
+        <v/>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6316,57 +6316,57 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C70" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D70" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H70" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I70" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J70" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K70" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L70" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M70" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N70" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O70" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6377,13 +6377,15 @@
       <c r="R70" s="6" t="n">
         <v/>
       </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="n">
-        <v/>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6396,156 +6398,154 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D71" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H71" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I71" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J71" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L71" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M71" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N71" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
+      <c r="Q71" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
+      </c>
       <c r="U71" s="8" t="n">
         <v/>
       </c>
       <c r="V71" s="8" t="n">
         <v/>
       </c>
-      <c r="W71" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr"/>
+      <c r="W71" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C72" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D72" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F72" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H72" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I72" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J72" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M72" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N72" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O72" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R72" s="6" t="n">
+        <v/>
       </c>
       <c r="S72" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T72" s="8" t="n">
@@ -6564,80 +6564,88 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C73" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H73" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I73" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M73" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N73" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O73" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
       </c>
-      <c r="Q73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R73" s="6" t="n">
-        <v/>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S73" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U73" s="8" t="n">
         <v/>
       </c>
-      <c r="V73" s="8" t="n">
-        <v/>
+      <c r="V73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W73" s="11" t="inlineStr">
         <is>
@@ -6646,88 +6654,82 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C74" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D74" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E74" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F74" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H74" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I74" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J74" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L74" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M74" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N74" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O74" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R74" s="6" t="inlineStr">
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S74" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U74" s="8" t="n">
         <v/>
       </c>
-      <c r="V74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V74" s="8" t="n">
+        <v/>
       </c>
       <c r="W74" s="11" t="inlineStr">
         <is>
@@ -6736,77 +6738,79 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C75" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D75" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E75" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F75" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H75" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I75" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J75" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M75" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N75" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O75" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="inlineStr">
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S75" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="n">
+        <v/>
+      </c>
       <c r="U75" s="8" t="n">
         <v/>
       </c>
@@ -6818,76 +6822,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C76" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D76" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E76" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F76" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H76" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I76" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J76" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K76" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O76" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R76" s="6" t="n">
+        <v/>
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T76" s="8" t="n">
@@ -6909,50 +6905,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C77" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E77" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H77" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I77" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J77" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L77" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M77" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O77" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6963,23 +6959,29 @@
       <c r="R77" s="6" t="n">
         <v/>
       </c>
-      <c r="S77" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U77" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V77" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W77" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V77" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W77" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X77" t="inlineStr"/>
@@ -6987,50 +6989,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E78" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F78" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H78" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I78" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J78" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L78" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M78" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N78" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O78" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7041,80 +7043,78 @@
       <c r="R78" s="6" t="n">
         <v/>
       </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U78" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V78" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S78" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V78" s="8" t="n">
+        <v/>
       </c>
       <c r="W78" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C79" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E79" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F79" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H79" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I79" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N79" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O79" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7146,57 +7146,57 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E80" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F80" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H80" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I80" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J80" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L80" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M80" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N80" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O80" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7204,16 +7204,20 @@
       <c r="Q80" s="6" t="n">
         <v/>
       </c>
-      <c r="R80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S80" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7235,71 +7239,71 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C81" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D81" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E81" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H81" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I81" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K81" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L81" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M81" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N81" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O81" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
       </c>
-      <c r="Q81" s="6" t="n">
-        <v/>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S81" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
       </c>
       <c r="U81" s="8" t="n">
         <v/>
@@ -7307,76 +7311,70 @@
       <c r="V81" s="8" t="n">
         <v/>
       </c>
-      <c r="W81" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W81" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C82" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D82" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E82" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F82" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H82" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I82" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J82" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K82" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L82" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O82" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
       </c>
-      <c r="Q82" s="6" t="inlineStr">
+      <c r="Q82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S82" s="10" t="inlineStr">
@@ -7403,50 +7401,50 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C83" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D83" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F83" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H83" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I83" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M83" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N83" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7454,18 +7452,18 @@
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R83" s="6" t="n">
+        <v/>
       </c>
       <c r="S83" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7478,74 +7476,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C84" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D84" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E84" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F84" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H84" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I84" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J84" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K84" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L84" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M84" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N84" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O84" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
       </c>
-      <c r="Q84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R84" s="6" t="n">
-        <v/>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S84" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7558,83 +7562,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C85" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D85" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E85" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F85" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I85" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J85" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M85" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O85" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
       </c>
-      <c r="Q85" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R85" s="6" t="inlineStr">
+      <c r="Q85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S85" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U85" s="8" t="n">
-        <v/>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V85" s="8" t="n">
         <v/>
@@ -7644,55 +7644,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr"/>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C86" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D86" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E86" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F86" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H86" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I86" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L86" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O86" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7703,20 +7707,16 @@
       <c r="R86" s="6" t="n">
         <v/>
       </c>
-      <c r="S86" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U86" s="8" t="n">
+        <v/>
       </c>
       <c r="V86" s="8" t="n">
         <v/>
@@ -7735,63 +7735,69 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C87" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D87" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E87" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F87" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H87" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I87" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J87" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K87" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L87" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M87" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N87" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O87" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R87" s="6" t="n">
-        <v/>
+        <v>77914.31</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S87" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T87" s="8" t="n">
@@ -7808,174 +7814,172 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C88" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D88" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E88" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F88" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H88" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I88" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J88" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K88" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L88" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M88" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N88" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O88" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P88" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q88" s="6" t="inlineStr">
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V88" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R88" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S88" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W88" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="W88" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>76830.28</v>
+        <v>78162.48</v>
       </c>
       <c r="C89" t="n">
-        <v>79568.95</v>
+        <v>78242.55</v>
       </c>
       <c r="D89" t="n">
-        <v>76367.38</v>
+        <v>74944.59</v>
       </c>
       <c r="E89" t="n">
-        <v>78163.38</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>1325.23</v>
+        <v>-2550.88</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0326</v>
       </c>
       <c r="H89" t="n">
-        <v>3201.58</v>
+        <v>3297.95</v>
       </c>
       <c r="I89" t="n">
-        <v>75581.11</v>
+        <v>73165.8</v>
       </c>
       <c r="J89" t="n">
-        <v>75861.45</v>
+        <v>75059.41</v>
       </c>
       <c r="K89" t="n">
-        <v>76379.52</v>
+        <v>76562.59</v>
       </c>
       <c r="L89" t="n">
-        <v>76897.59</v>
+        <v>78065.77</v>
       </c>
       <c r="M89" t="n">
-        <v>77296.78999999999</v>
+        <v>79764.17</v>
       </c>
       <c r="N89" t="n">
-        <v>77696</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O89" t="n">
-        <v>78332.92999999999</v>
+        <v>82770.53</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
       </c>
-      <c r="Q89" s="6" t="n">
-        <v/>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S89" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S89" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
       </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
@@ -7984,74 +7988,70 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>78162.48</v>
+        <v>76143.81</v>
       </c>
       <c r="C90" t="n">
-        <v>78242.55</v>
+        <v>76418.07000000001</v>
       </c>
       <c r="D90" t="n">
-        <v>74944.59</v>
+        <v>76143.81</v>
       </c>
       <c r="E90" t="n">
-        <v>75612.50999999999</v>
+        <v>76161.10000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>-2550.88</v>
+        <v>548.59</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0073</v>
       </c>
       <c r="H90" t="n">
-        <v>3297.95</v>
+        <v>274.26</v>
       </c>
       <c r="I90" t="n">
-        <v>73165.8</v>
+        <v>71646.64</v>
       </c>
       <c r="J90" t="n">
-        <v>75059.41</v>
+        <v>71824.02</v>
       </c>
       <c r="K90" t="n">
-        <v>76562.59</v>
+        <v>73963.53</v>
       </c>
       <c r="L90" t="n">
-        <v>78065.77</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="M90" t="n">
-        <v>79764.17</v>
+        <v>77261.48</v>
       </c>
       <c r="N90" t="n">
-        <v>81462.57000000001</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="O90" t="n">
-        <v>82770.53</v>
+        <v>81540.5</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">
@@ -8070,118 +8070,36 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>75586.50999999999</v>
-      </c>
-      <c r="C91" t="n">
-        <v>76249.8</v>
-      </c>
-      <c r="D91" t="n">
-        <v>75288.47</v>
-      </c>
-      <c r="E91" t="n">
-        <v>75816.42</v>
-      </c>
-      <c r="F91" t="n">
-        <v>203.91</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H91" t="n">
-        <v>961.33</v>
-      </c>
-      <c r="I91" t="n">
-        <v>71646.64</v>
-      </c>
-      <c r="J91" t="n">
-        <v>71824.02</v>
-      </c>
-      <c r="K91" t="n">
-        <v>73963.53</v>
-      </c>
-      <c r="L91" t="n">
-        <v>76103.03999999999</v>
-      </c>
-      <c r="M91" t="n">
-        <v>77261.48</v>
-      </c>
-      <c r="N91" t="n">
-        <v>78419.92999999999</v>
-      </c>
-      <c r="O91" t="n">
-        <v>81540.5</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I92" s="13" t="n">
-        <v>74327.14</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>74878.74000000001</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>75335.75999999999</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>75792.78</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>76297.09</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>76801.39</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>77211.12</v>
+      <c r="I91" s="13" t="n">
+        <v>75869.55</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>75826.92</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>76023.97</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>76221.02</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>76298.23</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>76375.44</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>76692.33</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7995,29 +7995,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>76143.81</v>
+        <v>75611.8</v>
       </c>
       <c r="C90" t="n">
-        <v>76418.07000000001</v>
+        <v>76474.08</v>
       </c>
       <c r="D90" t="n">
-        <v>76143.81</v>
+        <v>74995.52</v>
       </c>
       <c r="E90" t="n">
-        <v>76161.10000000001</v>
+        <v>76150.32000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>548.59</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.0071</v>
       </c>
       <c r="H90" t="n">
-        <v>274.26</v>
+        <v>1478.55</v>
       </c>
       <c r="I90" t="n">
         <v>71646.64</v>
@@ -8075,31 +8075,111 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>76143.81</v>
+      </c>
+      <c r="C91" t="n">
+        <v>76968.78999999999</v>
+      </c>
+      <c r="D91" t="n">
+        <v>75951.2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>76301.81</v>
+      </c>
+      <c r="F91" t="n">
+        <v>151.49</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1017.59</v>
+      </c>
+      <c r="I91" t="n">
+        <v>73516.97</v>
+      </c>
+      <c r="J91" t="n">
+        <v>74879.53</v>
+      </c>
+      <c r="K91" t="n">
+        <v>75411.03999999999</v>
+      </c>
+      <c r="L91" t="n">
+        <v>75942.56</v>
+      </c>
+      <c r="M91" t="n">
+        <v>76889.60000000001</v>
+      </c>
+      <c r="N91" t="n">
+        <v>77836.63</v>
+      </c>
+      <c r="O91" t="n">
+        <v>77952.63</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
-        <v>75869.55</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>75826.92</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>76023.97</v>
-      </c>
-      <c r="L91" s="13" t="n">
-        <v>76221.02</v>
-      </c>
-      <c r="M91" s="13" t="n">
-        <v>76298.23</v>
-      </c>
-      <c r="N91" s="13" t="n">
-        <v>76375.44</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>76692.33</v>
+      <c r="I92" s="13" t="n">
+        <v>74933.62</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>75205.13</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>75793.02</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>76380.89999999999</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>76810.61</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>77240.31</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>77986.38</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8090,13 +8090,13 @@
         <v>75951.2</v>
       </c>
       <c r="E91" t="n">
-        <v>76301.81</v>
+        <v>76368.75</v>
       </c>
       <c r="F91" t="n">
-        <v>151.49</v>
+        <v>218.43</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0029</v>
       </c>
       <c r="H91" t="n">
         <v>1017.59</v>
@@ -8164,19 +8164,19 @@
         <v>74933.62</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>75205.13</v>
+        <v>75305.53999999999</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>75793.02</v>
+        <v>75859.96000000001</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>76380.89999999999</v>
+        <v>76414.37</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>76810.61</v>
+        <v>76877.53999999999</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>77240.31</v>
+        <v>77340.71000000001</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>77986.38</v>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,19 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,69 +634,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63535.81</v>
+        <v>64242.32</v>
       </c>
       <c r="C2" t="n">
-        <v>64307.14</v>
+        <v>64506.58</v>
       </c>
       <c r="D2" t="n">
-        <v>63149.66</v>
+        <v>63221</v>
       </c>
       <c r="E2" t="n">
-        <v>64239.68</v>
+        <v>63237.54</v>
       </c>
       <c r="F2" t="n">
-        <v>698.84</v>
+        <v>-1002.14</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.0156</v>
       </c>
       <c r="H2" t="n">
-        <v>1157.48</v>
+        <v>1285.58</v>
       </c>
       <c r="I2" t="n">
-        <v>60982.94</v>
+        <v>61992.18</v>
       </c>
       <c r="J2" t="n">
-        <v>62557.66</v>
+        <v>63337.84</v>
       </c>
       <c r="K2" t="n">
-        <v>62894.52</v>
+        <v>63660.94</v>
       </c>
       <c r="L2" t="n">
-        <v>63231.37</v>
+        <v>63984.04</v>
       </c>
       <c r="M2" t="n">
-        <v>64187.16</v>
+        <v>64818.41</v>
       </c>
       <c r="N2" t="n">
-        <v>65142.94</v>
+        <v>65652.78999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>64860.86</v>
+        <v>65464.61</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,144 +708,148 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64242.32</v>
+        <v>63240.79</v>
       </c>
       <c r="C3" t="n">
-        <v>64506.58</v>
+        <v>65544</v>
       </c>
       <c r="D3" t="n">
-        <v>63221</v>
+        <v>63233.53</v>
       </c>
       <c r="E3" t="n">
-        <v>63237.54</v>
+        <v>63952.11</v>
       </c>
       <c r="F3" t="n">
-        <v>-1002.14</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0113</v>
       </c>
       <c r="H3" t="n">
-        <v>1285.58</v>
+        <v>2310.47</v>
       </c>
       <c r="I3" t="n">
-        <v>61992.18</v>
+        <v>61935.42</v>
       </c>
       <c r="J3" t="n">
-        <v>63337.84</v>
+        <v>61638.84</v>
       </c>
       <c r="K3" t="n">
-        <v>63660.94</v>
+        <v>62594.75</v>
       </c>
       <c r="L3" t="n">
-        <v>63984.04</v>
+        <v>63550.66</v>
       </c>
       <c r="M3" t="n">
-        <v>64818.41</v>
+        <v>63880.33</v>
       </c>
       <c r="N3" t="n">
-        <v>65652.78999999999</v>
+        <v>64209.99</v>
       </c>
       <c r="O3" t="n">
-        <v>65464.61</v>
+        <v>65792.16</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63240.79</v>
+        <v>63952.79</v>
       </c>
       <c r="C4" t="n">
-        <v>65544</v>
+        <v>64196.56</v>
       </c>
       <c r="D4" t="n">
-        <v>63233.53</v>
+        <v>61893.21</v>
       </c>
       <c r="E4" t="n">
-        <v>63952.11</v>
+        <v>62668.02</v>
       </c>
       <c r="F4" t="n">
-        <v>714.5700000000001</v>
+        <v>-1284.09</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0201</v>
       </c>
       <c r="H4" t="n">
-        <v>2310.47</v>
+        <v>2303.36</v>
       </c>
       <c r="I4" t="n">
-        <v>61935.42</v>
+        <v>60923.06</v>
       </c>
       <c r="J4" t="n">
-        <v>61638.84</v>
+        <v>61423.31</v>
       </c>
       <c r="K4" t="n">
-        <v>62594.75</v>
+        <v>62796.87</v>
       </c>
       <c r="L4" t="n">
-        <v>63550.66</v>
+        <v>64170.44</v>
       </c>
       <c r="M4" t="n">
-        <v>63880.33</v>
+        <v>65107.34</v>
       </c>
       <c r="N4" t="n">
-        <v>64209.99</v>
+        <v>66044.24000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>65792.16</v>
+        <v>67854.47</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,98 +857,96 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63952.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C5" t="n">
-        <v>64196.56</v>
+        <v>63097.76</v>
       </c>
       <c r="D5" t="n">
-        <v>61893.21</v>
+        <v>59029.86</v>
       </c>
       <c r="E5" t="n">
-        <v>62668.02</v>
+        <v>60995.13</v>
       </c>
       <c r="F5" t="n">
-        <v>-1284.09</v>
+        <v>-1672.89</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0267</v>
       </c>
       <c r="H5" t="n">
-        <v>2303.36</v>
+        <v>4067.9</v>
       </c>
       <c r="I5" t="n">
-        <v>60923.06</v>
+        <v>59589.85</v>
       </c>
       <c r="J5" t="n">
-        <v>61423.31</v>
+        <v>60176.23</v>
       </c>
       <c r="K5" t="n">
-        <v>62796.87</v>
+        <v>61516.34</v>
       </c>
       <c r="L5" t="n">
-        <v>64170.44</v>
+        <v>62856.45</v>
       </c>
       <c r="M5" t="n">
-        <v>65107.34</v>
+        <v>63819.7</v>
       </c>
       <c r="N5" t="n">
-        <v>66044.24000000001</v>
+        <v>64782.94</v>
       </c>
       <c r="O5" t="n">
-        <v>67854.47</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>66499.92</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -963,7 +960,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -973,67 +970,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C6" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D6" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E6" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F6" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H6" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I6" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J6" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K6" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L6" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M6" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N6" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O6" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1047,7 +1040,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1057,50 +1050,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C7" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D7" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E7" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F7" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H7" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I7" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J7" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K7" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L7" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M7" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N7" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O7" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,14 +1101,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1127,60 +1118,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C8" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D8" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E8" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F8" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H8" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I8" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J8" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K8" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L8" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M8" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N8" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O8" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,7 +1186,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1205,7 +1200,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1219,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C9" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D9" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E9" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H9" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I9" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J9" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K9" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L9" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M9" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N9" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O9" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,12 +1265,14 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1287,64 +1284,60 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C10" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D10" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E10" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F10" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H10" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I10" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J10" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K10" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L10" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M10" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N10" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O10" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,98 +1345,104 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C11" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D11" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E11" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F11" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H11" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I11" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J11" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K11" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L11" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M11" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N11" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O11" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1451,146 +1450,146 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C12" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D12" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E12" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F12" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H12" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I12" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J12" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K12" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L12" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M12" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N12" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O12" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C13" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D13" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E13" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H13" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I13" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J13" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K13" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L13" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M13" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N13" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O13" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,82 +1600,80 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C14" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D14" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E14" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F14" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H14" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I14" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J14" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K14" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L14" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M14" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N14" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O14" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,7 +1684,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1703,7 +1700,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1717,50 +1714,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C15" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D15" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E15" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F15" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I15" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J15" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K15" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L15" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M15" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N15" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O15" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,7 +1768,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1787,7 +1784,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1801,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C16" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D16" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E16" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F16" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H16" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I16" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J16" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K16" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L16" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M16" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N16" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O16" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,10 +1849,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1871,7 +1870,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1885,63 +1884,65 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C17" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D17" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E17" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F17" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H17" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I17" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J17" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K17" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L17" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M17" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N17" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O17" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1957,87 +1958,81 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C18" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D18" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E18" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F18" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H18" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I18" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J18" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K18" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L18" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M18" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N18" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O18" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2045,77 +2040,81 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C19" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D19" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E19" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F19" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H19" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I19" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J19" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K19" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L19" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M19" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N19" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O19" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2127,146 +2126,144 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C20" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D20" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E20" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F20" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H20" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I20" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J20" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K20" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L20" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M20" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N20" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O20" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C21" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D21" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E21" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F21" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H21" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I21" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J21" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K21" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L21" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M21" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N21" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O21" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2277,7 +2274,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2293,64 +2290,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C22" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D22" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E22" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F22" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H22" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I22" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J22" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K22" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L22" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M22" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N22" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O22" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2363,13 +2360,11 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2377,64 +2372,64 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C23" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D23" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E23" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F23" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H23" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J23" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K23" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L23" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M23" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N23" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O23" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,13 +2440,15 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2459,77 +2456,79 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C24" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D24" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E24" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F24" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H24" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I24" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J24" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K24" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L24" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M24" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N24" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O24" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>64879.44</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2537,158 +2536,154 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C25" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D25" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E25" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F25" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H25" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I25" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J25" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K25" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L25" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M25" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N25" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O25" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C26" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D26" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E26" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F26" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H26" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I26" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J26" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K26" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L26" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M26" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N26" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O26" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2699,91 +2694,95 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C27" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D27" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E27" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F27" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H27" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I27" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J27" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K27" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L27" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M27" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N27" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O27" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2795,81 +2794,79 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C28" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D28" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E28" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F28" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H28" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I28" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J28" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K28" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L28" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M28" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N28" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O28" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2881,64 +2878,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C29" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D29" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E29" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F29" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H29" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I29" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J29" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K29" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L29" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M29" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N29" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O29" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2946,18 +2943,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2965,64 +2962,60 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C30" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D30" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E30" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F30" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H30" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I30" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J30" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K30" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L30" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M30" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N30" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3030,18 +3023,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3049,87 +3042,99 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C31" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D31" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E31" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F31" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I31" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J31" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K31" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L31" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M31" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N31" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O31" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3143,142 +3148,130 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C32" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D32" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E32" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F32" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H32" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I32" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J32" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K32" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L32" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M32" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N32" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O32" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E33" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F33" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H33" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I33" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J33" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K33" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L33" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N33" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O33" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3286,18 +3279,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3305,75 +3298,81 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C34" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D34" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E34" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F34" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H34" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I34" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J34" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K34" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L34" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N34" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3385,79 +3384,77 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C35" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D35" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E35" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H35" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I35" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J35" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K35" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L35" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M35" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N35" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3471,7 +3468,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3485,50 +3482,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C36" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D36" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E36" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F36" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H36" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I36" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J36" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K36" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L36" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M36" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N36" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O36" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3536,14 +3533,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3555,64 +3550,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C37" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D37" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E37" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F37" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H37" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I37" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J37" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K37" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L37" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M37" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N37" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O37" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3625,177 +3620,177 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C38" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D38" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E38" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F38" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H38" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I38" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J38" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K38" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L38" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M38" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C39" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D39" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E39" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F39" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H39" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I39" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J39" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K39" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L39" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M39" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N39" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O39" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3807,7 +3802,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3821,50 +3816,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C40" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D40" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E40" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F40" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I40" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J40" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K40" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L40" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M40" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N40" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O40" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3872,16 +3867,20 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3889,64 +3888,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C41" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D41" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E41" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F41" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H41" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I41" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J41" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K41" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L41" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M41" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N41" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O41" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,19 +3953,17 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3975,7 +3972,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3989,69 +3986,71 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C42" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D42" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E42" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F42" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H42" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I42" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J42" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K42" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L42" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M42" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N42" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O42" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4059,81 +4058,77 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C43" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D43" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E43" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F43" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H43" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I43" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J43" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K43" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L43" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M43" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N43" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O43" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4145,64 +4140,60 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C44" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D44" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E44" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F44" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H44" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I44" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J44" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K44" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L44" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M44" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N44" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O44" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4215,85 +4206,97 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C45" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D45" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E45" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F45" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H45" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I45" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J45" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K45" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L45" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M45" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N45" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O45" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4301,94 +4304,88 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C46" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D46" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E46" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F46" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H46" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I46" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J46" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K46" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L46" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M46" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N46" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O46" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U46" s="8" t="n">
@@ -4397,64 +4394,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C47" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D47" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E47" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F47" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I47" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J47" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K47" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L47" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M47" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N47" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O47" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,7 +4462,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4481,7 +4478,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4495,50 +4492,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C48" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D48" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E48" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F48" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H48" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I48" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J48" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K48" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L48" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M48" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N48" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O48" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4546,18 +4543,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4565,64 +4562,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C49" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D49" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E49" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F49" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I49" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J49" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K49" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L49" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M49" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N49" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O49" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4630,83 +4627,85 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C50" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D50" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E50" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F50" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H50" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I50" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J50" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K50" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L50" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M50" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N50" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4717,82 +4716,78 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C51" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D51" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E51" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F51" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H51" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I51" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J51" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K51" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L51" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M51" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N51" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O51" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4800,96 +4795,106 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C52" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D52" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E52" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F52" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H52" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I52" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J52" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K52" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L52" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M52" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N52" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O52" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4897,97 +4902,85 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C53" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D53" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E53" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F53" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H53" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I53" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J53" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K53" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L53" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M53" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N53" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O53" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4995,7 +4988,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5005,50 +4998,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C54" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D54" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E54" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F54" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H54" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I54" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J54" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K54" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L54" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M54" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N54" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O54" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5056,18 +5049,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5075,60 +5068,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C55" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D55" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E55" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F55" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H55" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I55" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J55" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K55" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L55" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M55" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N55" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O55" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5136,18 +5133,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5155,64 +5152,60 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C56" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D56" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E56" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H56" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I56" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J56" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K56" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L56" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M56" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N56" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O56" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5222,12 +5215,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5239,7 +5232,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5249,50 +5242,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C57" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D57" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E57" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F57" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H57" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I57" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J57" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K57" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L57" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M57" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N57" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O57" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5300,14 +5293,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5319,77 +5310,87 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C58" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D58" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E58" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F58" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H58" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I58" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J58" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K58" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L58" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M58" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N58" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O58" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5397,152 +5398,148 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C59" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D59" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E59" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F59" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H59" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I59" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J59" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K59" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L59" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M59" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N59" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O59" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C60" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D60" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E60" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F60" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H60" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I60" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J60" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K60" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L60" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M60" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N60" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O60" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5553,27 +5550,21 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5583,50 +5574,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C61" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D61" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E61" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F61" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H61" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I61" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J61" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K61" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L61" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M61" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N61" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O61" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5634,24 +5625,32 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5661,50 +5660,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C62" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D62" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E62" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H62" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I62" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J62" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K62" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L62" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N62" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O62" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5712,32 +5711,26 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5747,50 +5740,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C63" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E63" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F63" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H63" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I63" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J63" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K63" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L63" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N63" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O63" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5801,23 +5794,27 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5827,50 +5824,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C64" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F64" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H64" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I64" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J64" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K64" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M64" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N64" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O64" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5883,78 +5880,76 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W64" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C65" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D65" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E65" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F65" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I65" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J65" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K65" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L65" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M65" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N65" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O65" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5962,12 +5957,14 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -5979,7 +5976,7 @@
       <c r="V65" s="8" t="n">
         <v/>
       </c>
-      <c r="W65" s="9" t="inlineStr">
+      <c r="W65" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5993,50 +5990,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C66" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D66" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E66" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F66" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H66" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I66" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J66" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K66" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L66" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M66" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N66" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O66" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6044,18 +6041,18 @@
       <c r="Q66" s="6" t="n">
         <v/>
       </c>
-      <c r="R66" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="n">
-        <v/>
+      <c r="R66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S66" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U66" s="8" t="n">
         <v/>
@@ -6063,64 +6060,60 @@
       <c r="V66" s="8" t="n">
         <v/>
       </c>
-      <c r="W66" s="9" t="inlineStr">
+      <c r="W66" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C67" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D67" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E67" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F67" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H67" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I67" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J67" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L67" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M67" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N67" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O67" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6133,12 +6126,12 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T67" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U67" s="8" t="n">
@@ -6147,60 +6140,64 @@
       <c r="V67" s="8" t="n">
         <v/>
       </c>
-      <c r="W67" s="9" t="inlineStr">
+      <c r="W67" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C68" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D68" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E68" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F68" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H68" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I68" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J68" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K68" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L68" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O68" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6211,15 +6208,13 @@
       <c r="R68" s="6" t="n">
         <v/>
       </c>
-      <c r="S68" s="10" t="inlineStr">
+      <c r="S68" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T68" s="8" t="n">
+        <v/>
       </c>
       <c r="U68" s="8" t="n">
         <v/>
@@ -6227,64 +6222,64 @@
       <c r="V68" s="8" t="n">
         <v/>
       </c>
-      <c r="W68" s="9" t="inlineStr">
+      <c r="W68" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C69" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D69" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H69" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I69" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J69" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K69" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L69" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N69" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O69" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6297,11 +6292,13 @@
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6309,83 +6306,81 @@
       <c r="V69" s="8" t="n">
         <v/>
       </c>
-      <c r="W69" s="9" t="inlineStr">
+      <c r="W69" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D70" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H70" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I70" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J70" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L70" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M70" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N70" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O70" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R70" s="6" t="n">
-        <v/>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v/>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6395,75 +6390,75 @@
       </c>
       <c r="W70" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C71" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D71" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F71" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H71" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I71" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J71" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M71" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N71" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S71" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T71" s="8" t="n">
@@ -6475,255 +6470,259 @@
       <c r="V71" s="8" t="n">
         <v/>
       </c>
-      <c r="W71" s="11" t="inlineStr">
+      <c r="W71" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C72" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H72" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I72" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M72" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N72" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O72" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S72" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="n">
-        <v/>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U72" s="8" t="n">
         <v/>
       </c>
-      <c r="V72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W72" s="11" t="inlineStr">
+      <c r="V72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W72" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C73" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D73" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E73" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F73" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H73" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I73" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J73" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L73" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M73" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N73" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O73" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
       </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R73" s="6" t="inlineStr">
+      <c r="Q73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U73" s="8" t="n">
         <v/>
       </c>
-      <c r="V73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W73" s="11" t="inlineStr">
+      <c r="V73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W73" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C74" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D74" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E74" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F74" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H74" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I74" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J74" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M74" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N74" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O74" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R74" s="6" t="n">
-        <v/>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6731,81 +6730,73 @@
       <c r="V74" s="8" t="n">
         <v/>
       </c>
-      <c r="W74" s="11" t="inlineStr">
+      <c r="W74" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C75" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D75" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E75" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F75" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H75" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I75" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J75" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K75" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N75" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O75" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S75" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T75" s="8" t="n">
@@ -6817,7 +6808,7 @@
       <c r="V75" s="8" t="n">
         <v/>
       </c>
-      <c r="W75" s="11" t="inlineStr">
+      <c r="W75" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -6827,50 +6818,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C76" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E76" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H76" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I76" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J76" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L76" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M76" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6883,21 +6874,27 @@
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V76" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V76" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W76" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X76" t="inlineStr"/>
@@ -6905,50 +6902,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E77" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F77" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H77" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I77" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J77" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L77" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M77" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N77" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O77" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6961,78 +6958,76 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V77" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W77" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W77" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr"/>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C78" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E78" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F78" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H78" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I78" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N78" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O78" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7043,7 +7038,7 @@
       <c r="R78" s="6" t="n">
         <v/>
       </c>
-      <c r="S78" s="10" t="inlineStr">
+      <c r="S78" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -7057,64 +7052,64 @@
       <c r="V78" s="8" t="n">
         <v/>
       </c>
-      <c r="W78" s="9" t="inlineStr">
+      <c r="W78" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E79" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F79" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H79" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I79" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J79" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L79" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M79" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N79" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O79" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7122,16 +7117,20 @@
       <c r="Q79" s="6" t="n">
         <v/>
       </c>
-      <c r="R79" s="6" t="n">
-        <v/>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S79" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7139,7 +7138,7 @@
       <c r="V79" s="8" t="n">
         <v/>
       </c>
-      <c r="W79" s="9" t="inlineStr">
+      <c r="W79" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -7153,56 +7152,58 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C80" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D80" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H80" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I80" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K80" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L80" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M80" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N80" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
       </c>
-      <c r="Q80" s="6" t="n">
-        <v/>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
@@ -7211,13 +7212,11 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7227,77 +7226,71 @@
       </c>
       <c r="W80" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C81" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D81" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E81" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F81" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H81" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I81" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J81" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K81" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L81" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M81" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O81" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
       </c>
-      <c r="Q81" s="6" t="inlineStr">
+      <c r="Q81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S81" s="10" t="inlineStr">
+      <c r="S81" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -7311,7 +7304,7 @@
       <c r="V81" s="8" t="n">
         <v/>
       </c>
-      <c r="W81" s="11" t="inlineStr">
+      <c r="W81" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -7321,50 +7314,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C82" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D82" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E82" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F82" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H82" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I82" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M82" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N82" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O82" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7372,18 +7365,18 @@
       <c r="Q82" s="6" t="n">
         <v/>
       </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S82" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="n">
-        <v/>
+      <c r="R82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U82" s="8" t="n">
         <v/>
@@ -7391,226 +7384,232 @@
       <c r="V82" s="8" t="n">
         <v/>
       </c>
-      <c r="W82" s="11" t="inlineStr">
+      <c r="W82" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C83" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D83" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E83" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F83" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H83" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I83" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J83" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K83" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L83" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M83" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N83" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
       </c>
-      <c r="Q83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S83" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
+      </c>
       <c r="U83" s="8" t="n">
         <v/>
       </c>
       <c r="V83" s="8" t="n">
         <v/>
       </c>
-      <c r="W83" s="11" t="inlineStr">
+      <c r="W83" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C84" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D84" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E84" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F84" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I84" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J84" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O84" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R84" s="6" t="inlineStr">
+      <c r="Q84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U84" s="8" t="n">
-        <v/>
+      <c r="U84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V84" s="8" t="n">
         <v/>
       </c>
-      <c r="W84" s="11" t="inlineStr">
+      <c r="W84" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C85" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D85" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E85" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F85" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H85" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I85" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L85" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M85" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O85" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7623,23 +7622,19 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v/>
       </c>
       <c r="V85" s="8" t="n">
         <v/>
       </c>
-      <c r="W85" s="11" t="inlineStr">
+      <c r="W85" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -7653,63 +7648,69 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C86" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D86" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E86" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F86" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H86" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I86" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J86" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K86" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L86" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M86" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N86" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O86" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S86" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>77914.31</v>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T86" s="8" t="n">
@@ -7721,154 +7722,158 @@
       <c r="V86" s="8" t="n">
         <v/>
       </c>
-      <c r="W86" s="11" t="inlineStr">
+      <c r="W86" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C87" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D87" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E87" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F87" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H87" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I87" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J87" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K87" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L87" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M87" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N87" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O87" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P87" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q87" s="6" t="inlineStr">
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V87" s="8" t="n">
-        <v/>
-      </c>
       <c r="W87" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>76830.28</v>
+        <v>78162.48</v>
       </c>
       <c r="C88" t="n">
-        <v>79568.95</v>
+        <v>78242.55</v>
       </c>
       <c r="D88" t="n">
-        <v>76367.38</v>
+        <v>74944.59</v>
       </c>
       <c r="E88" t="n">
-        <v>78163.38</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>1325.23</v>
+        <v>-2550.88</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0326</v>
       </c>
       <c r="H88" t="n">
-        <v>3201.58</v>
+        <v>3297.95</v>
       </c>
       <c r="I88" t="n">
-        <v>75581.11</v>
+        <v>73165.8</v>
       </c>
       <c r="J88" t="n">
-        <v>75861.45</v>
+        <v>75059.41</v>
       </c>
       <c r="K88" t="n">
-        <v>76379.52</v>
+        <v>76562.59</v>
       </c>
       <c r="L88" t="n">
-        <v>76897.59</v>
+        <v>78065.77</v>
       </c>
       <c r="M88" t="n">
-        <v>77296.78999999999</v>
+        <v>79764.17</v>
       </c>
       <c r="N88" t="n">
-        <v>77696</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O88" t="n">
-        <v>78332.92999999999</v>
+        <v>82770.53</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
       </c>
-      <c r="Q88" s="6" t="n">
-        <v/>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
@@ -7877,99 +7882,89 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W88" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W88" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>78162.48</v>
+        <v>75611.8</v>
       </c>
       <c r="C89" t="n">
-        <v>78242.55</v>
+        <v>76474.08</v>
       </c>
       <c r="D89" t="n">
-        <v>74944.59</v>
+        <v>74995.52</v>
       </c>
       <c r="E89" t="n">
-        <v>75612.50999999999</v>
+        <v>76150.32000000001</v>
       </c>
       <c r="F89" t="n">
-        <v>-2550.88</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0071</v>
       </c>
       <c r="H89" t="n">
-        <v>3297.95</v>
+        <v>1478.55</v>
       </c>
       <c r="I89" t="n">
-        <v>73165.8</v>
+        <v>71646.64</v>
       </c>
       <c r="J89" t="n">
-        <v>75059.41</v>
+        <v>71824.02</v>
       </c>
       <c r="K89" t="n">
-        <v>76562.59</v>
+        <v>73963.53</v>
       </c>
       <c r="L89" t="n">
-        <v>78065.77</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="M89" t="n">
-        <v>79764.17</v>
+        <v>77261.48</v>
       </c>
       <c r="N89" t="n">
-        <v>81462.57000000001</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="O89" t="n">
-        <v>82770.53</v>
+        <v>81540.5</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
       </c>
-      <c r="Q89" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R89" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R89" s="6" t="n">
+        <v/>
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T89" s="8" t="n">
@@ -7981,64 +7976,64 @@
       <c r="V89" s="8" t="n">
         <v/>
       </c>
-      <c r="W89" s="9" t="inlineStr">
+      <c r="W89" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>75611.8</v>
+        <v>76350.67999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>76474.08</v>
+        <v>76399.25999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>74995.52</v>
+        <v>76300.22</v>
       </c>
       <c r="E90" t="n">
-        <v>76150.32000000001</v>
+        <v>76307.59</v>
       </c>
       <c r="F90" t="n">
-        <v>537.8099999999999</v>
+        <v>157.27</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0021</v>
       </c>
       <c r="H90" t="n">
-        <v>1478.55</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>71646.64</v>
+        <v>73516.97</v>
       </c>
       <c r="J90" t="n">
-        <v>71824.02</v>
+        <v>74879.53</v>
       </c>
       <c r="K90" t="n">
-        <v>73963.53</v>
+        <v>75411.03999999999</v>
       </c>
       <c r="L90" t="n">
-        <v>76103.03999999999</v>
+        <v>75942.56</v>
       </c>
       <c r="M90" t="n">
-        <v>77261.48</v>
+        <v>76889.60000000001</v>
       </c>
       <c r="N90" t="n">
-        <v>78419.92999999999</v>
+        <v>77836.63</v>
       </c>
       <c r="O90" t="n">
-        <v>81540.5</v>
+        <v>77952.63</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8049,7 +8044,7 @@
       <c r="R90" s="6" t="n">
         <v/>
       </c>
-      <c r="S90" s="7" t="inlineStr">
+      <c r="S90" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -8063,7 +8058,7 @@
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="9" t="inlineStr">
+      <c r="W90" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -8072,114 +8067,6 @@
         <is>
           <t>弱警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>76143.81</v>
-      </c>
-      <c r="C91" t="n">
-        <v>76968.78999999999</v>
-      </c>
-      <c r="D91" t="n">
-        <v>75951.2</v>
-      </c>
-      <c r="E91" t="n">
-        <v>76368.75</v>
-      </c>
-      <c r="F91" t="n">
-        <v>218.43</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="H91" t="n">
-        <v>1017.59</v>
-      </c>
-      <c r="I91" t="n">
-        <v>73516.97</v>
-      </c>
-      <c r="J91" t="n">
-        <v>74879.53</v>
-      </c>
-      <c r="K91" t="n">
-        <v>75411.03999999999</v>
-      </c>
-      <c r="L91" t="n">
-        <v>75942.56</v>
-      </c>
-      <c r="M91" t="n">
-        <v>76889.60000000001</v>
-      </c>
-      <c r="N91" t="n">
-        <v>77836.63</v>
-      </c>
-      <c r="O91" t="n">
-        <v>77952.63</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I92" s="13" t="n">
-        <v>74933.62</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>75305.53999999999</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>75859.96000000001</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>76414.37</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>76877.53999999999</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>77340.71000000001</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>77986.38</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7997,22 +7997,22 @@
         <v>76350.67999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>76399.25999999999</v>
+        <v>76409.84</v>
       </c>
       <c r="D90" t="n">
         <v>76300.22</v>
       </c>
       <c r="E90" t="n">
-        <v>76307.59</v>
+        <v>76503.82000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>157.27</v>
+        <v>353.5</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0046</v>
       </c>
       <c r="H90" t="n">
-        <v>99.04000000000001</v>
+        <v>109.62</v>
       </c>
       <c r="I90" t="n">
         <v>73516.97</v>
@@ -8046,11 +8046,13 @@
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U90" s="8" t="n">
         <v/>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,64 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64242.32</v>
+        <v>63952.79</v>
       </c>
       <c r="C2" t="n">
-        <v>64506.58</v>
+        <v>64196.56</v>
       </c>
       <c r="D2" t="n">
-        <v>63221</v>
+        <v>61893.21</v>
       </c>
       <c r="E2" t="n">
-        <v>63237.54</v>
+        <v>62668.02</v>
       </c>
       <c r="F2" t="n">
-        <v>-1002.14</v>
+        <v>-1284.09</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0156</v>
+        <v>-0.0201</v>
       </c>
       <c r="H2" t="n">
-        <v>1285.58</v>
+        <v>2303.36</v>
       </c>
       <c r="I2" t="n">
-        <v>61992.18</v>
+        <v>60923.06</v>
       </c>
       <c r="J2" t="n">
-        <v>63337.84</v>
+        <v>61423.31</v>
       </c>
       <c r="K2" t="n">
-        <v>63660.94</v>
+        <v>62796.87</v>
       </c>
       <c r="L2" t="n">
-        <v>63984.04</v>
+        <v>64170.44</v>
       </c>
       <c r="M2" t="n">
-        <v>64818.41</v>
+        <v>65107.34</v>
       </c>
       <c r="N2" t="n">
-        <v>65652.78999999999</v>
+        <v>66044.24000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>65464.61</v>
+        <v>67854.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -708,93 +706,95 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63240.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C3" t="n">
-        <v>65544</v>
+        <v>63097.76</v>
       </c>
       <c r="D3" t="n">
-        <v>63233.53</v>
+        <v>59029.86</v>
       </c>
       <c r="E3" t="n">
-        <v>63952.11</v>
+        <v>60995.13</v>
       </c>
       <c r="F3" t="n">
-        <v>714.5700000000001</v>
+        <v>-1672.89</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0267</v>
       </c>
       <c r="H3" t="n">
-        <v>2310.47</v>
+        <v>4067.9</v>
       </c>
       <c r="I3" t="n">
-        <v>61935.42</v>
+        <v>59589.85</v>
       </c>
       <c r="J3" t="n">
-        <v>61638.84</v>
+        <v>60176.23</v>
       </c>
       <c r="K3" t="n">
-        <v>62594.75</v>
+        <v>61516.34</v>
       </c>
       <c r="L3" t="n">
-        <v>63550.66</v>
+        <v>62856.45</v>
       </c>
       <c r="M3" t="n">
-        <v>63880.33</v>
+        <v>63819.7</v>
       </c>
       <c r="N3" t="n">
-        <v>64209.99</v>
+        <v>64782.94</v>
       </c>
       <c r="O3" t="n">
-        <v>65792.16</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>66499.92</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -806,50 +806,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63952.79</v>
+        <v>60992.07</v>
       </c>
       <c r="C4" t="n">
-        <v>64196.56</v>
+        <v>61868.91</v>
       </c>
       <c r="D4" t="n">
-        <v>61893.21</v>
+        <v>58075.92</v>
       </c>
       <c r="E4" t="n">
-        <v>62668.02</v>
+        <v>59721.68</v>
       </c>
       <c r="F4" t="n">
-        <v>-1284.09</v>
+        <v>-1273.46</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0209</v>
       </c>
       <c r="H4" t="n">
-        <v>2303.36</v>
+        <v>3792.98</v>
       </c>
       <c r="I4" t="n">
-        <v>60923.06</v>
+        <v>54961.95</v>
       </c>
       <c r="J4" t="n">
-        <v>61423.31</v>
+        <v>56892.89</v>
       </c>
       <c r="K4" t="n">
-        <v>62796.87</v>
+        <v>58961.18</v>
       </c>
       <c r="L4" t="n">
-        <v>64170.44</v>
+        <v>61029.47</v>
       </c>
       <c r="M4" t="n">
-        <v>65107.34</v>
+        <v>63029.08</v>
       </c>
       <c r="N4" t="n">
-        <v>66044.24000000001</v>
+        <v>65028.7</v>
       </c>
       <c r="O4" t="n">
-        <v>67854.47</v>
+        <v>67165.66</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -878,77 +878,75 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62663.03</v>
+        <v>59712.05</v>
       </c>
       <c r="C5" t="n">
-        <v>63097.76</v>
+        <v>60647.19</v>
       </c>
       <c r="D5" t="n">
-        <v>59029.86</v>
+        <v>58269.12</v>
       </c>
       <c r="E5" t="n">
-        <v>60995.13</v>
+        <v>60016.43</v>
       </c>
       <c r="F5" t="n">
-        <v>-1672.89</v>
+        <v>294.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0267</v>
+        <v>0.0049</v>
       </c>
       <c r="H5" t="n">
-        <v>4067.9</v>
+        <v>2378.06</v>
       </c>
       <c r="I5" t="n">
-        <v>59589.85</v>
+        <v>54282.94</v>
       </c>
       <c r="J5" t="n">
-        <v>60176.23</v>
+        <v>55803.32</v>
       </c>
       <c r="K5" t="n">
-        <v>61516.34</v>
+        <v>57825.18</v>
       </c>
       <c r="L5" t="n">
-        <v>62856.45</v>
+        <v>59847.04</v>
       </c>
       <c r="M5" t="n">
-        <v>63819.7</v>
+        <v>61618.17</v>
       </c>
       <c r="N5" t="n">
-        <v>64782.94</v>
+        <v>63389.29</v>
       </c>
       <c r="O5" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>65661.89</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -962,58 +960,62 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60992.07</v>
+        <v>60016.31</v>
       </c>
       <c r="C6" t="n">
-        <v>61868.91</v>
+        <v>60835.05</v>
       </c>
       <c r="D6" t="n">
-        <v>58075.92</v>
+        <v>59794.62</v>
       </c>
       <c r="E6" t="n">
-        <v>59721.68</v>
+        <v>59940.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-1273.46</v>
+        <v>-76.33</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0013</v>
       </c>
       <c r="H6" t="n">
-        <v>3792.98</v>
+        <v>1040.43</v>
       </c>
       <c r="I6" t="n">
-        <v>54961.95</v>
+        <v>55891.06</v>
       </c>
       <c r="J6" t="n">
-        <v>56892.89</v>
+        <v>57917.5</v>
       </c>
       <c r="K6" t="n">
-        <v>58961.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L6" t="n">
-        <v>61029.47</v>
+        <v>59737.29</v>
       </c>
       <c r="M6" t="n">
-        <v>63029.08</v>
+        <v>61205.46</v>
       </c>
       <c r="N6" t="n">
-        <v>65028.7</v>
+        <v>62673.63</v>
       </c>
       <c r="O6" t="n">
-        <v>67165.66</v>
+        <v>63025.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,14 +1023,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1042,58 +1042,62 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59712.05</v>
+        <v>59940.35</v>
       </c>
       <c r="C7" t="n">
-        <v>60647.19</v>
+        <v>60432.71</v>
       </c>
       <c r="D7" t="n">
-        <v>58269.12</v>
+        <v>58879.63</v>
       </c>
       <c r="E7" t="n">
-        <v>60016.43</v>
+        <v>59532.34</v>
       </c>
       <c r="F7" t="n">
-        <v>294.75</v>
+        <v>-407.76</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0068</v>
       </c>
       <c r="H7" t="n">
-        <v>2378.06</v>
+        <v>1553.07</v>
       </c>
       <c r="I7" t="n">
-        <v>54282.94</v>
+        <v>58754.2</v>
       </c>
       <c r="J7" t="n">
-        <v>55803.32</v>
+        <v>58712.3</v>
       </c>
       <c r="K7" t="n">
-        <v>57825.18</v>
+        <v>59419.88</v>
       </c>
       <c r="L7" t="n">
-        <v>59847.04</v>
+        <v>60127.47</v>
       </c>
       <c r="M7" t="n">
-        <v>61618.17</v>
+        <v>60460.31</v>
       </c>
       <c r="N7" t="n">
-        <v>63389.29</v>
+        <v>60793.16</v>
       </c>
       <c r="O7" t="n">
-        <v>65661.89</v>
+        <v>61875.47</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,12 +1105,14 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1120,62 +1126,62 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60016.31</v>
+        <v>59522.79</v>
       </c>
       <c r="C8" t="n">
-        <v>60835.05</v>
+        <v>60682.34</v>
       </c>
       <c r="D8" t="n">
-        <v>59794.62</v>
+        <v>58856.19</v>
       </c>
       <c r="E8" t="n">
-        <v>59940.1</v>
+        <v>60138.38</v>
       </c>
       <c r="F8" t="n">
-        <v>-76.33</v>
+        <v>606.04</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0102</v>
       </c>
       <c r="H8" t="n">
-        <v>1040.43</v>
+        <v>1826.15</v>
       </c>
       <c r="I8" t="n">
-        <v>55891.06</v>
+        <v>57326.56</v>
       </c>
       <c r="J8" t="n">
-        <v>57917.5</v>
+        <v>57917.35</v>
       </c>
       <c r="K8" t="n">
-        <v>58827.4</v>
+        <v>58755.8</v>
       </c>
       <c r="L8" t="n">
-        <v>59737.29</v>
+        <v>59594.25</v>
       </c>
       <c r="M8" t="n">
-        <v>61205.46</v>
+        <v>60308.88</v>
       </c>
       <c r="N8" t="n">
-        <v>62673.63</v>
+        <v>61023.5</v>
       </c>
       <c r="O8" t="n">
-        <v>63025.25</v>
+        <v>61985.78</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,11 +1194,13 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1202,72 +1210,74 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59940.35</v>
+        <v>60136.45</v>
       </c>
       <c r="C9" t="n">
-        <v>60432.71</v>
+        <v>60173.22</v>
       </c>
       <c r="D9" t="n">
-        <v>58879.63</v>
+        <v>58111.67</v>
       </c>
       <c r="E9" t="n">
-        <v>59532.34</v>
+        <v>58558.86</v>
       </c>
       <c r="F9" t="n">
-        <v>-407.76</v>
+        <v>-1579.52</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0263</v>
       </c>
       <c r="H9" t="n">
-        <v>1553.07</v>
+        <v>2061.55</v>
       </c>
       <c r="I9" t="n">
-        <v>58754.2</v>
+        <v>57030.04</v>
       </c>
       <c r="J9" t="n">
-        <v>58712.3</v>
+        <v>58496.78</v>
       </c>
       <c r="K9" t="n">
-        <v>59419.88</v>
+        <v>59225.3</v>
       </c>
       <c r="L9" t="n">
-        <v>60127.47</v>
+        <v>59953.82</v>
       </c>
       <c r="M9" t="n">
-        <v>60460.31</v>
+        <v>61051.46</v>
       </c>
       <c r="N9" t="n">
-        <v>60793.16</v>
+        <v>62149.09</v>
       </c>
       <c r="O9" t="n">
-        <v>61875.47</v>
+        <v>62508.49</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
@@ -1286,58 +1296,62 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59522.79</v>
+        <v>58562.45</v>
       </c>
       <c r="C10" t="n">
-        <v>60682.34</v>
+        <v>61223.77</v>
       </c>
       <c r="D10" t="n">
-        <v>58856.19</v>
+        <v>57747.77</v>
       </c>
       <c r="E10" t="n">
-        <v>60138.38</v>
+        <v>60003.76</v>
       </c>
       <c r="F10" t="n">
-        <v>606.04</v>
+        <v>1444.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0247</v>
       </c>
       <c r="H10" t="n">
-        <v>1826.15</v>
+        <v>3476</v>
       </c>
       <c r="I10" t="n">
-        <v>57326.56</v>
+        <v>56050.12</v>
       </c>
       <c r="J10" t="n">
-        <v>57917.35</v>
+        <v>56205.52</v>
       </c>
       <c r="K10" t="n">
-        <v>58755.8</v>
+        <v>57528.09</v>
       </c>
       <c r="L10" t="n">
-        <v>59594.25</v>
+        <v>58850.65</v>
       </c>
       <c r="M10" t="n">
-        <v>60308.88</v>
+        <v>59589.63</v>
       </c>
       <c r="N10" t="n">
-        <v>61023.5</v>
+        <v>60328.61</v>
       </c>
       <c r="O10" t="n">
-        <v>61985.78</v>
+        <v>62234.77</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,95 +1369,95 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60136.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C11" t="n">
-        <v>60173.22</v>
+        <v>62117.88</v>
       </c>
       <c r="D11" t="n">
-        <v>58111.67</v>
+        <v>59532.32</v>
       </c>
       <c r="E11" t="n">
-        <v>58558.86</v>
+        <v>61485.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-1579.52</v>
+        <v>1481.54</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H11" t="n">
-        <v>2061.55</v>
+        <v>2585.55</v>
       </c>
       <c r="I11" t="n">
-        <v>57030.04</v>
+        <v>54271.76</v>
       </c>
       <c r="J11" t="n">
-        <v>58496.78</v>
+        <v>56786.75</v>
       </c>
       <c r="K11" t="n">
-        <v>59225.3</v>
+        <v>58265.76</v>
       </c>
       <c r="L11" t="n">
-        <v>59953.82</v>
+        <v>59744.76</v>
       </c>
       <c r="M11" t="n">
-        <v>61051.46</v>
+        <v>61741.76</v>
       </c>
       <c r="N11" t="n">
-        <v>62149.09</v>
+        <v>63738.76</v>
       </c>
       <c r="O11" t="n">
-        <v>62508.49</v>
+        <v>64699.77</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1452,7 +1466,7 @@
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1460,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58562.45</v>
+        <v>61492.07</v>
       </c>
       <c r="C12" t="n">
-        <v>61223.77</v>
+        <v>62879.01</v>
       </c>
       <c r="D12" t="n">
-        <v>57747.77</v>
+        <v>61176.72</v>
       </c>
       <c r="E12" t="n">
-        <v>60003.76</v>
+        <v>62544.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1444.9</v>
+        <v>1058.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H12" t="n">
-        <v>3476</v>
+        <v>1702.29</v>
       </c>
       <c r="I12" t="n">
-        <v>56050.12</v>
+        <v>56946.77</v>
       </c>
       <c r="J12" t="n">
-        <v>56205.52</v>
+        <v>59229.85</v>
       </c>
       <c r="K12" t="n">
-        <v>57528.09</v>
+        <v>60192.53</v>
       </c>
       <c r="L12" t="n">
-        <v>58850.65</v>
+        <v>61155.2</v>
       </c>
       <c r="M12" t="n">
-        <v>59589.63</v>
+        <v>62778.08</v>
       </c>
       <c r="N12" t="n">
-        <v>60328.61</v>
+        <v>64400.95</v>
       </c>
       <c r="O12" t="n">
-        <v>62234.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,75 +1535,69 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60004.77</v>
+        <v>62545.13</v>
       </c>
       <c r="C13" t="n">
-        <v>62117.88</v>
+        <v>63398.41</v>
       </c>
       <c r="D13" t="n">
-        <v>59532.32</v>
+        <v>62287.59</v>
       </c>
       <c r="E13" t="n">
-        <v>61485.3</v>
+        <v>63088.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1481.54</v>
+        <v>544.11</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>2585.55</v>
+        <v>1110.82</v>
       </c>
       <c r="I13" t="n">
-        <v>54271.76</v>
+        <v>59474.44</v>
       </c>
       <c r="J13" t="n">
-        <v>56786.75</v>
+        <v>61100.08</v>
       </c>
       <c r="K13" t="n">
-        <v>58265.76</v>
+        <v>61693.06</v>
       </c>
       <c r="L13" t="n">
-        <v>59744.76</v>
+        <v>62286.03</v>
       </c>
       <c r="M13" t="n">
-        <v>61741.76</v>
+        <v>63395.34</v>
       </c>
       <c r="N13" t="n">
-        <v>63738.76</v>
+        <v>64504.65</v>
       </c>
       <c r="O13" t="n">
-        <v>64699.77</v>
+        <v>64581.29</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1618,62 +1626,58 @@
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61492.07</v>
+        <v>63089.06</v>
       </c>
       <c r="C14" t="n">
-        <v>62879.01</v>
+        <v>63935.85</v>
       </c>
       <c r="D14" t="n">
-        <v>61176.72</v>
+        <v>62413.99</v>
       </c>
       <c r="E14" t="n">
-        <v>62544.2</v>
+        <v>63547.88</v>
       </c>
       <c r="F14" t="n">
-        <v>1058.9</v>
+        <v>459.58</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0073</v>
       </c>
       <c r="H14" t="n">
-        <v>1702.29</v>
+        <v>1521.86</v>
       </c>
       <c r="I14" t="n">
-        <v>56946.77</v>
+        <v>61176.76</v>
       </c>
       <c r="J14" t="n">
-        <v>59229.85</v>
+        <v>62100.13</v>
       </c>
       <c r="K14" t="n">
-        <v>60192.53</v>
+        <v>62532.89</v>
       </c>
       <c r="L14" t="n">
-        <v>61155.2</v>
+        <v>62965.65</v>
       </c>
       <c r="M14" t="n">
-        <v>62778.08</v>
+        <v>63643.72</v>
       </c>
       <c r="N14" t="n">
-        <v>64400.95</v>
+        <v>64321.78</v>
       </c>
       <c r="O14" t="n">
-        <v>64703.43</v>
+        <v>64509.23</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,8 +1685,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1702,71 +1708,71 @@
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62545.13</v>
+        <v>63551.02</v>
       </c>
       <c r="C15" t="n">
-        <v>63398.41</v>
+        <v>64597.57</v>
       </c>
       <c r="D15" t="n">
-        <v>62287.59</v>
+        <v>61275.83</v>
       </c>
       <c r="E15" t="n">
-        <v>63088.3</v>
+        <v>63995.02</v>
       </c>
       <c r="F15" t="n">
-        <v>544.11</v>
+        <v>447.13</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H15" t="n">
-        <v>1110.82</v>
+        <v>3321.74</v>
       </c>
       <c r="I15" t="n">
-        <v>59474.44</v>
+        <v>60892.14</v>
       </c>
       <c r="J15" t="n">
-        <v>61100.08</v>
+        <v>62212.51</v>
       </c>
       <c r="K15" t="n">
-        <v>61693.06</v>
+        <v>62786.96</v>
       </c>
       <c r="L15" t="n">
-        <v>62286.03</v>
+        <v>63361.4</v>
       </c>
       <c r="M15" t="n">
-        <v>63395.34</v>
+        <v>64308.81</v>
       </c>
       <c r="N15" t="n">
-        <v>64504.65</v>
+        <v>65256.22</v>
       </c>
       <c r="O15" t="n">
-        <v>64581.29</v>
+        <v>65457.7</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1786,62 +1792,62 @@
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63089.06</v>
+        <v>63994.6</v>
       </c>
       <c r="C16" t="n">
-        <v>63935.85</v>
+        <v>64257.63</v>
       </c>
       <c r="D16" t="n">
-        <v>62413.99</v>
+        <v>62623.93</v>
       </c>
       <c r="E16" t="n">
-        <v>63547.88</v>
+        <v>63297.39</v>
       </c>
       <c r="F16" t="n">
-        <v>459.58</v>
+        <v>-697.62</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0109</v>
       </c>
       <c r="H16" t="n">
-        <v>1521.86</v>
+        <v>1633.7</v>
       </c>
       <c r="I16" t="n">
-        <v>61176.76</v>
+        <v>57954.09</v>
       </c>
       <c r="J16" t="n">
-        <v>62100.13</v>
+        <v>61202.43</v>
       </c>
       <c r="K16" t="n">
-        <v>62532.89</v>
+        <v>62334.14</v>
       </c>
       <c r="L16" t="n">
-        <v>62965.65</v>
+        <v>63465.86</v>
       </c>
       <c r="M16" t="n">
-        <v>63643.72</v>
+        <v>65655.89</v>
       </c>
       <c r="N16" t="n">
-        <v>64321.78</v>
+        <v>67845.92</v>
       </c>
       <c r="O16" t="n">
-        <v>64509.23</v>
+        <v>67919.31</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,20 +1855,16 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1872,62 +1874,62 @@
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63551.02</v>
+        <v>63293.52</v>
       </c>
       <c r="C17" t="n">
-        <v>64597.57</v>
+        <v>63706.89</v>
       </c>
       <c r="D17" t="n">
-        <v>61275.83</v>
+        <v>61492.65</v>
       </c>
       <c r="E17" t="n">
-        <v>63995.02</v>
+        <v>62257.57</v>
       </c>
       <c r="F17" t="n">
-        <v>447.13</v>
+        <v>-1039.82</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0164</v>
       </c>
       <c r="H17" t="n">
-        <v>3321.74</v>
+        <v>2214.24</v>
       </c>
       <c r="I17" t="n">
-        <v>60892.14</v>
+        <v>60990.23</v>
       </c>
       <c r="J17" t="n">
-        <v>62212.51</v>
+        <v>61592</v>
       </c>
       <c r="K17" t="n">
-        <v>62786.96</v>
+        <v>62480.54</v>
       </c>
       <c r="L17" t="n">
-        <v>63361.4</v>
+        <v>63369.09</v>
       </c>
       <c r="M17" t="n">
-        <v>64308.81</v>
+        <v>64114.24</v>
       </c>
       <c r="N17" t="n">
-        <v>65256.22</v>
+        <v>64859.4</v>
       </c>
       <c r="O17" t="n">
-        <v>65457.7</v>
+        <v>65891.33</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,19 +1941,17 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1960,62 +1960,62 @@
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63994.6</v>
+        <v>62257.32</v>
       </c>
       <c r="C18" t="n">
-        <v>64257.63</v>
+        <v>63422.94</v>
       </c>
       <c r="D18" t="n">
-        <v>62623.93</v>
+        <v>61645.75</v>
       </c>
       <c r="E18" t="n">
-        <v>63297.39</v>
+        <v>63193.15</v>
       </c>
       <c r="F18" t="n">
-        <v>-697.62</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.015</v>
       </c>
       <c r="H18" t="n">
-        <v>1633.7</v>
+        <v>1777.19</v>
       </c>
       <c r="I18" t="n">
-        <v>57954.09</v>
+        <v>59278.41</v>
       </c>
       <c r="J18" t="n">
-        <v>61202.43</v>
+        <v>59872.24</v>
       </c>
       <c r="K18" t="n">
-        <v>62334.14</v>
+        <v>61150.46</v>
       </c>
       <c r="L18" t="n">
-        <v>63465.86</v>
+        <v>62428.67</v>
       </c>
       <c r="M18" t="n">
-        <v>65655.89</v>
+        <v>63364.69</v>
       </c>
       <c r="N18" t="n">
-        <v>67845.92</v>
+        <v>64300.72</v>
       </c>
       <c r="O18" t="n">
-        <v>67919.31</v>
+        <v>65921.12</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,13 +2026,15 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2042,7 +2044,7 @@
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2054,72 +2056,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63293.52</v>
+        <v>63194.36</v>
       </c>
       <c r="C19" t="n">
-        <v>63706.89</v>
+        <v>64658.97</v>
       </c>
       <c r="D19" t="n">
-        <v>61492.65</v>
+        <v>62902.06</v>
       </c>
       <c r="E19" t="n">
-        <v>62257.57</v>
+        <v>64127.14</v>
       </c>
       <c r="F19" t="n">
-        <v>-1039.82</v>
+        <v>933.99</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.0148</v>
       </c>
       <c r="H19" t="n">
-        <v>2214.24</v>
+        <v>1756.91</v>
       </c>
       <c r="I19" t="n">
-        <v>60990.23</v>
+        <v>59868.57</v>
       </c>
       <c r="J19" t="n">
-        <v>61592</v>
+        <v>61745.36</v>
       </c>
       <c r="K19" t="n">
-        <v>62480.54</v>
+        <v>62304.55</v>
       </c>
       <c r="L19" t="n">
-        <v>63369.09</v>
+        <v>62863.75</v>
       </c>
       <c r="M19" t="n">
-        <v>64114.24</v>
+        <v>64081.74</v>
       </c>
       <c r="N19" t="n">
-        <v>64859.4</v>
+        <v>65299.74</v>
       </c>
       <c r="O19" t="n">
-        <v>65891.33</v>
+        <v>65200.13</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2136,50 +2136,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62257.32</v>
+        <v>64127.97</v>
       </c>
       <c r="C20" t="n">
-        <v>63422.94</v>
+        <v>64445.46</v>
       </c>
       <c r="D20" t="n">
-        <v>61645.75</v>
+        <v>63785.62</v>
       </c>
       <c r="E20" t="n">
-        <v>63193.15</v>
+        <v>63802.03</v>
       </c>
       <c r="F20" t="n">
-        <v>935.5700000000001</v>
+        <v>-325.11</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.015</v>
+        <v>-0.0051</v>
       </c>
       <c r="H20" t="n">
-        <v>1777.19</v>
+        <v>659.84</v>
       </c>
       <c r="I20" t="n">
-        <v>59278.41</v>
+        <v>61145.16</v>
       </c>
       <c r="J20" t="n">
-        <v>59872.24</v>
+        <v>62543.55</v>
       </c>
       <c r="K20" t="n">
-        <v>61150.46</v>
+        <v>63248.69</v>
       </c>
       <c r="L20" t="n">
-        <v>62428.67</v>
+        <v>63953.83</v>
       </c>
       <c r="M20" t="n">
-        <v>63364.69</v>
+        <v>65005.59</v>
       </c>
       <c r="N20" t="n">
-        <v>64300.72</v>
+        <v>66057.36</v>
       </c>
       <c r="O20" t="n">
-        <v>65921.12</v>
+        <v>66415.88</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,15 +2190,13 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2208,7 +2206,7 @@
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2220,50 +2218,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63194.36</v>
+        <v>63791.4</v>
       </c>
       <c r="C21" t="n">
-        <v>64658.97</v>
+        <v>64243.13</v>
       </c>
       <c r="D21" t="n">
-        <v>62902.06</v>
+        <v>63606.82</v>
       </c>
       <c r="E21" t="n">
-        <v>64127.14</v>
+        <v>63758.22</v>
       </c>
       <c r="F21" t="n">
-        <v>933.99</v>
+        <v>-43.81</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>1756.91</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>59868.57</v>
+        <v>63125.78</v>
       </c>
       <c r="J21" t="n">
-        <v>61745.36</v>
+        <v>62985.43</v>
       </c>
       <c r="K21" t="n">
-        <v>62304.55</v>
+        <v>63472.11</v>
       </c>
       <c r="L21" t="n">
-        <v>62863.75</v>
+        <v>63958.78</v>
       </c>
       <c r="M21" t="n">
-        <v>64081.74</v>
+        <v>64131.95</v>
       </c>
       <c r="N21" t="n">
-        <v>65299.74</v>
+        <v>64305.11</v>
       </c>
       <c r="O21" t="n">
-        <v>65200.13</v>
+        <v>65105.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,14 +2272,14 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2292,7 +2290,7 @@
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2304,75 +2302,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64127.97</v>
+        <v>63757.17</v>
       </c>
       <c r="C22" t="n">
-        <v>64445.46</v>
+        <v>64340.88</v>
       </c>
       <c r="D22" t="n">
-        <v>63785.62</v>
+        <v>61769</v>
       </c>
       <c r="E22" t="n">
-        <v>63802.03</v>
+        <v>62239.12</v>
       </c>
       <c r="F22" t="n">
-        <v>-325.11</v>
+        <v>-1519.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0238</v>
       </c>
       <c r="H22" t="n">
-        <v>659.84</v>
+        <v>2571.88</v>
       </c>
       <c r="I22" t="n">
-        <v>61145.16</v>
+        <v>62970.52</v>
       </c>
       <c r="J22" t="n">
-        <v>62543.55</v>
+        <v>63038.53</v>
       </c>
       <c r="K22" t="n">
-        <v>63248.69</v>
+        <v>63440.06</v>
       </c>
       <c r="L22" t="n">
-        <v>63953.83</v>
+        <v>63841.6</v>
       </c>
       <c r="M22" t="n">
-        <v>65005.59</v>
+        <v>64076.37</v>
       </c>
       <c r="N22" t="n">
-        <v>66057.36</v>
+        <v>64311.15</v>
       </c>
       <c r="O22" t="n">
-        <v>66415.88</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2386,50 +2394,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63791.4</v>
+        <v>62238.59</v>
       </c>
       <c r="C23" t="n">
-        <v>64243.13</v>
+        <v>65046.13</v>
       </c>
       <c r="D23" t="n">
-        <v>63606.82</v>
+        <v>62207.52</v>
       </c>
       <c r="E23" t="n">
-        <v>63758.22</v>
+        <v>64956.11</v>
       </c>
       <c r="F23" t="n">
-        <v>-43.81</v>
+        <v>2716.99</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0437</v>
       </c>
       <c r="H23" t="n">
-        <v>636.3099999999999</v>
+        <v>2838.61</v>
       </c>
       <c r="I23" t="n">
-        <v>63125.78</v>
+        <v>59197.12</v>
       </c>
       <c r="J23" t="n">
-        <v>62985.43</v>
+        <v>59259.33</v>
       </c>
       <c r="K23" t="n">
-        <v>63472.11</v>
+        <v>60953.18</v>
       </c>
       <c r="L23" t="n">
-        <v>63958.78</v>
+        <v>62647.03</v>
       </c>
       <c r="M23" t="n">
-        <v>64131.95</v>
+        <v>63525.06</v>
       </c>
       <c r="N23" t="n">
-        <v>64305.11</v>
+        <v>64403.09</v>
       </c>
       <c r="O23" t="n">
-        <v>65105.3</v>
+        <v>66912.77</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,9 +2448,9 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2450,15 +2458,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2466,87 +2476,77 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63757.17</v>
+        <v>64959.81</v>
       </c>
       <c r="C24" t="n">
-        <v>64340.88</v>
+        <v>65507.59</v>
       </c>
       <c r="D24" t="n">
-        <v>61769</v>
+        <v>64442.82</v>
       </c>
       <c r="E24" t="n">
-        <v>62239.12</v>
+        <v>64712.38</v>
       </c>
       <c r="F24" t="n">
-        <v>-1519.1</v>
+        <v>-243.74</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0238</v>
+        <v>-0.0038</v>
       </c>
       <c r="H24" t="n">
-        <v>2571.88</v>
+        <v>1064.77</v>
       </c>
       <c r="I24" t="n">
-        <v>62970.52</v>
+        <v>59368.91</v>
       </c>
       <c r="J24" t="n">
-        <v>63038.53</v>
+        <v>62782.15</v>
       </c>
       <c r="K24" t="n">
-        <v>63440.06</v>
+        <v>63536.81</v>
       </c>
       <c r="L24" t="n">
-        <v>63841.6</v>
+        <v>64291.47</v>
       </c>
       <c r="M24" t="n">
-        <v>64076.37</v>
+        <v>66375.42</v>
       </c>
       <c r="N24" t="n">
-        <v>64311.15</v>
+        <v>68459.37</v>
       </c>
       <c r="O24" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67884.74000000001</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2558,132 +2558,136 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62238.59</v>
+        <v>64713.3</v>
       </c>
       <c r="C25" t="n">
-        <v>65046.13</v>
+        <v>64931.86</v>
       </c>
       <c r="D25" t="n">
-        <v>62207.52</v>
+        <v>63701.8</v>
       </c>
       <c r="E25" t="n">
-        <v>64956.11</v>
+        <v>63789.28</v>
       </c>
       <c r="F25" t="n">
-        <v>2716.99</v>
+        <v>-923.09</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0143</v>
       </c>
       <c r="H25" t="n">
-        <v>2838.61</v>
+        <v>1230.05</v>
       </c>
       <c r="I25" t="n">
-        <v>59197.12</v>
+        <v>63378.05</v>
       </c>
       <c r="J25" t="n">
-        <v>59259.33</v>
+        <v>63516.19</v>
       </c>
       <c r="K25" t="n">
-        <v>60953.18</v>
+        <v>64179.99</v>
       </c>
       <c r="L25" t="n">
-        <v>62647.03</v>
+        <v>64843.79</v>
       </c>
       <c r="M25" t="n">
-        <v>63525.06</v>
+        <v>65244.76</v>
       </c>
       <c r="N25" t="n">
-        <v>64403.09</v>
+        <v>65645.73</v>
       </c>
       <c r="O25" t="n">
-        <v>66912.77</v>
+        <v>66572.37</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64959.81</v>
+        <v>63789.91</v>
       </c>
       <c r="C26" t="n">
-        <v>65507.59</v>
+        <v>64332.02</v>
       </c>
       <c r="D26" t="n">
-        <v>64442.82</v>
+        <v>62489.45</v>
       </c>
       <c r="E26" t="n">
-        <v>64712.38</v>
+        <v>63899.46</v>
       </c>
       <c r="F26" t="n">
-        <v>-243.74</v>
+        <v>110.18</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.0017</v>
       </c>
       <c r="H26" t="n">
-        <v>1064.77</v>
+        <v>1842.57</v>
       </c>
       <c r="I26" t="n">
-        <v>59368.91</v>
+        <v>62471.75</v>
       </c>
       <c r="J26" t="n">
-        <v>62782.15</v>
+        <v>62295.46</v>
       </c>
       <c r="K26" t="n">
-        <v>63536.81</v>
+        <v>63174.26</v>
       </c>
       <c r="L26" t="n">
-        <v>64291.47</v>
+        <v>64053.06</v>
       </c>
       <c r="M26" t="n">
-        <v>66375.42</v>
+        <v>64404.31</v>
       </c>
       <c r="N26" t="n">
-        <v>68459.37</v>
+        <v>64755.56</v>
       </c>
       <c r="O26" t="n">
-        <v>67884.74000000001</v>
+        <v>66161.91</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,12 +2695,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2708,150 +2714,144 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64713.3</v>
+        <v>63899.18</v>
       </c>
       <c r="C27" t="n">
-        <v>64931.86</v>
+        <v>64816.5</v>
       </c>
       <c r="D27" t="n">
-        <v>63701.8</v>
+        <v>63845.02</v>
       </c>
       <c r="E27" t="n">
-        <v>63789.28</v>
+        <v>64796.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-923.09</v>
+        <v>897.14</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.014</v>
       </c>
       <c r="H27" t="n">
-        <v>1230.05</v>
+        <v>971.49</v>
       </c>
       <c r="I27" t="n">
-        <v>63378.05</v>
+        <v>60646.89</v>
       </c>
       <c r="J27" t="n">
-        <v>63516.19</v>
+        <v>62301.26</v>
       </c>
       <c r="K27" t="n">
-        <v>64179.99</v>
+        <v>62978.18</v>
       </c>
       <c r="L27" t="n">
-        <v>64843.79</v>
+        <v>63655.1</v>
       </c>
       <c r="M27" t="n">
-        <v>65244.76</v>
+        <v>64820.74</v>
       </c>
       <c r="N27" t="n">
-        <v>65645.73</v>
+        <v>65986.39</v>
       </c>
       <c r="O27" t="n">
-        <v>66572.37</v>
+        <v>66174.59</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63789.91</v>
+        <v>64799.28</v>
       </c>
       <c r="C28" t="n">
-        <v>64332.02</v>
+        <v>64909.89</v>
       </c>
       <c r="D28" t="n">
-        <v>62489.45</v>
+        <v>64250.91</v>
       </c>
       <c r="E28" t="n">
-        <v>63899.46</v>
+        <v>64690.8</v>
       </c>
       <c r="F28" t="n">
-        <v>110.18</v>
+        <v>-105.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0016</v>
       </c>
       <c r="H28" t="n">
-        <v>1842.57</v>
+        <v>658.97</v>
       </c>
       <c r="I28" t="n">
-        <v>62471.75</v>
+        <v>62873.53</v>
       </c>
       <c r="J28" t="n">
-        <v>62295.46</v>
+        <v>64058.03</v>
       </c>
       <c r="K28" t="n">
-        <v>63174.26</v>
+        <v>64310.86</v>
       </c>
       <c r="L28" t="n">
-        <v>64053.06</v>
+        <v>64563.68</v>
       </c>
       <c r="M28" t="n">
-        <v>64404.31</v>
+        <v>65282.35</v>
       </c>
       <c r="N28" t="n">
-        <v>64755.56</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>66161.91</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2864,9 +2864,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2878,73 +2878,77 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63899.18</v>
+        <v>64684.42</v>
       </c>
       <c r="C29" t="n">
-        <v>64816.5</v>
+        <v>65735.72</v>
       </c>
       <c r="D29" t="n">
-        <v>63845.02</v>
+        <v>63720.39</v>
       </c>
       <c r="E29" t="n">
-        <v>64796.6</v>
+        <v>65230.03</v>
       </c>
       <c r="F29" t="n">
-        <v>897.14</v>
+        <v>539.22</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>971.49</v>
+        <v>2015.33</v>
       </c>
       <c r="I29" t="n">
-        <v>60646.89</v>
+        <v>63591.94</v>
       </c>
       <c r="J29" t="n">
-        <v>62301.26</v>
+        <v>64087.03</v>
       </c>
       <c r="K29" t="n">
-        <v>62978.18</v>
+        <v>64361.32</v>
       </c>
       <c r="L29" t="n">
-        <v>63655.1</v>
+        <v>64635.6</v>
       </c>
       <c r="M29" t="n">
-        <v>64820.74</v>
+        <v>65020.29</v>
       </c>
       <c r="N29" t="n">
-        <v>65986.39</v>
+        <v>65404.98</v>
       </c>
       <c r="O29" t="n">
-        <v>66174.59</v>
+        <v>65568.86</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2953,69 +2957,77 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64799.28</v>
+        <v>65228.87</v>
       </c>
       <c r="C30" t="n">
-        <v>64909.89</v>
+        <v>66910.06</v>
       </c>
       <c r="D30" t="n">
-        <v>64250.91</v>
+        <v>65113.66</v>
       </c>
       <c r="E30" t="n">
-        <v>64690.8</v>
+        <v>66505.12</v>
       </c>
       <c r="F30" t="n">
-        <v>-105.8</v>
+        <v>1275.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0195</v>
       </c>
       <c r="H30" t="n">
-        <v>658.97</v>
+        <v>1796.41</v>
       </c>
       <c r="I30" t="n">
-        <v>62873.53</v>
+        <v>61705.06</v>
       </c>
       <c r="J30" t="n">
-        <v>64058.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K30" t="n">
-        <v>64310.86</v>
+        <v>64222.36</v>
       </c>
       <c r="L30" t="n">
-        <v>64563.68</v>
+        <v>64979.04</v>
       </c>
       <c r="M30" t="n">
-        <v>65282.35</v>
+        <v>66237.69</v>
       </c>
       <c r="N30" t="n">
-        <v>66001.00999999999</v>
+        <v>67496.34</v>
       </c>
       <c r="O30" t="n">
-        <v>65787.99000000001</v>
+        <v>67751.05</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,18 +3035,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3042,236 +3054,230 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64684.42</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>65735.72</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>63720.39</v>
+        <v>65514.18</v>
       </c>
       <c r="E31" t="n">
-        <v>65230.03</v>
+        <v>66100.8</v>
       </c>
       <c r="F31" t="n">
-        <v>539.22</v>
+        <v>-404.33</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0083</v>
+        <v>-0.0061</v>
       </c>
       <c r="H31" t="n">
-        <v>2015.33</v>
+        <v>1180.47</v>
       </c>
       <c r="I31" t="n">
-        <v>63591.94</v>
+        <v>63317.25</v>
       </c>
       <c r="J31" t="n">
-        <v>64087.03</v>
+        <v>64955.35</v>
       </c>
       <c r="K31" t="n">
-        <v>64361.32</v>
+        <v>65606.92</v>
       </c>
       <c r="L31" t="n">
-        <v>64635.6</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>65020.29</v>
+        <v>67403.33</v>
       </c>
       <c r="N31" t="n">
-        <v>65404.98</v>
+        <v>68548.16</v>
       </c>
       <c r="O31" t="n">
-        <v>65568.86</v>
+        <v>68706.47</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65228.87</v>
+        <v>66100.13</v>
       </c>
       <c r="C32" t="n">
-        <v>66910.06</v>
+        <v>66282.38</v>
       </c>
       <c r="D32" t="n">
-        <v>65113.66</v>
+        <v>64610.61</v>
       </c>
       <c r="E32" t="n">
-        <v>66505.12</v>
+        <v>65044.81</v>
       </c>
       <c r="F32" t="n">
-        <v>1275.1</v>
+        <v>-1055.98</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.016</v>
       </c>
       <c r="H32" t="n">
-        <v>1796.41</v>
+        <v>1671.77</v>
       </c>
       <c r="I32" t="n">
-        <v>61705.06</v>
+        <v>64333.7</v>
       </c>
       <c r="J32" t="n">
-        <v>63465.69</v>
+        <v>64918.52</v>
       </c>
       <c r="K32" t="n">
-        <v>64222.36</v>
+        <v>65510.56</v>
       </c>
       <c r="L32" t="n">
-        <v>64979.04</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>66237.69</v>
+        <v>66691.03</v>
       </c>
       <c r="N32" t="n">
-        <v>67496.34</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>67751.05</v>
+        <v>67875.12</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66506.78999999999</v>
+        <v>65044.96</v>
       </c>
       <c r="C33" t="n">
-        <v>66694.64999999999</v>
+        <v>65760.48</v>
       </c>
       <c r="D33" t="n">
-        <v>65514.18</v>
+        <v>63686.04</v>
       </c>
       <c r="E33" t="n">
-        <v>66100.8</v>
+        <v>64098.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-404.33</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0145</v>
       </c>
       <c r="H33" t="n">
-        <v>1180.47</v>
+        <v>2074.45</v>
       </c>
       <c r="I33" t="n">
-        <v>63317.25</v>
+        <v>62938.84</v>
       </c>
       <c r="J33" t="n">
-        <v>64955.35</v>
+        <v>63172.2</v>
       </c>
       <c r="K33" t="n">
-        <v>65606.92</v>
+        <v>64208.93</v>
       </c>
       <c r="L33" t="n">
-        <v>66258.49000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M33" t="n">
-        <v>67403.33</v>
+        <v>65880.7</v>
       </c>
       <c r="N33" t="n">
-        <v>68548.16</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>68706.47</v>
+        <v>67954.16</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3281,12 +3287,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3298,81 +3304,77 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66100.13</v>
+        <v>64098.49</v>
       </c>
       <c r="C34" t="n">
-        <v>66282.38</v>
+        <v>64386.06</v>
       </c>
       <c r="D34" t="n">
-        <v>64610.61</v>
+        <v>63753.03</v>
       </c>
       <c r="E34" t="n">
-        <v>65044.81</v>
+        <v>64311.81</v>
       </c>
       <c r="F34" t="n">
-        <v>-1055.98</v>
+        <v>213.32</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0033</v>
       </c>
       <c r="H34" t="n">
-        <v>1671.77</v>
+        <v>633.04</v>
       </c>
       <c r="I34" t="n">
-        <v>64333.7</v>
+        <v>61611.59</v>
       </c>
       <c r="J34" t="n">
-        <v>64918.52</v>
+        <v>61711.67</v>
       </c>
       <c r="K34" t="n">
-        <v>65510.56</v>
+        <v>63061.27</v>
       </c>
       <c r="L34" t="n">
-        <v>66102.60000000001</v>
+        <v>64410.88</v>
       </c>
       <c r="M34" t="n">
-        <v>66691.03</v>
+        <v>65135.72</v>
       </c>
       <c r="N34" t="n">
-        <v>67279.46000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O34" t="n">
-        <v>67875.12</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3384,64 +3386,64 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65044.96</v>
+        <v>64311.79</v>
       </c>
       <c r="C35" t="n">
-        <v>65760.48</v>
+        <v>65503.77</v>
       </c>
       <c r="D35" t="n">
-        <v>63686.04</v>
+        <v>64233.45</v>
       </c>
       <c r="E35" t="n">
-        <v>64098.5</v>
+        <v>65340.3</v>
       </c>
       <c r="F35" t="n">
-        <v>-946.3200000000001</v>
+        <v>1028.49</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.016</v>
       </c>
       <c r="H35" t="n">
-        <v>2074.45</v>
+        <v>1270.32</v>
       </c>
       <c r="I35" t="n">
-        <v>62938.84</v>
+        <v>63119.99</v>
       </c>
       <c r="J35" t="n">
-        <v>63172.2</v>
+        <v>63799.91</v>
       </c>
       <c r="K35" t="n">
-        <v>64208.93</v>
+        <v>63995.29</v>
       </c>
       <c r="L35" t="n">
-        <v>65245.65</v>
+        <v>64190.68</v>
       </c>
       <c r="M35" t="n">
-        <v>65880.7</v>
+        <v>64628.33</v>
       </c>
       <c r="N35" t="n">
-        <v>66515.74000000001</v>
+        <v>65065.98</v>
       </c>
       <c r="O35" t="n">
-        <v>67954.16</v>
+        <v>65019.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,96 +3451,100 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64098.49</v>
+        <v>65340.59</v>
       </c>
       <c r="C36" t="n">
-        <v>64386.06</v>
+        <v>65658.34</v>
       </c>
       <c r="D36" t="n">
-        <v>63753.03</v>
+        <v>63562.48</v>
       </c>
       <c r="E36" t="n">
-        <v>64311.81</v>
+        <v>63724.9</v>
       </c>
       <c r="F36" t="n">
-        <v>213.32</v>
+        <v>-1615.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0247</v>
       </c>
       <c r="H36" t="n">
-        <v>633.04</v>
+        <v>2095.85</v>
       </c>
       <c r="I36" t="n">
-        <v>61611.59</v>
+        <v>62963.14</v>
       </c>
       <c r="J36" t="n">
-        <v>61711.67</v>
+        <v>64305.83</v>
       </c>
       <c r="K36" t="n">
-        <v>63061.27</v>
+        <v>64705.14</v>
       </c>
       <c r="L36" t="n">
-        <v>64410.88</v>
+        <v>65104.46</v>
       </c>
       <c r="M36" t="n">
-        <v>65135.72</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>65860.56</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>67834.92999999999</v>
+        <v>66774.09</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3552,7 +3558,7 @@
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -3564,50 +3570,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64311.79</v>
+        <v>63723.49</v>
       </c>
       <c r="C37" t="n">
-        <v>65503.77</v>
+        <v>64026.92</v>
       </c>
       <c r="D37" t="n">
-        <v>64233.45</v>
+        <v>62714.8</v>
       </c>
       <c r="E37" t="n">
-        <v>65340.3</v>
+        <v>63871.36</v>
       </c>
       <c r="F37" t="n">
-        <v>1028.49</v>
+        <v>146.46</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0023</v>
       </c>
       <c r="H37" t="n">
-        <v>1270.32</v>
+        <v>1312.12</v>
       </c>
       <c r="I37" t="n">
-        <v>63119.99</v>
+        <v>61466.63</v>
       </c>
       <c r="J37" t="n">
-        <v>63799.91</v>
+        <v>61186.29</v>
       </c>
       <c r="K37" t="n">
-        <v>63995.29</v>
+        <v>62676.97</v>
       </c>
       <c r="L37" t="n">
-        <v>64190.68</v>
+        <v>64167.65</v>
       </c>
       <c r="M37" t="n">
-        <v>64628.33</v>
+        <v>64772.82</v>
       </c>
       <c r="N37" t="n">
-        <v>65065.98</v>
+        <v>65377.99</v>
       </c>
       <c r="O37" t="n">
-        <v>65019.1</v>
+        <v>67754.19</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3618,101 +3624,99 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65340.59</v>
+        <v>63871.39</v>
       </c>
       <c r="C38" t="n">
-        <v>65658.34</v>
+        <v>64638.7</v>
       </c>
       <c r="D38" t="n">
-        <v>63562.48</v>
+        <v>63206.21</v>
       </c>
       <c r="E38" t="n">
-        <v>63724.9</v>
+        <v>63908.17</v>
       </c>
       <c r="F38" t="n">
-        <v>-1615.4</v>
+        <v>36.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>2095.85</v>
+        <v>1432.48</v>
       </c>
       <c r="I38" t="n">
-        <v>62963.14</v>
+        <v>61402.69</v>
       </c>
       <c r="J38" t="n">
-        <v>64305.83</v>
+        <v>62809.5</v>
       </c>
       <c r="K38" t="n">
-        <v>64705.14</v>
+        <v>63215.3</v>
       </c>
       <c r="L38" t="n">
-        <v>65104.46</v>
+        <v>63621.11</v>
       </c>
       <c r="M38" t="n">
-        <v>65975.46000000001</v>
+        <v>64527.42</v>
       </c>
       <c r="N38" t="n">
-        <v>66846.46000000001</v>
+        <v>65433.73</v>
       </c>
       <c r="O38" t="n">
-        <v>66774.09</v>
+        <v>65339.04</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3720,64 +3724,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63723.49</v>
+        <v>63908.62</v>
       </c>
       <c r="C39" t="n">
-        <v>64026.92</v>
+        <v>65071.45</v>
       </c>
       <c r="D39" t="n">
-        <v>62714.8</v>
+        <v>63533.91</v>
       </c>
       <c r="E39" t="n">
-        <v>63871.36</v>
+        <v>64725.31</v>
       </c>
       <c r="F39" t="n">
-        <v>146.46</v>
+        <v>817.14</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0128</v>
       </c>
       <c r="H39" t="n">
-        <v>1312.12</v>
+        <v>1537.54</v>
       </c>
       <c r="I39" t="n">
-        <v>61466.63</v>
+        <v>61773.73</v>
       </c>
       <c r="J39" t="n">
-        <v>61186.29</v>
+        <v>62468.54</v>
       </c>
       <c r="K39" t="n">
-        <v>62676.97</v>
+        <v>63191.93</v>
       </c>
       <c r="L39" t="n">
-        <v>64167.65</v>
+        <v>63915.31</v>
       </c>
       <c r="M39" t="n">
-        <v>64772.82</v>
+        <v>64624.41</v>
       </c>
       <c r="N39" t="n">
-        <v>65377.99</v>
+        <v>65333.51</v>
       </c>
       <c r="O39" t="n">
-        <v>67754.19</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3788,13 +3792,15 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3802,85 +3808,85 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63871.39</v>
+        <v>64723.97</v>
       </c>
       <c r="C40" t="n">
-        <v>64638.7</v>
+        <v>65328.18</v>
       </c>
       <c r="D40" t="n">
-        <v>63206.21</v>
+        <v>62410.87</v>
       </c>
       <c r="E40" t="n">
-        <v>63908.17</v>
+        <v>62813.75</v>
       </c>
       <c r="F40" t="n">
-        <v>36.8</v>
+        <v>-1911.56</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0295</v>
       </c>
       <c r="H40" t="n">
-        <v>1432.48</v>
+        <v>2917.32</v>
       </c>
       <c r="I40" t="n">
-        <v>61402.69</v>
+        <v>61996.37</v>
       </c>
       <c r="J40" t="n">
-        <v>62809.5</v>
+        <v>63399.09</v>
       </c>
       <c r="K40" t="n">
-        <v>63215.3</v>
+        <v>63956.54</v>
       </c>
       <c r="L40" t="n">
-        <v>63621.11</v>
+        <v>64513.99</v>
       </c>
       <c r="M40" t="n">
-        <v>64527.42</v>
+        <v>65494.08</v>
       </c>
       <c r="N40" t="n">
-        <v>65433.73</v>
+        <v>66474.16</v>
       </c>
       <c r="O40" t="n">
-        <v>65339.04</v>
+        <v>66608.98</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3888,64 +3894,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63908.62</v>
+        <v>62813.66</v>
       </c>
       <c r="C41" t="n">
-        <v>65071.45</v>
+        <v>63091.6</v>
       </c>
       <c r="D41" t="n">
-        <v>63533.91</v>
+        <v>62233.01</v>
       </c>
       <c r="E41" t="n">
-        <v>64725.31</v>
+        <v>62763.32</v>
       </c>
       <c r="F41" t="n">
-        <v>817.14</v>
+        <v>-50.43</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0008</v>
       </c>
       <c r="H41" t="n">
-        <v>1537.54</v>
+        <v>858.59</v>
       </c>
       <c r="I41" t="n">
-        <v>61773.73</v>
+        <v>59493.55</v>
       </c>
       <c r="J41" t="n">
-        <v>62468.54</v>
+        <v>59368.54</v>
       </c>
       <c r="K41" t="n">
-        <v>63191.93</v>
+        <v>61355.09</v>
       </c>
       <c r="L41" t="n">
-        <v>63915.31</v>
+        <v>63341.64</v>
       </c>
       <c r="M41" t="n">
-        <v>64624.41</v>
+        <v>64272.4</v>
       </c>
       <c r="N41" t="n">
-        <v>65333.51</v>
+        <v>65203.17</v>
       </c>
       <c r="O41" t="n">
-        <v>66071.17999999999</v>
+        <v>68245.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3956,15 +3962,13 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3972,167 +3976,169 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>64723.97</v>
+        <v>62763.45</v>
       </c>
       <c r="C42" t="n">
-        <v>65328.18</v>
+        <v>63714.61</v>
       </c>
       <c r="D42" t="n">
-        <v>62410.87</v>
+        <v>62745.25</v>
       </c>
       <c r="E42" t="n">
-        <v>62813.75</v>
+        <v>63482</v>
       </c>
       <c r="F42" t="n">
-        <v>-1911.56</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0295</v>
+        <v>0.0115</v>
       </c>
       <c r="H42" t="n">
-        <v>2917.32</v>
+        <v>969.36</v>
       </c>
       <c r="I42" t="n">
-        <v>61996.37</v>
+        <v>61374.43</v>
       </c>
       <c r="J42" t="n">
-        <v>63399.09</v>
+        <v>61955.24</v>
       </c>
       <c r="K42" t="n">
-        <v>63956.54</v>
+        <v>62334.03</v>
       </c>
       <c r="L42" t="n">
-        <v>64513.99</v>
+        <v>62712.81</v>
       </c>
       <c r="M42" t="n">
-        <v>65494.08</v>
+        <v>63192.61</v>
       </c>
       <c r="N42" t="n">
-        <v>66474.16</v>
+        <v>63672.41</v>
       </c>
       <c r="O42" t="n">
-        <v>66608.98</v>
+        <v>63950.18</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>62813.66</v>
+        <v>63485.44</v>
       </c>
       <c r="C43" t="n">
-        <v>63091.6</v>
+        <v>64020.32</v>
       </c>
       <c r="D43" t="n">
-        <v>62233.01</v>
+        <v>62226.58</v>
       </c>
       <c r="E43" t="n">
-        <v>62763.32</v>
+        <v>63460.9</v>
       </c>
       <c r="F43" t="n">
-        <v>-50.43</v>
+        <v>-21.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0003</v>
       </c>
       <c r="H43" t="n">
-        <v>858.59</v>
+        <v>1793.75</v>
       </c>
       <c r="I43" t="n">
-        <v>59493.55</v>
+        <v>61775.89</v>
       </c>
       <c r="J43" t="n">
-        <v>59368.54</v>
+        <v>62638.67</v>
       </c>
       <c r="K43" t="n">
-        <v>61355.09</v>
+        <v>62997.32</v>
       </c>
       <c r="L43" t="n">
-        <v>63341.64</v>
+        <v>63355.97</v>
       </c>
       <c r="M43" t="n">
-        <v>64272.4</v>
+        <v>63966.68</v>
       </c>
       <c r="N43" t="n">
-        <v>65203.17</v>
+        <v>64577.39</v>
       </c>
       <c r="O43" t="n">
-        <v>68245.5</v>
+        <v>64683.97</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4140,60 +4146,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>62763.45</v>
+        <v>63458.41</v>
       </c>
       <c r="C44" t="n">
-        <v>63714.61</v>
+        <v>64466.94</v>
       </c>
       <c r="D44" t="n">
-        <v>62745.25</v>
+        <v>63277.68</v>
       </c>
       <c r="E44" t="n">
-        <v>63482</v>
+        <v>64055.95</v>
       </c>
       <c r="F44" t="n">
-        <v>718.6799999999999</v>
+        <v>595.05</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0094</v>
       </c>
       <c r="H44" t="n">
-        <v>969.36</v>
+        <v>1189.25</v>
       </c>
       <c r="I44" t="n">
-        <v>61374.43</v>
+        <v>60432.83</v>
       </c>
       <c r="J44" t="n">
-        <v>61955.24</v>
+        <v>61835.88</v>
       </c>
       <c r="K44" t="n">
-        <v>62334.03</v>
+        <v>62564.03</v>
       </c>
       <c r="L44" t="n">
-        <v>62712.81</v>
+        <v>63292.17</v>
       </c>
       <c r="M44" t="n">
-        <v>63192.61</v>
+        <v>64357.77</v>
       </c>
       <c r="N44" t="n">
-        <v>63672.41</v>
+        <v>65423.37</v>
       </c>
       <c r="O44" t="n">
-        <v>63950.18</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,18 +4221,16 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4236,72 +4244,68 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63485.44</v>
+        <v>64054.88</v>
       </c>
       <c r="C45" t="n">
-        <v>64020.32</v>
+        <v>64954.35</v>
       </c>
       <c r="D45" t="n">
-        <v>62226.58</v>
+        <v>63829.72</v>
       </c>
       <c r="E45" t="n">
-        <v>63460.9</v>
+        <v>64597.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-21.1</v>
+        <v>541.55</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>1793.75</v>
+        <v>1124.63</v>
       </c>
       <c r="I45" t="n">
-        <v>61775.89</v>
+        <v>62088.43</v>
       </c>
       <c r="J45" t="n">
-        <v>62638.67</v>
+        <v>62958.52</v>
       </c>
       <c r="K45" t="n">
-        <v>62997.32</v>
+        <v>63461.33</v>
       </c>
       <c r="L45" t="n">
-        <v>63355.97</v>
+        <v>63964.13</v>
       </c>
       <c r="M45" t="n">
-        <v>63966.68</v>
+        <v>64650.58</v>
       </c>
       <c r="N45" t="n">
-        <v>64577.39</v>
+        <v>65337.03</v>
       </c>
       <c r="O45" t="n">
-        <v>64683.97</v>
+        <v>65656.19</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4310,64 +4314,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63458.41</v>
+        <v>64595.45</v>
       </c>
       <c r="C46" t="n">
-        <v>64466.94</v>
+        <v>64934.49</v>
       </c>
       <c r="D46" t="n">
-        <v>63277.68</v>
+        <v>64098.48</v>
       </c>
       <c r="E46" t="n">
-        <v>64055.95</v>
+        <v>64262.11</v>
       </c>
       <c r="F46" t="n">
-        <v>595.05</v>
+        <v>-335.39</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0052</v>
       </c>
       <c r="H46" t="n">
-        <v>1189.25</v>
+        <v>836.02</v>
       </c>
       <c r="I46" t="n">
-        <v>60432.83</v>
+        <v>62705.09</v>
       </c>
       <c r="J46" t="n">
-        <v>61835.88</v>
+        <v>63575.6</v>
       </c>
       <c r="K46" t="n">
-        <v>62564.03</v>
+        <v>64035.19</v>
       </c>
       <c r="L46" t="n">
-        <v>63292.17</v>
+        <v>64494.77</v>
       </c>
       <c r="M46" t="n">
-        <v>64357.77</v>
+        <v>65159.81</v>
       </c>
       <c r="N46" t="n">
-        <v>65423.37</v>
+        <v>65824.86</v>
       </c>
       <c r="O46" t="n">
-        <v>65814.07000000001</v>
+        <v>66078.98</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,83 +4379,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64054.88</v>
+        <v>64257.49</v>
       </c>
       <c r="C47" t="n">
-        <v>64954.35</v>
+        <v>65330.61</v>
       </c>
       <c r="D47" t="n">
-        <v>63829.72</v>
+        <v>64113.27</v>
       </c>
       <c r="E47" t="n">
-        <v>64597.5</v>
+        <v>64880.19</v>
       </c>
       <c r="F47" t="n">
-        <v>541.55</v>
+        <v>618.08</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>1124.63</v>
+        <v>1217.34</v>
       </c>
       <c r="I47" t="n">
-        <v>62088.43</v>
+        <v>63262.46</v>
       </c>
       <c r="J47" t="n">
-        <v>62958.52</v>
+        <v>63298.91</v>
       </c>
       <c r="K47" t="n">
-        <v>63461.33</v>
+        <v>63844.11</v>
       </c>
       <c r="L47" t="n">
-        <v>63964.13</v>
+        <v>64389.3</v>
       </c>
       <c r="M47" t="n">
-        <v>64650.58</v>
+        <v>64680.12</v>
       </c>
       <c r="N47" t="n">
-        <v>65337.03</v>
+        <v>64970.94</v>
       </c>
       <c r="O47" t="n">
-        <v>65656.19</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4469,16 +4473,18 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4492,50 +4498,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64595.45</v>
+        <v>64882.55</v>
       </c>
       <c r="C48" t="n">
-        <v>64934.49</v>
+        <v>65140.48</v>
       </c>
       <c r="D48" t="n">
-        <v>64098.48</v>
+        <v>64797.11</v>
       </c>
       <c r="E48" t="n">
-        <v>64262.11</v>
+        <v>64904.69</v>
       </c>
       <c r="F48" t="n">
-        <v>-335.39</v>
+        <v>24.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0004</v>
       </c>
       <c r="H48" t="n">
-        <v>836.02</v>
+        <v>343.37</v>
       </c>
       <c r="I48" t="n">
-        <v>62705.09</v>
+        <v>62895.94</v>
       </c>
       <c r="J48" t="n">
-        <v>63575.6</v>
+        <v>63741.98</v>
       </c>
       <c r="K48" t="n">
-        <v>64035.19</v>
+        <v>64271.52</v>
       </c>
       <c r="L48" t="n">
-        <v>64494.77</v>
+        <v>64801.07</v>
       </c>
       <c r="M48" t="n">
-        <v>65159.81</v>
+        <v>65488.86</v>
       </c>
       <c r="N48" t="n">
-        <v>65824.86</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>66078.98</v>
+        <v>66547.95</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4543,14 +4549,12 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4562,64 +4566,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64257.49</v>
+        <v>64906.55</v>
       </c>
       <c r="C49" t="n">
-        <v>65330.61</v>
+        <v>65401.69</v>
       </c>
       <c r="D49" t="n">
-        <v>64113.27</v>
+        <v>64677.6</v>
       </c>
       <c r="E49" t="n">
-        <v>64880.19</v>
+        <v>64844.89</v>
       </c>
       <c r="F49" t="n">
-        <v>618.08</v>
+        <v>-59.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0009</v>
       </c>
       <c r="H49" t="n">
-        <v>1217.34</v>
+        <v>724.09</v>
       </c>
       <c r="I49" t="n">
-        <v>63262.46</v>
+        <v>64453.75</v>
       </c>
       <c r="J49" t="n">
-        <v>63298.91</v>
+        <v>64529.27</v>
       </c>
       <c r="K49" t="n">
-        <v>63844.11</v>
+        <v>64733</v>
       </c>
       <c r="L49" t="n">
-        <v>64389.3</v>
+        <v>64936.74</v>
       </c>
       <c r="M49" t="n">
-        <v>64680.12</v>
+        <v>65076.37</v>
       </c>
       <c r="N49" t="n">
-        <v>64970.94</v>
+        <v>65216</v>
       </c>
       <c r="O49" t="n">
-        <v>65770.50999999999</v>
+        <v>65483.85</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4627,12 +4631,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4642,87 +4648,95 @@
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64882.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C50" t="n">
-        <v>65140.48</v>
+        <v>65321.84</v>
       </c>
       <c r="D50" t="n">
-        <v>64797.11</v>
+        <v>63752.57</v>
       </c>
       <c r="E50" t="n">
-        <v>64904.69</v>
+        <v>63910.59</v>
       </c>
       <c r="F50" t="n">
-        <v>24.5</v>
+        <v>-934.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0144</v>
       </c>
       <c r="H50" t="n">
-        <v>343.37</v>
+        <v>1569.27</v>
       </c>
       <c r="I50" t="n">
-        <v>62895.94</v>
+        <v>63953.51</v>
       </c>
       <c r="J50" t="n">
-        <v>63741.98</v>
+        <v>64023.42</v>
       </c>
       <c r="K50" t="n">
-        <v>64271.52</v>
+        <v>64482.84</v>
       </c>
       <c r="L50" t="n">
-        <v>64801.07</v>
+        <v>64942.27</v>
       </c>
       <c r="M50" t="n">
-        <v>65488.86</v>
+        <v>65206.93</v>
       </c>
       <c r="N50" t="n">
-        <v>66176.64999999999</v>
+        <v>65471.6</v>
       </c>
       <c r="O50" t="n">
-        <v>66547.95</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4730,64 +4744,60 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64906.55</v>
+        <v>63910.18</v>
       </c>
       <c r="C51" t="n">
-        <v>65401.69</v>
+        <v>64433.68</v>
       </c>
       <c r="D51" t="n">
-        <v>64677.6</v>
+        <v>63185.47</v>
       </c>
       <c r="E51" t="n">
-        <v>64844.89</v>
+        <v>63551.88</v>
       </c>
       <c r="F51" t="n">
-        <v>-59.8</v>
+        <v>-358.71</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0056</v>
       </c>
       <c r="H51" t="n">
-        <v>724.09</v>
+        <v>1248.21</v>
       </c>
       <c r="I51" t="n">
-        <v>64453.75</v>
+        <v>62183.29</v>
       </c>
       <c r="J51" t="n">
-        <v>64529.27</v>
+        <v>62028</v>
       </c>
       <c r="K51" t="n">
-        <v>64733</v>
+        <v>63125.95</v>
       </c>
       <c r="L51" t="n">
-        <v>64936.74</v>
+        <v>64223.89</v>
       </c>
       <c r="M51" t="n">
-        <v>65076.37</v>
+        <v>64695.22</v>
       </c>
       <c r="N51" t="n">
-        <v>65216</v>
+        <v>65166.55</v>
       </c>
       <c r="O51" t="n">
-        <v>65483.85</v>
+        <v>66891.11</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4797,171 +4807,161 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64845.38</v>
+        <v>63551.87</v>
       </c>
       <c r="C52" t="n">
-        <v>65321.84</v>
+        <v>64381.08</v>
       </c>
       <c r="D52" t="n">
-        <v>63752.57</v>
+        <v>63251.11</v>
       </c>
       <c r="E52" t="n">
-        <v>63910.59</v>
+        <v>63402.43</v>
       </c>
       <c r="F52" t="n">
-        <v>-934.3</v>
+        <v>-149.44</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0024</v>
       </c>
       <c r="H52" t="n">
-        <v>1569.27</v>
+        <v>1129.96</v>
       </c>
       <c r="I52" t="n">
-        <v>63953.51</v>
+        <v>61937.27</v>
       </c>
       <c r="J52" t="n">
-        <v>64023.42</v>
+        <v>62174.82</v>
       </c>
       <c r="K52" t="n">
-        <v>64482.84</v>
+        <v>62927.77</v>
       </c>
       <c r="L52" t="n">
-        <v>64942.27</v>
+        <v>63680.73</v>
       </c>
       <c r="M52" t="n">
-        <v>65206.93</v>
+        <v>64175.98</v>
       </c>
       <c r="N52" t="n">
-        <v>65471.6</v>
+        <v>64671.23</v>
       </c>
       <c r="O52" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+        <v>65681.89</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63910.18</v>
+        <v>63404.43</v>
       </c>
       <c r="C53" t="n">
-        <v>64433.68</v>
+        <v>63926.33</v>
       </c>
       <c r="D53" t="n">
-        <v>63185.47</v>
+        <v>62799.29</v>
       </c>
       <c r="E53" t="n">
-        <v>63551.88</v>
+        <v>63402.17</v>
       </c>
       <c r="F53" t="n">
-        <v>-358.71</v>
+        <v>-0.26</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0</v>
       </c>
       <c r="H53" t="n">
-        <v>1248.21</v>
+        <v>1127.04</v>
       </c>
       <c r="I53" t="n">
-        <v>62183.29</v>
+        <v>62121.15</v>
       </c>
       <c r="J53" t="n">
-        <v>62028</v>
+        <v>62065.64</v>
       </c>
       <c r="K53" t="n">
-        <v>63125.95</v>
+        <v>62837.45</v>
       </c>
       <c r="L53" t="n">
-        <v>64223.89</v>
+        <v>63609.26</v>
       </c>
       <c r="M53" t="n">
-        <v>64695.22</v>
+        <v>63967.42</v>
       </c>
       <c r="N53" t="n">
-        <v>65166.55</v>
+        <v>64325.57</v>
       </c>
       <c r="O53" t="n">
-        <v>66891.11</v>
+        <v>65511.04</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4971,12 +4971,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4988,7 +4988,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4998,50 +4998,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63551.87</v>
+        <v>63402.09</v>
       </c>
       <c r="C54" t="n">
-        <v>64381.08</v>
+        <v>63551.56</v>
       </c>
       <c r="D54" t="n">
-        <v>63251.11</v>
+        <v>62487.7</v>
       </c>
       <c r="E54" t="n">
-        <v>63402.43</v>
+        <v>62975.59</v>
       </c>
       <c r="F54" t="n">
-        <v>-149.44</v>
+        <v>-426.58</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0067</v>
       </c>
       <c r="H54" t="n">
-        <v>1129.96</v>
+        <v>1063.86</v>
       </c>
       <c r="I54" t="n">
-        <v>61937.27</v>
+        <v>61672.25</v>
       </c>
       <c r="J54" t="n">
-        <v>62174.82</v>
+        <v>62294.81</v>
       </c>
       <c r="K54" t="n">
-        <v>62927.77</v>
+        <v>62838.65</v>
       </c>
       <c r="L54" t="n">
-        <v>63680.73</v>
+        <v>63382.49</v>
       </c>
       <c r="M54" t="n">
-        <v>64175.98</v>
+        <v>63965.69</v>
       </c>
       <c r="N54" t="n">
-        <v>64671.23</v>
+        <v>64548.9</v>
       </c>
       <c r="O54" t="n">
-        <v>65681.89</v>
+        <v>65053.38</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5049,18 +5049,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5068,64 +5068,60 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63404.43</v>
+        <v>62974.34</v>
       </c>
       <c r="C55" t="n">
-        <v>63926.33</v>
+        <v>63119.13</v>
       </c>
       <c r="D55" t="n">
-        <v>62799.29</v>
+        <v>62850.96</v>
       </c>
       <c r="E55" t="n">
-        <v>63402.17</v>
+        <v>63024.32</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.26</v>
+        <v>48.73</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0</v>
+        <v>0.0008</v>
       </c>
       <c r="H55" t="n">
-        <v>1127.04</v>
+        <v>268.17</v>
       </c>
       <c r="I55" t="n">
-        <v>62121.15</v>
+        <v>61423.84</v>
       </c>
       <c r="J55" t="n">
-        <v>62065.64</v>
+        <v>61889.71</v>
       </c>
       <c r="K55" t="n">
-        <v>62837.45</v>
+        <v>62443.66</v>
       </c>
       <c r="L55" t="n">
-        <v>63609.26</v>
+        <v>62997.61</v>
       </c>
       <c r="M55" t="n">
-        <v>63967.42</v>
+        <v>63507.53</v>
       </c>
       <c r="N55" t="n">
-        <v>64325.57</v>
+        <v>64017.44</v>
       </c>
       <c r="O55" t="n">
-        <v>65511.04</v>
+        <v>64615.43</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5133,14 +5129,12 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5152,70 +5146,76 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63402.09</v>
+        <v>63023.42</v>
       </c>
       <c r="C56" t="n">
-        <v>63551.56</v>
+        <v>63310.78</v>
       </c>
       <c r="D56" t="n">
-        <v>62487.7</v>
+        <v>62648.57</v>
       </c>
       <c r="E56" t="n">
-        <v>62975.59</v>
+        <v>62818.65</v>
       </c>
       <c r="F56" t="n">
-        <v>-426.58</v>
+        <v>-205.67</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0033</v>
       </c>
       <c r="H56" t="n">
-        <v>1063.86</v>
+        <v>662.2</v>
       </c>
       <c r="I56" t="n">
-        <v>61672.25</v>
+        <v>62582.79</v>
       </c>
       <c r="J56" t="n">
-        <v>62294.81</v>
+        <v>62775.79</v>
       </c>
       <c r="K56" t="n">
-        <v>62838.65</v>
+        <v>62890.23</v>
       </c>
       <c r="L56" t="n">
-        <v>63382.49</v>
+        <v>63004.68</v>
       </c>
       <c r="M56" t="n">
-        <v>63965.69</v>
+        <v>63158.41</v>
       </c>
       <c r="N56" t="n">
-        <v>64548.9</v>
+        <v>63312.13</v>
       </c>
       <c r="O56" t="n">
-        <v>65053.38</v>
+        <v>63387.3</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
@@ -5223,8 +5223,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5232,60 +5234,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>62974.34</v>
+        <v>62819.38</v>
       </c>
       <c r="C57" t="n">
-        <v>63119.13</v>
+        <v>64547.85</v>
       </c>
       <c r="D57" t="n">
-        <v>62850.96</v>
+        <v>62687.1</v>
       </c>
       <c r="E57" t="n">
-        <v>63024.32</v>
+        <v>64506.25</v>
       </c>
       <c r="F57" t="n">
-        <v>48.73</v>
+        <v>1687.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0269</v>
       </c>
       <c r="H57" t="n">
-        <v>268.17</v>
+        <v>1860.75</v>
       </c>
       <c r="I57" t="n">
-        <v>61423.84</v>
+        <v>61986.37</v>
       </c>
       <c r="J57" t="n">
-        <v>61889.71</v>
+        <v>62075.94</v>
       </c>
       <c r="K57" t="n">
-        <v>62443.66</v>
+        <v>62487.55</v>
       </c>
       <c r="L57" t="n">
-        <v>62997.61</v>
+        <v>62899.16</v>
       </c>
       <c r="M57" t="n">
-        <v>63507.53</v>
+        <v>63149.75</v>
       </c>
       <c r="N57" t="n">
-        <v>64017.44</v>
+        <v>63400.34</v>
       </c>
       <c r="O57" t="n">
-        <v>64615.43</v>
+        <v>63972.98</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5298,99 +5304,95 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63023.42</v>
+        <v>64506.52</v>
       </c>
       <c r="C58" t="n">
-        <v>63310.78</v>
+        <v>64987.71</v>
       </c>
       <c r="D58" t="n">
-        <v>62648.57</v>
+        <v>63980.32</v>
       </c>
       <c r="E58" t="n">
-        <v>62818.65</v>
+        <v>64680.71</v>
       </c>
       <c r="F58" t="n">
-        <v>-205.67</v>
+        <v>174.46</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0027</v>
       </c>
       <c r="H58" t="n">
-        <v>662.2</v>
+        <v>1007.39</v>
       </c>
       <c r="I58" t="n">
-        <v>62582.79</v>
+        <v>60826.36</v>
       </c>
       <c r="J58" t="n">
-        <v>62775.79</v>
+        <v>63089.9</v>
       </c>
       <c r="K58" t="n">
-        <v>62890.23</v>
+        <v>63575.88</v>
       </c>
       <c r="L58" t="n">
-        <v>63004.68</v>
+        <v>64061.86</v>
       </c>
       <c r="M58" t="n">
-        <v>63158.41</v>
+        <v>65436.63</v>
       </c>
       <c r="N58" t="n">
-        <v>63312.13</v>
+        <v>66811.39</v>
       </c>
       <c r="O58" t="n">
-        <v>63387.3</v>
+        <v>66408.59</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5400,62 +5402,58 @@
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>62819.38</v>
+        <v>64680.05</v>
       </c>
       <c r="C59" t="n">
-        <v>64547.85</v>
+        <v>69996.95</v>
       </c>
       <c r="D59" t="n">
-        <v>62687.1</v>
+        <v>64111.07</v>
       </c>
       <c r="E59" t="n">
-        <v>64506.25</v>
+        <v>69266.19</v>
       </c>
       <c r="F59" t="n">
-        <v>1687.6</v>
+        <v>4585.48</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0709</v>
       </c>
       <c r="H59" t="n">
-        <v>1860.75</v>
+        <v>5885.88</v>
       </c>
       <c r="I59" t="n">
-        <v>61986.37</v>
+        <v>62972.94</v>
       </c>
       <c r="J59" t="n">
-        <v>62075.94</v>
+        <v>63771.67</v>
       </c>
       <c r="K59" t="n">
-        <v>62487.55</v>
+        <v>64177.02</v>
       </c>
       <c r="L59" t="n">
-        <v>62899.16</v>
+        <v>64582.36</v>
       </c>
       <c r="M59" t="n">
-        <v>63149.75</v>
+        <v>65184.4</v>
       </c>
       <c r="N59" t="n">
-        <v>63400.34</v>
+        <v>65786.44</v>
       </c>
       <c r="O59" t="n">
-        <v>63972.98</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5463,8 +5461,10 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5496,50 +5496,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64506.52</v>
+        <v>69268.25</v>
       </c>
       <c r="C60" t="n">
-        <v>64987.71</v>
+        <v>73369.8</v>
       </c>
       <c r="D60" t="n">
-        <v>63980.32</v>
+        <v>68867.53</v>
       </c>
       <c r="E60" t="n">
-        <v>64680.71</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>174.46</v>
+        <v>3766.57</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0544</v>
       </c>
       <c r="H60" t="n">
-        <v>1007.39</v>
+        <v>4502.27</v>
       </c>
       <c r="I60" t="n">
-        <v>60826.36</v>
+        <v>58225.19</v>
       </c>
       <c r="J60" t="n">
-        <v>63089.9</v>
+        <v>64486.39</v>
       </c>
       <c r="K60" t="n">
-        <v>63575.88</v>
+        <v>66323.25</v>
       </c>
       <c r="L60" t="n">
-        <v>64061.86</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>65436.63</v>
+        <v>72209.13</v>
       </c>
       <c r="N60" t="n">
-        <v>66811.39</v>
+        <v>76258.16</v>
       </c>
       <c r="O60" t="n">
-        <v>66408.59</v>
+        <v>75882.84</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5552,11 +5552,13 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5564,7 +5566,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5574,50 +5576,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64680.05</v>
+        <v>73031.09</v>
       </c>
       <c r="C61" t="n">
-        <v>69996.95</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>64111.07</v>
+        <v>73011.41</v>
       </c>
       <c r="E61" t="n">
-        <v>69266.19</v>
+        <v>78335.19</v>
       </c>
       <c r="F61" t="n">
-        <v>4585.48</v>
+        <v>5302.43</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0726</v>
       </c>
       <c r="H61" t="n">
-        <v>5885.88</v>
+        <v>6452.3</v>
       </c>
       <c r="I61" t="n">
-        <v>62972.94</v>
+        <v>64365.26</v>
       </c>
       <c r="J61" t="n">
-        <v>63771.67</v>
+        <v>69487.53</v>
       </c>
       <c r="K61" t="n">
-        <v>64177.02</v>
+        <v>70781.62</v>
       </c>
       <c r="L61" t="n">
-        <v>64582.36</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>65184.4</v>
+        <v>75283.89</v>
       </c>
       <c r="N61" t="n">
-        <v>65786.44</v>
+        <v>78492.08</v>
       </c>
       <c r="O61" t="n">
-        <v>65995.10000000001</v>
+        <v>77872.08</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5625,32 +5627,30 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5660,50 +5660,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>69268.25</v>
+        <v>78332.55</v>
       </c>
       <c r="C62" t="n">
-        <v>73369.8</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>68867.53</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>73032.75999999999</v>
+        <v>77083.41</v>
       </c>
       <c r="F62" t="n">
-        <v>3766.57</v>
+        <v>-1251.77</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0544</v>
+        <v>-0.016</v>
       </c>
       <c r="H62" t="n">
-        <v>4502.27</v>
+        <v>2274.44</v>
       </c>
       <c r="I62" t="n">
-        <v>58225.19</v>
+        <v>66559.12</v>
       </c>
       <c r="J62" t="n">
-        <v>64486.39</v>
+        <v>72931.7</v>
       </c>
       <c r="K62" t="n">
-        <v>66323.25</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>68160.10000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M62" t="n">
-        <v>72209.13</v>
+        <v>81561.34</v>
       </c>
       <c r="N62" t="n">
-        <v>76258.16</v>
+        <v>85836.3</v>
       </c>
       <c r="O62" t="n">
-        <v>75882.84</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5714,15 +5714,13 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5730,60 +5728,64 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>73031.09</v>
+        <v>77082.84</v>
       </c>
       <c r="C63" t="n">
-        <v>79463.71000000001</v>
+        <v>78036.87</v>
       </c>
       <c r="D63" t="n">
-        <v>73011.41</v>
+        <v>75624.95</v>
       </c>
       <c r="E63" t="n">
-        <v>78335.19</v>
+        <v>77755.27</v>
       </c>
       <c r="F63" t="n">
-        <v>5302.43</v>
+        <v>671.85</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>6452.3</v>
+        <v>2411.92</v>
       </c>
       <c r="I63" t="n">
-        <v>64365.26</v>
+        <v>74252.27</v>
       </c>
       <c r="J63" t="n">
-        <v>69487.53</v>
+        <v>74518.72</v>
       </c>
       <c r="K63" t="n">
-        <v>70781.62</v>
+        <v>75946.2</v>
       </c>
       <c r="L63" t="n">
-        <v>72075.71000000001</v>
+        <v>77373.67</v>
       </c>
       <c r="M63" t="n">
-        <v>75283.89</v>
+        <v>78220.63</v>
       </c>
       <c r="N63" t="n">
-        <v>78492.08</v>
+        <v>79067.59</v>
       </c>
       <c r="O63" t="n">
-        <v>77872.08</v>
+        <v>81075.59</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5791,83 +5793,83 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>78332.55</v>
+        <v>77748.88</v>
       </c>
       <c r="C64" t="n">
-        <v>78801.14999999999</v>
+        <v>79970.11</v>
       </c>
       <c r="D64" t="n">
-        <v>76526.71000000001</v>
+        <v>76688.83</v>
       </c>
       <c r="E64" t="n">
-        <v>77083.41</v>
+        <v>78964.48</v>
       </c>
       <c r="F64" t="n">
-        <v>-1251.77</v>
+        <v>1209.22</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0156</v>
       </c>
       <c r="H64" t="n">
-        <v>2274.44</v>
+        <v>3281.28</v>
       </c>
       <c r="I64" t="n">
-        <v>66559.12</v>
+        <v>73213.02</v>
       </c>
       <c r="J64" t="n">
-        <v>72931.7</v>
+        <v>75805.52</v>
       </c>
       <c r="K64" t="n">
-        <v>75109.03999999999</v>
+        <v>76549.3</v>
       </c>
       <c r="L64" t="n">
-        <v>77286.38</v>
+        <v>77293.09</v>
       </c>
       <c r="M64" t="n">
-        <v>81561.34</v>
+        <v>78961.23</v>
       </c>
       <c r="N64" t="n">
-        <v>85836.3</v>
+        <v>80629.37</v>
       </c>
       <c r="O64" t="n">
-        <v>85916.00999999999</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5878,13 +5880,15 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5892,64 +5896,60 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="11" t="inlineStr">
+      <c r="W64" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>77082.84</v>
+        <v>78960.09</v>
       </c>
       <c r="C65" t="n">
-        <v>78036.87</v>
+        <v>81235.03</v>
       </c>
       <c r="D65" t="n">
-        <v>75624.95</v>
+        <v>77870.62</v>
       </c>
       <c r="E65" t="n">
-        <v>77755.27</v>
+        <v>78564.98</v>
       </c>
       <c r="F65" t="n">
-        <v>671.85</v>
+        <v>-399.51</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0051</v>
       </c>
       <c r="H65" t="n">
-        <v>2411.92</v>
+        <v>3364.41</v>
       </c>
       <c r="I65" t="n">
-        <v>74252.27</v>
+        <v>73407.55</v>
       </c>
       <c r="J65" t="n">
-        <v>74518.72</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>75946.2</v>
+        <v>77323.84</v>
       </c>
       <c r="L65" t="n">
-        <v>77373.67</v>
+        <v>78646.98</v>
       </c>
       <c r="M65" t="n">
-        <v>78220.63</v>
+        <v>80605.12</v>
       </c>
       <c r="N65" t="n">
-        <v>79067.59</v>
+        <v>82563.27</v>
       </c>
       <c r="O65" t="n">
-        <v>81075.59</v>
+        <v>83251.39</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5957,83 +5957,83 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
       <c r="U65" s="8" t="n">
         <v/>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
       </c>
-      <c r="W65" s="11" t="inlineStr">
+      <c r="W65" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>77748.88</v>
+        <v>78538.59</v>
       </c>
       <c r="C66" t="n">
-        <v>79970.11</v>
+        <v>79240.5</v>
       </c>
       <c r="D66" t="n">
-        <v>76688.83</v>
+        <v>77639.84</v>
       </c>
       <c r="E66" t="n">
-        <v>78964.48</v>
+        <v>79027.42</v>
       </c>
       <c r="F66" t="n">
-        <v>1209.22</v>
+        <v>462.45</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.0059</v>
       </c>
       <c r="H66" t="n">
-        <v>3281.28</v>
+        <v>1600.66</v>
       </c>
       <c r="I66" t="n">
-        <v>73213.02</v>
+        <v>74506.22</v>
       </c>
       <c r="J66" t="n">
-        <v>75805.52</v>
+        <v>74706.64</v>
       </c>
       <c r="K66" t="n">
-        <v>76549.3</v>
+        <v>76882.77</v>
       </c>
       <c r="L66" t="n">
-        <v>77293.09</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>78961.23</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>80629.37</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O66" t="n">
-        <v>80448.78999999999</v>
+        <v>84599.44</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6044,15 +6044,13 @@
       <c r="R66" s="6" t="n">
         <v/>
       </c>
-      <c r="S66" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v/>
       </c>
       <c r="U66" s="8" t="n">
         <v/>
@@ -6060,60 +6058,64 @@
       <c r="V66" s="8" t="n">
         <v/>
       </c>
-      <c r="W66" s="11" t="inlineStr">
+      <c r="W66" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>78960.09</v>
+        <v>79037.92</v>
       </c>
       <c r="C67" t="n">
-        <v>81235.03</v>
+        <v>80806.56</v>
       </c>
       <c r="D67" t="n">
-        <v>77870.62</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>78564.98</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>-399.51</v>
+        <v>1230.12</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0156</v>
       </c>
       <c r="H67" t="n">
-        <v>3364.41</v>
+        <v>2215.46</v>
       </c>
       <c r="I67" t="n">
-        <v>73407.55</v>
+        <v>76039.17</v>
       </c>
       <c r="J67" t="n">
-        <v>76000.71000000001</v>
+        <v>77720.38</v>
       </c>
       <c r="K67" t="n">
-        <v>77323.84</v>
+        <v>78227.09</v>
       </c>
       <c r="L67" t="n">
-        <v>78646.98</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>80605.12</v>
+        <v>79827.75</v>
       </c>
       <c r="N67" t="n">
-        <v>82563.27</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O67" t="n">
-        <v>83251.39</v>
+        <v>80841.16</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6124,14 +6126,14 @@
       <c r="R67" s="6" t="n">
         <v/>
       </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T67" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U67" s="8" t="n">
@@ -6140,77 +6142,77 @@
       <c r="V67" s="8" t="n">
         <v/>
       </c>
-      <c r="W67" s="11" t="inlineStr">
+      <c r="W67" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>78538.59</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>79240.5</v>
+        <v>81346.95</v>
       </c>
       <c r="D68" t="n">
-        <v>77639.84</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>79027.42</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>462.45</v>
+        <v>-2427.25</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0302</v>
       </c>
       <c r="H68" t="n">
-        <v>1600.66</v>
+        <v>4437.6</v>
       </c>
       <c r="I68" t="n">
-        <v>74506.22</v>
+        <v>76375.64</v>
       </c>
       <c r="J68" t="n">
-        <v>74706.64</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>76882.77</v>
+        <v>79149.81</v>
       </c>
       <c r="L68" t="n">
-        <v>79058.89999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M68" t="n">
-        <v>80247.17999999999</v>
+        <v>81365.27</v>
       </c>
       <c r="N68" t="n">
-        <v>81435.46000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O68" t="n">
-        <v>84599.44</v>
+        <v>83022.02</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R68" s="6" t="n">
-        <v/>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T68" s="8" t="n">
@@ -6224,62 +6226,62 @@
       </c>
       <c r="W68" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>79037.92</v>
+        <v>77830.89</v>
       </c>
       <c r="C69" t="n">
-        <v>80806.56</v>
+        <v>78327.95</v>
       </c>
       <c r="D69" t="n">
-        <v>78591.10000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>80257.53999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F69" t="n">
-        <v>1230.12</v>
+        <v>415.52</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.0053</v>
       </c>
       <c r="H69" t="n">
-        <v>2215.46</v>
+        <v>946.05</v>
       </c>
       <c r="I69" t="n">
-        <v>76039.17</v>
+        <v>72471.75</v>
       </c>
       <c r="J69" t="n">
-        <v>77720.38</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>78227.09</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>78733.78999999999</v>
+        <v>78479.22</v>
       </c>
       <c r="M69" t="n">
-        <v>79827.75</v>
+        <v>80049.09</v>
       </c>
       <c r="N69" t="n">
-        <v>80921.71000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O69" t="n">
-        <v>80841.16</v>
+        <v>85784.55</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6290,15 +6292,13 @@
       <c r="R69" s="6" t="n">
         <v/>
       </c>
-      <c r="S69" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v/>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6308,87 +6308,95 @@
       </c>
       <c r="W69" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>80264.64999999999</v>
+        <v>78246.17</v>
       </c>
       <c r="C70" t="n">
-        <v>81346.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>76909.35000000001</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>77830.28999999999</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-2427.25</v>
+        <v>-578.24</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0302</v>
+        <v>-0.0074</v>
       </c>
       <c r="H70" t="n">
-        <v>4437.6</v>
+        <v>2317.03</v>
       </c>
       <c r="I70" t="n">
-        <v>76375.64</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>78321.42999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>79149.81</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>79978.19</v>
+        <v>78050.37</v>
       </c>
       <c r="M70" t="n">
-        <v>81365.27</v>
+        <v>78718.84</v>
       </c>
       <c r="N70" t="n">
-        <v>82752.35000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O70" t="n">
-        <v>83022.02</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R70" s="6" t="inlineStr">
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="n">
-        <v/>
-      </c>
       <c r="U70" s="8" t="n">
         <v/>
       </c>
-      <c r="V70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W70" s="9" t="inlineStr">
+      <c r="V70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W70" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -6402,50 +6410,50 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>77830.89</v>
+        <v>77673.7</v>
       </c>
       <c r="C71" t="n">
-        <v>78327.95</v>
+        <v>79247.34</v>
       </c>
       <c r="D71" t="n">
-        <v>77381.89999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E71" t="n">
-        <v>78245.81</v>
+        <v>78548.63</v>
       </c>
       <c r="F71" t="n">
-        <v>415.52</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0113</v>
       </c>
       <c r="H71" t="n">
-        <v>946.05</v>
+        <v>1868.91</v>
       </c>
       <c r="I71" t="n">
-        <v>72471.75</v>
+        <v>74739.12</v>
       </c>
       <c r="J71" t="n">
-        <v>72743.75999999999</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>75611.49000000001</v>
+        <v>76509.05</v>
       </c>
       <c r="L71" t="n">
-        <v>78479.22</v>
+        <v>77941.12</v>
       </c>
       <c r="M71" t="n">
-        <v>80049.09</v>
+        <v>78826.09</v>
       </c>
       <c r="N71" t="n">
-        <v>81618.96000000001</v>
+        <v>79711.05</v>
       </c>
       <c r="O71" t="n">
-        <v>85784.55</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6456,13 +6464,15 @@
       <c r="R71" s="6" t="n">
         <v/>
       </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="n">
-        <v/>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U71" s="8" t="n">
         <v/>
@@ -6470,7 +6480,7 @@
       <c r="V71" s="8" t="n">
         <v/>
       </c>
-      <c r="W71" s="9" t="inlineStr">
+      <c r="W71" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -6484,50 +6494,50 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>78246.17</v>
+        <v>78539.86</v>
       </c>
       <c r="C72" t="n">
-        <v>79373.17999999999</v>
+        <v>79196.52</v>
       </c>
       <c r="D72" t="n">
-        <v>77056.14999999999</v>
+        <v>76399.06</v>
       </c>
       <c r="E72" t="n">
-        <v>77667.57000000001</v>
+        <v>77403.62</v>
       </c>
       <c r="F72" t="n">
-        <v>-578.24</v>
+        <v>-1145.01</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0146</v>
       </c>
       <c r="H72" t="n">
-        <v>2317.03</v>
+        <v>2797.45</v>
       </c>
       <c r="I72" t="n">
-        <v>76435.85000000001</v>
+        <v>75509.53</v>
       </c>
       <c r="J72" t="n">
-        <v>77495.21000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>77772.78999999999</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>78050.37</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>78718.84</v>
+        <v>79483.09</v>
       </c>
       <c r="N72" t="n">
-        <v>79387.3</v>
+        <v>80535.41</v>
       </c>
       <c r="O72" t="n">
-        <v>79273.99000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6547,77 +6557,69 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T72" s="8" t="n">
+        <v/>
       </c>
       <c r="U72" s="8" t="n">
         <v/>
       </c>
-      <c r="V72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W72" s="9" t="inlineStr">
+      <c r="V72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W72" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>77673.7</v>
+        <v>77402.14</v>
       </c>
       <c r="C73" t="n">
-        <v>79247.34</v>
+        <v>77737.55</v>
       </c>
       <c r="D73" t="n">
-        <v>77378.44</v>
+        <v>76248.3</v>
       </c>
       <c r="E73" t="n">
-        <v>78548.63</v>
+        <v>77300.48</v>
       </c>
       <c r="F73" t="n">
-        <v>881.0599999999999</v>
+        <v>-103.15</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0013</v>
       </c>
       <c r="H73" t="n">
-        <v>1868.91</v>
+        <v>1489.24</v>
       </c>
       <c r="I73" t="n">
-        <v>74739.12</v>
+        <v>73601.61</v>
       </c>
       <c r="J73" t="n">
-        <v>75076.99000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K73" t="n">
-        <v>76509.05</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>77941.12</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M73" t="n">
-        <v>78826.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>79711.05</v>
+        <v>80004</v>
       </c>
       <c r="O73" t="n">
-        <v>81690.21000000001</v>
+        <v>81993.97</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6628,15 +6630,13 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
       </c>
       <c r="U73" s="8" t="n">
         <v/>
@@ -6644,95 +6644,93 @@
       <c r="V73" s="8" t="n">
         <v/>
       </c>
-      <c r="W73" s="9" t="inlineStr">
+      <c r="W73" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>78539.86</v>
+        <v>77300.16</v>
       </c>
       <c r="C74" t="n">
-        <v>79196.52</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>76399.06</v>
+        <v>76940.88</v>
       </c>
       <c r="E74" t="n">
-        <v>77403.62</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>-1145.01</v>
+        <v>3971.27</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0514</v>
       </c>
       <c r="H74" t="n">
-        <v>2797.45</v>
+        <v>5321.33</v>
       </c>
       <c r="I74" t="n">
-        <v>75509.53</v>
+        <v>74759.06</v>
       </c>
       <c r="J74" t="n">
-        <v>76797.60000000001</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>77614.17999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L74" t="n">
-        <v>78430.75999999999</v>
+        <v>77146.7</v>
       </c>
       <c r="M74" t="n">
-        <v>79483.09</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>80535.41</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O74" t="n">
-        <v>81116.25</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
+      <c r="U74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V74" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V74" s="8" t="n">
-        <v/>
-      </c>
       <c r="W74" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X74" t="inlineStr"/>
@@ -6740,50 +6738,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>77402.14</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C75" t="n">
-        <v>77737.55</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>76248.3</v>
+        <v>78641.62</v>
       </c>
       <c r="E75" t="n">
-        <v>77300.48</v>
+        <v>79671.97</v>
       </c>
       <c r="F75" t="n">
-        <v>-103.15</v>
+        <v>-1599.77</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0197</v>
       </c>
       <c r="H75" t="n">
-        <v>1489.24</v>
+        <v>2791.52</v>
       </c>
       <c r="I75" t="n">
-        <v>73601.61</v>
+        <v>71619.55</v>
       </c>
       <c r="J75" t="n">
-        <v>74409.09</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>76004.89999999999</v>
+        <v>78611.08</v>
       </c>
       <c r="L75" t="n">
-        <v>77600.71000000001</v>
+        <v>80436.64</v>
       </c>
       <c r="M75" t="n">
-        <v>78802.35000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N75" t="n">
-        <v>80004</v>
+        <v>87428.17</v>
       </c>
       <c r="O75" t="n">
-        <v>81993.97</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6810,58 +6808,62 @@
       </c>
       <c r="W75" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>77300.16</v>
+        <v>79671.7</v>
       </c>
       <c r="C76" t="n">
-        <v>82262.21000000001</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>76940.88</v>
+        <v>79465.06</v>
       </c>
       <c r="E76" t="n">
-        <v>81271.74000000001</v>
+        <v>79823.87</v>
       </c>
       <c r="F76" t="n">
-        <v>3971.27</v>
+        <v>151.9</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0514</v>
+        <v>0.0019</v>
       </c>
       <c r="H76" t="n">
-        <v>5321.33</v>
+        <v>729.45</v>
       </c>
       <c r="I76" t="n">
-        <v>74759.06</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>75965.00999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>76555.86</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>77146.7</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>78045.10000000001</v>
+        <v>81067.73</v>
       </c>
       <c r="N76" t="n">
-        <v>78943.49000000001</v>
+        <v>82280.78</v>
       </c>
       <c r="O76" t="n">
-        <v>79226.78999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6872,80 +6874,78 @@
       <c r="R76" s="6" t="n">
         <v/>
       </c>
-      <c r="S76" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V76" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W76" s="11" t="inlineStr">
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U76" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V76" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W76" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>81271.53999999999</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C77" t="n">
-        <v>81433.14999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>78641.62</v>
+        <v>79327.5</v>
       </c>
       <c r="E77" t="n">
-        <v>79671.97</v>
+        <v>80350.05</v>
       </c>
       <c r="F77" t="n">
-        <v>-1599.77</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0066</v>
       </c>
       <c r="H77" t="n">
-        <v>2791.52</v>
+        <v>1203.15</v>
       </c>
       <c r="I77" t="n">
-        <v>71619.55</v>
+        <v>78735.62</v>
       </c>
       <c r="J77" t="n">
-        <v>76785.50999999999</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>78611.08</v>
+        <v>79459.14</v>
       </c>
       <c r="L77" t="n">
-        <v>80436.64</v>
+        <v>79826.83</v>
       </c>
       <c r="M77" t="n">
-        <v>83932.41</v>
+        <v>80188.59</v>
       </c>
       <c r="N77" t="n">
-        <v>87428.17</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O77" t="n">
-        <v>87583.53999999999</v>
+        <v>80923.95</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6953,16 +6953,20 @@
       <c r="Q77" s="6" t="n">
         <v/>
       </c>
-      <c r="R77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="n">
-        <v/>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6970,77 +6974,81 @@
       <c r="V77" s="8" t="n">
         <v/>
       </c>
-      <c r="W77" s="11" t="inlineStr">
+      <c r="W77" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>79671.7</v>
+        <v>80349.2</v>
       </c>
       <c r="C78" t="n">
-        <v>80194.50999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D78" t="n">
-        <v>79465.06</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>79823.87</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>151.9</v>
+        <v>-1234.2</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0154</v>
       </c>
       <c r="H78" t="n">
-        <v>729.45</v>
+        <v>1747.38</v>
       </c>
       <c r="I78" t="n">
-        <v>75850.10000000001</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>76697.74000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K78" t="n">
-        <v>78276.21000000001</v>
+        <v>79748.47</v>
       </c>
       <c r="L78" t="n">
-        <v>79854.67999999999</v>
+        <v>80139.56</v>
       </c>
       <c r="M78" t="n">
-        <v>81067.73</v>
+        <v>80951.62</v>
       </c>
       <c r="N78" t="n">
-        <v>82280.78</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O78" t="n">
-        <v>84224.67</v>
+        <v>81733.8</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R78" s="6" t="n">
-        <v/>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T78" s="8" t="n">
@@ -7054,62 +7062,58 @@
       </c>
       <c r="W78" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>79824.60000000001</v>
+        <v>79114.91</v>
       </c>
       <c r="C79" t="n">
-        <v>80530.64999999999</v>
+        <v>79463.27</v>
       </c>
       <c r="D79" t="n">
-        <v>79327.5</v>
+        <v>77635.69</v>
       </c>
       <c r="E79" t="n">
-        <v>80350.05</v>
+        <v>78438.58</v>
       </c>
       <c r="F79" t="n">
-        <v>526.1799999999999</v>
+        <v>-677.27</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0086</v>
       </c>
       <c r="H79" t="n">
-        <v>1203.15</v>
+        <v>1827.59</v>
       </c>
       <c r="I79" t="n">
-        <v>78735.62</v>
+        <v>76937.55</v>
       </c>
       <c r="J79" t="n">
-        <v>79091.46000000001</v>
+        <v>77147.08</v>
       </c>
       <c r="K79" t="n">
-        <v>79459.14</v>
+        <v>78242.16</v>
       </c>
       <c r="L79" t="n">
-        <v>79826.83</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>80188.59</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N79" t="n">
-        <v>80550.35000000001</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O79" t="n">
-        <v>80923.95</v>
+        <v>82179.7</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7119,19 +7123,17 @@
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S79" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
+      </c>
       <c r="U79" s="8" t="n">
         <v/>
       </c>
@@ -7140,154 +7142,154 @@
       </c>
       <c r="W79" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>80349.2</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>80432.31</v>
+        <v>79737.3</v>
       </c>
       <c r="D80" t="n">
-        <v>78684.92999999999</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>79115.85000000001</v>
+        <v>78259.52</v>
       </c>
       <c r="F80" t="n">
-        <v>-1234.2</v>
+        <v>-179.05</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0023</v>
       </c>
       <c r="H80" t="n">
-        <v>1747.38</v>
+        <v>1969.15</v>
       </c>
       <c r="I80" t="n">
-        <v>78124.35000000001</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>79357.38</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>79748.47</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>80139.56</v>
+        <v>78494.03</v>
       </c>
       <c r="M80" t="n">
-        <v>80951.62</v>
+        <v>79352.37</v>
       </c>
       <c r="N80" t="n">
-        <v>81763.67999999999</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O80" t="n">
-        <v>81733.8</v>
+        <v>81290.86</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
       </c>
-      <c r="Q80" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R80" s="6" t="inlineStr">
+      <c r="Q80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
-      </c>
       <c r="U80" s="8" t="n">
         <v/>
       </c>
       <c r="V80" s="8" t="n">
         <v/>
       </c>
-      <c r="W80" s="9" t="inlineStr">
+      <c r="W80" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>79114.91</v>
+        <v>78260.38</v>
       </c>
       <c r="C81" t="n">
-        <v>79463.27</v>
+        <v>78520.97</v>
       </c>
       <c r="D81" t="n">
-        <v>77635.69</v>
+        <v>76470.64</v>
       </c>
       <c r="E81" t="n">
-        <v>78438.58</v>
+        <v>76568.12</v>
       </c>
       <c r="F81" t="n">
-        <v>-677.27</v>
+        <v>-1691.4</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0216</v>
       </c>
       <c r="H81" t="n">
-        <v>1827.59</v>
+        <v>2050.33</v>
       </c>
       <c r="I81" t="n">
-        <v>76937.55</v>
+        <v>75799</v>
       </c>
       <c r="J81" t="n">
-        <v>77147.08</v>
+        <v>76043.78</v>
       </c>
       <c r="K81" t="n">
-        <v>78242.16</v>
+        <v>77274.95</v>
       </c>
       <c r="L81" t="n">
-        <v>79337.24000000001</v>
+        <v>78506.12</v>
       </c>
       <c r="M81" t="n">
-        <v>79989.53999999999</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>80641.85000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O81" t="n">
-        <v>82179.7</v>
+        <v>81706.45</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
       </c>
-      <c r="Q81" s="6" t="n">
-        <v/>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
@@ -7304,7 +7306,7 @@
       <c r="V81" s="8" t="n">
         <v/>
       </c>
-      <c r="W81" s="9" t="inlineStr">
+      <c r="W81" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -7314,50 +7316,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>78440.60000000001</v>
+        <v>76559.12</v>
       </c>
       <c r="C82" t="n">
-        <v>79737.3</v>
+        <v>79818.34</v>
       </c>
       <c r="D82" t="n">
-        <v>77768.14999999999</v>
+        <v>76162.91</v>
       </c>
       <c r="E82" t="n">
-        <v>78259.52</v>
+        <v>77173.8</v>
       </c>
       <c r="F82" t="n">
-        <v>-179.05</v>
+        <v>605.67</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>1969.15</v>
+        <v>3655.42</v>
       </c>
       <c r="I82" t="n">
-        <v>75808.10000000001</v>
+        <v>74420.31</v>
       </c>
       <c r="J82" t="n">
-        <v>76555.53999999999</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>77524.78999999999</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>78494.03</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>79352.37</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>80210.71000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O82" t="n">
-        <v>81290.86</v>
+        <v>80571.3</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7368,9 +7370,9 @@
       <c r="R82" s="6" t="n">
         <v/>
       </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T82" s="8" t="inlineStr">
@@ -7378,13 +7380,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U82" s="8" t="n">
-        <v/>
+      <c r="U82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V82" s="8" t="n">
         <v/>
       </c>
-      <c r="W82" s="9" t="inlineStr">
+      <c r="W82" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -7398,67 +7402,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>78260.38</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C83" t="n">
-        <v>78520.97</v>
+        <v>77479.66</v>
       </c>
       <c r="D83" t="n">
-        <v>76470.64</v>
+        <v>77045</v>
       </c>
       <c r="E83" t="n">
-        <v>76568.12</v>
+        <v>77270.47</v>
       </c>
       <c r="F83" t="n">
-        <v>-1691.4</v>
+        <v>96.67</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.0013</v>
       </c>
       <c r="H83" t="n">
-        <v>2050.33</v>
+        <v>434.66</v>
       </c>
       <c r="I83" t="n">
-        <v>75799</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>76043.78</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>77274.95</v>
+        <v>75346.09</v>
       </c>
       <c r="L83" t="n">
-        <v>78506.12</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>79244.10000000001</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>79982.07000000001</v>
+        <v>80420.8</v>
       </c>
       <c r="O83" t="n">
-        <v>81706.45</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
       </c>
-      <c r="Q83" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v/>
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T83" s="8" t="n">
@@ -7470,146 +7470,148 @@
       <c r="V83" s="8" t="n">
         <v/>
       </c>
-      <c r="W83" s="9" t="inlineStr">
+      <c r="W83" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>76559.12</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C84" t="n">
-        <v>79818.34</v>
+        <v>77415.66</v>
       </c>
       <c r="D84" t="n">
-        <v>76162.91</v>
+        <v>76498.38</v>
       </c>
       <c r="E84" t="n">
-        <v>77173.8</v>
+        <v>76838.16</v>
       </c>
       <c r="F84" t="n">
-        <v>605.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H84" t="n">
-        <v>3655.42</v>
+        <v>917.27</v>
       </c>
       <c r="I84" t="n">
-        <v>74420.31</v>
+        <v>76610.34</v>
       </c>
       <c r="J84" t="n">
-        <v>74053.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K84" t="n">
-        <v>75542.96000000001</v>
+        <v>77053.14</v>
       </c>
       <c r="L84" t="n">
-        <v>77031.96000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M84" t="n">
-        <v>77593.28999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N84" t="n">
-        <v>78154.61</v>
+        <v>77709.2</v>
       </c>
       <c r="O84" t="n">
-        <v>80571.3</v>
-      </c>
-      <c r="P84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
+        <v>77914.31</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U84" s="8" t="inlineStr">
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U84" s="8" t="n">
+        <v/>
+      </c>
       <c r="V84" s="8" t="n">
         <v/>
       </c>
-      <c r="W84" s="9" t="inlineStr">
+      <c r="W84" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>77175.07000000001</v>
+        <v>76830.28</v>
       </c>
       <c r="C85" t="n">
-        <v>77479.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D85" t="n">
-        <v>77045</v>
+        <v>76367.38</v>
       </c>
       <c r="E85" t="n">
-        <v>77270.47</v>
+        <v>78163.38</v>
       </c>
       <c r="F85" t="n">
-        <v>96.67</v>
+        <v>1325.23</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0172</v>
       </c>
       <c r="H85" t="n">
-        <v>434.66</v>
+        <v>3201.58</v>
       </c>
       <c r="I85" t="n">
-        <v>72507.49000000001</v>
+        <v>75581.11</v>
       </c>
       <c r="J85" t="n">
-        <v>73109.96000000001</v>
+        <v>75861.45</v>
       </c>
       <c r="K85" t="n">
-        <v>75346.09</v>
+        <v>76379.52</v>
       </c>
       <c r="L85" t="n">
-        <v>77582.21000000001</v>
+        <v>76897.59</v>
       </c>
       <c r="M85" t="n">
-        <v>79001.50999999999</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>80420.8</v>
+        <v>77696</v>
       </c>
       <c r="O85" t="n">
-        <v>83473.75999999999</v>
+        <v>78332.92999999999</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7617,97 +7619,103 @@
       <c r="Q85" s="6" t="n">
         <v/>
       </c>
-      <c r="R85" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V85" s="8" t="n">
-        <v/>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S85" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V85" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W85" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>77270.17999999999</v>
+        <v>78162.48</v>
       </c>
       <c r="C86" t="n">
-        <v>77415.66</v>
+        <v>78242.55</v>
       </c>
       <c r="D86" t="n">
-        <v>76498.38</v>
+        <v>74944.59</v>
       </c>
       <c r="E86" t="n">
-        <v>76838.16</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>-432.31</v>
+        <v>-2550.88</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0326</v>
       </c>
       <c r="H86" t="n">
-        <v>917.27</v>
+        <v>3297.95</v>
       </c>
       <c r="I86" t="n">
-        <v>76610.34</v>
+        <v>73165.8</v>
       </c>
       <c r="J86" t="n">
-        <v>76839.88</v>
+        <v>75059.41</v>
       </c>
       <c r="K86" t="n">
-        <v>77053.14</v>
+        <v>76562.59</v>
       </c>
       <c r="L86" t="n">
-        <v>77266.39999999999</v>
+        <v>78065.77</v>
       </c>
       <c r="M86" t="n">
-        <v>77487.8</v>
+        <v>79764.17</v>
       </c>
       <c r="N86" t="n">
-        <v>77709.2</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O86" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P86" s="6" t="inlineStr">
+        <v>82770.53</v>
+      </c>
+      <c r="P86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -7724,58 +7732,62 @@
       </c>
       <c r="W86" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>76830.28</v>
+        <v>75611.8</v>
       </c>
       <c r="C87" t="n">
-        <v>79568.95</v>
+        <v>76474.08</v>
       </c>
       <c r="D87" t="n">
-        <v>76367.38</v>
+        <v>74995.52</v>
       </c>
       <c r="E87" t="n">
-        <v>78163.38</v>
+        <v>76150.32000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>1325.23</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0071</v>
       </c>
       <c r="H87" t="n">
-        <v>3201.58</v>
+        <v>1478.55</v>
       </c>
       <c r="I87" t="n">
-        <v>75581.11</v>
+        <v>71646.64</v>
       </c>
       <c r="J87" t="n">
-        <v>75861.45</v>
+        <v>71824.02</v>
       </c>
       <c r="K87" t="n">
-        <v>76379.52</v>
+        <v>73963.53</v>
       </c>
       <c r="L87" t="n">
-        <v>76897.59</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="M87" t="n">
-        <v>77296.78999999999</v>
+        <v>77261.48</v>
       </c>
       <c r="N87" t="n">
-        <v>77696</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="O87" t="n">
-        <v>78332.92999999999</v>
+        <v>81540.5</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7783,32 +7795,24 @@
       <c r="Q87" s="6" t="n">
         <v/>
       </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R87" s="6" t="n">
+        <v/>
       </c>
       <c r="S87" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W87" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W87" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -7822,136 +7826,130 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>78162.48</v>
+        <v>76152.05</v>
       </c>
       <c r="C88" t="n">
-        <v>78242.55</v>
+        <v>77079.16</v>
       </c>
       <c r="D88" t="n">
-        <v>74944.59</v>
+        <v>75945.55</v>
       </c>
       <c r="E88" t="n">
-        <v>75612.50999999999</v>
+        <v>76403.77</v>
       </c>
       <c r="F88" t="n">
-        <v>-2550.88</v>
+        <v>253.45</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0033</v>
       </c>
       <c r="H88" t="n">
-        <v>3297.95</v>
+        <v>1133.61</v>
       </c>
       <c r="I88" t="n">
-        <v>73165.8</v>
+        <v>73516.97</v>
       </c>
       <c r="J88" t="n">
-        <v>75059.41</v>
+        <v>74879.53</v>
       </c>
       <c r="K88" t="n">
-        <v>76562.59</v>
+        <v>75411.03999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>78065.77</v>
+        <v>75942.56</v>
       </c>
       <c r="M88" t="n">
-        <v>79764.17</v>
+        <v>76889.60000000001</v>
       </c>
       <c r="N88" t="n">
-        <v>81462.57000000001</v>
+        <v>77836.63</v>
       </c>
       <c r="O88" t="n">
-        <v>82770.53</v>
+        <v>77952.63</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
       </c>
-      <c r="Q88" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="Q88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
       <c r="U88" s="8" t="n">
         <v/>
       </c>
       <c r="V88" s="8" t="n">
         <v/>
       </c>
-      <c r="W88" s="11" t="inlineStr">
+      <c r="W88" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>75611.8</v>
+        <v>76405.02</v>
       </c>
       <c r="C89" t="n">
-        <v>76474.08</v>
+        <v>81331.77</v>
       </c>
       <c r="D89" t="n">
-        <v>74995.52</v>
+        <v>76228.33</v>
       </c>
       <c r="E89" t="n">
-        <v>76150.32000000001</v>
+        <v>80901.46000000001</v>
       </c>
       <c r="F89" t="n">
-        <v>537.8099999999999</v>
+        <v>4497.69</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0589</v>
       </c>
       <c r="H89" t="n">
-        <v>1478.55</v>
+        <v>5103.44</v>
       </c>
       <c r="I89" t="n">
-        <v>71646.64</v>
+        <v>74811.95</v>
       </c>
       <c r="J89" t="n">
-        <v>71824.02</v>
+        <v>75215.87</v>
       </c>
       <c r="K89" t="n">
-        <v>73963.53</v>
+        <v>75836.97</v>
       </c>
       <c r="L89" t="n">
-        <v>76103.03999999999</v>
+        <v>76458.07000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>77261.48</v>
+        <v>76970.58</v>
       </c>
       <c r="N89" t="n">
-        <v>78419.92999999999</v>
+        <v>77483.09</v>
       </c>
       <c r="O89" t="n">
-        <v>81540.5</v>
+        <v>78212.77</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7964,76 +7962,78 @@
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W89" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W89" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>76350.67999999999</v>
+        <v>80900.28999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>76409.84</v>
+        <v>81911.14</v>
       </c>
       <c r="D90" t="n">
-        <v>76300.22</v>
+        <v>80814.94</v>
       </c>
       <c r="E90" t="n">
-        <v>76503.82000000001</v>
+        <v>81233.67999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>353.5</v>
+        <v>332.22</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0041</v>
       </c>
       <c r="H90" t="n">
-        <v>109.62</v>
+        <v>1096.2</v>
       </c>
       <c r="I90" t="n">
-        <v>73516.97</v>
+        <v>71124.89</v>
       </c>
       <c r="J90" t="n">
-        <v>74879.53</v>
+        <v>76858.73</v>
       </c>
       <c r="K90" t="n">
-        <v>75411.03999999999</v>
+        <v>78349.74000000001</v>
       </c>
       <c r="L90" t="n">
-        <v>75942.56</v>
+        <v>79840.75</v>
       </c>
       <c r="M90" t="n">
-        <v>76889.60000000001</v>
+        <v>83453.17999999999</v>
       </c>
       <c r="N90" t="n">
-        <v>77836.63</v>
+        <v>87065.61</v>
       </c>
       <c r="O90" t="n">
-        <v>77952.63</v>
+        <v>86435.2</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8046,13 +8046,11 @@
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="n">
+        <v/>
       </c>
       <c r="U90" s="8" t="n">
         <v/>
@@ -8060,14 +8058,94 @@
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="11" t="inlineStr">
+      <c r="W90" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>81226.62</v>
+      </c>
+      <c r="C91" t="n">
+        <v>81371.77</v>
+      </c>
+      <c r="D91" t="n">
+        <v>80217.06</v>
+      </c>
+      <c r="E91" t="n">
+        <v>81254.85000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="I91" t="n">
+        <v>79718.73</v>
+      </c>
+      <c r="J91" t="n">
+        <v>80072.8</v>
+      </c>
+      <c r="K91" t="n">
+        <v>80685.58</v>
+      </c>
+      <c r="L91" t="n">
+        <v>81298.36</v>
+      </c>
+      <c r="M91" t="n">
+        <v>81781.78</v>
+      </c>
+      <c r="N91" t="n">
+        <v>82265.2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>83007.34</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -634,56 +634,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63952.79</v>
+        <v>62663.03</v>
       </c>
       <c r="C2" t="n">
-        <v>64196.56</v>
+        <v>63097.76</v>
       </c>
       <c r="D2" t="n">
-        <v>61893.21</v>
+        <v>59029.86</v>
       </c>
       <c r="E2" t="n">
-        <v>62668.02</v>
+        <v>60995.13</v>
       </c>
       <c r="F2" t="n">
-        <v>-1284.09</v>
+        <v>-1672.89</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0201</v>
+        <v>-0.0267</v>
       </c>
       <c r="H2" t="n">
-        <v>2303.36</v>
+        <v>4067.9</v>
       </c>
       <c r="I2" t="n">
-        <v>60923.06</v>
+        <v>59589.85</v>
       </c>
       <c r="J2" t="n">
-        <v>61423.31</v>
+        <v>60176.23</v>
       </c>
       <c r="K2" t="n">
-        <v>62796.87</v>
+        <v>61516.34</v>
       </c>
       <c r="L2" t="n">
-        <v>64170.44</v>
+        <v>62856.45</v>
       </c>
       <c r="M2" t="n">
-        <v>65107.34</v>
+        <v>63819.7</v>
       </c>
       <c r="N2" t="n">
-        <v>66044.24000000001</v>
+        <v>64782.94</v>
       </c>
       <c r="O2" t="n">
-        <v>67854.47</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>66499.92</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -718,60 +722,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C3" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D3" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E3" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F3" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H3" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I3" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J3" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K3" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L3" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M3" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N3" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O3" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
@@ -806,50 +806,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C4" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D4" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E4" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F4" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H4" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I4" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J4" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K4" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L4" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M4" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N4" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O4" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,14 +857,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -883,57 +881,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C5" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D5" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E5" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F5" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H5" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I5" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J5" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K5" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L5" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M5" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N5" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O5" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -972,50 +970,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C6" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D6" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E6" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F6" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H6" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I6" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J6" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K6" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L6" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M6" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N6" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O6" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,12 +1021,14 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1047,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C7" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D7" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E7" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F7" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H7" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I7" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J7" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K7" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L7" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M7" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N7" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O7" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,19 +1105,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1131,77 +1131,79 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C8" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D8" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E8" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F8" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H8" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I8" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J8" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K8" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L8" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M8" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N8" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O8" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1215,82 +1217,82 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C9" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D9" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E9" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F9" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H9" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I9" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J9" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K9" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L9" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M9" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N9" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O9" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1301,57 +1303,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C10" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D10" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E10" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H10" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I10" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J10" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K10" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L10" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M10" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N10" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O10" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1369,14 +1371,12 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1385,59 +1385,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C11" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D11" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E11" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H11" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I11" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J11" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K11" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L11" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M11" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N11" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O11" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1474,50 +1470,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C12" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D12" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E12" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I12" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J12" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K12" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L12" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M12" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N12" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O12" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1554,50 +1550,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C13" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D13" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E13" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F13" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H13" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I13" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J13" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K13" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L13" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M13" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N13" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O13" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,8 +1601,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
@@ -1634,56 +1632,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C14" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D14" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E14" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F14" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H14" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I14" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J14" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K14" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L14" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M14" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N14" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O14" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
@@ -1711,78 +1711,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C15" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D15" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E15" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F15" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H15" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I15" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J15" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K15" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L15" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M15" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N15" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O15" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1797,70 +1795,74 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C16" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D16" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E16" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F16" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H16" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I16" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J16" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K16" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L16" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M16" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N16" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O16" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1879,79 +1881,77 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C17" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D17" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E17" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F17" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H17" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I17" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J17" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K17" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L17" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M17" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N17" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O17" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1965,57 +1965,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C18" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D18" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E18" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F18" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H18" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I18" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J18" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K18" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L18" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M18" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N18" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O18" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2047,59 +2047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C19" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D19" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E19" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F19" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H19" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I19" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J19" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K19" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L19" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M19" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N19" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O19" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,15 +2106,13 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2131,55 +2125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C20" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D20" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E20" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F20" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H20" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J20" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K20" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L20" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M20" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N20" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O20" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2195,8 +2193,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2211,70 +2211,76 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C21" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D21" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E21" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F21" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H21" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I21" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J21" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K21" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L21" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M21" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N21" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O21" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2282,162 +2288,154 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C22" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D22" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E22" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F22" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H22" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I22" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J22" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K22" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L22" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M22" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N22" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O22" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C23" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D23" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E23" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F23" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H23" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I23" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J23" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K23" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L23" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M23" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N23" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O23" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2450,18 +2448,14 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2471,68 +2465,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C24" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D24" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E24" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F24" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H24" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I24" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J24" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K24" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L24" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M24" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N24" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O24" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2551,65 +2553,63 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C25" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D25" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E25" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F25" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H25" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I25" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J25" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K25" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L25" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M25" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N25" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O25" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2637,57 +2637,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C26" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D26" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E26" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F26" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H26" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I26" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J26" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K26" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L26" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M26" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N26" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O26" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,18 +2695,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2719,59 +2719,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C27" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D27" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E27" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F27" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H27" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I27" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J27" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K27" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L27" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M27" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N27" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2779,18 +2775,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2803,61 +2799,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C28" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D28" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E28" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F28" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I28" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J28" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K28" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L28" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M28" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N28" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O28" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2866,17 +2868,23 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2892,63 +2900,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C29" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D29" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E29" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F29" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H29" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I29" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J29" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K29" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L29" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M29" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N29" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O29" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2957,77 +2961,69 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E30" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F30" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H30" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I30" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J30" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K30" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L30" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N30" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O30" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,18 +3031,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3059,61 +3055,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C31" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D31" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E31" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F31" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H31" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I31" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J31" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K31" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L31" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N31" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3122,7 +3124,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3141,69 +3143,67 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C32" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D32" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E32" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H32" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I32" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J32" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K32" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L32" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M32" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N32" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
@@ -3234,50 +3234,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C33" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D33" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E33" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F33" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H33" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I33" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J33" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K33" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L33" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M33" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N33" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O33" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3285,14 +3285,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3311,57 +3309,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C34" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D34" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E34" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F34" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H34" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I34" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J34" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K34" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L34" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M34" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N34" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O34" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,179 +3370,179 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C35" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D35" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E35" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F35" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H35" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I35" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J35" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K35" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L35" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M35" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C36" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D36" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E36" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F36" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H36" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I36" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J36" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K36" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L36" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M36" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N36" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O36" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3570,50 +3568,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C37" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D37" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E37" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F37" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I37" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J37" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K37" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L37" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M37" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N37" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O37" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3621,16 +3619,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3645,57 +3647,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C38" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D38" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E38" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F38" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H38" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I38" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J38" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K38" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L38" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M38" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N38" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O38" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3703,19 +3705,17 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3738,70 +3738,72 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C39" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D39" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E39" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F39" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H39" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I39" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J39" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K39" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L39" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M39" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N39" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O39" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3815,74 +3817,70 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C40" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D40" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E40" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F40" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H40" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I40" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J40" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K40" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L40" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M40" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N40" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O40" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3899,59 +3897,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C41" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D41" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E41" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F41" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H41" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I41" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J41" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K41" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L41" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M41" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N41" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O41" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3962,16 +3956,20 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3981,68 +3979,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C42" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D42" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E42" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F42" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H42" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I42" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J42" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K42" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L42" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M42" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N42" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O42" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4050,10 +4056,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4065,79 +4069,75 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C43" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D43" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E43" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F43" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H43" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I43" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J43" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K43" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L43" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M43" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N43" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O43" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4153,57 +4153,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C44" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D44" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E44" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F44" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I44" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J44" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K44" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L44" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M44" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N44" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O44" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4244,50 +4244,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C45" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D45" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E45" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F45" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H45" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I45" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J45" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K45" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L45" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M45" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N45" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O45" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4295,19 +4295,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C46" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D46" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E46" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F46" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I46" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J46" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K46" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L46" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M46" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N46" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O46" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4379,22 +4379,24 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4405,57 +4407,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C47" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D47" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E47" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F47" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H47" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I47" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J47" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K47" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L47" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M47" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N47" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4468,18 +4470,14 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4491,57 +4489,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C48" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D48" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E48" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F48" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H48" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I48" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J48" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K48" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L48" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M48" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N48" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O48" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4549,19 +4547,25 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4573,63 +4577,67 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C49" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D49" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E49" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F49" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H49" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I49" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J49" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K49" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L49" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M49" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N49" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O49" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
@@ -4638,7 +4646,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4646,10 +4654,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4659,84 +4665,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C50" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D50" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E50" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F50" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H50" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I50" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J50" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K50" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L50" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M50" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N50" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O50" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4754,50 +4750,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C51" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D51" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E51" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F51" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H51" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I51" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J51" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K51" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L51" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M51" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N51" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O51" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4805,18 +4801,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4829,55 +4825,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C52" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D52" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E52" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F52" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H52" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I52" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J52" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K52" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L52" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M52" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N52" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O52" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4885,18 +4885,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4909,59 +4909,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C53" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D53" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E53" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H53" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I53" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J53" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K53" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L53" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M53" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N53" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O53" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4971,12 +4967,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4998,50 +4994,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C54" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D54" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E54" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F54" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H54" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I54" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J54" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K54" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L54" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M54" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N54" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O54" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5049,14 +5045,12 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5073,72 +5067,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C55" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D55" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E55" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F55" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H55" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I55" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J55" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K55" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L55" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M55" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N55" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O55" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5153,145 +5157,141 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C56" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D56" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E56" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F56" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H56" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I56" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J56" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K56" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L56" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M56" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N56" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O56" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C57" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D57" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E57" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F57" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H57" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I57" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J57" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K57" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L57" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M57" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N57" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O57" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5304,23 +5304,17 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5332,50 +5326,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C58" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D58" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E58" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F58" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H58" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I58" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J58" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K58" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L58" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M58" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N58" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O58" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5383,22 +5377,30 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5410,50 +5412,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C59" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D59" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E59" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H59" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I59" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J59" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K59" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L59" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N59" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O59" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5461,10 +5463,8 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
@@ -5473,18 +5473,14 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5496,50 +5492,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C60" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E60" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F60" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H60" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I60" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J60" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K60" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L60" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N60" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O60" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5557,14 +5553,18 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5576,50 +5576,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C61" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F61" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H61" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I61" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J61" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K61" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M61" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N61" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O61" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5630,80 +5630,78 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C62" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D62" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E62" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F62" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I62" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J62" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K62" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L62" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M62" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N62" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O62" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5711,12 +5709,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5742,50 +5742,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C63" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D63" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E63" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F63" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H63" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I63" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J63" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K63" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L63" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M63" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N63" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O63" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5793,18 +5793,18 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R63" s="6" t="n">
+        <v/>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5817,59 +5817,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C64" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D64" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E64" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F64" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H64" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I64" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J64" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L64" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M64" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N64" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O64" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5880,14 +5876,14 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U64" s="8" t="n">
@@ -5901,55 +5897,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C65" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D65" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E65" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F65" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H65" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I65" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J65" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K65" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L65" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5965,10 +5965,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T65" s="8" t="n">
+        <v/>
       </c>
       <c r="U65" s="8" t="n">
         <v/>
@@ -5983,57 +5981,57 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C66" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D66" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H66" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I66" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J66" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K66" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L66" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N66" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O66" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6044,13 +6042,15 @@
       <c r="R66" s="6" t="n">
         <v/>
       </c>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="n">
-        <v/>
+      <c r="S66" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U66" s="8" t="n">
         <v/>
@@ -6063,156 +6063,154 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D67" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H67" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I67" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J67" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L67" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M67" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N67" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O67" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
       </c>
-      <c r="Q67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S67" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
+      <c r="Q67" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v/>
+      </c>
       <c r="U67" s="8" t="n">
         <v/>
       </c>
       <c r="V67" s="8" t="n">
         <v/>
       </c>
-      <c r="W67" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr"/>
+      <c r="W67" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C68" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D68" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F68" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H68" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I68" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J68" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M68" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N68" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O68" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R68" s="6" t="n">
+        <v/>
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T68" s="8" t="n">
@@ -6231,80 +6229,88 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C69" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H69" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I69" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M69" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N69" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O69" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
       </c>
-      <c r="Q69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R69" s="6" t="n">
-        <v/>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
       </c>
-      <c r="V69" s="8" t="n">
-        <v/>
+      <c r="V69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W69" s="11" t="inlineStr">
         <is>
@@ -6313,88 +6319,82 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C70" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D70" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E70" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F70" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H70" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I70" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J70" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L70" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M70" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N70" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O70" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R70" s="6" t="inlineStr">
+      <c r="Q70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S70" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U70" s="8" t="n">
         <v/>
       </c>
-      <c r="V70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V70" s="8" t="n">
+        <v/>
       </c>
       <c r="W70" s="11" t="inlineStr">
         <is>
@@ -6403,77 +6403,79 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C71" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D71" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E71" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F71" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H71" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I71" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J71" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N71" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O71" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S71" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
+      </c>
       <c r="U71" s="8" t="n">
         <v/>
       </c>
@@ -6485,76 +6487,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C72" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D72" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E72" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F72" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H72" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I72" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J72" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K72" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M72" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O72" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R72" s="6" t="n">
+        <v/>
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T72" s="8" t="n">
@@ -6576,50 +6570,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C73" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E73" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H73" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I73" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J73" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L73" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M73" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O73" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6630,23 +6624,29 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W73" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V73" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W73" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X73" t="inlineStr"/>
@@ -6654,50 +6654,50 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C74" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E74" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F74" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H74" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I74" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J74" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L74" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M74" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N74" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O74" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6708,80 +6708,78 @@
       <c r="R74" s="6" t="n">
         <v/>
       </c>
-      <c r="S74" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V74" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V74" s="8" t="n">
+        <v/>
       </c>
       <c r="W74" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C75" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E75" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F75" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H75" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I75" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M75" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N75" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O75" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6813,57 +6811,57 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E76" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F76" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H76" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I76" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J76" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L76" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M76" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N76" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6871,16 +6869,20 @@
       <c r="Q76" s="6" t="n">
         <v/>
       </c>
-      <c r="R76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S76" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S76" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
@@ -6902,71 +6904,71 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C77" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D77" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H77" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I77" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K77" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L77" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M77" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N77" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O77" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="n">
-        <v/>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S77" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6974,76 +6976,70 @@
       <c r="V77" s="8" t="n">
         <v/>
       </c>
-      <c r="W77" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W77" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C78" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D78" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E78" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F78" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H78" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I78" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J78" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K78" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L78" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N78" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
+      <c r="Q78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R78" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
@@ -7070,50 +7066,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D79" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E79" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F79" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H79" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I79" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M79" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N79" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O79" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7121,18 +7117,18 @@
       <c r="Q79" s="6" t="n">
         <v/>
       </c>
-      <c r="R79" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R79" s="6" t="n">
+        <v/>
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7145,74 +7141,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr"/>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C80" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D80" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E80" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F80" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H80" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I80" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J80" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K80" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L80" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M80" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N80" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O80" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
       </c>
-      <c r="Q80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R80" s="6" t="n">
-        <v/>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7225,83 +7227,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C81" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D81" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E81" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F81" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I81" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J81" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M81" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O81" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
       </c>
-      <c r="Q81" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R81" s="6" t="inlineStr">
+      <c r="Q81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S81" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U81" s="8" t="n">
-        <v/>
+      <c r="U81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V81" s="8" t="n">
         <v/>
@@ -7311,55 +7309,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C82" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D82" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E82" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F82" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H82" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I82" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L82" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O82" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7370,20 +7372,16 @@
       <c r="R82" s="6" t="n">
         <v/>
       </c>
-      <c r="S82" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U82" s="8" t="n">
+        <v/>
       </c>
       <c r="V82" s="8" t="n">
         <v/>
@@ -7402,63 +7400,69 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C83" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D83" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E83" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F83" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H83" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I83" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J83" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K83" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L83" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M83" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N83" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O83" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R83" s="6" t="n">
-        <v/>
+        <v>77914.31</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T83" s="8" t="n">
@@ -7475,174 +7479,172 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C84" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D84" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E84" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F84" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H84" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I84" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J84" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K84" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L84" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M84" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O84" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P84" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V84" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S84" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W84" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="W84" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>76830.28</v>
+        <v>78162.48</v>
       </c>
       <c r="C85" t="n">
-        <v>79568.95</v>
+        <v>78242.55</v>
       </c>
       <c r="D85" t="n">
-        <v>76367.38</v>
+        <v>74944.59</v>
       </c>
       <c r="E85" t="n">
-        <v>78163.38</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>1325.23</v>
+        <v>-2550.88</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0326</v>
       </c>
       <c r="H85" t="n">
-        <v>3201.58</v>
+        <v>3297.95</v>
       </c>
       <c r="I85" t="n">
-        <v>75581.11</v>
+        <v>73165.8</v>
       </c>
       <c r="J85" t="n">
-        <v>75861.45</v>
+        <v>75059.41</v>
       </c>
       <c r="K85" t="n">
-        <v>76379.52</v>
+        <v>76562.59</v>
       </c>
       <c r="L85" t="n">
-        <v>76897.59</v>
+        <v>78065.77</v>
       </c>
       <c r="M85" t="n">
-        <v>77296.78999999999</v>
+        <v>79764.17</v>
       </c>
       <c r="N85" t="n">
-        <v>77696</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O85" t="n">
-        <v>78332.92999999999</v>
+        <v>82770.53</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
       </c>
-      <c r="Q85" s="6" t="n">
-        <v/>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S85" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V85" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V85" s="8" t="n">
+        <v/>
       </c>
       <c r="W85" s="9" t="inlineStr">
         <is>
@@ -7651,74 +7653,70 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>78162.48</v>
+        <v>75611.8</v>
       </c>
       <c r="C86" t="n">
-        <v>78242.55</v>
+        <v>76474.08</v>
       </c>
       <c r="D86" t="n">
-        <v>74944.59</v>
+        <v>74995.52</v>
       </c>
       <c r="E86" t="n">
-        <v>75612.50999999999</v>
+        <v>76150.32000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>-2550.88</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0071</v>
       </c>
       <c r="H86" t="n">
-        <v>3297.95</v>
+        <v>1478.55</v>
       </c>
       <c r="I86" t="n">
-        <v>73165.8</v>
+        <v>71646.64</v>
       </c>
       <c r="J86" t="n">
-        <v>75059.41</v>
+        <v>71824.02</v>
       </c>
       <c r="K86" t="n">
-        <v>76562.59</v>
+        <v>73963.53</v>
       </c>
       <c r="L86" t="n">
-        <v>78065.77</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="M86" t="n">
-        <v>79764.17</v>
+        <v>77261.48</v>
       </c>
       <c r="N86" t="n">
-        <v>81462.57000000001</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="O86" t="n">
-        <v>82770.53</v>
+        <v>81540.5</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
       </c>
-      <c r="Q86" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S86" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T86" s="8" t="n">
@@ -7737,57 +7735,57 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>75611.8</v>
+        <v>76152.05</v>
       </c>
       <c r="C87" t="n">
-        <v>76474.08</v>
+        <v>77079.16</v>
       </c>
       <c r="D87" t="n">
-        <v>74995.52</v>
+        <v>75945.55</v>
       </c>
       <c r="E87" t="n">
-        <v>76150.32000000001</v>
+        <v>76403.77</v>
       </c>
       <c r="F87" t="n">
-        <v>537.8099999999999</v>
+        <v>253.45</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0033</v>
       </c>
       <c r="H87" t="n">
-        <v>1478.55</v>
+        <v>1133.61</v>
       </c>
       <c r="I87" t="n">
-        <v>71646.64</v>
+        <v>73516.97</v>
       </c>
       <c r="J87" t="n">
-        <v>71824.02</v>
+        <v>74879.53</v>
       </c>
       <c r="K87" t="n">
-        <v>73963.53</v>
+        <v>75411.03999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>76103.03999999999</v>
+        <v>75942.56</v>
       </c>
       <c r="M87" t="n">
-        <v>77261.48</v>
+        <v>76889.60000000001</v>
       </c>
       <c r="N87" t="n">
-        <v>78419.92999999999</v>
+        <v>77836.63</v>
       </c>
       <c r="O87" t="n">
-        <v>81540.5</v>
+        <v>77952.63</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7803,8 +7801,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T87" s="8" t="n">
-        <v/>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U87" s="8" t="n">
         <v/>
@@ -7817,59 +7817,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>76152.05</v>
+        <v>76405.02</v>
       </c>
       <c r="C88" t="n">
-        <v>77079.16</v>
+        <v>81331.77</v>
       </c>
       <c r="D88" t="n">
-        <v>75945.55</v>
+        <v>76228.33</v>
       </c>
       <c r="E88" t="n">
-        <v>76403.77</v>
+        <v>80901.46000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>253.45</v>
+        <v>4497.69</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0589</v>
       </c>
       <c r="H88" t="n">
-        <v>1133.61</v>
+        <v>5103.44</v>
       </c>
       <c r="I88" t="n">
-        <v>73516.97</v>
+        <v>74811.95</v>
       </c>
       <c r="J88" t="n">
-        <v>74879.53</v>
+        <v>75215.87</v>
       </c>
       <c r="K88" t="n">
-        <v>75411.03999999999</v>
+        <v>75836.97</v>
       </c>
       <c r="L88" t="n">
-        <v>75942.56</v>
+        <v>76458.07000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>76889.60000000001</v>
+        <v>76970.58</v>
       </c>
       <c r="N88" t="n">
-        <v>77836.63</v>
+        <v>77483.09</v>
       </c>
       <c r="O88" t="n">
-        <v>77952.63</v>
+        <v>78212.77</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7882,7 +7878,7 @@
       </c>
       <c r="S88" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T88" s="8" t="inlineStr">
@@ -7890,11 +7886,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V88" s="8" t="n">
-        <v/>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
@@ -7906,50 +7906,50 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>76405.02</v>
+        <v>80900.28999999999</v>
       </c>
       <c r="C89" t="n">
-        <v>81331.77</v>
+        <v>81911.14</v>
       </c>
       <c r="D89" t="n">
-        <v>76228.33</v>
+        <v>80814.94</v>
       </c>
       <c r="E89" t="n">
-        <v>80901.46000000001</v>
+        <v>81233.67999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>4497.69</v>
+        <v>332.22</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0589</v>
+        <v>0.0041</v>
       </c>
       <c r="H89" t="n">
-        <v>5103.44</v>
+        <v>1096.2</v>
       </c>
       <c r="I89" t="n">
-        <v>74811.95</v>
+        <v>71124.89</v>
       </c>
       <c r="J89" t="n">
-        <v>75215.87</v>
+        <v>76858.73</v>
       </c>
       <c r="K89" t="n">
-        <v>75836.97</v>
+        <v>78349.74000000001</v>
       </c>
       <c r="L89" t="n">
-        <v>76458.07000000001</v>
+        <v>79840.75</v>
       </c>
       <c r="M89" t="n">
-        <v>76970.58</v>
+        <v>83453.17999999999</v>
       </c>
       <c r="N89" t="n">
-        <v>77483.09</v>
+        <v>87065.61</v>
       </c>
       <c r="O89" t="n">
-        <v>78212.77</v>
+        <v>86435.2</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7962,23 +7962,17 @@
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
       </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
@@ -7990,50 +7984,50 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>80900.28999999999</v>
+        <v>81234.3</v>
       </c>
       <c r="C90" t="n">
-        <v>81911.14</v>
+        <v>81455.2</v>
       </c>
       <c r="D90" t="n">
-        <v>80814.94</v>
+        <v>80098.77</v>
       </c>
       <c r="E90" t="n">
-        <v>81233.67999999999</v>
+        <v>81142.61</v>
       </c>
       <c r="F90" t="n">
-        <v>332.22</v>
+        <v>-91.06999999999999</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0011</v>
       </c>
       <c r="H90" t="n">
-        <v>1096.2</v>
+        <v>1356.43</v>
       </c>
       <c r="I90" t="n">
-        <v>71124.89</v>
+        <v>79718.73</v>
       </c>
       <c r="J90" t="n">
-        <v>76858.73</v>
+        <v>80072.8</v>
       </c>
       <c r="K90" t="n">
-        <v>78349.74000000001</v>
+        <v>80685.58</v>
       </c>
       <c r="L90" t="n">
-        <v>79840.75</v>
+        <v>81298.36</v>
       </c>
       <c r="M90" t="n">
-        <v>83453.17999999999</v>
+        <v>81781.78</v>
       </c>
       <c r="N90" t="n">
-        <v>87065.61</v>
+        <v>82265.2</v>
       </c>
       <c r="O90" t="n">
-        <v>86435.2</v>
+        <v>83007.34</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8041,12 +8035,14 @@
       <c r="Q90" s="6" t="n">
         <v/>
       </c>
-      <c r="R90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">
@@ -8063,55 +8059,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>81226.62</v>
+        <v>81162.17999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>81371.77</v>
+        <v>87281.16</v>
       </c>
       <c r="D91" t="n">
-        <v>80217.06</v>
+        <v>80933.07000000001</v>
       </c>
       <c r="E91" t="n">
-        <v>81254.85000000001</v>
+        <v>86555.13</v>
       </c>
       <c r="F91" t="n">
-        <v>21.17</v>
+        <v>5412.52</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0667</v>
       </c>
       <c r="H91" t="n">
-        <v>1154.7</v>
+        <v>6348.09</v>
       </c>
       <c r="I91" t="n">
-        <v>79718.73</v>
+        <v>78742.34</v>
       </c>
       <c r="J91" t="n">
-        <v>80072.8</v>
+        <v>79968.99000000001</v>
       </c>
       <c r="K91" t="n">
-        <v>80685.58</v>
+        <v>80464.39</v>
       </c>
       <c r="L91" t="n">
-        <v>81298.36</v>
+        <v>80959.8</v>
       </c>
       <c r="M91" t="n">
-        <v>81781.78</v>
+        <v>81820.82000000001</v>
       </c>
       <c r="N91" t="n">
-        <v>82265.2</v>
+        <v>82681.85000000001</v>
       </c>
       <c r="O91" t="n">
-        <v>83007.34</v>
+        <v>82811.63</v>
       </c>
       <c r="P91" s="6" t="n">
         <v/>
@@ -8119,35 +8119,35 @@
       <c r="Q91" s="6" t="n">
         <v/>
       </c>
-      <c r="R91" s="6" t="inlineStr">
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V91" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W91" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -634,60 +634,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62663.03</v>
+        <v>60992.07</v>
       </c>
       <c r="C2" t="n">
-        <v>63097.76</v>
+        <v>61868.91</v>
       </c>
       <c r="D2" t="n">
-        <v>59029.86</v>
+        <v>58075.92</v>
       </c>
       <c r="E2" t="n">
-        <v>60995.13</v>
+        <v>59721.68</v>
       </c>
       <c r="F2" t="n">
-        <v>-1672.89</v>
+        <v>-1273.46</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0209</v>
       </c>
       <c r="H2" t="n">
-        <v>4067.9</v>
+        <v>3792.98</v>
       </c>
       <c r="I2" t="n">
-        <v>59589.85</v>
+        <v>54961.95</v>
       </c>
       <c r="J2" t="n">
-        <v>60176.23</v>
+        <v>56892.89</v>
       </c>
       <c r="K2" t="n">
-        <v>61516.34</v>
+        <v>58961.18</v>
       </c>
       <c r="L2" t="n">
-        <v>62856.45</v>
+        <v>61029.47</v>
       </c>
       <c r="M2" t="n">
-        <v>63819.7</v>
+        <v>63029.08</v>
       </c>
       <c r="N2" t="n">
-        <v>64782.94</v>
+        <v>65028.7</v>
       </c>
       <c r="O2" t="n">
-        <v>66499.92</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67165.66</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -722,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C3" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D3" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E3" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F3" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H3" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I3" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J3" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K3" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L3" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M3" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N3" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O3" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,14 +769,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -799,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C4" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D4" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E4" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F4" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H4" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I4" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J4" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K4" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L4" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M4" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N4" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O4" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -888,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C5" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D5" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E5" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F5" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H5" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I5" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J5" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K5" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L5" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M5" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N5" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O5" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,12 +933,14 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -963,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C6" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D6" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E6" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F6" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H6" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I6" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J6" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K6" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L6" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M6" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N6" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O6" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,19 +1017,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1047,77 +1043,79 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C7" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D7" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E7" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F7" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H7" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I7" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J7" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K7" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L7" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M7" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N7" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O7" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1131,82 +1129,82 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C8" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D8" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E8" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F8" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H8" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I8" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J8" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K8" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L8" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M8" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N8" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O8" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1217,57 +1215,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C9" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D9" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E9" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H9" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I9" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J9" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K9" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L9" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M9" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N9" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O9" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1285,14 +1283,12 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1301,59 +1297,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C10" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D10" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E10" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H10" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I10" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J10" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K10" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L10" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M10" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N10" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O10" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1390,50 +1382,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C11" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D11" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E11" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I11" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J11" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K11" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L11" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M11" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N11" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O11" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1470,50 +1462,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C12" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D12" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E12" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F12" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H12" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I12" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J12" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K12" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L12" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M12" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N12" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O12" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,8 +1513,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
@@ -1550,56 +1544,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C13" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D13" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E13" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F13" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H13" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I13" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J13" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K13" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L13" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M13" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N13" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O13" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
@@ -1627,78 +1623,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C14" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D14" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E14" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F14" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H14" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I14" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J14" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K14" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L14" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M14" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N14" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O14" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1713,70 +1707,74 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C15" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D15" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E15" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F15" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H15" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I15" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J15" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K15" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L15" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M15" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N15" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O15" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1795,79 +1793,77 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C16" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D16" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E16" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F16" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H16" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I16" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J16" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K16" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L16" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M16" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N16" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O16" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1881,57 +1877,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C17" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D17" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E17" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F17" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H17" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I17" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J17" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K17" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L17" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M17" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N17" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O17" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1963,59 +1959,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C18" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D18" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E18" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F18" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H18" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I18" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J18" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K18" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L18" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M18" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N18" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O18" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,15 +2018,13 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2047,55 +2037,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C19" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D19" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E19" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F19" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J19" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K19" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L19" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M19" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N19" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O19" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2111,8 +2105,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2127,70 +2123,76 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C20" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D20" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E20" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F20" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H20" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I20" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J20" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K20" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L20" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M20" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N20" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O20" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2198,162 +2200,154 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C21" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D21" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E21" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F21" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H21" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I21" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J21" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K21" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L21" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M21" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N21" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O21" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C22" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D22" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E22" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F22" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H22" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I22" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J22" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K22" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L22" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M22" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N22" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O22" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2366,18 +2360,14 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2387,68 +2377,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C23" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D23" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E23" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F23" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H23" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I23" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J23" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K23" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L23" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M23" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N23" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O23" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2467,65 +2465,63 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C24" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D24" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E24" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F24" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H24" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I24" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J24" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K24" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L24" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M24" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N24" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O24" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
@@ -2534,7 +2530,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2553,57 +2549,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C25" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D25" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E25" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F25" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H25" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I25" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J25" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K25" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L25" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M25" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N25" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O25" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,18 +2607,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2635,59 +2631,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C26" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D26" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E26" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F26" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H26" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I26" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J26" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K26" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L26" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M26" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N26" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,18 +2687,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2719,61 +2711,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C27" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D27" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E27" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F27" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I27" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J27" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K27" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L27" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M27" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N27" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O27" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
@@ -2782,17 +2780,23 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2808,63 +2812,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C28" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D28" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E28" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F28" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H28" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I28" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J28" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K28" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L28" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M28" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N28" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O28" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2873,77 +2873,69 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E29" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F29" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H29" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I29" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J29" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K29" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L29" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N29" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O29" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,18 +2943,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2975,61 +2967,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C30" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D30" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E30" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F30" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H30" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I30" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J30" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K30" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L30" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N30" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3038,7 +3036,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3057,69 +3055,67 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C31" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D31" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E31" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H31" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I31" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J31" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K31" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L31" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M31" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N31" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -3150,50 +3146,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C32" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D32" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E32" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F32" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H32" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I32" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J32" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K32" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L32" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M32" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N32" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O32" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3201,14 +3197,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3227,57 +3221,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C33" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D33" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E33" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F33" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H33" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I33" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J33" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K33" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L33" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M33" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N33" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O33" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3288,179 +3282,179 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C34" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D34" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E34" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F34" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H34" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I34" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J34" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K34" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L34" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M34" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C35" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D35" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E35" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F35" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H35" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I35" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J35" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K35" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L35" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M35" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N35" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O35" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3486,50 +3480,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C36" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D36" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E36" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F36" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I36" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J36" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K36" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L36" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M36" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N36" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O36" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3537,16 +3531,20 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3561,57 +3559,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C37" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D37" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E37" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F37" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H37" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I37" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J37" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K37" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L37" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M37" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N37" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O37" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3619,19 +3617,17 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3654,70 +3650,72 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C38" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D38" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E38" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F38" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H38" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I38" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J38" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K38" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L38" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M38" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N38" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O38" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3731,74 +3729,70 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C39" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D39" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E39" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F39" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H39" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I39" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J39" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K39" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L39" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M39" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N39" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O39" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3815,59 +3809,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C40" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D40" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E40" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F40" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H40" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I40" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J40" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K40" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L40" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M40" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N40" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O40" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3878,16 +3868,20 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3897,68 +3891,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C41" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D41" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E41" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F41" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H41" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I41" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J41" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K41" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L41" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M41" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N41" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O41" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3966,10 +3968,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3981,79 +3981,75 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C42" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D42" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E42" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F42" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H42" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I42" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J42" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K42" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L42" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M42" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N42" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O42" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4069,57 +4065,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C43" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D43" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E43" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F43" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I43" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J43" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K43" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L43" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M43" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N43" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O43" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4160,50 +4156,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C44" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D44" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E44" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F44" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H44" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I44" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J44" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K44" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L44" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M44" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N44" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O44" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,19 +4207,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4237,57 +4233,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C45" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D45" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E45" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F45" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I45" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J45" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K45" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L45" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M45" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N45" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O45" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4295,22 +4291,24 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4321,57 +4319,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C46" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D46" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E46" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F46" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H46" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I46" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J46" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K46" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L46" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M46" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N46" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4384,18 +4382,14 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4407,57 +4401,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C47" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D47" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E47" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F47" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H47" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I47" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J47" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K47" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L47" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M47" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N47" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O47" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,19 +4459,25 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4489,63 +4489,67 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C48" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D48" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E48" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F48" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H48" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I48" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J48" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K48" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L48" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M48" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N48" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O48" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4554,7 +4558,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4562,10 +4566,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4575,84 +4577,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C49" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D49" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E49" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F49" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H49" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I49" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J49" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K49" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L49" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M49" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N49" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O49" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4670,50 +4662,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C50" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D50" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E50" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F50" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H50" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I50" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J50" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K50" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L50" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M50" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N50" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O50" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4721,18 +4713,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4745,55 +4737,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C51" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D51" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E51" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F51" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H51" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I51" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J51" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K51" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L51" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M51" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N51" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O51" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4801,18 +4797,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4825,59 +4821,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C52" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D52" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E52" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H52" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I52" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J52" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K52" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L52" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M52" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N52" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O52" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4887,12 +4879,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4914,50 +4906,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C53" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D53" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E53" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F53" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H53" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I53" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J53" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K53" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L53" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M53" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N53" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O53" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4965,14 +4957,12 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4989,72 +4979,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C54" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D54" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E54" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F54" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H54" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I54" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J54" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K54" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L54" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M54" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N54" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O54" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5069,145 +5069,141 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C55" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D55" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E55" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F55" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H55" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I55" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J55" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K55" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L55" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M55" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N55" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O55" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C56" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D56" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E56" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F56" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H56" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I56" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J56" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K56" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L56" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M56" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N56" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O56" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5220,23 +5216,17 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5248,50 +5238,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C57" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D57" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E57" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F57" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H57" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I57" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J57" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K57" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L57" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M57" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N57" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O57" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5299,22 +5289,30 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5326,50 +5324,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C58" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D58" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E58" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H58" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I58" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J58" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K58" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L58" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N58" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O58" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5377,10 +5375,8 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
@@ -5389,18 +5385,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5412,50 +5404,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C59" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E59" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F59" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H59" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I59" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J59" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K59" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L59" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N59" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O59" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5473,14 +5465,18 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5492,50 +5488,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C60" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F60" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H60" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I60" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J60" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K60" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M60" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N60" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O60" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5546,80 +5542,78 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C61" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D61" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E61" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F61" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I61" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J61" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K61" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L61" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M61" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N61" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O61" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5627,12 +5621,14 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5658,50 +5654,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C62" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D62" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E62" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F62" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H62" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I62" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J62" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K62" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L62" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M62" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N62" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O62" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5709,18 +5705,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5733,59 +5729,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C63" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D63" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E63" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F63" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H63" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I63" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J63" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L63" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M63" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N63" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O63" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5796,14 +5788,14 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U63" s="8" t="n">
@@ -5817,55 +5809,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C64" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D64" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E64" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F64" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H64" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I64" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J64" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K64" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L64" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O64" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5881,10 +5877,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5899,57 +5893,57 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C65" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D65" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H65" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I65" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J65" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K65" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L65" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N65" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5960,13 +5954,15 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U65" s="8" t="n">
         <v/>
@@ -5979,156 +5975,154 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D66" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H66" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I66" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J66" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L66" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M66" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N66" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O66" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
       </c>
-      <c r="Q66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S66" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="inlineStr">
+      <c r="Q66" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v/>
+      </c>
       <c r="U66" s="8" t="n">
         <v/>
       </c>
       <c r="V66" s="8" t="n">
         <v/>
       </c>
-      <c r="W66" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr"/>
+      <c r="W66" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C67" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D67" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F67" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H67" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I67" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J67" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M67" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N67" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O67" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
       </c>
-      <c r="Q67" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R67" s="6" t="n">
+        <v/>
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T67" s="8" t="n">
@@ -6147,80 +6141,88 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C68" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H68" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I68" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M68" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N68" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O68" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R68" s="6" t="n">
-        <v/>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U68" s="8" t="n">
         <v/>
       </c>
-      <c r="V68" s="8" t="n">
-        <v/>
+      <c r="V68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W68" s="11" t="inlineStr">
         <is>
@@ -6229,88 +6231,82 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C69" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D69" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E69" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F69" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H69" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I69" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J69" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L69" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M69" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N69" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O69" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
       </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R69" s="6" t="inlineStr">
+      <c r="Q69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S69" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U69" s="8" t="n">
         <v/>
       </c>
-      <c r="V69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V69" s="8" t="n">
+        <v/>
       </c>
       <c r="W69" s="11" t="inlineStr">
         <is>
@@ -6319,77 +6315,79 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C70" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D70" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E70" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F70" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H70" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I70" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J70" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M70" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N70" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O70" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v/>
+      </c>
       <c r="U70" s="8" t="n">
         <v/>
       </c>
@@ -6401,76 +6399,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C71" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D71" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E71" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F71" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H71" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I71" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J71" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K71" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O71" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R71" s="6" t="n">
+        <v/>
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T71" s="8" t="n">
@@ -6492,50 +6482,50 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C72" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E72" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H72" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I72" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J72" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L72" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M72" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O72" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6546,23 +6536,29 @@
       <c r="R72" s="6" t="n">
         <v/>
       </c>
-      <c r="S72" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W72" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S72" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V72" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W72" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X72" t="inlineStr"/>
@@ -6570,50 +6566,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E73" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F73" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H73" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I73" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J73" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L73" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M73" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N73" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O73" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6624,80 +6620,78 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V73" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V73" s="8" t="n">
+        <v/>
       </c>
       <c r="W73" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr"/>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C74" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E74" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F74" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H74" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I74" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M74" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N74" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O74" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6729,57 +6723,57 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E75" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F75" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H75" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I75" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J75" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L75" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M75" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N75" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O75" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6787,16 +6781,20 @@
       <c r="Q75" s="6" t="n">
         <v/>
       </c>
-      <c r="R75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="n">
-        <v/>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S75" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U75" s="8" t="n">
         <v/>
@@ -6818,71 +6816,71 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C76" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D76" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H76" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I76" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K76" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L76" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M76" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N76" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O76" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="n">
-        <v/>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S76" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v/>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
@@ -6890,76 +6888,70 @@
       <c r="V76" s="8" t="n">
         <v/>
       </c>
-      <c r="W76" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W76" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C77" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D77" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E77" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F77" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H77" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I77" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J77" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K77" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L77" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M77" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O77" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
+      <c r="Q77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R77" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S77" s="7" t="inlineStr">
@@ -6986,50 +6978,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D78" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F78" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H78" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I78" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M78" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N78" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7037,18 +7029,18 @@
       <c r="Q78" s="6" t="n">
         <v/>
       </c>
-      <c r="R78" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R78" s="6" t="n">
+        <v/>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U78" s="8" t="n">
         <v/>
@@ -7061,74 +7053,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C79" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D79" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E79" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F79" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H79" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I79" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J79" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K79" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L79" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M79" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N79" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O79" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
       </c>
-      <c r="Q79" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R79" s="6" t="n">
-        <v/>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7141,83 +7139,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C80" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D80" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E80" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F80" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I80" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J80" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N80" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O80" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
       </c>
-      <c r="Q80" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R80" s="6" t="inlineStr">
+      <c r="Q80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U80" s="8" t="n">
-        <v/>
+      <c r="U80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V80" s="8" t="n">
         <v/>
@@ -7227,55 +7221,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D81" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E81" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F81" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H81" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I81" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L81" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M81" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O81" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7286,20 +7284,16 @@
       <c r="R81" s="6" t="n">
         <v/>
       </c>
-      <c r="S81" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U81" s="8" t="n">
+        <v/>
       </c>
       <c r="V81" s="8" t="n">
         <v/>
@@ -7318,63 +7312,69 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C82" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D82" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E82" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F82" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H82" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I82" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J82" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K82" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L82" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M82" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N82" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O82" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R82" s="6" t="n">
-        <v/>
+        <v>77914.31</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T82" s="8" t="n">
@@ -7391,174 +7391,172 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C83" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D83" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E83" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F83" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H83" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I83" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J83" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K83" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L83" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M83" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O83" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P83" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q83" s="6" t="inlineStr">
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V83" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S83" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U83" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V83" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W83" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr"/>
+      <c r="W83" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>76830.28</v>
+        <v>78162.48</v>
       </c>
       <c r="C84" t="n">
-        <v>79568.95</v>
+        <v>78242.55</v>
       </c>
       <c r="D84" t="n">
-        <v>76367.38</v>
+        <v>74944.59</v>
       </c>
       <c r="E84" t="n">
-        <v>78163.38</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>1325.23</v>
+        <v>-2550.88</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0326</v>
       </c>
       <c r="H84" t="n">
-        <v>3201.58</v>
+        <v>3297.95</v>
       </c>
       <c r="I84" t="n">
-        <v>75581.11</v>
+        <v>73165.8</v>
       </c>
       <c r="J84" t="n">
-        <v>75861.45</v>
+        <v>75059.41</v>
       </c>
       <c r="K84" t="n">
-        <v>76379.52</v>
+        <v>76562.59</v>
       </c>
       <c r="L84" t="n">
-        <v>76897.59</v>
+        <v>78065.77</v>
       </c>
       <c r="M84" t="n">
-        <v>77296.78999999999</v>
+        <v>79764.17</v>
       </c>
       <c r="N84" t="n">
-        <v>77696</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O84" t="n">
-        <v>78332.92999999999</v>
+        <v>82770.53</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
       </c>
-      <c r="Q84" s="6" t="n">
-        <v/>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V84" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V84" s="8" t="n">
+        <v/>
       </c>
       <c r="W84" s="9" t="inlineStr">
         <is>
@@ -7567,74 +7565,70 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>78162.48</v>
+        <v>75611.8</v>
       </c>
       <c r="C85" t="n">
-        <v>78242.55</v>
+        <v>76474.08</v>
       </c>
       <c r="D85" t="n">
-        <v>74944.59</v>
+        <v>74995.52</v>
       </c>
       <c r="E85" t="n">
-        <v>75612.50999999999</v>
+        <v>76150.32000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>-2550.88</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0071</v>
       </c>
       <c r="H85" t="n">
-        <v>3297.95</v>
+        <v>1478.55</v>
       </c>
       <c r="I85" t="n">
-        <v>73165.8</v>
+        <v>71646.64</v>
       </c>
       <c r="J85" t="n">
-        <v>75059.41</v>
+        <v>71824.02</v>
       </c>
       <c r="K85" t="n">
-        <v>76562.59</v>
+        <v>73963.53</v>
       </c>
       <c r="L85" t="n">
-        <v>78065.77</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="M85" t="n">
-        <v>79764.17</v>
+        <v>77261.48</v>
       </c>
       <c r="N85" t="n">
-        <v>81462.57000000001</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="O85" t="n">
-        <v>82770.53</v>
+        <v>81540.5</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
       </c>
-      <c r="Q85" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R85" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S85" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T85" s="8" t="n">
@@ -7653,57 +7647,57 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>75611.8</v>
+        <v>76152.05</v>
       </c>
       <c r="C86" t="n">
-        <v>76474.08</v>
+        <v>77079.16</v>
       </c>
       <c r="D86" t="n">
-        <v>74995.52</v>
+        <v>75945.55</v>
       </c>
       <c r="E86" t="n">
-        <v>76150.32000000001</v>
+        <v>76403.77</v>
       </c>
       <c r="F86" t="n">
-        <v>537.8099999999999</v>
+        <v>253.45</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0033</v>
       </c>
       <c r="H86" t="n">
-        <v>1478.55</v>
+        <v>1133.61</v>
       </c>
       <c r="I86" t="n">
-        <v>71646.64</v>
+        <v>73516.97</v>
       </c>
       <c r="J86" t="n">
-        <v>71824.02</v>
+        <v>74879.53</v>
       </c>
       <c r="K86" t="n">
-        <v>73963.53</v>
+        <v>75411.03999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>76103.03999999999</v>
+        <v>75942.56</v>
       </c>
       <c r="M86" t="n">
-        <v>77261.48</v>
+        <v>76889.60000000001</v>
       </c>
       <c r="N86" t="n">
-        <v>78419.92999999999</v>
+        <v>77836.63</v>
       </c>
       <c r="O86" t="n">
-        <v>81540.5</v>
+        <v>77952.63</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7719,8 +7713,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T86" s="8" t="n">
-        <v/>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7733,59 +7729,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>76152.05</v>
+        <v>76405.02</v>
       </c>
       <c r="C87" t="n">
-        <v>77079.16</v>
+        <v>81331.77</v>
       </c>
       <c r="D87" t="n">
-        <v>75945.55</v>
+        <v>76228.33</v>
       </c>
       <c r="E87" t="n">
-        <v>76403.77</v>
+        <v>80901.46000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>253.45</v>
+        <v>4497.69</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0589</v>
       </c>
       <c r="H87" t="n">
-        <v>1133.61</v>
+        <v>5103.44</v>
       </c>
       <c r="I87" t="n">
-        <v>73516.97</v>
+        <v>74811.95</v>
       </c>
       <c r="J87" t="n">
-        <v>74879.53</v>
+        <v>75215.87</v>
       </c>
       <c r="K87" t="n">
-        <v>75411.03999999999</v>
+        <v>75836.97</v>
       </c>
       <c r="L87" t="n">
-        <v>75942.56</v>
+        <v>76458.07000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>76889.60000000001</v>
+        <v>76970.58</v>
       </c>
       <c r="N87" t="n">
-        <v>77836.63</v>
+        <v>77483.09</v>
       </c>
       <c r="O87" t="n">
-        <v>77952.63</v>
+        <v>78212.77</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7798,7 +7790,7 @@
       </c>
       <c r="S87" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T87" s="8" t="inlineStr">
@@ -7806,11 +7798,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V87" s="8" t="n">
-        <v/>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W87" s="9" t="inlineStr">
         <is>
@@ -7822,50 +7818,50 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>76405.02</v>
+        <v>80900.28999999999</v>
       </c>
       <c r="C88" t="n">
-        <v>81331.77</v>
+        <v>81911.14</v>
       </c>
       <c r="D88" t="n">
-        <v>76228.33</v>
+        <v>80814.94</v>
       </c>
       <c r="E88" t="n">
-        <v>80901.46000000001</v>
+        <v>81233.67999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>4497.69</v>
+        <v>332.22</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0589</v>
+        <v>0.0041</v>
       </c>
       <c r="H88" t="n">
-        <v>5103.44</v>
+        <v>1096.2</v>
       </c>
       <c r="I88" t="n">
-        <v>74811.95</v>
+        <v>71124.89</v>
       </c>
       <c r="J88" t="n">
-        <v>75215.87</v>
+        <v>76858.73</v>
       </c>
       <c r="K88" t="n">
-        <v>75836.97</v>
+        <v>78349.74000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>76458.07000000001</v>
+        <v>79840.75</v>
       </c>
       <c r="M88" t="n">
-        <v>76970.58</v>
+        <v>83453.17999999999</v>
       </c>
       <c r="N88" t="n">
-        <v>77483.09</v>
+        <v>87065.61</v>
       </c>
       <c r="O88" t="n">
-        <v>78212.77</v>
+        <v>86435.2</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7878,23 +7874,17 @@
       </c>
       <c r="S88" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V88" s="8" t="n">
+        <v/>
       </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
@@ -7906,50 +7896,50 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>80900.28999999999</v>
+        <v>81234.3</v>
       </c>
       <c r="C89" t="n">
-        <v>81911.14</v>
+        <v>81455.2</v>
       </c>
       <c r="D89" t="n">
-        <v>80814.94</v>
+        <v>80098.77</v>
       </c>
       <c r="E89" t="n">
-        <v>81233.67999999999</v>
+        <v>81142.61</v>
       </c>
       <c r="F89" t="n">
-        <v>332.22</v>
+        <v>-91.06999999999999</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0011</v>
       </c>
       <c r="H89" t="n">
-        <v>1096.2</v>
+        <v>1356.43</v>
       </c>
       <c r="I89" t="n">
-        <v>71124.89</v>
+        <v>79718.73</v>
       </c>
       <c r="J89" t="n">
-        <v>76858.73</v>
+        <v>80072.8</v>
       </c>
       <c r="K89" t="n">
-        <v>78349.74000000001</v>
+        <v>80685.58</v>
       </c>
       <c r="L89" t="n">
-        <v>79840.75</v>
+        <v>81298.36</v>
       </c>
       <c r="M89" t="n">
-        <v>83453.17999999999</v>
+        <v>81781.78</v>
       </c>
       <c r="N89" t="n">
-        <v>87065.61</v>
+        <v>82265.2</v>
       </c>
       <c r="O89" t="n">
-        <v>86435.2</v>
+        <v>83007.34</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7957,12 +7947,14 @@
       <c r="Q89" s="6" t="n">
         <v/>
       </c>
-      <c r="R89" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S89" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T89" s="8" t="n">
@@ -7979,55 +7971,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>81234.3</v>
+        <v>81143.62</v>
       </c>
       <c r="C90" t="n">
-        <v>81455.2</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>80098.77</v>
+        <v>80867.09</v>
       </c>
       <c r="E90" t="n">
-        <v>81142.61</v>
+        <v>86602.91</v>
       </c>
       <c r="F90" t="n">
-        <v>-91.06999999999999</v>
+        <v>5460.3</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0673</v>
       </c>
       <c r="H90" t="n">
-        <v>1356.43</v>
+        <v>6496.67</v>
       </c>
       <c r="I90" t="n">
-        <v>79718.73</v>
+        <v>78742.34</v>
       </c>
       <c r="J90" t="n">
-        <v>80072.8</v>
+        <v>79968.99000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>80685.58</v>
+        <v>80464.39</v>
       </c>
       <c r="L90" t="n">
-        <v>81298.36</v>
+        <v>80959.8</v>
       </c>
       <c r="M90" t="n">
-        <v>81781.78</v>
+        <v>81820.82000000001</v>
       </c>
       <c r="N90" t="n">
-        <v>82265.2</v>
+        <v>82681.85000000001</v>
       </c>
       <c r="O90" t="n">
-        <v>83007.34</v>
+        <v>82811.63</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8035,83 +8031,83 @@
       <c r="Q90" s="6" t="n">
         <v/>
       </c>
-      <c r="R90" s="6" t="inlineStr">
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S90" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V90" s="8" t="n">
-        <v/>
+      <c r="U90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W90" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>81162.17999999999</v>
+        <v>86597.82000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>87281.16</v>
+        <v>86597.82000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>80933.07000000001</v>
+        <v>85158.69</v>
       </c>
       <c r="E91" t="n">
-        <v>86555.13</v>
+        <v>86217.53</v>
       </c>
       <c r="F91" t="n">
-        <v>5412.52</v>
+        <v>-385.38</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0667</v>
+        <v>-0.0044</v>
       </c>
       <c r="H91" t="n">
-        <v>6348.09</v>
+        <v>1439.13</v>
       </c>
       <c r="I91" t="n">
-        <v>78742.34</v>
+        <v>74370.41</v>
       </c>
       <c r="J91" t="n">
-        <v>79968.99000000001</v>
+        <v>81349.99000000001</v>
       </c>
       <c r="K91" t="n">
-        <v>80464.39</v>
+        <v>83354.58</v>
       </c>
       <c r="L91" t="n">
-        <v>80959.8</v>
+        <v>85359.17</v>
       </c>
       <c r="M91" t="n">
-        <v>81820.82000000001</v>
+        <v>89851.25</v>
       </c>
       <c r="N91" t="n">
-        <v>82681.85000000001</v>
+        <v>94343.33</v>
       </c>
       <c r="O91" t="n">
-        <v>82811.63</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P91" s="6" t="n">
         <v/>
@@ -8124,30 +8120,28 @@
       </c>
       <c r="S91" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V91" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
       </c>
       <c r="W91" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr"/>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8077,13 +8077,13 @@
         <v>85158.69</v>
       </c>
       <c r="E91" t="n">
-        <v>86217.53</v>
+        <v>86200.16</v>
       </c>
       <c r="F91" t="n">
-        <v>-385.38</v>
+        <v>-402.76</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0047</v>
       </c>
       <c r="H91" t="n">
         <v>1439.13</v>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8077,13 +8077,13 @@
         <v>85158.69</v>
       </c>
       <c r="E91" t="n">
-        <v>86200.16</v>
+        <v>86030.86</v>
       </c>
       <c r="F91" t="n">
-        <v>-402.76</v>
+        <v>-572.05</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0066</v>
       </c>
       <c r="H91" t="n">
         <v>1439.13</v>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60992.07</v>
+        <v>59712.05</v>
       </c>
       <c r="C2" t="n">
-        <v>61868.91</v>
+        <v>60647.19</v>
       </c>
       <c r="D2" t="n">
-        <v>58075.92</v>
+        <v>58269.12</v>
       </c>
       <c r="E2" t="n">
-        <v>59721.68</v>
+        <v>60016.43</v>
       </c>
       <c r="F2" t="n">
-        <v>-1273.46</v>
+        <v>294.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0209</v>
+        <v>0.0049</v>
       </c>
       <c r="H2" t="n">
-        <v>3792.98</v>
+        <v>2378.06</v>
       </c>
       <c r="I2" t="n">
-        <v>54961.95</v>
+        <v>54282.94</v>
       </c>
       <c r="J2" t="n">
-        <v>56892.89</v>
+        <v>55803.32</v>
       </c>
       <c r="K2" t="n">
-        <v>58961.18</v>
+        <v>57825.18</v>
       </c>
       <c r="L2" t="n">
-        <v>61029.47</v>
+        <v>59847.04</v>
       </c>
       <c r="M2" t="n">
-        <v>63029.08</v>
+        <v>61618.17</v>
       </c>
       <c r="N2" t="n">
-        <v>65028.7</v>
+        <v>63389.29</v>
       </c>
       <c r="O2" t="n">
-        <v>67165.66</v>
+        <v>65661.89</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,14 +685,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C3" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D3" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E3" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F3" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H3" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I3" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J3" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K3" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L3" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M3" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N3" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O3" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +770,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -800,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C4" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D4" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E4" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F4" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H4" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I4" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J4" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K4" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L4" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M4" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N4" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O4" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,12 +849,14 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -875,57 +875,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C5" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D5" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E5" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F5" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H5" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I5" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J5" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K5" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L5" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M5" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N5" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O5" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,19 +933,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -959,76 +959,78 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C6" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D6" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E6" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F6" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H6" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I6" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J6" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K6" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L6" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M6" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N6" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O6" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1043,82 +1045,82 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C7" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D7" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E7" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F7" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H7" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I7" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J7" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K7" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L7" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M7" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N7" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O7" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1129,57 +1131,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C8" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D8" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E8" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F8" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H8" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I8" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J8" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K8" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L8" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M8" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N8" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O8" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,21 +1192,19 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1213,59 +1213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C9" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D9" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E9" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H9" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I9" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J9" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K9" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L9" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M9" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N9" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O9" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1276,7 +1272,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1302,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C10" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D10" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E10" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I10" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J10" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K10" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L10" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M10" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N10" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O10" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,7 +1352,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1382,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C11" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D11" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E11" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F11" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H11" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I11" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J11" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K11" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L11" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M11" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N11" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O11" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,10 +1429,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1462,63 +1460,65 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C12" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D12" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E12" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F12" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H12" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I12" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J12" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K12" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L12" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M12" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N12" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O12" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1539,78 +1539,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C13" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D13" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E13" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F13" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H13" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I13" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J13" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K13" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L13" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M13" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N13" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O13" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1625,70 +1623,74 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C14" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D14" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E14" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F14" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H14" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I14" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J14" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K14" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L14" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M14" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N14" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O14" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1707,79 +1709,77 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C15" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D15" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E15" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F15" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H15" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I15" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J15" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K15" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L15" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M15" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N15" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O15" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1793,57 +1793,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C16" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D16" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E16" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F16" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H16" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I16" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J16" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K16" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L16" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M16" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N16" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O16" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,7 +1854,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1875,59 +1875,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C17" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D17" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E17" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F17" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H17" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I17" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J17" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K17" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L17" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M17" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N17" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O17" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,13 +1936,11 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1959,55 +1953,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C18" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D18" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E18" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F18" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H18" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J18" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K18" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L18" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M18" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N18" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O18" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2018,13 +2016,15 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2039,70 +2039,76 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C19" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D19" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E19" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F19" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H19" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I19" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J19" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K19" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L19" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M19" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N19" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O19" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>64879.44</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2110,162 +2116,154 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C20" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D20" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E20" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F20" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H20" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I20" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J20" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K20" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L20" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M20" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N20" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O20" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C21" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D21" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E21" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F21" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H21" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I21" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J21" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K21" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L21" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M21" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N21" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O21" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,20 +2274,16 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2299,68 +2293,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C22" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D22" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E22" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F22" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H22" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I22" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J22" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K22" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L22" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M22" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N22" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O22" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2379,74 +2381,72 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C23" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D23" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E23" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F23" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H23" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I23" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J23" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K23" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L23" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M23" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N23" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O23" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2465,57 +2465,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C24" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D24" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E24" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F24" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H24" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I24" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J24" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K24" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L24" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M24" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N24" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O24" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,18 +2523,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2547,59 +2547,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C25" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D25" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E25" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F25" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H25" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I25" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J25" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K25" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L25" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M25" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N25" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,18 +2603,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2631,80 +2627,92 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C26" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D26" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E26" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F26" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H26" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I26" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J26" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K26" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L26" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M26" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N26" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O26" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2720,142 +2728,130 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C27" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D27" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E27" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F27" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H27" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I27" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J27" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K27" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L27" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M27" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N27" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O27" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E28" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F28" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H28" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I28" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J28" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K28" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L28" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N28" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O28" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2863,18 +2859,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2887,70 +2883,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C29" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D29" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E29" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F29" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H29" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I29" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J29" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K29" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L29" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N29" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2969,72 +2971,70 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C30" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D30" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E30" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H30" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I30" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J30" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K30" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L30" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M30" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N30" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3062,50 +3062,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C31" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D31" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E31" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F31" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H31" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I31" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J31" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K31" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L31" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M31" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N31" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O31" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,14 +3113,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3139,57 +3137,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C32" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D32" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E32" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F32" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H32" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I32" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J32" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K32" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L32" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M32" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N32" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O32" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3202,177 +3200,177 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C33" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D33" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E33" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F33" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H33" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I33" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J33" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K33" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L33" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M33" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C34" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D34" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E34" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F34" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H34" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I34" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J34" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K34" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L34" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M34" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N34" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O34" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3398,50 +3396,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C35" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D35" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E35" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F35" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I35" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J35" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K35" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L35" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M35" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N35" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O35" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,16 +3447,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3473,57 +3475,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C36" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D36" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E36" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F36" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H36" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I36" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J36" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K36" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L36" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M36" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N36" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O36" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3531,19 +3533,17 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3566,69 +3566,71 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C37" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D37" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E37" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F37" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H37" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I37" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J37" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K37" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L37" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M37" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N37" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O37" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3643,74 +3645,70 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C38" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D38" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E38" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F38" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H38" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I38" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J38" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K38" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L38" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M38" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N38" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O38" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3727,59 +3725,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C39" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D39" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E39" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F39" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H39" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I39" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J39" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K39" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L39" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M39" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N39" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O39" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3792,14 +3786,18 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3809,68 +3807,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C40" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D40" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E40" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F40" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H40" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I40" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J40" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K40" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L40" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M40" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N40" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O40" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3878,10 +3884,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3893,79 +3897,75 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C41" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D41" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E41" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F41" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H41" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I41" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J41" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K41" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L41" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M41" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N41" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O41" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3981,57 +3981,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C42" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D42" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E42" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F42" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I42" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J42" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K42" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L42" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M42" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N42" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O42" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4042,7 +4042,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4072,50 +4072,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C43" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D43" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E43" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F43" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H43" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I43" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J43" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K43" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L43" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M43" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N43" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O43" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4123,18 +4123,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4149,57 +4149,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C44" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D44" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E44" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F44" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I44" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J44" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K44" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L44" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M44" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N44" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O44" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4207,22 +4207,24 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4233,57 +4235,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C45" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D45" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E45" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F45" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H45" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I45" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J45" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K45" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L45" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M45" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N45" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4294,20 +4296,16 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4319,57 +4317,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C46" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D46" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E46" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F46" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H46" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I46" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J46" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K46" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L46" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M46" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N46" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O46" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4377,19 +4375,25 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4401,72 +4405,76 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C47" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D47" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E47" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F47" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H47" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I47" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J47" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K47" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L47" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M47" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N47" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O47" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4474,10 +4482,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4487,84 +4493,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C48" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D48" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E48" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F48" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H48" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I48" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J48" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K48" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L48" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M48" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N48" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O48" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4582,50 +4578,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C49" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D49" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E49" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F49" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H49" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I49" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J49" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K49" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L49" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M49" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N49" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O49" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4633,18 +4629,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4657,55 +4653,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C50" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D50" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E50" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F50" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H50" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I50" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J50" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K50" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L50" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M50" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N50" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O50" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4713,18 +4713,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4737,59 +4737,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C51" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D51" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E51" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H51" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I51" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J51" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K51" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L51" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M51" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N51" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O51" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4799,12 +4795,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4826,50 +4822,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C52" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D52" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E52" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F52" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H52" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I52" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J52" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K52" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L52" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M52" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N52" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O52" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4877,14 +4873,12 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4901,72 +4895,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C53" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D53" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E53" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F53" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H53" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I53" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J53" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K53" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L53" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M53" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N53" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O53" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4981,145 +4985,141 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C54" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D54" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E54" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F54" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H54" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I54" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J54" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K54" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L54" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M54" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N54" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O54" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C55" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D55" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E55" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F55" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H55" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I55" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J55" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K55" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L55" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M55" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N55" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O55" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5130,25 +5130,19 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5160,50 +5154,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C56" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D56" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E56" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F56" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H56" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I56" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J56" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K56" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L56" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M56" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N56" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O56" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,22 +5205,30 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5238,50 +5240,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C57" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D57" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E57" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H57" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I57" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J57" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K57" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L57" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N57" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O57" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5289,30 +5291,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5324,50 +5320,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C58" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E58" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F58" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H58" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I58" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J58" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K58" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L58" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N58" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O58" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5378,21 +5374,25 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5404,50 +5404,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C59" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F59" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H59" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I59" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J59" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K59" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M59" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N59" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O59" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5460,78 +5460,76 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C60" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D60" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E60" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F60" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I60" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J60" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K60" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L60" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M60" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N60" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O60" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5539,12 +5537,14 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5570,50 +5570,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C61" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D61" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E61" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F61" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H61" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I61" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J61" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K61" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L61" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M61" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N61" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O61" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5621,18 +5621,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5645,59 +5645,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C62" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D62" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E62" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F62" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H62" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I62" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J62" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L62" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M62" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N62" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O62" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5710,12 +5706,12 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U62" s="8" t="n">
@@ -5729,55 +5725,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C63" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D63" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E63" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F63" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H63" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I63" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J63" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K63" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L63" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O63" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5788,15 +5788,13 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5811,57 +5809,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C64" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D64" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H64" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I64" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J64" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K64" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L64" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N64" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O64" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5874,11 +5872,13 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5891,78 +5891,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D65" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H65" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I65" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J65" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L65" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M65" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N65" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
       </c>
       <c r="U65" s="8" t="n">
         <v/>
@@ -5970,77 +5968,77 @@
       <c r="V65" s="8" t="n">
         <v/>
       </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="W65" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C66" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D66" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F66" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H66" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I66" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J66" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M66" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N66" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O66" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
       </c>
-      <c r="Q66" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R66" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S66" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T66" s="8" t="n">
@@ -6059,80 +6057,88 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C67" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H67" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I67" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M67" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N67" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O67" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
       </c>
-      <c r="Q67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="n">
-        <v/>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U67" s="8" t="n">
         <v/>
       </c>
-      <c r="V67" s="8" t="n">
-        <v/>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W67" s="11" t="inlineStr">
         <is>
@@ -6141,88 +6147,82 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C68" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D68" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E68" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F68" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H68" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I68" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J68" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L68" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M68" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N68" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O68" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R68" s="6" t="inlineStr">
+      <c r="Q68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U68" s="8" t="n">
         <v/>
       </c>
-      <c r="V68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V68" s="8" t="n">
+        <v/>
       </c>
       <c r="W68" s="11" t="inlineStr">
         <is>
@@ -6231,76 +6231,78 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C69" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D69" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E69" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F69" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H69" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I69" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J69" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N69" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O69" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
       </c>
-      <c r="Q69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R69" s="6" t="n">
-        <v/>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v/>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6313,76 +6315,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C70" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D70" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E70" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F70" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H70" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I70" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J70" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K70" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O70" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R70" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S70" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T70" s="8" t="n">
@@ -6404,50 +6398,50 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C71" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E71" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H71" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I71" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J71" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L71" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M71" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6460,21 +6454,27 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U71" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V71" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W71" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V71" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W71" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
@@ -6482,50 +6482,50 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E72" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F72" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H72" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I72" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J72" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L72" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M72" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N72" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O72" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6538,78 +6538,76 @@
       </c>
       <c r="S72" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V72" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V72" s="8" t="n">
+        <v/>
       </c>
       <c r="W72" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C73" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E73" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F73" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H73" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I73" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N73" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O73" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6620,7 +6618,7 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="7" t="inlineStr">
+      <c r="S73" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -6641,57 +6639,57 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E74" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F74" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H74" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I74" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J74" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L74" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M74" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N74" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O74" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6699,16 +6697,20 @@
       <c r="Q74" s="6" t="n">
         <v/>
       </c>
-      <c r="R74" s="6" t="n">
-        <v/>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6730,56 +6732,58 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C75" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D75" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H75" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I75" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K75" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L75" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M75" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N75" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O75" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="n">
-        <v/>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
@@ -6788,13 +6792,11 @@
       </c>
       <c r="S75" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="n">
+        <v/>
       </c>
       <c r="U75" s="8" t="n">
         <v/>
@@ -6802,79 +6804,73 @@
       <c r="V75" s="8" t="n">
         <v/>
       </c>
-      <c r="W75" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W75" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C76" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D76" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E76" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F76" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H76" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I76" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J76" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K76" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L76" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N76" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
+      <c r="Q76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S76" s="7" t="inlineStr">
+      <c r="S76" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -6898,50 +6894,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C77" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D77" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F77" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H77" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I77" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M77" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N77" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O77" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6949,18 +6945,18 @@
       <c r="Q77" s="6" t="n">
         <v/>
       </c>
-      <c r="R77" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="n">
-        <v/>
+      <c r="R77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6973,75 +6969,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr"/>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C78" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D78" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E78" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F78" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H78" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I78" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J78" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K78" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L78" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M78" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="inlineStr">
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S78" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
+      </c>
       <c r="U78" s="8" t="n">
         <v/>
       </c>
@@ -7053,83 +7055,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C79" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D79" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E79" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F79" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I79" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J79" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N79" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O79" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
       </c>
-      <c r="Q79" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R79" s="6" t="inlineStr">
+      <c r="Q79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U79" s="8" t="n">
-        <v/>
+      <c r="U79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V79" s="8" t="n">
         <v/>
@@ -7139,55 +7137,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr"/>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D80" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E80" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F80" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H80" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I80" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L80" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N80" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O80" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7200,18 +7202,14 @@
       </c>
       <c r="S80" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v/>
       </c>
       <c r="V80" s="8" t="n">
         <v/>
@@ -7230,63 +7228,69 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C81" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D81" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E81" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F81" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H81" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I81" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J81" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K81" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L81" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M81" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N81" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O81" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P81" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q81" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R81" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>77914.31</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S81" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T81" s="8" t="n">
@@ -7303,149 +7307,153 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C82" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D82" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E82" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F82" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H82" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I82" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J82" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K82" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L82" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M82" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O82" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P82" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q82" s="6" t="inlineStr">
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V82" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W82" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="W82" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>76830.28</v>
+        <v>78162.48</v>
       </c>
       <c r="C83" t="n">
-        <v>79568.95</v>
+        <v>78242.55</v>
       </c>
       <c r="D83" t="n">
-        <v>76367.38</v>
+        <v>74944.59</v>
       </c>
       <c r="E83" t="n">
-        <v>78163.38</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>1325.23</v>
+        <v>-2550.88</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0326</v>
       </c>
       <c r="H83" t="n">
-        <v>3201.58</v>
+        <v>3297.95</v>
       </c>
       <c r="I83" t="n">
-        <v>75581.11</v>
+        <v>73165.8</v>
       </c>
       <c r="J83" t="n">
-        <v>75861.45</v>
+        <v>75059.41</v>
       </c>
       <c r="K83" t="n">
-        <v>76379.52</v>
+        <v>76562.59</v>
       </c>
       <c r="L83" t="n">
-        <v>76897.59</v>
+        <v>78065.77</v>
       </c>
       <c r="M83" t="n">
-        <v>77296.78999999999</v>
+        <v>79764.17</v>
       </c>
       <c r="N83" t="n">
-        <v>77696</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>78332.92999999999</v>
+        <v>82770.53</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
       </c>
-      <c r="Q83" s="6" t="n">
-        <v/>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
@@ -7454,23 +7462,17 @@
       </c>
       <c r="S83" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V83" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U83" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V83" s="8" t="n">
+        <v/>
       </c>
       <c r="W83" s="9" t="inlineStr">
         <is>
@@ -7479,74 +7481,70 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>78162.48</v>
+        <v>75611.8</v>
       </c>
       <c r="C84" t="n">
-        <v>78242.55</v>
+        <v>76474.08</v>
       </c>
       <c r="D84" t="n">
-        <v>74944.59</v>
+        <v>74995.52</v>
       </c>
       <c r="E84" t="n">
-        <v>75612.50999999999</v>
+        <v>76150.32000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>-2550.88</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0071</v>
       </c>
       <c r="H84" t="n">
-        <v>3297.95</v>
+        <v>1478.55</v>
       </c>
       <c r="I84" t="n">
-        <v>73165.8</v>
+        <v>71646.64</v>
       </c>
       <c r="J84" t="n">
-        <v>75059.41</v>
+        <v>71824.02</v>
       </c>
       <c r="K84" t="n">
-        <v>76562.59</v>
+        <v>73963.53</v>
       </c>
       <c r="L84" t="n">
-        <v>78065.77</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="M84" t="n">
-        <v>79764.17</v>
+        <v>77261.48</v>
       </c>
       <c r="N84" t="n">
-        <v>81462.57000000001</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="O84" t="n">
-        <v>82770.53</v>
+        <v>81540.5</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R84" s="6" t="n">
+        <v/>
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T84" s="8" t="n">
@@ -7565,57 +7563,57 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>75611.8</v>
+        <v>76152.05</v>
       </c>
       <c r="C85" t="n">
-        <v>76474.08</v>
+        <v>77079.16</v>
       </c>
       <c r="D85" t="n">
-        <v>74995.52</v>
+        <v>75945.55</v>
       </c>
       <c r="E85" t="n">
-        <v>76150.32000000001</v>
+        <v>76403.77</v>
       </c>
       <c r="F85" t="n">
-        <v>537.8099999999999</v>
+        <v>253.45</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0033</v>
       </c>
       <c r="H85" t="n">
-        <v>1478.55</v>
+        <v>1133.61</v>
       </c>
       <c r="I85" t="n">
-        <v>71646.64</v>
+        <v>73516.97</v>
       </c>
       <c r="J85" t="n">
-        <v>71824.02</v>
+        <v>74879.53</v>
       </c>
       <c r="K85" t="n">
-        <v>73963.53</v>
+        <v>75411.03999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>76103.03999999999</v>
+        <v>75942.56</v>
       </c>
       <c r="M85" t="n">
-        <v>77261.48</v>
+        <v>76889.60000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>78419.92999999999</v>
+        <v>77836.63</v>
       </c>
       <c r="O85" t="n">
-        <v>81540.5</v>
+        <v>77952.63</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7626,13 +7624,15 @@
       <c r="R85" s="6" t="n">
         <v/>
       </c>
-      <c r="S85" s="10" t="inlineStr">
+      <c r="S85" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T85" s="8" t="n">
-        <v/>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U85" s="8" t="n">
         <v/>
@@ -7645,59 +7645,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>76152.05</v>
+        <v>76405.02</v>
       </c>
       <c r="C86" t="n">
-        <v>77079.16</v>
+        <v>81331.77</v>
       </c>
       <c r="D86" t="n">
-        <v>75945.55</v>
+        <v>76228.33</v>
       </c>
       <c r="E86" t="n">
-        <v>76403.77</v>
+        <v>80901.46000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>253.45</v>
+        <v>4497.69</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0589</v>
       </c>
       <c r="H86" t="n">
-        <v>1133.61</v>
+        <v>5103.44</v>
       </c>
       <c r="I86" t="n">
-        <v>73516.97</v>
+        <v>74811.95</v>
       </c>
       <c r="J86" t="n">
-        <v>74879.53</v>
+        <v>75215.87</v>
       </c>
       <c r="K86" t="n">
-        <v>75411.03999999999</v>
+        <v>75836.97</v>
       </c>
       <c r="L86" t="n">
-        <v>75942.56</v>
+        <v>76458.07000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>76889.60000000001</v>
+        <v>76970.58</v>
       </c>
       <c r="N86" t="n">
-        <v>77836.63</v>
+        <v>77483.09</v>
       </c>
       <c r="O86" t="n">
-        <v>77952.63</v>
+        <v>78212.77</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7708,9 +7704,9 @@
       <c r="R86" s="6" t="n">
         <v/>
       </c>
-      <c r="S86" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T86" s="8" t="inlineStr">
@@ -7718,11 +7714,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U86" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V86" s="8" t="n">
-        <v/>
+      <c r="U86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V86" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W86" s="9" t="inlineStr">
         <is>
@@ -7734,50 +7734,50 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>76405.02</v>
+        <v>80900.28999999999</v>
       </c>
       <c r="C87" t="n">
-        <v>81331.77</v>
+        <v>81911.14</v>
       </c>
       <c r="D87" t="n">
-        <v>76228.33</v>
+        <v>80814.94</v>
       </c>
       <c r="E87" t="n">
-        <v>80901.46000000001</v>
+        <v>81233.67999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>4497.69</v>
+        <v>332.22</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0589</v>
+        <v>0.0041</v>
       </c>
       <c r="H87" t="n">
-        <v>5103.44</v>
+        <v>1096.2</v>
       </c>
       <c r="I87" t="n">
-        <v>74811.95</v>
+        <v>71124.89</v>
       </c>
       <c r="J87" t="n">
-        <v>75215.87</v>
+        <v>76858.73</v>
       </c>
       <c r="K87" t="n">
-        <v>75836.97</v>
+        <v>78349.74000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>76458.07000000001</v>
+        <v>79840.75</v>
       </c>
       <c r="M87" t="n">
-        <v>76970.58</v>
+        <v>83453.17999999999</v>
       </c>
       <c r="N87" t="n">
-        <v>77483.09</v>
+        <v>87065.61</v>
       </c>
       <c r="O87" t="n">
-        <v>78212.77</v>
+        <v>86435.2</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7788,25 +7788,19 @@
       <c r="R87" s="6" t="n">
         <v/>
       </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
       </c>
       <c r="W87" s="9" t="inlineStr">
         <is>
@@ -7818,50 +7812,50 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>80900.28999999999</v>
+        <v>81234.3</v>
       </c>
       <c r="C88" t="n">
-        <v>81911.14</v>
+        <v>81455.2</v>
       </c>
       <c r="D88" t="n">
-        <v>80814.94</v>
+        <v>80098.77</v>
       </c>
       <c r="E88" t="n">
-        <v>81233.67999999999</v>
+        <v>81142.61</v>
       </c>
       <c r="F88" t="n">
-        <v>332.22</v>
+        <v>-91.06999999999999</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0011</v>
       </c>
       <c r="H88" t="n">
-        <v>1096.2</v>
+        <v>1356.43</v>
       </c>
       <c r="I88" t="n">
-        <v>71124.89</v>
+        <v>79718.73</v>
       </c>
       <c r="J88" t="n">
-        <v>76858.73</v>
+        <v>80072.8</v>
       </c>
       <c r="K88" t="n">
-        <v>78349.74000000001</v>
+        <v>80685.58</v>
       </c>
       <c r="L88" t="n">
-        <v>79840.75</v>
+        <v>81298.36</v>
       </c>
       <c r="M88" t="n">
-        <v>83453.17999999999</v>
+        <v>81781.78</v>
       </c>
       <c r="N88" t="n">
-        <v>87065.61</v>
+        <v>82265.2</v>
       </c>
       <c r="O88" t="n">
-        <v>86435.2</v>
+        <v>83007.34</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7869,12 +7863,14 @@
       <c r="Q88" s="6" t="n">
         <v/>
       </c>
-      <c r="R88" s="6" t="n">
-        <v/>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S88" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T88" s="8" t="n">
@@ -7891,55 +7887,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>81234.3</v>
+        <v>81143.62</v>
       </c>
       <c r="C89" t="n">
-        <v>81455.2</v>
+        <v>87363.75999999999</v>
       </c>
       <c r="D89" t="n">
-        <v>80098.77</v>
+        <v>80867.09</v>
       </c>
       <c r="E89" t="n">
-        <v>81142.61</v>
+        <v>86602.91</v>
       </c>
       <c r="F89" t="n">
-        <v>-91.06999999999999</v>
+        <v>5460.3</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0673</v>
       </c>
       <c r="H89" t="n">
-        <v>1356.43</v>
+        <v>6496.67</v>
       </c>
       <c r="I89" t="n">
-        <v>79718.73</v>
+        <v>78742.34</v>
       </c>
       <c r="J89" t="n">
-        <v>80072.8</v>
+        <v>79968.99000000001</v>
       </c>
       <c r="K89" t="n">
-        <v>80685.58</v>
+        <v>80464.39</v>
       </c>
       <c r="L89" t="n">
-        <v>81298.36</v>
+        <v>80959.8</v>
       </c>
       <c r="M89" t="n">
-        <v>81781.78</v>
+        <v>81820.82000000001</v>
       </c>
       <c r="N89" t="n">
-        <v>82265.2</v>
+        <v>82681.85000000001</v>
       </c>
       <c r="O89" t="n">
-        <v>83007.34</v>
+        <v>82811.63</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7947,83 +7947,83 @@
       <c r="Q89" s="6" t="n">
         <v/>
       </c>
-      <c r="R89" s="6" t="inlineStr">
+      <c r="R89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S89" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V89" s="8" t="n">
-        <v/>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>81143.62</v>
+        <v>86195.28</v>
       </c>
       <c r="C90" t="n">
-        <v>87363.75999999999</v>
+        <v>86706.03</v>
       </c>
       <c r="D90" t="n">
-        <v>80867.09</v>
+        <v>86180.16</v>
       </c>
       <c r="E90" t="n">
-        <v>86602.91</v>
+        <v>86402.27</v>
       </c>
       <c r="F90" t="n">
-        <v>5460.3</v>
+        <v>-200.64</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0673</v>
+        <v>-0.0023</v>
       </c>
       <c r="H90" t="n">
-        <v>6496.67</v>
+        <v>525.88</v>
       </c>
       <c r="I90" t="n">
-        <v>78742.34</v>
+        <v>74370.41</v>
       </c>
       <c r="J90" t="n">
-        <v>79968.99000000001</v>
+        <v>81349.99000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>80464.39</v>
+        <v>83354.58</v>
       </c>
       <c r="L90" t="n">
-        <v>80959.8</v>
+        <v>85359.17</v>
       </c>
       <c r="M90" t="n">
-        <v>81820.82000000001</v>
+        <v>89851.25</v>
       </c>
       <c r="N90" t="n">
-        <v>82681.85000000001</v>
+        <v>94343.33</v>
       </c>
       <c r="O90" t="n">
-        <v>82811.63</v>
+        <v>93860.42999999999</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8034,110 +8034,26 @@
       <c r="R90" s="6" t="n">
         <v/>
       </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V90" s="8" t="n">
+        <v/>
       </c>
       <c r="W90" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>86597.82000000001</v>
-      </c>
-      <c r="C91" t="n">
-        <v>86597.82000000001</v>
-      </c>
-      <c r="D91" t="n">
-        <v>85158.69</v>
-      </c>
-      <c r="E91" t="n">
-        <v>86030.86</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-572.05</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.0066</v>
-      </c>
-      <c r="H91" t="n">
-        <v>1439.13</v>
-      </c>
-      <c r="I91" t="n">
-        <v>74370.41</v>
-      </c>
-      <c r="J91" t="n">
-        <v>81349.99000000001</v>
-      </c>
-      <c r="K91" t="n">
-        <v>83354.58</v>
-      </c>
-      <c r="L91" t="n">
-        <v>85359.17</v>
-      </c>
-      <c r="M91" t="n">
-        <v>89851.25</v>
-      </c>
-      <c r="N91" t="n">
-        <v>94343.33</v>
-      </c>
-      <c r="O91" t="n">
-        <v>93860.42999999999</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7993,13 +7993,13 @@
         <v>86180.16</v>
       </c>
       <c r="E90" t="n">
-        <v>86402.27</v>
+        <v>86187.53999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>-200.64</v>
+        <v>-415.38</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0048</v>
       </c>
       <c r="H90" t="n">
         <v>525.88</v>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7993,13 +7993,13 @@
         <v>86180.16</v>
       </c>
       <c r="E90" t="n">
-        <v>86187.53999999999</v>
+        <v>86465.98</v>
       </c>
       <c r="F90" t="n">
-        <v>-415.38</v>
+        <v>-136.94</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0016</v>
       </c>
       <c r="H90" t="n">
         <v>525.88</v>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -7987,22 +7987,22 @@
         <v>86195.28</v>
       </c>
       <c r="C90" t="n">
-        <v>86706.03</v>
+        <v>86740.96000000001</v>
       </c>
       <c r="D90" t="n">
         <v>86180.16</v>
       </c>
       <c r="E90" t="n">
-        <v>86465.98</v>
+        <v>86716.46000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>-136.94</v>
+        <v>113.55</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0013</v>
       </c>
       <c r="H90" t="n">
-        <v>525.88</v>
+        <v>560.8</v>
       </c>
       <c r="I90" t="n">
         <v>74370.41</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7980,29 +7980,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>86195.28</v>
+        <v>86604.38</v>
       </c>
       <c r="C90" t="n">
-        <v>86740.96000000001</v>
+        <v>86700</v>
       </c>
       <c r="D90" t="n">
-        <v>86180.16</v>
+        <v>85098.00999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>86716.46000000001</v>
+        <v>86172.28</v>
       </c>
       <c r="F90" t="n">
-        <v>113.55</v>
+        <v>-430.63</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.005</v>
       </c>
       <c r="H90" t="n">
-        <v>560.8</v>
+        <v>1601.99</v>
       </c>
       <c r="I90" t="n">
         <v>74370.41</v>
@@ -8054,6 +8054,92 @@
         </is>
       </c>
       <c r="X90" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>86195.28</v>
+      </c>
+      <c r="C91" t="n">
+        <v>87243.36</v>
+      </c>
+      <c r="D91" t="n">
+        <v>85272.09</v>
+      </c>
+      <c r="E91" t="n">
+        <v>85449.99000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-722.29</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1971.27</v>
+      </c>
+      <c r="I91" t="n">
+        <v>83496.02</v>
+      </c>
+      <c r="J91" t="n">
+        <v>84706.92999999999</v>
+      </c>
+      <c r="K91" t="n">
+        <v>85371.28999999999</v>
+      </c>
+      <c r="L91" t="n">
+        <v>86035.64</v>
+      </c>
+      <c r="M91" t="n">
+        <v>86973.28</v>
+      </c>
+      <c r="N91" t="n">
+        <v>87910.91</v>
+      </c>
+      <c r="O91" t="n">
+        <v>88301.99000000001</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -8072,19 +8072,19 @@
         <v>87243.36</v>
       </c>
       <c r="D91" t="n">
-        <v>85272.09</v>
+        <v>83785.38</v>
       </c>
       <c r="E91" t="n">
-        <v>85449.99000000001</v>
+        <v>84547.02</v>
       </c>
       <c r="F91" t="n">
-        <v>-722.29</v>
+        <v>-1625.26</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0189</v>
       </c>
       <c r="H91" t="n">
-        <v>1971.27</v>
+        <v>3457.98</v>
       </c>
       <c r="I91" t="n">
         <v>83496.02</v>
@@ -8110,12 +8110,14 @@
       <c r="P91" s="6" t="n">
         <v/>
       </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S91" s="10" t="inlineStr">
@@ -8134,9 +8136,9 @@
       <c r="V91" s="8" t="n">
         <v/>
       </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W91" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">

--- a/three_gate/analysis/BTC_daily.xlsx
+++ b/three_gate/analysis/BTC_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59712.05</v>
+        <v>60016.31</v>
       </c>
       <c r="C2" t="n">
-        <v>60647.19</v>
+        <v>60835.05</v>
       </c>
       <c r="D2" t="n">
-        <v>58269.12</v>
+        <v>59794.62</v>
       </c>
       <c r="E2" t="n">
-        <v>60016.43</v>
+        <v>59940.1</v>
       </c>
       <c r="F2" t="n">
-        <v>294.75</v>
+        <v>-76.33</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0013</v>
       </c>
       <c r="H2" t="n">
-        <v>2378.06</v>
+        <v>1040.43</v>
       </c>
       <c r="I2" t="n">
-        <v>54282.94</v>
+        <v>55891.06</v>
       </c>
       <c r="J2" t="n">
-        <v>55803.32</v>
+        <v>57917.5</v>
       </c>
       <c r="K2" t="n">
-        <v>57825.18</v>
+        <v>58827.4</v>
       </c>
       <c r="L2" t="n">
-        <v>59847.04</v>
+        <v>59737.29</v>
       </c>
       <c r="M2" t="n">
-        <v>61618.17</v>
+        <v>61205.46</v>
       </c>
       <c r="N2" t="n">
-        <v>63389.29</v>
+        <v>62673.63</v>
       </c>
       <c r="O2" t="n">
-        <v>65661.89</v>
+        <v>63025.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -716,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60016.31</v>
+        <v>59940.35</v>
       </c>
       <c r="C3" t="n">
-        <v>60835.05</v>
+        <v>60432.71</v>
       </c>
       <c r="D3" t="n">
-        <v>59794.62</v>
+        <v>58879.63</v>
       </c>
       <c r="E3" t="n">
-        <v>59940.1</v>
+        <v>59532.34</v>
       </c>
       <c r="F3" t="n">
-        <v>-76.33</v>
+        <v>-407.76</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0068</v>
       </c>
       <c r="H3" t="n">
-        <v>1040.43</v>
+        <v>1553.07</v>
       </c>
       <c r="I3" t="n">
-        <v>55891.06</v>
+        <v>58754.2</v>
       </c>
       <c r="J3" t="n">
-        <v>57917.5</v>
+        <v>58712.3</v>
       </c>
       <c r="K3" t="n">
-        <v>58827.4</v>
+        <v>59419.88</v>
       </c>
       <c r="L3" t="n">
-        <v>59737.29</v>
+        <v>60127.47</v>
       </c>
       <c r="M3" t="n">
-        <v>61205.46</v>
+        <v>60460.31</v>
       </c>
       <c r="N3" t="n">
-        <v>62673.63</v>
+        <v>60793.16</v>
       </c>
       <c r="O3" t="n">
-        <v>63025.25</v>
+        <v>61875.47</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,12 +767,14 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -791,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59940.35</v>
+        <v>59522.79</v>
       </c>
       <c r="C4" t="n">
-        <v>60432.71</v>
+        <v>60682.34</v>
       </c>
       <c r="D4" t="n">
-        <v>58879.63</v>
+        <v>58856.19</v>
       </c>
       <c r="E4" t="n">
-        <v>59532.34</v>
+        <v>60138.38</v>
       </c>
       <c r="F4" t="n">
-        <v>-407.76</v>
+        <v>606.04</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>1553.07</v>
+        <v>1826.15</v>
       </c>
       <c r="I4" t="n">
-        <v>58754.2</v>
+        <v>57326.56</v>
       </c>
       <c r="J4" t="n">
-        <v>58712.3</v>
+        <v>57917.35</v>
       </c>
       <c r="K4" t="n">
-        <v>59419.88</v>
+        <v>58755.8</v>
       </c>
       <c r="L4" t="n">
-        <v>60127.47</v>
+        <v>59594.25</v>
       </c>
       <c r="M4" t="n">
-        <v>60460.31</v>
+        <v>60308.88</v>
       </c>
       <c r="N4" t="n">
-        <v>60793.16</v>
+        <v>61023.5</v>
       </c>
       <c r="O4" t="n">
-        <v>61875.47</v>
+        <v>61985.78</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,19 +851,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -875,77 +877,79 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59522.79</v>
+        <v>60136.45</v>
       </c>
       <c r="C5" t="n">
-        <v>60682.34</v>
+        <v>60173.22</v>
       </c>
       <c r="D5" t="n">
-        <v>58856.19</v>
+        <v>58111.67</v>
       </c>
       <c r="E5" t="n">
-        <v>60138.38</v>
+        <v>58558.86</v>
       </c>
       <c r="F5" t="n">
-        <v>606.04</v>
+        <v>-1579.52</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0263</v>
       </c>
       <c r="H5" t="n">
-        <v>1826.15</v>
+        <v>2061.55</v>
       </c>
       <c r="I5" t="n">
-        <v>57326.56</v>
+        <v>57030.04</v>
       </c>
       <c r="J5" t="n">
-        <v>57917.35</v>
+        <v>58496.78</v>
       </c>
       <c r="K5" t="n">
-        <v>58755.8</v>
+        <v>59225.3</v>
       </c>
       <c r="L5" t="n">
-        <v>59594.25</v>
+        <v>59953.82</v>
       </c>
       <c r="M5" t="n">
-        <v>60308.88</v>
+        <v>61051.46</v>
       </c>
       <c r="N5" t="n">
-        <v>61023.5</v>
+        <v>62149.09</v>
       </c>
       <c r="O5" t="n">
-        <v>61985.78</v>
+        <v>62508.49</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -959,82 +963,82 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60136.45</v>
+        <v>58562.45</v>
       </c>
       <c r="C6" t="n">
-        <v>60173.22</v>
+        <v>61223.77</v>
       </c>
       <c r="D6" t="n">
-        <v>58111.67</v>
+        <v>57747.77</v>
       </c>
       <c r="E6" t="n">
-        <v>58558.86</v>
+        <v>60003.76</v>
       </c>
       <c r="F6" t="n">
-        <v>-1579.52</v>
+        <v>1444.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.0247</v>
       </c>
       <c r="H6" t="n">
-        <v>2061.55</v>
+        <v>3476</v>
       </c>
       <c r="I6" t="n">
-        <v>57030.04</v>
+        <v>56050.12</v>
       </c>
       <c r="J6" t="n">
-        <v>58496.78</v>
+        <v>56205.52</v>
       </c>
       <c r="K6" t="n">
-        <v>59225.3</v>
+        <v>57528.09</v>
       </c>
       <c r="L6" t="n">
-        <v>59953.82</v>
+        <v>58850.65</v>
       </c>
       <c r="M6" t="n">
-        <v>61051.46</v>
+        <v>59589.63</v>
       </c>
       <c r="N6" t="n">
-        <v>62149.09</v>
+        <v>60328.61</v>
       </c>
       <c r="O6" t="n">
-        <v>62508.49</v>
+        <v>62234.77</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1045,57 +1049,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58562.45</v>
+        <v>60004.77</v>
       </c>
       <c r="C7" t="n">
-        <v>61223.77</v>
+        <v>62117.88</v>
       </c>
       <c r="D7" t="n">
-        <v>57747.77</v>
+        <v>59532.32</v>
       </c>
       <c r="E7" t="n">
-        <v>60003.76</v>
+        <v>61485.3</v>
       </c>
       <c r="F7" t="n">
-        <v>1444.9</v>
+        <v>1481.54</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.0247</v>
       </c>
       <c r="H7" t="n">
-        <v>3476</v>
+        <v>2585.55</v>
       </c>
       <c r="I7" t="n">
-        <v>56050.12</v>
+        <v>54271.76</v>
       </c>
       <c r="J7" t="n">
-        <v>56205.52</v>
+        <v>56786.75</v>
       </c>
       <c r="K7" t="n">
-        <v>57528.09</v>
+        <v>58265.76</v>
       </c>
       <c r="L7" t="n">
-        <v>58850.65</v>
+        <v>59744.76</v>
       </c>
       <c r="M7" t="n">
-        <v>59589.63</v>
+        <v>61741.76</v>
       </c>
       <c r="N7" t="n">
-        <v>60328.61</v>
+        <v>63738.76</v>
       </c>
       <c r="O7" t="n">
-        <v>62234.77</v>
+        <v>64699.77</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1113,14 +1117,12 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1129,59 +1131,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60004.77</v>
+        <v>61492.07</v>
       </c>
       <c r="C8" t="n">
-        <v>62117.88</v>
+        <v>62879.01</v>
       </c>
       <c r="D8" t="n">
-        <v>59532.32</v>
+        <v>61176.72</v>
       </c>
       <c r="E8" t="n">
-        <v>61485.3</v>
+        <v>62544.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1481.54</v>
+        <v>1058.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0172</v>
       </c>
       <c r="H8" t="n">
-        <v>2585.55</v>
+        <v>1702.29</v>
       </c>
       <c r="I8" t="n">
-        <v>54271.76</v>
+        <v>56946.77</v>
       </c>
       <c r="J8" t="n">
-        <v>56786.75</v>
+        <v>59229.85</v>
       </c>
       <c r="K8" t="n">
-        <v>58265.76</v>
+        <v>60192.53</v>
       </c>
       <c r="L8" t="n">
-        <v>59744.76</v>
+        <v>61155.2</v>
       </c>
       <c r="M8" t="n">
-        <v>61741.76</v>
+        <v>62778.08</v>
       </c>
       <c r="N8" t="n">
-        <v>63738.76</v>
+        <v>64400.95</v>
       </c>
       <c r="O8" t="n">
-        <v>64699.77</v>
+        <v>64703.43</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1218,50 +1216,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61492.07</v>
+        <v>62545.13</v>
       </c>
       <c r="C9" t="n">
-        <v>62879.01</v>
+        <v>63398.41</v>
       </c>
       <c r="D9" t="n">
-        <v>61176.72</v>
+        <v>62287.59</v>
       </c>
       <c r="E9" t="n">
-        <v>62544.2</v>
+        <v>63088.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1058.9</v>
+        <v>544.11</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1702.29</v>
+        <v>1110.82</v>
       </c>
       <c r="I9" t="n">
-        <v>56946.77</v>
+        <v>59474.44</v>
       </c>
       <c r="J9" t="n">
-        <v>59229.85</v>
+        <v>61100.08</v>
       </c>
       <c r="K9" t="n">
-        <v>60192.53</v>
+        <v>61693.06</v>
       </c>
       <c r="L9" t="n">
-        <v>61155.2</v>
+        <v>62286.03</v>
       </c>
       <c r="M9" t="n">
-        <v>62778.08</v>
+        <v>63395.34</v>
       </c>
       <c r="N9" t="n">
-        <v>64400.95</v>
+        <v>64504.65</v>
       </c>
       <c r="O9" t="n">
-        <v>64703.43</v>
+        <v>64581.29</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1298,50 +1296,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62545.13</v>
+        <v>63089.06</v>
       </c>
       <c r="C10" t="n">
-        <v>63398.41</v>
+        <v>63935.85</v>
       </c>
       <c r="D10" t="n">
-        <v>62287.59</v>
+        <v>62413.99</v>
       </c>
       <c r="E10" t="n">
-        <v>63088.3</v>
+        <v>63547.88</v>
       </c>
       <c r="F10" t="n">
-        <v>544.11</v>
+        <v>459.58</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="H10" t="n">
-        <v>1110.82</v>
+        <v>1521.86</v>
       </c>
       <c r="I10" t="n">
-        <v>59474.44</v>
+        <v>61176.76</v>
       </c>
       <c r="J10" t="n">
-        <v>61100.08</v>
+        <v>62100.13</v>
       </c>
       <c r="K10" t="n">
-        <v>61693.06</v>
+        <v>62532.89</v>
       </c>
       <c r="L10" t="n">
-        <v>62286.03</v>
+        <v>62965.65</v>
       </c>
       <c r="M10" t="n">
-        <v>63395.34</v>
+        <v>63643.72</v>
       </c>
       <c r="N10" t="n">
-        <v>64504.65</v>
+        <v>64321.78</v>
       </c>
       <c r="O10" t="n">
-        <v>64581.29</v>
+        <v>64509.23</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,8 +1347,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1378,56 +1378,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63089.06</v>
+        <v>63551.02</v>
       </c>
       <c r="C11" t="n">
-        <v>63935.85</v>
+        <v>64597.57</v>
       </c>
       <c r="D11" t="n">
-        <v>62413.99</v>
+        <v>61275.83</v>
       </c>
       <c r="E11" t="n">
-        <v>63547.88</v>
+        <v>63995.02</v>
       </c>
       <c r="F11" t="n">
-        <v>459.58</v>
+        <v>447.13</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.007</v>
       </c>
       <c r="H11" t="n">
-        <v>1521.86</v>
+        <v>3321.74</v>
       </c>
       <c r="I11" t="n">
-        <v>61176.76</v>
+        <v>60892.14</v>
       </c>
       <c r="J11" t="n">
-        <v>62100.13</v>
+        <v>62212.51</v>
       </c>
       <c r="K11" t="n">
-        <v>62532.89</v>
+        <v>62786.96</v>
       </c>
       <c r="L11" t="n">
-        <v>62965.65</v>
+        <v>63361.4</v>
       </c>
       <c r="M11" t="n">
-        <v>63643.72</v>
+        <v>64308.81</v>
       </c>
       <c r="N11" t="n">
-        <v>64321.78</v>
+        <v>65256.22</v>
       </c>
       <c r="O11" t="n">
-        <v>64509.23</v>
+        <v>65457.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
@@ -1455,78 +1457,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63551.02</v>
+        <v>63994.6</v>
       </c>
       <c r="C12" t="n">
-        <v>64597.57</v>
+        <v>64257.63</v>
       </c>
       <c r="D12" t="n">
-        <v>61275.83</v>
+        <v>62623.93</v>
       </c>
       <c r="E12" t="n">
-        <v>63995.02</v>
+        <v>63297.39</v>
       </c>
       <c r="F12" t="n">
-        <v>447.13</v>
+        <v>-697.62</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0109</v>
       </c>
       <c r="H12" t="n">
-        <v>3321.74</v>
+        <v>1633.7</v>
       </c>
       <c r="I12" t="n">
-        <v>60892.14</v>
+        <v>57954.09</v>
       </c>
       <c r="J12" t="n">
-        <v>62212.51</v>
+        <v>61202.43</v>
       </c>
       <c r="K12" t="n">
-        <v>62786.96</v>
+        <v>62334.14</v>
       </c>
       <c r="L12" t="n">
-        <v>63361.4</v>
+        <v>63465.86</v>
       </c>
       <c r="M12" t="n">
-        <v>64308.81</v>
+        <v>65655.89</v>
       </c>
       <c r="N12" t="n">
-        <v>65256.22</v>
+        <v>67845.92</v>
       </c>
       <c r="O12" t="n">
-        <v>65457.7</v>
+        <v>67919.31</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,70 +1541,74 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63994.6</v>
+        <v>63293.52</v>
       </c>
       <c r="C13" t="n">
-        <v>64257.63</v>
+        <v>63706.89</v>
       </c>
       <c r="D13" t="n">
-        <v>62623.93</v>
+        <v>61492.65</v>
       </c>
       <c r="E13" t="n">
-        <v>63297.39</v>
+        <v>62257.57</v>
       </c>
       <c r="F13" t="n">
-        <v>-697.62</v>
+        <v>-1039.82</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0164</v>
       </c>
       <c r="H13" t="n">
-        <v>1633.7</v>
+        <v>2214.24</v>
       </c>
       <c r="I13" t="n">
-        <v>57954.09</v>
+        <v>60990.23</v>
       </c>
       <c r="J13" t="n">
-        <v>61202.43</v>
+        <v>61592</v>
       </c>
       <c r="K13" t="n">
-        <v>62334.14</v>
+        <v>62480.54</v>
       </c>
       <c r="L13" t="n">
-        <v>63465.86</v>
+        <v>63369.09</v>
       </c>
       <c r="M13" t="n">
-        <v>65655.89</v>
+        <v>64114.24</v>
       </c>
       <c r="N13" t="n">
-        <v>67845.92</v>
+        <v>64859.4</v>
       </c>
       <c r="O13" t="n">
-        <v>67919.31</v>
+        <v>65891.33</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1623,79 +1627,77 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63293.52</v>
+        <v>62257.32</v>
       </c>
       <c r="C14" t="n">
-        <v>63706.89</v>
+        <v>63422.94</v>
       </c>
       <c r="D14" t="n">
-        <v>61492.65</v>
+        <v>61645.75</v>
       </c>
       <c r="E14" t="n">
-        <v>62257.57</v>
+        <v>63193.15</v>
       </c>
       <c r="F14" t="n">
-        <v>-1039.82</v>
+        <v>935.5700000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.015</v>
       </c>
       <c r="H14" t="n">
-        <v>2214.24</v>
+        <v>1777.19</v>
       </c>
       <c r="I14" t="n">
-        <v>60990.23</v>
+        <v>59278.41</v>
       </c>
       <c r="J14" t="n">
-        <v>61592</v>
+        <v>59872.24</v>
       </c>
       <c r="K14" t="n">
-        <v>62480.54</v>
+        <v>61150.46</v>
       </c>
       <c r="L14" t="n">
-        <v>63369.09</v>
+        <v>62428.67</v>
       </c>
       <c r="M14" t="n">
-        <v>64114.24</v>
+        <v>63364.69</v>
       </c>
       <c r="N14" t="n">
-        <v>64859.4</v>
+        <v>64300.72</v>
       </c>
       <c r="O14" t="n">
-        <v>65891.33</v>
+        <v>65921.12</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1709,57 +1711,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62257.32</v>
+        <v>63194.36</v>
       </c>
       <c r="C15" t="n">
-        <v>63422.94</v>
+        <v>64658.97</v>
       </c>
       <c r="D15" t="n">
-        <v>61645.75</v>
+        <v>62902.06</v>
       </c>
       <c r="E15" t="n">
-        <v>63193.15</v>
+        <v>64127.14</v>
       </c>
       <c r="F15" t="n">
-        <v>935.5700000000001</v>
+        <v>933.99</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="H15" t="n">
-        <v>1777.19</v>
+        <v>1756.91</v>
       </c>
       <c r="I15" t="n">
-        <v>59278.41</v>
+        <v>59868.57</v>
       </c>
       <c r="J15" t="n">
-        <v>59872.24</v>
+        <v>61745.36</v>
       </c>
       <c r="K15" t="n">
-        <v>61150.46</v>
+        <v>62304.55</v>
       </c>
       <c r="L15" t="n">
-        <v>62428.67</v>
+        <v>62863.75</v>
       </c>
       <c r="M15" t="n">
-        <v>63364.69</v>
+        <v>64081.74</v>
       </c>
       <c r="N15" t="n">
-        <v>64300.72</v>
+        <v>65299.74</v>
       </c>
       <c r="O15" t="n">
-        <v>65921.12</v>
+        <v>65200.13</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1791,59 +1793,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63194.36</v>
+        <v>64127.97</v>
       </c>
       <c r="C16" t="n">
-        <v>64658.97</v>
+        <v>64445.46</v>
       </c>
       <c r="D16" t="n">
-        <v>62902.06</v>
+        <v>63785.62</v>
       </c>
       <c r="E16" t="n">
-        <v>64127.14</v>
+        <v>63802.03</v>
       </c>
       <c r="F16" t="n">
-        <v>933.99</v>
+        <v>-325.11</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0051</v>
       </c>
       <c r="H16" t="n">
-        <v>1756.91</v>
+        <v>659.84</v>
       </c>
       <c r="I16" t="n">
-        <v>59868.57</v>
+        <v>61145.16</v>
       </c>
       <c r="J16" t="n">
-        <v>61745.36</v>
+        <v>62543.55</v>
       </c>
       <c r="K16" t="n">
-        <v>62304.55</v>
+        <v>63248.69</v>
       </c>
       <c r="L16" t="n">
-        <v>62863.75</v>
+        <v>63953.83</v>
       </c>
       <c r="M16" t="n">
-        <v>64081.74</v>
+        <v>65005.59</v>
       </c>
       <c r="N16" t="n">
-        <v>65299.74</v>
+        <v>66057.36</v>
       </c>
       <c r="O16" t="n">
-        <v>65200.13</v>
+        <v>66415.88</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,15 +1852,13 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1875,55 +1871,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64127.97</v>
+        <v>63791.4</v>
       </c>
       <c r="C17" t="n">
-        <v>64445.46</v>
+        <v>64243.13</v>
       </c>
       <c r="D17" t="n">
-        <v>63785.62</v>
+        <v>63606.82</v>
       </c>
       <c r="E17" t="n">
-        <v>63802.03</v>
+        <v>63758.22</v>
       </c>
       <c r="F17" t="n">
-        <v>-325.11</v>
+        <v>-43.81</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0051</v>
+        <v>-0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>659.84</v>
+        <v>636.3099999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>61145.16</v>
+        <v>63125.78</v>
       </c>
       <c r="J17" t="n">
-        <v>62543.55</v>
+        <v>62985.43</v>
       </c>
       <c r="K17" t="n">
-        <v>63248.69</v>
+        <v>63472.11</v>
       </c>
       <c r="L17" t="n">
-        <v>63953.83</v>
+        <v>63958.78</v>
       </c>
       <c r="M17" t="n">
-        <v>65005.59</v>
+        <v>64131.95</v>
       </c>
       <c r="N17" t="n">
-        <v>66057.36</v>
+        <v>64305.11</v>
       </c>
       <c r="O17" t="n">
-        <v>66415.88</v>
+        <v>65105.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,8 +1939,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1955,70 +1957,76 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63791.4</v>
+        <v>63757.17</v>
       </c>
       <c r="C18" t="n">
-        <v>64243.13</v>
+        <v>64340.88</v>
       </c>
       <c r="D18" t="n">
-        <v>63606.82</v>
+        <v>61769</v>
       </c>
       <c r="E18" t="n">
-        <v>63758.22</v>
+        <v>62239.12</v>
       </c>
       <c r="F18" t="n">
-        <v>-43.81</v>
+        <v>-1519.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0238</v>
       </c>
       <c r="H18" t="n">
-        <v>636.3099999999999</v>
+        <v>2571.88</v>
       </c>
       <c r="I18" t="n">
-        <v>63125.78</v>
+        <v>62970.52</v>
       </c>
       <c r="J18" t="n">
-        <v>62985.43</v>
+        <v>63038.53</v>
       </c>
       <c r="K18" t="n">
-        <v>63472.11</v>
+        <v>63440.06</v>
       </c>
       <c r="L18" t="n">
-        <v>63958.78</v>
+        <v>63841.6</v>
       </c>
       <c r="M18" t="n">
-        <v>64131.95</v>
+        <v>64076.37</v>
       </c>
       <c r="N18" t="n">
-        <v>64305.11</v>
+        <v>64311.15</v>
       </c>
       <c r="O18" t="n">
-        <v>65105.3</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>64879.44</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2026,162 +2034,154 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63757.17</v>
+        <v>62238.59</v>
       </c>
       <c r="C19" t="n">
-        <v>64340.88</v>
+        <v>65046.13</v>
       </c>
       <c r="D19" t="n">
-        <v>61769</v>
+        <v>62207.52</v>
       </c>
       <c r="E19" t="n">
-        <v>62239.12</v>
+        <v>64956.11</v>
       </c>
       <c r="F19" t="n">
-        <v>-1519.1</v>
+        <v>2716.99</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0437</v>
       </c>
       <c r="H19" t="n">
-        <v>2571.88</v>
+        <v>2838.61</v>
       </c>
       <c r="I19" t="n">
-        <v>62970.52</v>
+        <v>59197.12</v>
       </c>
       <c r="J19" t="n">
-        <v>63038.53</v>
+        <v>59259.33</v>
       </c>
       <c r="K19" t="n">
-        <v>63440.06</v>
+        <v>60953.18</v>
       </c>
       <c r="L19" t="n">
-        <v>63841.6</v>
+        <v>62647.03</v>
       </c>
       <c r="M19" t="n">
-        <v>64076.37</v>
+        <v>63525.06</v>
       </c>
       <c r="N19" t="n">
-        <v>64311.15</v>
+        <v>64403.09</v>
       </c>
       <c r="O19" t="n">
-        <v>64879.44</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>66912.77</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62238.59</v>
+        <v>64959.81</v>
       </c>
       <c r="C20" t="n">
-        <v>65046.13</v>
+        <v>65507.59</v>
       </c>
       <c r="D20" t="n">
-        <v>62207.52</v>
+        <v>64442.82</v>
       </c>
       <c r="E20" t="n">
-        <v>64956.11</v>
+        <v>64712.38</v>
       </c>
       <c r="F20" t="n">
-        <v>2716.99</v>
+        <v>-243.74</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0038</v>
       </c>
       <c r="H20" t="n">
-        <v>2838.61</v>
+        <v>1064.77</v>
       </c>
       <c r="I20" t="n">
-        <v>59197.12</v>
+        <v>59368.91</v>
       </c>
       <c r="J20" t="n">
-        <v>59259.33</v>
+        <v>62782.15</v>
       </c>
       <c r="K20" t="n">
-        <v>60953.18</v>
+        <v>63536.81</v>
       </c>
       <c r="L20" t="n">
-        <v>62647.03</v>
+        <v>64291.47</v>
       </c>
       <c r="M20" t="n">
-        <v>63525.06</v>
+        <v>66375.42</v>
       </c>
       <c r="N20" t="n">
-        <v>64403.09</v>
+        <v>68459.37</v>
       </c>
       <c r="O20" t="n">
-        <v>66912.77</v>
+        <v>67884.74000000001</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,18 +2194,14 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2215,68 +2211,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64959.81</v>
+        <v>64713.3</v>
       </c>
       <c r="C21" t="n">
-        <v>65507.59</v>
+        <v>64931.86</v>
       </c>
       <c r="D21" t="n">
-        <v>64442.82</v>
+        <v>63701.8</v>
       </c>
       <c r="E21" t="n">
-        <v>64712.38</v>
+        <v>63789.28</v>
       </c>
       <c r="F21" t="n">
-        <v>-243.74</v>
+        <v>-923.09</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0143</v>
       </c>
       <c r="H21" t="n">
-        <v>1064.77</v>
+        <v>1230.05</v>
       </c>
       <c r="I21" t="n">
-        <v>59368.91</v>
+        <v>63378.05</v>
       </c>
       <c r="J21" t="n">
-        <v>62782.15</v>
+        <v>63516.19</v>
       </c>
       <c r="K21" t="n">
-        <v>63536.81</v>
+        <v>64179.99</v>
       </c>
       <c r="L21" t="n">
-        <v>64291.47</v>
+        <v>64843.79</v>
       </c>
       <c r="M21" t="n">
-        <v>66375.42</v>
+        <v>65244.76</v>
       </c>
       <c r="N21" t="n">
-        <v>68459.37</v>
+        <v>65645.73</v>
       </c>
       <c r="O21" t="n">
-        <v>67884.74000000001</v>
+        <v>66572.37</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2295,65 +2299,63 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64713.3</v>
+        <v>63789.91</v>
       </c>
       <c r="C22" t="n">
-        <v>64931.86</v>
+        <v>64332.02</v>
       </c>
       <c r="D22" t="n">
-        <v>63701.8</v>
+        <v>62489.45</v>
       </c>
       <c r="E22" t="n">
-        <v>63789.28</v>
+        <v>63899.46</v>
       </c>
       <c r="F22" t="n">
-        <v>-923.09</v>
+        <v>110.18</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0017</v>
       </c>
       <c r="H22" t="n">
-        <v>1230.05</v>
+        <v>1842.57</v>
       </c>
       <c r="I22" t="n">
-        <v>63378.05</v>
+        <v>62471.75</v>
       </c>
       <c r="J22" t="n">
-        <v>63516.19</v>
+        <v>62295.46</v>
       </c>
       <c r="K22" t="n">
-        <v>64179.99</v>
+        <v>63174.26</v>
       </c>
       <c r="L22" t="n">
-        <v>64843.79</v>
+        <v>64053.06</v>
       </c>
       <c r="M22" t="n">
-        <v>65244.76</v>
+        <v>64404.31</v>
       </c>
       <c r="N22" t="n">
-        <v>65645.73</v>
+        <v>64755.56</v>
       </c>
       <c r="O22" t="n">
-        <v>66572.37</v>
+        <v>66161.91</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
@@ -2362,7 +2364,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2381,57 +2383,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63789.91</v>
+        <v>63899.18</v>
       </c>
       <c r="C23" t="n">
-        <v>64332.02</v>
+        <v>64816.5</v>
       </c>
       <c r="D23" t="n">
-        <v>62489.45</v>
+        <v>63845.02</v>
       </c>
       <c r="E23" t="n">
-        <v>63899.46</v>
+        <v>64796.6</v>
       </c>
       <c r="F23" t="n">
-        <v>110.18</v>
+        <v>897.14</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="H23" t="n">
-        <v>1842.57</v>
+        <v>971.49</v>
       </c>
       <c r="I23" t="n">
-        <v>62471.75</v>
+        <v>60646.89</v>
       </c>
       <c r="J23" t="n">
-        <v>62295.46</v>
+        <v>62301.26</v>
       </c>
       <c r="K23" t="n">
-        <v>63174.26</v>
+        <v>62978.18</v>
       </c>
       <c r="L23" t="n">
-        <v>64053.06</v>
+        <v>63655.1</v>
       </c>
       <c r="M23" t="n">
-        <v>64404.31</v>
+        <v>64820.74</v>
       </c>
       <c r="N23" t="n">
-        <v>64755.56</v>
+        <v>65986.39</v>
       </c>
       <c r="O23" t="n">
-        <v>66161.91</v>
+        <v>66174.59</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,18 +2441,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2463,59 +2465,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63899.18</v>
+        <v>64799.28</v>
       </c>
       <c r="C24" t="n">
-        <v>64816.5</v>
+        <v>64909.89</v>
       </c>
       <c r="D24" t="n">
-        <v>63845.02</v>
+        <v>64250.91</v>
       </c>
       <c r="E24" t="n">
-        <v>64796.6</v>
+        <v>64690.8</v>
       </c>
       <c r="F24" t="n">
-        <v>897.14</v>
+        <v>-105.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0016</v>
       </c>
       <c r="H24" t="n">
-        <v>971.49</v>
+        <v>658.97</v>
       </c>
       <c r="I24" t="n">
-        <v>60646.89</v>
+        <v>62873.53</v>
       </c>
       <c r="J24" t="n">
-        <v>62301.26</v>
+        <v>64058.03</v>
       </c>
       <c r="K24" t="n">
-        <v>62978.18</v>
+        <v>64310.86</v>
       </c>
       <c r="L24" t="n">
-        <v>63655.1</v>
+        <v>64563.68</v>
       </c>
       <c r="M24" t="n">
-        <v>64820.74</v>
+        <v>65282.35</v>
       </c>
       <c r="N24" t="n">
-        <v>65986.39</v>
+        <v>66001.00999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>66174.59</v>
+        <v>65787.99000000001</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,18 +2521,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2547,61 +2545,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64799.28</v>
+        <v>64684.42</v>
       </c>
       <c r="C25" t="n">
-        <v>64909.89</v>
+        <v>65735.72</v>
       </c>
       <c r="D25" t="n">
-        <v>64250.91</v>
+        <v>63720.39</v>
       </c>
       <c r="E25" t="n">
-        <v>64690.8</v>
+        <v>65230.03</v>
       </c>
       <c r="F25" t="n">
-        <v>-105.8</v>
+        <v>539.22</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0083</v>
       </c>
       <c r="H25" t="n">
-        <v>658.97</v>
+        <v>2015.33</v>
       </c>
       <c r="I25" t="n">
-        <v>62873.53</v>
+        <v>63591.94</v>
       </c>
       <c r="J25" t="n">
-        <v>64058.03</v>
+        <v>64087.03</v>
       </c>
       <c r="K25" t="n">
-        <v>64310.86</v>
+        <v>64361.32</v>
       </c>
       <c r="L25" t="n">
-        <v>64563.68</v>
+        <v>64635.6</v>
       </c>
       <c r="M25" t="n">
-        <v>65282.35</v>
+        <v>65020.29</v>
       </c>
       <c r="N25" t="n">
-        <v>66001.00999999999</v>
+        <v>65404.98</v>
       </c>
       <c r="O25" t="n">
-        <v>65787.99000000001</v>
+        <v>65568.86</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2610,17 +2614,23 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2636,63 +2646,59 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64684.42</v>
+        <v>65228.87</v>
       </c>
       <c r="C26" t="n">
-        <v>65735.72</v>
+        <v>66910.06</v>
       </c>
       <c r="D26" t="n">
-        <v>63720.39</v>
+        <v>65113.66</v>
       </c>
       <c r="E26" t="n">
-        <v>65230.03</v>
+        <v>66505.12</v>
       </c>
       <c r="F26" t="n">
-        <v>539.22</v>
+        <v>1275.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0195</v>
       </c>
       <c r="H26" t="n">
-        <v>2015.33</v>
+        <v>1796.41</v>
       </c>
       <c r="I26" t="n">
-        <v>63591.94</v>
+        <v>61705.06</v>
       </c>
       <c r="J26" t="n">
-        <v>64087.03</v>
+        <v>63465.69</v>
       </c>
       <c r="K26" t="n">
-        <v>64361.32</v>
+        <v>64222.36</v>
       </c>
       <c r="L26" t="n">
-        <v>64635.6</v>
+        <v>64979.04</v>
       </c>
       <c r="M26" t="n">
-        <v>65020.29</v>
+        <v>66237.69</v>
       </c>
       <c r="N26" t="n">
-        <v>65404.98</v>
+        <v>67496.34</v>
       </c>
       <c r="O26" t="n">
-        <v>65568.86</v>
+        <v>67751.05</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
@@ -2701,77 +2707,69 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65228.87</v>
+        <v>66506.78999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>66910.06</v>
+        <v>66694.64999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>65113.66</v>
+        <v>65514.18</v>
       </c>
       <c r="E27" t="n">
-        <v>66505.12</v>
+        <v>66100.8</v>
       </c>
       <c r="F27" t="n">
-        <v>1275.1</v>
+        <v>-404.33</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0195</v>
+        <v>-0.0061</v>
       </c>
       <c r="H27" t="n">
-        <v>1796.41</v>
+        <v>1180.47</v>
       </c>
       <c r="I27" t="n">
-        <v>61705.06</v>
+        <v>63317.25</v>
       </c>
       <c r="J27" t="n">
-        <v>63465.69</v>
+        <v>64955.35</v>
       </c>
       <c r="K27" t="n">
-        <v>64222.36</v>
+        <v>65606.92</v>
       </c>
       <c r="L27" t="n">
-        <v>64979.04</v>
+        <v>66258.49000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>66237.69</v>
+        <v>67403.33</v>
       </c>
       <c r="N27" t="n">
-        <v>67496.34</v>
+        <v>68548.16</v>
       </c>
       <c r="O27" t="n">
-        <v>67751.05</v>
+        <v>68706.47</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2779,18 +2777,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2803,61 +2801,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66506.78999999999</v>
+        <v>66100.13</v>
       </c>
       <c r="C28" t="n">
-        <v>66694.64999999999</v>
+        <v>66282.38</v>
       </c>
       <c r="D28" t="n">
-        <v>65514.18</v>
+        <v>64610.61</v>
       </c>
       <c r="E28" t="n">
-        <v>66100.8</v>
+        <v>65044.81</v>
       </c>
       <c r="F28" t="n">
-        <v>-404.33</v>
+        <v>-1055.98</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.016</v>
       </c>
       <c r="H28" t="n">
-        <v>1180.47</v>
+        <v>1671.77</v>
       </c>
       <c r="I28" t="n">
-        <v>63317.25</v>
+        <v>64333.7</v>
       </c>
       <c r="J28" t="n">
-        <v>64955.35</v>
+        <v>64918.52</v>
       </c>
       <c r="K28" t="n">
-        <v>65606.92</v>
+        <v>65510.56</v>
       </c>
       <c r="L28" t="n">
-        <v>66258.49000000001</v>
+        <v>66102.60000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>67403.33</v>
+        <v>66691.03</v>
       </c>
       <c r="N28" t="n">
-        <v>68548.16</v>
+        <v>67279.46000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>68706.47</v>
+        <v>67875.12</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2866,7 +2870,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2885,69 +2889,67 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66100.13</v>
+        <v>65044.96</v>
       </c>
       <c r="C29" t="n">
-        <v>66282.38</v>
+        <v>65760.48</v>
       </c>
       <c r="D29" t="n">
-        <v>64610.61</v>
+        <v>63686.04</v>
       </c>
       <c r="E29" t="n">
-        <v>65044.81</v>
+        <v>64098.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-1055.98</v>
+        <v>-946.3200000000001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0145</v>
       </c>
       <c r="H29" t="n">
-        <v>1671.77</v>
+        <v>2074.45</v>
       </c>
       <c r="I29" t="n">
-        <v>64333.7</v>
+        <v>62938.84</v>
       </c>
       <c r="J29" t="n">
-        <v>64918.52</v>
+        <v>63172.2</v>
       </c>
       <c r="K29" t="n">
-        <v>65510.56</v>
+        <v>64208.93</v>
       </c>
       <c r="L29" t="n">
-        <v>66102.60000000001</v>
+        <v>65245.65</v>
       </c>
       <c r="M29" t="n">
-        <v>66691.03</v>
+        <v>65880.7</v>
       </c>
       <c r="N29" t="n">
-        <v>67279.46000000001</v>
+        <v>66515.74000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>67875.12</v>
+        <v>67954.16</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -2978,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65044.96</v>
+        <v>64098.49</v>
       </c>
       <c r="C30" t="n">
-        <v>65760.48</v>
+        <v>64386.06</v>
       </c>
       <c r="D30" t="n">
-        <v>63686.04</v>
+        <v>63753.03</v>
       </c>
       <c r="E30" t="n">
-        <v>64098.5</v>
+        <v>64311.81</v>
       </c>
       <c r="F30" t="n">
-        <v>-946.3200000000001</v>
+        <v>213.32</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0033</v>
       </c>
       <c r="H30" t="n">
-        <v>2074.45</v>
+        <v>633.04</v>
       </c>
       <c r="I30" t="n">
-        <v>62938.84</v>
+        <v>61611.59</v>
       </c>
       <c r="J30" t="n">
-        <v>63172.2</v>
+        <v>61711.67</v>
       </c>
       <c r="K30" t="n">
-        <v>64208.93</v>
+        <v>63061.27</v>
       </c>
       <c r="L30" t="n">
-        <v>65245.65</v>
+        <v>64410.88</v>
       </c>
       <c r="M30" t="n">
-        <v>65880.7</v>
+        <v>65135.72</v>
       </c>
       <c r="N30" t="n">
-        <v>66515.74000000001</v>
+        <v>65860.56</v>
       </c>
       <c r="O30" t="n">
-        <v>67954.16</v>
+        <v>67834.92999999999</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3029,14 +3031,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3055,57 +3055,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64098.49</v>
+        <v>64311.79</v>
       </c>
       <c r="C31" t="n">
-        <v>64386.06</v>
+        <v>65503.77</v>
       </c>
       <c r="D31" t="n">
-        <v>63753.03</v>
+        <v>64233.45</v>
       </c>
       <c r="E31" t="n">
-        <v>64311.81</v>
+        <v>65340.3</v>
       </c>
       <c r="F31" t="n">
-        <v>213.32</v>
+        <v>1028.49</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="H31" t="n">
-        <v>633.04</v>
+        <v>1270.32</v>
       </c>
       <c r="I31" t="n">
-        <v>61611.59</v>
+        <v>63119.99</v>
       </c>
       <c r="J31" t="n">
-        <v>61711.67</v>
+        <v>63799.91</v>
       </c>
       <c r="K31" t="n">
-        <v>63061.27</v>
+        <v>63995.29</v>
       </c>
       <c r="L31" t="n">
-        <v>64410.88</v>
+        <v>64190.68</v>
       </c>
       <c r="M31" t="n">
-        <v>65135.72</v>
+        <v>64628.33</v>
       </c>
       <c r="N31" t="n">
-        <v>65860.56</v>
+        <v>65065.98</v>
       </c>
       <c r="O31" t="n">
-        <v>67834.92999999999</v>
+        <v>65019.1</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3116,179 +3116,179 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64311.79</v>
+        <v>65340.59</v>
       </c>
       <c r="C32" t="n">
-        <v>65503.77</v>
+        <v>65658.34</v>
       </c>
       <c r="D32" t="n">
-        <v>64233.45</v>
+        <v>63562.48</v>
       </c>
       <c r="E32" t="n">
-        <v>65340.3</v>
+        <v>63724.9</v>
       </c>
       <c r="F32" t="n">
-        <v>1028.49</v>
+        <v>-1615.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0247</v>
       </c>
       <c r="H32" t="n">
-        <v>1270.32</v>
+        <v>2095.85</v>
       </c>
       <c r="I32" t="n">
-        <v>63119.99</v>
+        <v>62963.14</v>
       </c>
       <c r="J32" t="n">
-        <v>63799.91</v>
+        <v>64305.83</v>
       </c>
       <c r="K32" t="n">
-        <v>63995.29</v>
+        <v>64705.14</v>
       </c>
       <c r="L32" t="n">
-        <v>64190.68</v>
+        <v>65104.46</v>
       </c>
       <c r="M32" t="n">
-        <v>64628.33</v>
+        <v>65975.46000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>65065.98</v>
+        <v>66846.46000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>65019.1</v>
+        <v>66774.09</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65340.59</v>
+        <v>63723.49</v>
       </c>
       <c r="C33" t="n">
-        <v>65658.34</v>
+        <v>64026.92</v>
       </c>
       <c r="D33" t="n">
-        <v>63562.48</v>
+        <v>62714.8</v>
       </c>
       <c r="E33" t="n">
-        <v>63724.9</v>
+        <v>63871.36</v>
       </c>
       <c r="F33" t="n">
-        <v>-1615.4</v>
+        <v>146.46</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0023</v>
       </c>
       <c r="H33" t="n">
-        <v>2095.85</v>
+        <v>1312.12</v>
       </c>
       <c r="I33" t="n">
-        <v>62963.14</v>
+        <v>61466.63</v>
       </c>
       <c r="J33" t="n">
-        <v>64305.83</v>
+        <v>61186.29</v>
       </c>
       <c r="K33" t="n">
-        <v>64705.14</v>
+        <v>62676.97</v>
       </c>
       <c r="L33" t="n">
-        <v>65104.46</v>
+        <v>64167.65</v>
       </c>
       <c r="M33" t="n">
-        <v>65975.46000000001</v>
+        <v>64772.82</v>
       </c>
       <c r="N33" t="n">
-        <v>66846.46000000001</v>
+        <v>65377.99</v>
       </c>
       <c r="O33" t="n">
-        <v>66774.09</v>
+        <v>67754.19</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3314,50 +3314,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63723.49</v>
+        <v>63871.39</v>
       </c>
       <c r="C34" t="n">
-        <v>64026.92</v>
+        <v>64638.7</v>
       </c>
       <c r="D34" t="n">
-        <v>62714.8</v>
+        <v>63206.21</v>
       </c>
       <c r="E34" t="n">
-        <v>63871.36</v>
+        <v>63908.17</v>
       </c>
       <c r="F34" t="n">
-        <v>146.46</v>
+        <v>36.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>1312.12</v>
+        <v>1432.48</v>
       </c>
       <c r="I34" t="n">
-        <v>61466.63</v>
+        <v>61402.69</v>
       </c>
       <c r="J34" t="n">
-        <v>61186.29</v>
+        <v>62809.5</v>
       </c>
       <c r="K34" t="n">
-        <v>62676.97</v>
+        <v>63215.3</v>
       </c>
       <c r="L34" t="n">
-        <v>64167.65</v>
+        <v>63621.11</v>
       </c>
       <c r="M34" t="n">
-        <v>64772.82</v>
+        <v>64527.42</v>
       </c>
       <c r="N34" t="n">
-        <v>65377.99</v>
+        <v>65433.73</v>
       </c>
       <c r="O34" t="n">
-        <v>67754.19</v>
+        <v>65339.04</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3365,16 +3365,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3389,57 +3393,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63871.39</v>
+        <v>63908.62</v>
       </c>
       <c r="C35" t="n">
-        <v>64638.7</v>
+        <v>65071.45</v>
       </c>
       <c r="D35" t="n">
-        <v>63206.21</v>
+        <v>63533.91</v>
       </c>
       <c r="E35" t="n">
-        <v>63908.17</v>
+        <v>64725.31</v>
       </c>
       <c r="F35" t="n">
-        <v>36.8</v>
+        <v>817.14</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0128</v>
       </c>
       <c r="H35" t="n">
-        <v>1432.48</v>
+        <v>1537.54</v>
       </c>
       <c r="I35" t="n">
-        <v>61402.69</v>
+        <v>61773.73</v>
       </c>
       <c r="J35" t="n">
-        <v>62809.5</v>
+        <v>62468.54</v>
       </c>
       <c r="K35" t="n">
-        <v>63215.3</v>
+        <v>63191.93</v>
       </c>
       <c r="L35" t="n">
-        <v>63621.11</v>
+        <v>63915.31</v>
       </c>
       <c r="M35" t="n">
-        <v>64527.42</v>
+        <v>64624.41</v>
       </c>
       <c r="N35" t="n">
-        <v>65433.73</v>
+        <v>65333.51</v>
       </c>
       <c r="O35" t="n">
-        <v>65339.04</v>
+        <v>66071.17999999999</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3447,19 +3451,17 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3482,70 +3484,72 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63908.62</v>
+        <v>64723.97</v>
       </c>
       <c r="C36" t="n">
-        <v>65071.45</v>
+        <v>65328.18</v>
       </c>
       <c r="D36" t="n">
-        <v>63533.91</v>
+        <v>62410.87</v>
       </c>
       <c r="E36" t="n">
-        <v>64725.31</v>
+        <v>62813.75</v>
       </c>
       <c r="F36" t="n">
-        <v>817.14</v>
+        <v>-1911.56</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0295</v>
       </c>
       <c r="H36" t="n">
-        <v>1537.54</v>
+        <v>2917.32</v>
       </c>
       <c r="I36" t="n">
-        <v>61773.73</v>
+        <v>61996.37</v>
       </c>
       <c r="J36" t="n">
-        <v>62468.54</v>
+        <v>63399.09</v>
       </c>
       <c r="K36" t="n">
-        <v>63191.93</v>
+        <v>63956.54</v>
       </c>
       <c r="L36" t="n">
-        <v>63915.31</v>
+        <v>64513.99</v>
       </c>
       <c r="M36" t="n">
-        <v>64624.41</v>
+        <v>65494.08</v>
       </c>
       <c r="N36" t="n">
-        <v>65333.51</v>
+        <v>66474.16</v>
       </c>
       <c r="O36" t="n">
-        <v>66071.17999999999</v>
+        <v>66608.98</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3559,74 +3563,70 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64723.97</v>
+        <v>62813.66</v>
       </c>
       <c r="C37" t="n">
-        <v>65328.18</v>
+        <v>63091.6</v>
       </c>
       <c r="D37" t="n">
-        <v>62410.87</v>
+        <v>62233.01</v>
       </c>
       <c r="E37" t="n">
-        <v>62813.75</v>
+        <v>62763.32</v>
       </c>
       <c r="F37" t="n">
-        <v>-1911.56</v>
+        <v>-50.43</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0295</v>
+        <v>-0.0008</v>
       </c>
       <c r="H37" t="n">
-        <v>2917.32</v>
+        <v>858.59</v>
       </c>
       <c r="I37" t="n">
-        <v>61996.37</v>
+        <v>59493.55</v>
       </c>
       <c r="J37" t="n">
-        <v>63399.09</v>
+        <v>59368.54</v>
       </c>
       <c r="K37" t="n">
-        <v>63956.54</v>
+        <v>61355.09</v>
       </c>
       <c r="L37" t="n">
-        <v>64513.99</v>
+        <v>63341.64</v>
       </c>
       <c r="M37" t="n">
-        <v>65494.08</v>
+        <v>64272.4</v>
       </c>
       <c r="N37" t="n">
-        <v>66474.16</v>
+        <v>65203.17</v>
       </c>
       <c r="O37" t="n">
-        <v>66608.98</v>
+        <v>68245.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3643,59 +3643,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>62813.66</v>
+        <v>62763.45</v>
       </c>
       <c r="C38" t="n">
-        <v>63091.6</v>
+        <v>63714.61</v>
       </c>
       <c r="D38" t="n">
-        <v>62233.01</v>
+        <v>62745.25</v>
       </c>
       <c r="E38" t="n">
-        <v>62763.32</v>
+        <v>63482</v>
       </c>
       <c r="F38" t="n">
-        <v>-50.43</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0115</v>
       </c>
       <c r="H38" t="n">
-        <v>858.59</v>
+        <v>969.36</v>
       </c>
       <c r="I38" t="n">
-        <v>59493.55</v>
+        <v>61374.43</v>
       </c>
       <c r="J38" t="n">
-        <v>59368.54</v>
+        <v>61955.24</v>
       </c>
       <c r="K38" t="n">
-        <v>61355.09</v>
+        <v>62334.03</v>
       </c>
       <c r="L38" t="n">
-        <v>63341.64</v>
+        <v>62712.81</v>
       </c>
       <c r="M38" t="n">
-        <v>64272.4</v>
+        <v>63192.61</v>
       </c>
       <c r="N38" t="n">
-        <v>65203.17</v>
+        <v>63672.41</v>
       </c>
       <c r="O38" t="n">
-        <v>68245.5</v>
+        <v>63950.18</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3706,16 +3702,20 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3725,68 +3725,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>62763.45</v>
+        <v>63485.44</v>
       </c>
       <c r="C39" t="n">
-        <v>63714.61</v>
+        <v>64020.32</v>
       </c>
       <c r="D39" t="n">
-        <v>62745.25</v>
+        <v>62226.58</v>
       </c>
       <c r="E39" t="n">
-        <v>63482</v>
+        <v>63460.9</v>
       </c>
       <c r="F39" t="n">
-        <v>718.6799999999999</v>
+        <v>-21.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0003</v>
       </c>
       <c r="H39" t="n">
-        <v>969.36</v>
+        <v>1793.75</v>
       </c>
       <c r="I39" t="n">
-        <v>61374.43</v>
+        <v>61775.89</v>
       </c>
       <c r="J39" t="n">
-        <v>61955.24</v>
+        <v>62638.67</v>
       </c>
       <c r="K39" t="n">
-        <v>62334.03</v>
+        <v>62997.32</v>
       </c>
       <c r="L39" t="n">
-        <v>62712.81</v>
+        <v>63355.97</v>
       </c>
       <c r="M39" t="n">
-        <v>63192.61</v>
+        <v>63966.68</v>
       </c>
       <c r="N39" t="n">
-        <v>63672.41</v>
+        <v>64577.39</v>
       </c>
       <c r="O39" t="n">
-        <v>63950.18</v>
+        <v>64683.97</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3794,10 +3802,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3809,79 +3815,75 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63485.44</v>
+        <v>63458.41</v>
       </c>
       <c r="C40" t="n">
-        <v>64020.32</v>
+        <v>64466.94</v>
       </c>
       <c r="D40" t="n">
-        <v>62226.58</v>
+        <v>63277.68</v>
       </c>
       <c r="E40" t="n">
-        <v>63460.9</v>
+        <v>64055.95</v>
       </c>
       <c r="F40" t="n">
-        <v>-21.1</v>
+        <v>595.05</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="H40" t="n">
-        <v>1793.75</v>
+        <v>1189.25</v>
       </c>
       <c r="I40" t="n">
-        <v>61775.89</v>
+        <v>60432.83</v>
       </c>
       <c r="J40" t="n">
-        <v>62638.67</v>
+        <v>61835.88</v>
       </c>
       <c r="K40" t="n">
-        <v>62997.32</v>
+        <v>62564.03</v>
       </c>
       <c r="L40" t="n">
-        <v>63355.97</v>
+        <v>63292.17</v>
       </c>
       <c r="M40" t="n">
-        <v>63966.68</v>
+        <v>64357.77</v>
       </c>
       <c r="N40" t="n">
-        <v>64577.39</v>
+        <v>65423.37</v>
       </c>
       <c r="O40" t="n">
-        <v>64683.97</v>
+        <v>65814.07000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3897,57 +3899,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63458.41</v>
+        <v>64054.88</v>
       </c>
       <c r="C41" t="n">
-        <v>64466.94</v>
+        <v>64954.35</v>
       </c>
       <c r="D41" t="n">
-        <v>63277.68</v>
+        <v>63829.72</v>
       </c>
       <c r="E41" t="n">
-        <v>64055.95</v>
+        <v>64597.5</v>
       </c>
       <c r="F41" t="n">
-        <v>595.05</v>
+        <v>541.55</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>1189.25</v>
+        <v>1124.63</v>
       </c>
       <c r="I41" t="n">
-        <v>60432.83</v>
+        <v>62088.43</v>
       </c>
       <c r="J41" t="n">
-        <v>61835.88</v>
+        <v>62958.52</v>
       </c>
       <c r="K41" t="n">
-        <v>62564.03</v>
+        <v>63461.33</v>
       </c>
       <c r="L41" t="n">
-        <v>63292.17</v>
+        <v>63964.13</v>
       </c>
       <c r="M41" t="n">
-        <v>64357.77</v>
+        <v>64650.58</v>
       </c>
       <c r="N41" t="n">
-        <v>65423.37</v>
+        <v>65337.03</v>
       </c>
       <c r="O41" t="n">
-        <v>65814.07000000001</v>
+        <v>65656.19</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3988,50 +3990,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>64054.88</v>
+        <v>64595.45</v>
       </c>
       <c r="C42" t="n">
-        <v>64954.35</v>
+        <v>64934.49</v>
       </c>
       <c r="D42" t="n">
-        <v>63829.72</v>
+        <v>64098.48</v>
       </c>
       <c r="E42" t="n">
-        <v>64597.5</v>
+        <v>64262.11</v>
       </c>
       <c r="F42" t="n">
-        <v>541.55</v>
+        <v>-335.39</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="H42" t="n">
-        <v>1124.63</v>
+        <v>836.02</v>
       </c>
       <c r="I42" t="n">
-        <v>62088.43</v>
+        <v>62705.09</v>
       </c>
       <c r="J42" t="n">
-        <v>62958.52</v>
+        <v>63575.6</v>
       </c>
       <c r="K42" t="n">
-        <v>63461.33</v>
+        <v>64035.19</v>
       </c>
       <c r="L42" t="n">
-        <v>63964.13</v>
+        <v>64494.77</v>
       </c>
       <c r="M42" t="n">
-        <v>64650.58</v>
+        <v>65159.81</v>
       </c>
       <c r="N42" t="n">
-        <v>65337.03</v>
+        <v>65824.86</v>
       </c>
       <c r="O42" t="n">
-        <v>65656.19</v>
+        <v>66078.98</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4039,19 +4041,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4065,57 +4067,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64595.45</v>
+        <v>64257.49</v>
       </c>
       <c r="C43" t="n">
-        <v>64934.49</v>
+        <v>65330.61</v>
       </c>
       <c r="D43" t="n">
-        <v>64098.48</v>
+        <v>64113.27</v>
       </c>
       <c r="E43" t="n">
-        <v>64262.11</v>
+        <v>64880.19</v>
       </c>
       <c r="F43" t="n">
-        <v>-335.39</v>
+        <v>618.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>836.02</v>
+        <v>1217.34</v>
       </c>
       <c r="I43" t="n">
-        <v>62705.09</v>
+        <v>63262.46</v>
       </c>
       <c r="J43" t="n">
-        <v>63575.6</v>
+        <v>63298.91</v>
       </c>
       <c r="K43" t="n">
-        <v>64035.19</v>
+        <v>63844.11</v>
       </c>
       <c r="L43" t="n">
-        <v>64494.77</v>
+        <v>64389.3</v>
       </c>
       <c r="M43" t="n">
-        <v>65159.81</v>
+        <v>64680.12</v>
       </c>
       <c r="N43" t="n">
-        <v>65824.86</v>
+        <v>64970.94</v>
       </c>
       <c r="O43" t="n">
-        <v>66078.98</v>
+        <v>65770.50999999999</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4123,22 +4125,24 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4149,57 +4153,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64257.49</v>
+        <v>64882.55</v>
       </c>
       <c r="C44" t="n">
-        <v>65330.61</v>
+        <v>65140.48</v>
       </c>
       <c r="D44" t="n">
-        <v>64113.27</v>
+        <v>64797.11</v>
       </c>
       <c r="E44" t="n">
-        <v>64880.19</v>
+        <v>64904.69</v>
       </c>
       <c r="F44" t="n">
-        <v>618.08</v>
+        <v>24.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H44" t="n">
-        <v>1217.34</v>
+        <v>343.37</v>
       </c>
       <c r="I44" t="n">
-        <v>63262.46</v>
+        <v>62895.94</v>
       </c>
       <c r="J44" t="n">
-        <v>63298.91</v>
+        <v>63741.98</v>
       </c>
       <c r="K44" t="n">
-        <v>63844.11</v>
+        <v>64271.52</v>
       </c>
       <c r="L44" t="n">
-        <v>64389.3</v>
+        <v>64801.07</v>
       </c>
       <c r="M44" t="n">
-        <v>64680.12</v>
+        <v>65488.86</v>
       </c>
       <c r="N44" t="n">
-        <v>64970.94</v>
+        <v>66176.64999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>65770.50999999999</v>
+        <v>66547.95</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4212,18 +4216,14 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4235,57 +4235,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64882.55</v>
+        <v>64906.55</v>
       </c>
       <c r="C45" t="n">
-        <v>65140.48</v>
+        <v>65401.69</v>
       </c>
       <c r="D45" t="n">
-        <v>64797.11</v>
+        <v>64677.6</v>
       </c>
       <c r="E45" t="n">
-        <v>64904.69</v>
+        <v>64844.89</v>
       </c>
       <c r="F45" t="n">
-        <v>24.5</v>
+        <v>-59.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="H45" t="n">
-        <v>343.37</v>
+        <v>724.09</v>
       </c>
       <c r="I45" t="n">
-        <v>62895.94</v>
+        <v>64453.75</v>
       </c>
       <c r="J45" t="n">
-        <v>63741.98</v>
+        <v>64529.27</v>
       </c>
       <c r="K45" t="n">
-        <v>64271.52</v>
+        <v>64733</v>
       </c>
       <c r="L45" t="n">
-        <v>64801.07</v>
+        <v>64936.74</v>
       </c>
       <c r="M45" t="n">
-        <v>65488.86</v>
+        <v>65076.37</v>
       </c>
       <c r="N45" t="n">
-        <v>66176.64999999999</v>
+        <v>65216</v>
       </c>
       <c r="O45" t="n">
-        <v>66547.95</v>
+        <v>65483.85</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4293,19 +4293,25 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4317,63 +4323,67 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64906.55</v>
+        <v>64845.38</v>
       </c>
       <c r="C46" t="n">
-        <v>65401.69</v>
+        <v>65321.84</v>
       </c>
       <c r="D46" t="n">
-        <v>64677.6</v>
+        <v>63752.57</v>
       </c>
       <c r="E46" t="n">
-        <v>64844.89</v>
+        <v>63910.59</v>
       </c>
       <c r="F46" t="n">
-        <v>-59.8</v>
+        <v>-934.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0144</v>
       </c>
       <c r="H46" t="n">
-        <v>724.09</v>
+        <v>1569.27</v>
       </c>
       <c r="I46" t="n">
-        <v>64453.75</v>
+        <v>63953.51</v>
       </c>
       <c r="J46" t="n">
-        <v>64529.27</v>
+        <v>64023.42</v>
       </c>
       <c r="K46" t="n">
-        <v>64733</v>
+        <v>64482.84</v>
       </c>
       <c r="L46" t="n">
-        <v>64936.74</v>
+        <v>64942.27</v>
       </c>
       <c r="M46" t="n">
-        <v>65076.37</v>
+        <v>65206.93</v>
       </c>
       <c r="N46" t="n">
-        <v>65216</v>
+        <v>65471.6</v>
       </c>
       <c r="O46" t="n">
-        <v>65483.85</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>66125.78</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
@@ -4382,7 +4392,7 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4390,10 +4400,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4403,84 +4411,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64845.38</v>
+        <v>63910.18</v>
       </c>
       <c r="C47" t="n">
-        <v>65321.84</v>
+        <v>64433.68</v>
       </c>
       <c r="D47" t="n">
-        <v>63752.57</v>
+        <v>63185.47</v>
       </c>
       <c r="E47" t="n">
-        <v>63910.59</v>
+        <v>63551.88</v>
       </c>
       <c r="F47" t="n">
-        <v>-934.3</v>
+        <v>-358.71</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.0056</v>
       </c>
       <c r="H47" t="n">
-        <v>1569.27</v>
+        <v>1248.21</v>
       </c>
       <c r="I47" t="n">
-        <v>63953.51</v>
+        <v>62183.29</v>
       </c>
       <c r="J47" t="n">
-        <v>64023.42</v>
+        <v>62028</v>
       </c>
       <c r="K47" t="n">
-        <v>64482.84</v>
+        <v>63125.95</v>
       </c>
       <c r="L47" t="n">
-        <v>64942.27</v>
+        <v>64223.89</v>
       </c>
       <c r="M47" t="n">
-        <v>65206.93</v>
+        <v>64695.22</v>
       </c>
       <c r="N47" t="n">
-        <v>65471.6</v>
+        <v>65166.55</v>
       </c>
       <c r="O47" t="n">
-        <v>66125.78</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
+        <v>66891.11</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4498,50 +4496,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63910.18</v>
+        <v>63551.87</v>
       </c>
       <c r="C48" t="n">
-        <v>64433.68</v>
+        <v>64381.08</v>
       </c>
       <c r="D48" t="n">
-        <v>63185.47</v>
+        <v>63251.11</v>
       </c>
       <c r="E48" t="n">
-        <v>63551.88</v>
+        <v>63402.43</v>
       </c>
       <c r="F48" t="n">
-        <v>-358.71</v>
+        <v>-149.44</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0024</v>
       </c>
       <c r="H48" t="n">
-        <v>1248.21</v>
+        <v>1129.96</v>
       </c>
       <c r="I48" t="n">
-        <v>62183.29</v>
+        <v>61937.27</v>
       </c>
       <c r="J48" t="n">
-        <v>62028</v>
+        <v>62174.82</v>
       </c>
       <c r="K48" t="n">
-        <v>63125.95</v>
+        <v>62927.77</v>
       </c>
       <c r="L48" t="n">
-        <v>64223.89</v>
+        <v>63680.73</v>
       </c>
       <c r="M48" t="n">
-        <v>64695.22</v>
+        <v>64175.98</v>
       </c>
       <c r="N48" t="n">
-        <v>65166.55</v>
+        <v>64671.23</v>
       </c>
       <c r="O48" t="n">
-        <v>66891.11</v>
+        <v>65681.89</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4549,18 +4547,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4573,55 +4571,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63551.87</v>
+        <v>63404.43</v>
       </c>
       <c r="C49" t="n">
-        <v>64381.08</v>
+        <v>63926.33</v>
       </c>
       <c r="D49" t="n">
-        <v>63251.11</v>
+        <v>62799.29</v>
       </c>
       <c r="E49" t="n">
-        <v>63402.43</v>
+        <v>63402.17</v>
       </c>
       <c r="F49" t="n">
-        <v>-149.44</v>
+        <v>-0.26</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0</v>
       </c>
       <c r="H49" t="n">
-        <v>1129.96</v>
+        <v>1127.04</v>
       </c>
       <c r="I49" t="n">
-        <v>61937.27</v>
+        <v>62121.15</v>
       </c>
       <c r="J49" t="n">
-        <v>62174.82</v>
+        <v>62065.64</v>
       </c>
       <c r="K49" t="n">
-        <v>62927.77</v>
+        <v>62837.45</v>
       </c>
       <c r="L49" t="n">
-        <v>63680.73</v>
+        <v>63609.26</v>
       </c>
       <c r="M49" t="n">
-        <v>64175.98</v>
+        <v>63967.42</v>
       </c>
       <c r="N49" t="n">
-        <v>64671.23</v>
+        <v>64325.57</v>
       </c>
       <c r="O49" t="n">
-        <v>65681.89</v>
+        <v>65511.04</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4629,18 +4631,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4653,59 +4655,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63404.43</v>
+        <v>63402.09</v>
       </c>
       <c r="C50" t="n">
-        <v>63926.33</v>
+        <v>63551.56</v>
       </c>
       <c r="D50" t="n">
-        <v>62799.29</v>
+        <v>62487.7</v>
       </c>
       <c r="E50" t="n">
-        <v>63402.17</v>
+        <v>62975.59</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.26</v>
+        <v>-426.58</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0067</v>
       </c>
       <c r="H50" t="n">
-        <v>1127.04</v>
+        <v>1063.86</v>
       </c>
       <c r="I50" t="n">
-        <v>62121.15</v>
+        <v>61672.25</v>
       </c>
       <c r="J50" t="n">
-        <v>62065.64</v>
+        <v>62294.81</v>
       </c>
       <c r="K50" t="n">
-        <v>62837.45</v>
+        <v>62838.65</v>
       </c>
       <c r="L50" t="n">
-        <v>63609.26</v>
+        <v>63382.49</v>
       </c>
       <c r="M50" t="n">
-        <v>63967.42</v>
+        <v>63965.69</v>
       </c>
       <c r="N50" t="n">
-        <v>64325.57</v>
+        <v>64548.9</v>
       </c>
       <c r="O50" t="n">
-        <v>65511.04</v>
+        <v>65053.38</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4715,12 +4713,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4742,50 +4740,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63402.09</v>
+        <v>62974.34</v>
       </c>
       <c r="C51" t="n">
-        <v>63551.56</v>
+        <v>63119.13</v>
       </c>
       <c r="D51" t="n">
-        <v>62487.7</v>
+        <v>62850.96</v>
       </c>
       <c r="E51" t="n">
-        <v>62975.59</v>
+        <v>63024.32</v>
       </c>
       <c r="F51" t="n">
-        <v>-426.58</v>
+        <v>48.73</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0008</v>
       </c>
       <c r="H51" t="n">
-        <v>1063.86</v>
+        <v>268.17</v>
       </c>
       <c r="I51" t="n">
-        <v>61672.25</v>
+        <v>61423.84</v>
       </c>
       <c r="J51" t="n">
-        <v>62294.81</v>
+        <v>61889.71</v>
       </c>
       <c r="K51" t="n">
-        <v>62838.65</v>
+        <v>62443.66</v>
       </c>
       <c r="L51" t="n">
-        <v>63382.49</v>
+        <v>62997.61</v>
       </c>
       <c r="M51" t="n">
-        <v>63965.69</v>
+        <v>63507.53</v>
       </c>
       <c r="N51" t="n">
-        <v>64548.9</v>
+        <v>64017.44</v>
       </c>
       <c r="O51" t="n">
-        <v>65053.38</v>
+        <v>64615.43</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4793,14 +4791,12 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4817,72 +4813,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>62974.34</v>
+        <v>63023.42</v>
       </c>
       <c r="C52" t="n">
-        <v>63119.13</v>
+        <v>63310.78</v>
       </c>
       <c r="D52" t="n">
-        <v>62850.96</v>
+        <v>62648.57</v>
       </c>
       <c r="E52" t="n">
-        <v>63024.32</v>
+        <v>62818.65</v>
       </c>
       <c r="F52" t="n">
-        <v>48.73</v>
+        <v>-205.67</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0033</v>
       </c>
       <c r="H52" t="n">
-        <v>268.17</v>
+        <v>662.2</v>
       </c>
       <c r="I52" t="n">
-        <v>61423.84</v>
+        <v>62582.79</v>
       </c>
       <c r="J52" t="n">
-        <v>61889.71</v>
+        <v>62775.79</v>
       </c>
       <c r="K52" t="n">
-        <v>62443.66</v>
+        <v>62890.23</v>
       </c>
       <c r="L52" t="n">
-        <v>62997.61</v>
+        <v>63004.68</v>
       </c>
       <c r="M52" t="n">
-        <v>63507.53</v>
+        <v>63158.41</v>
       </c>
       <c r="N52" t="n">
-        <v>64017.44</v>
+        <v>63312.13</v>
       </c>
       <c r="O52" t="n">
-        <v>64615.43</v>
+        <v>63387.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4897,145 +4903,141 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63023.42</v>
+        <v>62819.38</v>
       </c>
       <c r="C53" t="n">
-        <v>63310.78</v>
+        <v>64547.85</v>
       </c>
       <c r="D53" t="n">
-        <v>62648.57</v>
+        <v>62687.1</v>
       </c>
       <c r="E53" t="n">
-        <v>62818.65</v>
+        <v>64506.25</v>
       </c>
       <c r="F53" t="n">
-        <v>-205.67</v>
+        <v>1687.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0269</v>
       </c>
       <c r="H53" t="n">
-        <v>662.2</v>
+        <v>1860.75</v>
       </c>
       <c r="I53" t="n">
-        <v>62582.79</v>
+        <v>61986.37</v>
       </c>
       <c r="J53" t="n">
-        <v>62775.79</v>
+        <v>62075.94</v>
       </c>
       <c r="K53" t="n">
-        <v>62890.23</v>
+        <v>62487.55</v>
       </c>
       <c r="L53" t="n">
-        <v>63004.68</v>
+        <v>62899.16</v>
       </c>
       <c r="M53" t="n">
-        <v>63158.41</v>
+        <v>63149.75</v>
       </c>
       <c r="N53" t="n">
-        <v>63312.13</v>
+        <v>63400.34</v>
       </c>
       <c r="O53" t="n">
-        <v>63387.3</v>
+        <v>63972.98</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>62819.38</v>
+        <v>64506.52</v>
       </c>
       <c r="C54" t="n">
-        <v>64547.85</v>
+        <v>64987.71</v>
       </c>
       <c r="D54" t="n">
-        <v>62687.1</v>
+        <v>63980.32</v>
       </c>
       <c r="E54" t="n">
-        <v>64506.25</v>
+        <v>64680.71</v>
       </c>
       <c r="F54" t="n">
-        <v>1687.6</v>
+        <v>174.46</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0027</v>
       </c>
       <c r="H54" t="n">
-        <v>1860.75</v>
+        <v>1007.39</v>
       </c>
       <c r="I54" t="n">
-        <v>61986.37</v>
+        <v>60826.36</v>
       </c>
       <c r="J54" t="n">
-        <v>62075.94</v>
+        <v>63089.9</v>
       </c>
       <c r="K54" t="n">
-        <v>62487.55</v>
+        <v>63575.88</v>
       </c>
       <c r="L54" t="n">
-        <v>62899.16</v>
+        <v>64061.86</v>
       </c>
       <c r="M54" t="n">
-        <v>63149.75</v>
+        <v>65436.63</v>
       </c>
       <c r="N54" t="n">
-        <v>63400.34</v>
+        <v>66811.39</v>
       </c>
       <c r="O54" t="n">
-        <v>63972.98</v>
+        <v>66408.59</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5048,23 +5050,17 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5076,50 +5072,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64506.52</v>
+        <v>64680.05</v>
       </c>
       <c r="C55" t="n">
-        <v>64987.71</v>
+        <v>69996.95</v>
       </c>
       <c r="D55" t="n">
-        <v>63980.32</v>
+        <v>64111.07</v>
       </c>
       <c r="E55" t="n">
-        <v>64680.71</v>
+        <v>69266.19</v>
       </c>
       <c r="F55" t="n">
-        <v>174.46</v>
+        <v>4585.48</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0709</v>
       </c>
       <c r="H55" t="n">
-        <v>1007.39</v>
+        <v>5885.88</v>
       </c>
       <c r="I55" t="n">
-        <v>60826.36</v>
+        <v>62972.94</v>
       </c>
       <c r="J55" t="n">
-        <v>63089.9</v>
+        <v>63771.67</v>
       </c>
       <c r="K55" t="n">
-        <v>63575.88</v>
+        <v>64177.02</v>
       </c>
       <c r="L55" t="n">
-        <v>64061.86</v>
+        <v>64582.36</v>
       </c>
       <c r="M55" t="n">
-        <v>65436.63</v>
+        <v>65184.4</v>
       </c>
       <c r="N55" t="n">
-        <v>66811.39</v>
+        <v>65786.44</v>
       </c>
       <c r="O55" t="n">
-        <v>66408.59</v>
+        <v>65995.10000000001</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,22 +5123,30 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5154,50 +5158,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64680.05</v>
+        <v>69268.25</v>
       </c>
       <c r="C56" t="n">
-        <v>69996.95</v>
+        <v>73369.8</v>
       </c>
       <c r="D56" t="n">
-        <v>64111.07</v>
+        <v>68867.53</v>
       </c>
       <c r="E56" t="n">
-        <v>69266.19</v>
+        <v>73032.75999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>4585.48</v>
+        <v>3766.57</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0544</v>
       </c>
       <c r="H56" t="n">
-        <v>5885.88</v>
+        <v>4502.27</v>
       </c>
       <c r="I56" t="n">
-        <v>62972.94</v>
+        <v>58225.19</v>
       </c>
       <c r="J56" t="n">
-        <v>63771.67</v>
+        <v>64486.39</v>
       </c>
       <c r="K56" t="n">
-        <v>64177.02</v>
+        <v>66323.25</v>
       </c>
       <c r="L56" t="n">
-        <v>64582.36</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>65184.4</v>
+        <v>72209.13</v>
       </c>
       <c r="N56" t="n">
-        <v>65786.44</v>
+        <v>76258.16</v>
       </c>
       <c r="O56" t="n">
-        <v>65995.10000000001</v>
+        <v>75882.84</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5205,10 +5209,8 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
@@ -5217,18 +5219,14 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5240,50 +5238,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>69268.25</v>
+        <v>73031.09</v>
       </c>
       <c r="C57" t="n">
-        <v>73369.8</v>
+        <v>79463.71000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>68867.53</v>
+        <v>73011.41</v>
       </c>
       <c r="E57" t="n">
-        <v>73032.75999999999</v>
+        <v>78335.19</v>
       </c>
       <c r="F57" t="n">
-        <v>3766.57</v>
+        <v>5302.43</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0726</v>
       </c>
       <c r="H57" t="n">
-        <v>4502.27</v>
+        <v>6452.3</v>
       </c>
       <c r="I57" t="n">
-        <v>58225.19</v>
+        <v>64365.26</v>
       </c>
       <c r="J57" t="n">
-        <v>64486.39</v>
+        <v>69487.53</v>
       </c>
       <c r="K57" t="n">
-        <v>66323.25</v>
+        <v>70781.62</v>
       </c>
       <c r="L57" t="n">
-        <v>68160.10000000001</v>
+        <v>72075.71000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>72209.13</v>
+        <v>75283.89</v>
       </c>
       <c r="N57" t="n">
-        <v>76258.16</v>
+        <v>78492.08</v>
       </c>
       <c r="O57" t="n">
-        <v>75882.84</v>
+        <v>77872.08</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5301,14 +5299,18 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5320,50 +5322,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>73031.09</v>
+        <v>78332.55</v>
       </c>
       <c r="C58" t="n">
-        <v>79463.71000000001</v>
+        <v>78801.14999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>73011.41</v>
+        <v>76526.71000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>78335.19</v>
+        <v>77083.41</v>
       </c>
       <c r="F58" t="n">
-        <v>5302.43</v>
+        <v>-1251.77</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0726</v>
+        <v>-0.016</v>
       </c>
       <c r="H58" t="n">
-        <v>6452.3</v>
+        <v>2274.44</v>
       </c>
       <c r="I58" t="n">
-        <v>64365.26</v>
+        <v>66559.12</v>
       </c>
       <c r="J58" t="n">
-        <v>69487.53</v>
+        <v>72931.7</v>
       </c>
       <c r="K58" t="n">
-        <v>70781.62</v>
+        <v>75109.03999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>72075.71000000001</v>
+        <v>77286.38</v>
       </c>
       <c r="M58" t="n">
-        <v>75283.89</v>
+        <v>81561.34</v>
       </c>
       <c r="N58" t="n">
-        <v>78492.08</v>
+        <v>85836.3</v>
       </c>
       <c r="O58" t="n">
-        <v>77872.08</v>
+        <v>85916.00999999999</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5374,80 +5376,78 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>78332.55</v>
+        <v>77082.84</v>
       </c>
       <c r="C59" t="n">
-        <v>78801.14999999999</v>
+        <v>78036.87</v>
       </c>
       <c r="D59" t="n">
-        <v>76526.71000000001</v>
+        <v>75624.95</v>
       </c>
       <c r="E59" t="n">
-        <v>77083.41</v>
+        <v>77755.27</v>
       </c>
       <c r="F59" t="n">
-        <v>-1251.77</v>
+        <v>671.85</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>2274.44</v>
+        <v>2411.92</v>
       </c>
       <c r="I59" t="n">
-        <v>66559.12</v>
+        <v>74252.27</v>
       </c>
       <c r="J59" t="n">
-        <v>72931.7</v>
+        <v>74518.72</v>
       </c>
       <c r="K59" t="n">
-        <v>75109.03999999999</v>
+        <v>75946.2</v>
       </c>
       <c r="L59" t="n">
-        <v>77286.38</v>
+        <v>77373.67</v>
       </c>
       <c r="M59" t="n">
-        <v>81561.34</v>
+        <v>78220.63</v>
       </c>
       <c r="N59" t="n">
-        <v>85836.3</v>
+        <v>79067.59</v>
       </c>
       <c r="O59" t="n">
-        <v>85916.00999999999</v>
+        <v>81075.59</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5455,12 +5455,14 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5486,50 +5488,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>77082.84</v>
+        <v>77748.88</v>
       </c>
       <c r="C60" t="n">
-        <v>78036.87</v>
+        <v>79970.11</v>
       </c>
       <c r="D60" t="n">
-        <v>75624.95</v>
+        <v>76688.83</v>
       </c>
       <c r="E60" t="n">
-        <v>77755.27</v>
+        <v>78964.48</v>
       </c>
       <c r="F60" t="n">
-        <v>671.85</v>
+        <v>1209.22</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H60" t="n">
-        <v>2411.92</v>
+        <v>3281.28</v>
       </c>
       <c r="I60" t="n">
-        <v>74252.27</v>
+        <v>73213.02</v>
       </c>
       <c r="J60" t="n">
-        <v>74518.72</v>
+        <v>75805.52</v>
       </c>
       <c r="K60" t="n">
-        <v>75946.2</v>
+        <v>76549.3</v>
       </c>
       <c r="L60" t="n">
-        <v>77373.67</v>
+        <v>77293.09</v>
       </c>
       <c r="M60" t="n">
-        <v>78220.63</v>
+        <v>78961.23</v>
       </c>
       <c r="N60" t="n">
-        <v>79067.59</v>
+        <v>80629.37</v>
       </c>
       <c r="O60" t="n">
-        <v>81075.59</v>
+        <v>80448.78999999999</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5537,18 +5539,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5561,59 +5563,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>77748.88</v>
+        <v>78960.09</v>
       </c>
       <c r="C61" t="n">
-        <v>79970.11</v>
+        <v>81235.03</v>
       </c>
       <c r="D61" t="n">
-        <v>76688.83</v>
+        <v>77870.62</v>
       </c>
       <c r="E61" t="n">
-        <v>78964.48</v>
+        <v>78564.98</v>
       </c>
       <c r="F61" t="n">
-        <v>1209.22</v>
+        <v>-399.51</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0051</v>
       </c>
       <c r="H61" t="n">
-        <v>3281.28</v>
+        <v>3364.41</v>
       </c>
       <c r="I61" t="n">
-        <v>73213.02</v>
+        <v>73407.55</v>
       </c>
       <c r="J61" t="n">
-        <v>75805.52</v>
+        <v>76000.71000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>76549.3</v>
+        <v>77323.84</v>
       </c>
       <c r="L61" t="n">
-        <v>77293.09</v>
+        <v>78646.98</v>
       </c>
       <c r="M61" t="n">
-        <v>78961.23</v>
+        <v>80605.12</v>
       </c>
       <c r="N61" t="n">
-        <v>80629.37</v>
+        <v>82563.27</v>
       </c>
       <c r="O61" t="n">
-        <v>80448.78999999999</v>
+        <v>83251.39</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5624,14 +5622,14 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U61" s="8" t="n">
@@ -5645,55 +5643,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>78960.09</v>
+        <v>78538.59</v>
       </c>
       <c r="C62" t="n">
-        <v>81235.03</v>
+        <v>79240.5</v>
       </c>
       <c r="D62" t="n">
-        <v>77870.62</v>
+        <v>77639.84</v>
       </c>
       <c r="E62" t="n">
-        <v>78564.98</v>
+        <v>79027.42</v>
       </c>
       <c r="F62" t="n">
-        <v>-399.51</v>
+        <v>462.45</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="H62" t="n">
-        <v>3364.41</v>
+        <v>1600.66</v>
       </c>
       <c r="I62" t="n">
-        <v>73407.55</v>
+        <v>74506.22</v>
       </c>
       <c r="J62" t="n">
-        <v>76000.71000000001</v>
+        <v>74706.64</v>
       </c>
       <c r="K62" t="n">
-        <v>77323.84</v>
+        <v>76882.77</v>
       </c>
       <c r="L62" t="n">
-        <v>78646.98</v>
+        <v>79058.89999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>80605.12</v>
+        <v>80247.17999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>82563.27</v>
+        <v>81435.46000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>83251.39</v>
+        <v>84599.44</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5709,10 +5711,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5727,57 +5727,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>78538.59</v>
+        <v>79037.92</v>
       </c>
       <c r="C63" t="n">
-        <v>79240.5</v>
+        <v>80806.56</v>
       </c>
       <c r="D63" t="n">
-        <v>77639.84</v>
+        <v>78591.10000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>79027.42</v>
+        <v>80257.53999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>462.45</v>
+        <v>1230.12</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0156</v>
       </c>
       <c r="H63" t="n">
-        <v>1600.66</v>
+        <v>2215.46</v>
       </c>
       <c r="I63" t="n">
-        <v>74506.22</v>
+        <v>76039.17</v>
       </c>
       <c r="J63" t="n">
-        <v>74706.64</v>
+        <v>77720.38</v>
       </c>
       <c r="K63" t="n">
-        <v>76882.77</v>
+        <v>78227.09</v>
       </c>
       <c r="L63" t="n">
-        <v>79058.89999999999</v>
+        <v>78733.78999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>80247.17999999999</v>
+        <v>79827.75</v>
       </c>
       <c r="N63" t="n">
-        <v>81435.46000000001</v>
+        <v>80921.71000000001</v>
       </c>
       <c r="O63" t="n">
-        <v>84599.44</v>
+        <v>80841.16</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5788,13 +5788,15 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5807,156 +5809,154 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>79037.92</v>
+        <v>80264.64999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>80806.56</v>
+        <v>81346.95</v>
       </c>
       <c r="D64" t="n">
-        <v>78591.10000000001</v>
+        <v>76909.35000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>80257.53999999999</v>
+        <v>77830.28999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>1230.12</v>
+        <v>-2427.25</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0156</v>
+        <v>-0.0302</v>
       </c>
       <c r="H64" t="n">
-        <v>2215.46</v>
+        <v>4437.6</v>
       </c>
       <c r="I64" t="n">
-        <v>76039.17</v>
+        <v>76375.64</v>
       </c>
       <c r="J64" t="n">
-        <v>77720.38</v>
+        <v>78321.42999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>78227.09</v>
+        <v>79149.81</v>
       </c>
       <c r="L64" t="n">
-        <v>78733.78999999999</v>
+        <v>79978.19</v>
       </c>
       <c r="M64" t="n">
-        <v>79827.75</v>
+        <v>81365.27</v>
       </c>
       <c r="N64" t="n">
-        <v>80921.71000000001</v>
+        <v>82752.35000000001</v>
       </c>
       <c r="O64" t="n">
-        <v>80841.16</v>
+        <v>83022.02</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
+      <c r="Q64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
       <c r="U64" s="8" t="n">
         <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>80264.64999999999</v>
+        <v>77830.89</v>
       </c>
       <c r="C65" t="n">
-        <v>81346.95</v>
+        <v>78327.95</v>
       </c>
       <c r="D65" t="n">
-        <v>76909.35000000001</v>
+        <v>77381.89999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>77830.28999999999</v>
+        <v>78245.81</v>
       </c>
       <c r="F65" t="n">
-        <v>-2427.25</v>
+        <v>415.52</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0302</v>
+        <v>0.0053</v>
       </c>
       <c r="H65" t="n">
-        <v>4437.6</v>
+        <v>946.05</v>
       </c>
       <c r="I65" t="n">
-        <v>76375.64</v>
+        <v>72471.75</v>
       </c>
       <c r="J65" t="n">
-        <v>78321.42999999999</v>
+        <v>72743.75999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>79149.81</v>
+        <v>75611.49000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>79978.19</v>
+        <v>78479.22</v>
       </c>
       <c r="M65" t="n">
-        <v>81365.27</v>
+        <v>80049.09</v>
       </c>
       <c r="N65" t="n">
-        <v>82752.35000000001</v>
+        <v>81618.96000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>83022.02</v>
+        <v>85784.55</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
       </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -5975,80 +5975,88 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>77830.89</v>
+        <v>78246.17</v>
       </c>
       <c r="C66" t="n">
-        <v>78327.95</v>
+        <v>79373.17999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>77381.89999999999</v>
+        <v>77056.14999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>78245.81</v>
+        <v>77667.57000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>415.52</v>
+        <v>-578.24</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0074</v>
       </c>
       <c r="H66" t="n">
-        <v>946.05</v>
+        <v>2317.03</v>
       </c>
       <c r="I66" t="n">
-        <v>72471.75</v>
+        <v>76435.85000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>72743.75999999999</v>
+        <v>77495.21000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>75611.49000000001</v>
+        <v>77772.78999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>78479.22</v>
+        <v>78050.37</v>
       </c>
       <c r="M66" t="n">
-        <v>80049.09</v>
+        <v>78718.84</v>
       </c>
       <c r="N66" t="n">
-        <v>81618.96000000001</v>
+        <v>79387.3</v>
       </c>
       <c r="O66" t="n">
-        <v>85784.55</v>
+        <v>79273.99000000001</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
       </c>
-      <c r="Q66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R66" s="6" t="n">
-        <v/>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U66" s="8" t="n">
         <v/>
       </c>
-      <c r="V66" s="8" t="n">
-        <v/>
+      <c r="V66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W66" s="11" t="inlineStr">
         <is>
@@ -6057,88 +6065,82 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>78246.17</v>
+        <v>77673.7</v>
       </c>
       <c r="C67" t="n">
-        <v>79373.17999999999</v>
+        <v>79247.34</v>
       </c>
       <c r="D67" t="n">
-        <v>77056.14999999999</v>
+        <v>77378.44</v>
       </c>
       <c r="E67" t="n">
-        <v>77667.57000000001</v>
+        <v>78548.63</v>
       </c>
       <c r="F67" t="n">
-        <v>-578.24</v>
+        <v>881.0599999999999</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="H67" t="n">
-        <v>2317.03</v>
+        <v>1868.91</v>
       </c>
       <c r="I67" t="n">
-        <v>76435.85000000001</v>
+        <v>74739.12</v>
       </c>
       <c r="J67" t="n">
-        <v>77495.21000000001</v>
+        <v>75076.99000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>77772.78999999999</v>
+        <v>76509.05</v>
       </c>
       <c r="L67" t="n">
-        <v>78050.37</v>
+        <v>77941.12</v>
       </c>
       <c r="M67" t="n">
-        <v>78718.84</v>
+        <v>78826.09</v>
       </c>
       <c r="N67" t="n">
-        <v>79387.3</v>
+        <v>79711.05</v>
       </c>
       <c r="O67" t="n">
-        <v>79273.99000000001</v>
+        <v>81690.21000000001</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
       </c>
-      <c r="Q67" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R67" s="6" t="inlineStr">
+      <c r="Q67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S67" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U67" s="8" t="n">
         <v/>
       </c>
-      <c r="V67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V67" s="8" t="n">
+        <v/>
       </c>
       <c r="W67" s="11" t="inlineStr">
         <is>
@@ -6147,77 +6149,79 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>77673.7</v>
+        <v>78539.86</v>
       </c>
       <c r="C68" t="n">
-        <v>79247.34</v>
+        <v>79196.52</v>
       </c>
       <c r="D68" t="n">
-        <v>77378.44</v>
+        <v>76399.06</v>
       </c>
       <c r="E68" t="n">
-        <v>78548.63</v>
+        <v>77403.62</v>
       </c>
       <c r="F68" t="n">
-        <v>881.0599999999999</v>
+        <v>-1145.01</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0146</v>
       </c>
       <c r="H68" t="n">
-        <v>1868.91</v>
+        <v>2797.45</v>
       </c>
       <c r="I68" t="n">
-        <v>74739.12</v>
+        <v>75509.53</v>
       </c>
       <c r="J68" t="n">
-        <v>75076.99000000001</v>
+        <v>76797.60000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>76509.05</v>
+        <v>77614.17999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>77941.12</v>
+        <v>78430.75999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>78826.09</v>
+        <v>79483.09</v>
       </c>
       <c r="N68" t="n">
-        <v>79711.05</v>
+        <v>80535.41</v>
       </c>
       <c r="O68" t="n">
-        <v>81690.21000000001</v>
+        <v>81116.25</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
+      </c>
       <c r="U68" s="8" t="n">
         <v/>
       </c>
@@ -6229,76 +6233,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>78539.86</v>
+        <v>77402.14</v>
       </c>
       <c r="C69" t="n">
-        <v>79196.52</v>
+        <v>77737.55</v>
       </c>
       <c r="D69" t="n">
-        <v>76399.06</v>
+        <v>76248.3</v>
       </c>
       <c r="E69" t="n">
-        <v>77403.62</v>
+        <v>77300.48</v>
       </c>
       <c r="F69" t="n">
-        <v>-1145.01</v>
+        <v>-103.15</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0013</v>
       </c>
       <c r="H69" t="n">
-        <v>2797.45</v>
+        <v>1489.24</v>
       </c>
       <c r="I69" t="n">
-        <v>75509.53</v>
+        <v>73601.61</v>
       </c>
       <c r="J69" t="n">
-        <v>76797.60000000001</v>
+        <v>74409.09</v>
       </c>
       <c r="K69" t="n">
-        <v>77614.17999999999</v>
+        <v>76004.89999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>78430.75999999999</v>
+        <v>77600.71000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>79483.09</v>
+        <v>78802.35000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>80535.41</v>
+        <v>80004</v>
       </c>
       <c r="O69" t="n">
-        <v>81116.25</v>
+        <v>81993.97</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
       </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R69" s="6" t="n">
+        <v/>
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T69" s="8" t="n">
@@ -6320,50 +6316,50 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>77402.14</v>
+        <v>77300.16</v>
       </c>
       <c r="C70" t="n">
-        <v>77737.55</v>
+        <v>82262.21000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>76248.3</v>
+        <v>76940.88</v>
       </c>
       <c r="E70" t="n">
-        <v>77300.48</v>
+        <v>81271.74000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-103.15</v>
+        <v>3971.27</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0514</v>
       </c>
       <c r="H70" t="n">
-        <v>1489.24</v>
+        <v>5321.33</v>
       </c>
       <c r="I70" t="n">
-        <v>73601.61</v>
+        <v>74759.06</v>
       </c>
       <c r="J70" t="n">
-        <v>74409.09</v>
+        <v>75965.00999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>76004.89999999999</v>
+        <v>76555.86</v>
       </c>
       <c r="L70" t="n">
-        <v>77600.71000000001</v>
+        <v>77146.7</v>
       </c>
       <c r="M70" t="n">
-        <v>78802.35000000001</v>
+        <v>78045.10000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>80004</v>
+        <v>78943.49000000001</v>
       </c>
       <c r="O70" t="n">
-        <v>81993.97</v>
+        <v>79226.78999999999</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6374,23 +6370,29 @@
       <c r="R70" s="6" t="n">
         <v/>
       </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W70" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V70" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W70" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X70" t="inlineStr"/>
@@ -6398,50 +6400,50 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>77300.16</v>
+        <v>81271.53999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>82262.21000000001</v>
+        <v>81433.14999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>76940.88</v>
+        <v>78641.62</v>
       </c>
       <c r="E71" t="n">
-        <v>81271.74000000001</v>
+        <v>79671.97</v>
       </c>
       <c r="F71" t="n">
-        <v>3971.27</v>
+        <v>-1599.77</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0514</v>
+        <v>-0.0197</v>
       </c>
       <c r="H71" t="n">
-        <v>5321.33</v>
+        <v>2791.52</v>
       </c>
       <c r="I71" t="n">
-        <v>74759.06</v>
+        <v>71619.55</v>
       </c>
       <c r="J71" t="n">
-        <v>75965.00999999999</v>
+        <v>76785.50999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>76555.86</v>
+        <v>78611.08</v>
       </c>
       <c r="L71" t="n">
-        <v>77146.7</v>
+        <v>80436.64</v>
       </c>
       <c r="M71" t="n">
-        <v>78045.10000000001</v>
+        <v>83932.41</v>
       </c>
       <c r="N71" t="n">
-        <v>78943.49000000001</v>
+        <v>87428.17</v>
       </c>
       <c r="O71" t="n">
-        <v>79226.78999999999</v>
+        <v>87583.53999999999</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6452,80 +6454,78 @@
       <c r="R71" s="6" t="n">
         <v/>
       </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V71" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V71" s="8" t="n">
+        <v/>
       </c>
       <c r="W71" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>81271.53999999999</v>
+        <v>79671.7</v>
       </c>
       <c r="C72" t="n">
-        <v>81433.14999999999</v>
+        <v>80194.50999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>78641.62</v>
+        <v>79465.06</v>
       </c>
       <c r="E72" t="n">
-        <v>79671.97</v>
+        <v>79823.87</v>
       </c>
       <c r="F72" t="n">
-        <v>-1599.77</v>
+        <v>151.9</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0197</v>
+        <v>0.0019</v>
       </c>
       <c r="H72" t="n">
-        <v>2791.52</v>
+        <v>729.45</v>
       </c>
       <c r="I72" t="n">
-        <v>71619.55</v>
+        <v>75850.10000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>76785.50999999999</v>
+        <v>76697.74000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>78611.08</v>
+        <v>78276.21000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>80436.64</v>
+        <v>79854.67999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>83932.41</v>
+        <v>81067.73</v>
       </c>
       <c r="N72" t="n">
-        <v>87428.17</v>
+        <v>82280.78</v>
       </c>
       <c r="O72" t="n">
-        <v>87583.53999999999</v>
+        <v>84224.67</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6557,57 +6557,57 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>79671.7</v>
+        <v>79824.60000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>80194.50999999999</v>
+        <v>80530.64999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>79465.06</v>
+        <v>79327.5</v>
       </c>
       <c r="E73" t="n">
-        <v>79823.87</v>
+        <v>80350.05</v>
       </c>
       <c r="F73" t="n">
-        <v>151.9</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
       <c r="H73" t="n">
-        <v>729.45</v>
+        <v>1203.15</v>
       </c>
       <c r="I73" t="n">
-        <v>75850.10000000001</v>
+        <v>78735.62</v>
       </c>
       <c r="J73" t="n">
-        <v>76697.74000000001</v>
+        <v>79091.46000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>78276.21000000001</v>
+        <v>79459.14</v>
       </c>
       <c r="L73" t="n">
-        <v>79854.67999999999</v>
+        <v>79826.83</v>
       </c>
       <c r="M73" t="n">
-        <v>81067.73</v>
+        <v>80188.59</v>
       </c>
       <c r="N73" t="n">
-        <v>82280.78</v>
+        <v>80550.35000000001</v>
       </c>
       <c r="O73" t="n">
-        <v>84224.67</v>
+        <v>80923.95</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6615,16 +6615,20 @@
       <c r="Q73" s="6" t="n">
         <v/>
       </c>
-      <c r="R73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U73" s="8" t="n">
         <v/>
@@ -6646,71 +6650,71 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>79824.60000000001</v>
+        <v>80349.2</v>
       </c>
       <c r="C74" t="n">
-        <v>80530.64999999999</v>
+        <v>80432.31</v>
       </c>
       <c r="D74" t="n">
-        <v>79327.5</v>
+        <v>78684.92999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>80350.05</v>
+        <v>79115.85000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>526.1799999999999</v>
+        <v>-1234.2</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0154</v>
       </c>
       <c r="H74" t="n">
-        <v>1203.15</v>
+        <v>1747.38</v>
       </c>
       <c r="I74" t="n">
-        <v>78735.62</v>
+        <v>78124.35000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>79091.46000000001</v>
+        <v>79357.38</v>
       </c>
       <c r="K74" t="n">
-        <v>79459.14</v>
+        <v>79748.47</v>
       </c>
       <c r="L74" t="n">
-        <v>79826.83</v>
+        <v>80139.56</v>
       </c>
       <c r="M74" t="n">
-        <v>80188.59</v>
+        <v>80951.62</v>
       </c>
       <c r="N74" t="n">
-        <v>80550.35000000001</v>
+        <v>81763.67999999999</v>
       </c>
       <c r="O74" t="n">
-        <v>80923.95</v>
+        <v>81733.8</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6718,76 +6722,70 @@
       <c r="V74" s="8" t="n">
         <v/>
       </c>
-      <c r="W74" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W74" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>80349.2</v>
+        <v>79114.91</v>
       </c>
       <c r="C75" t="n">
-        <v>80432.31</v>
+        <v>79463.27</v>
       </c>
       <c r="D75" t="n">
-        <v>78684.92999999999</v>
+        <v>77635.69</v>
       </c>
       <c r="E75" t="n">
-        <v>79115.85000000001</v>
+        <v>78438.58</v>
       </c>
       <c r="F75" t="n">
-        <v>-1234.2</v>
+        <v>-677.27</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0086</v>
       </c>
       <c r="H75" t="n">
-        <v>1747.38</v>
+        <v>1827.59</v>
       </c>
       <c r="I75" t="n">
-        <v>78124.35000000001</v>
+        <v>76937.55</v>
       </c>
       <c r="J75" t="n">
-        <v>79357.38</v>
+        <v>77147.08</v>
       </c>
       <c r="K75" t="n">
-        <v>79748.47</v>
+        <v>78242.16</v>
       </c>
       <c r="L75" t="n">
-        <v>80139.56</v>
+        <v>79337.24000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>80951.62</v>
+        <v>79989.53999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>81763.67999999999</v>
+        <v>80641.85000000001</v>
       </c>
       <c r="O75" t="n">
-        <v>81733.8</v>
+        <v>82179.7</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S75" s="10" t="inlineStr">
@@ -6814,50 +6812,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>79114.91</v>
+        <v>78440.60000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>79463.27</v>
+        <v>79737.3</v>
       </c>
       <c r="D76" t="n">
-        <v>77635.69</v>
+        <v>77768.14999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>78438.58</v>
+        <v>78259.52</v>
       </c>
       <c r="F76" t="n">
-        <v>-677.27</v>
+        <v>-179.05</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0023</v>
       </c>
       <c r="H76" t="n">
-        <v>1827.59</v>
+        <v>1969.15</v>
       </c>
       <c r="I76" t="n">
-        <v>76937.55</v>
+        <v>75808.10000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>77147.08</v>
+        <v>76555.53999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>78242.16</v>
+        <v>77524.78999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>79337.24000000001</v>
+        <v>78494.03</v>
       </c>
       <c r="M76" t="n">
-        <v>79989.53999999999</v>
+        <v>79352.37</v>
       </c>
       <c r="N76" t="n">
-        <v>80641.85000000001</v>
+        <v>80210.71000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>82179.7</v>
+        <v>81290.86</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6865,18 +6863,18 @@
       <c r="Q76" s="6" t="n">
         <v/>
       </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R76" s="6" t="n">
+        <v/>
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
@@ -6889,74 +6887,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>78440.60000000001</v>
+        <v>78260.38</v>
       </c>
       <c r="C77" t="n">
-        <v>79737.3</v>
+        <v>78520.97</v>
       </c>
       <c r="D77" t="n">
-        <v>77768.14999999999</v>
+        <v>76470.64</v>
       </c>
       <c r="E77" t="n">
-        <v>78259.52</v>
+        <v>76568.12</v>
       </c>
       <c r="F77" t="n">
-        <v>-179.05</v>
+        <v>-1691.4</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0216</v>
       </c>
       <c r="H77" t="n">
-        <v>1969.15</v>
+        <v>2050.33</v>
       </c>
       <c r="I77" t="n">
-        <v>75808.10000000001</v>
+        <v>75799</v>
       </c>
       <c r="J77" t="n">
-        <v>76555.53999999999</v>
+        <v>76043.78</v>
       </c>
       <c r="K77" t="n">
-        <v>77524.78999999999</v>
+        <v>77274.95</v>
       </c>
       <c r="L77" t="n">
-        <v>78494.03</v>
+        <v>78506.12</v>
       </c>
       <c r="M77" t="n">
-        <v>79352.37</v>
+        <v>79244.10000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>80210.71000000001</v>
+        <v>79982.07000000001</v>
       </c>
       <c r="O77" t="n">
-        <v>81290.86</v>
+        <v>81706.45</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R77" s="6" t="n">
-        <v/>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S77" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6969,83 +6973,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>78260.38</v>
+        <v>76559.12</v>
       </c>
       <c r="C78" t="n">
-        <v>78520.97</v>
+        <v>79818.34</v>
       </c>
       <c r="D78" t="n">
-        <v>76470.64</v>
+        <v>76162.91</v>
       </c>
       <c r="E78" t="n">
-        <v>76568.12</v>
+        <v>77173.8</v>
       </c>
       <c r="F78" t="n">
-        <v>-1691.4</v>
+        <v>605.67</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0216</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>2050.33</v>
+        <v>3655.42</v>
       </c>
       <c r="I78" t="n">
-        <v>75799</v>
+        <v>74420.31</v>
       </c>
       <c r="J78" t="n">
-        <v>76043.78</v>
+        <v>74053.96000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>77274.95</v>
+        <v>75542.96000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>78506.12</v>
+        <v>77031.96000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>79244.10000000001</v>
+        <v>77593.28999999999</v>
       </c>
       <c r="N78" t="n">
-        <v>79982.07000000001</v>
+        <v>78154.61</v>
       </c>
       <c r="O78" t="n">
-        <v>81706.45</v>
+        <v>80571.3</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R78" s="6" t="inlineStr">
+      <c r="Q78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S78" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U78" s="8" t="n">
-        <v/>
+      <c r="U78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V78" s="8" t="n">
         <v/>
@@ -7055,55 +7055,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>76559.12</v>
+        <v>77175.07000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>79818.34</v>
+        <v>77479.66</v>
       </c>
       <c r="D79" t="n">
-        <v>76162.91</v>
+        <v>77045</v>
       </c>
       <c r="E79" t="n">
-        <v>77173.8</v>
+        <v>77270.47</v>
       </c>
       <c r="F79" t="n">
-        <v>605.67</v>
+        <v>96.67</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="H79" t="n">
-        <v>3655.42</v>
+        <v>434.66</v>
       </c>
       <c r="I79" t="n">
-        <v>74420.31</v>
+        <v>72507.49000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>74053.96000000001</v>
+        <v>73109.96000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>75542.96000000001</v>
+        <v>75346.09</v>
       </c>
       <c r="L79" t="n">
-        <v>77031.96000000001</v>
+        <v>77582.21000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>77593.28999999999</v>
+        <v>79001.50999999999</v>
       </c>
       <c r="N79" t="n">
-        <v>78154.61</v>
+        <v>80420.8</v>
       </c>
       <c r="O79" t="n">
-        <v>80571.3</v>
+        <v>83473.75999999999</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7114,20 +7118,16 @@
       <c r="R79" s="6" t="n">
         <v/>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U79" s="8" t="n">
+        <v/>
       </c>
       <c r="V79" s="8" t="n">
         <v/>
@@ -7146,63 +7146,69 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>77175.07000000001</v>
+        <v>77270.17999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>77479.66</v>
+        <v>77415.66</v>
       </c>
       <c r="D80" t="n">
-        <v>77045</v>
+        <v>76498.38</v>
       </c>
       <c r="E80" t="n">
-        <v>77270.47</v>
+        <v>76838.16</v>
       </c>
       <c r="F80" t="n">
-        <v>96.67</v>
+        <v>-432.31</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0056</v>
       </c>
       <c r="H80" t="n">
-        <v>434.66</v>
+        <v>917.27</v>
       </c>
       <c r="I80" t="n">
-        <v>72507.49000000001</v>
+        <v>76610.34</v>
       </c>
       <c r="J80" t="n">
-        <v>73109.96000000001</v>
+        <v>76839.88</v>
       </c>
       <c r="K80" t="n">
-        <v>75346.09</v>
+        <v>77053.14</v>
       </c>
       <c r="L80" t="n">
-        <v>77582.21000000001</v>
+        <v>77266.39999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>79001.50999999999</v>
+        <v>77487.8</v>
       </c>
       <c r="N80" t="n">
-        <v>80420.8</v>
+        <v>77709.2</v>
       </c>
       <c r="O80" t="n">
-        <v>83473.75999999999</v>
-      </c>
-      <c r="P80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R80" s="6" t="n">
-        <v/>
+        <v>77914.31</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S80" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T80" s="8" t="n">
@@ -7219,174 +7225,172 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>77270.17999999999</v>
+        <v>76830.28</v>
       </c>
       <c r="C81" t="n">
-        <v>77415.66</v>
+        <v>79568.95</v>
       </c>
       <c r="D81" t="n">
-        <v>76498.38</v>
+        <v>76367.38</v>
       </c>
       <c r="E81" t="n">
-        <v>76838.16</v>
+        <v>78163.38</v>
       </c>
       <c r="F81" t="n">
-        <v>-432.31</v>
+        <v>1325.23</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0172</v>
       </c>
       <c r="H81" t="n">
-        <v>917.27</v>
+        <v>3201.58</v>
       </c>
       <c r="I81" t="n">
-        <v>76610.34</v>
+        <v>75581.11</v>
       </c>
       <c r="J81" t="n">
-        <v>76839.88</v>
+        <v>75861.45</v>
       </c>
       <c r="K81" t="n">
-        <v>77053.14</v>
+        <v>76379.52</v>
       </c>
       <c r="L81" t="n">
-        <v>77266.39999999999</v>
+        <v>76897.59</v>
       </c>
       <c r="M81" t="n">
-        <v>77487.8</v>
+        <v>77296.78999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>77709.2</v>
+        <v>77696</v>
       </c>
       <c r="O81" t="n">
-        <v>77914.31</v>
-      </c>
-      <c r="P81" s="6" t="inlineStr">
+        <v>78332.92999999999</v>
+      </c>
+      <c r="P81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q81" s="6" t="inlineStr">
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+    